--- a/data/FRAGRANCES.xlsx
+++ b/data/FRAGRANCES.xlsx
@@ -38,15 +38,15 @@
     <t>Rating</t>
   </si>
   <si>
+    <t>Facts</t>
+  </si>
+  <si>
+    <t>Date tried</t>
+  </si>
+  <si>
     <t>100 Bon</t>
   </si>
   <si>
-    <t>Facts</t>
-  </si>
-  <si>
-    <t>Date tried</t>
-  </si>
-  <si>
     <t>Rose &amp; Black Pepper</t>
   </si>
   <si>
@@ -62,21 +62,21 @@
     <t>Brand carried by Scent Split and The Perfumed Court, this one not.</t>
   </si>
   <si>
+    <t>American Perfumer</t>
+  </si>
+  <si>
     <t>19-69</t>
   </si>
   <si>
+    <t>Black Walnut</t>
+  </si>
+  <si>
+    <t>House brand of the Chicago shop. Buy direct.</t>
+  </si>
+  <si>
     <t>Miami Blue</t>
   </si>
   <si>
-    <t>American Perfumer</t>
-  </si>
-  <si>
-    <t>Black Walnut</t>
-  </si>
-  <si>
-    <t>House brand of the Chicago shop. Buy direct.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Disappointing, smells nothing like cocaine </t>
   </si>
   <si>
@@ -113,36 +113,36 @@
     <t>So gross what is the deal with this hot and cold brand?</t>
   </si>
   <si>
+    <t>Spelled Akro. Ministry of Scent sample sold out.</t>
+  </si>
+  <si>
     <t>Aedes de Venustas</t>
   </si>
   <si>
     <t>Café Tabac</t>
   </si>
   <si>
-    <t>Spelled Akro. Ministry of Scent sample sold out.</t>
+    <t>Astier de Villatte</t>
   </si>
   <si>
     <t xml:space="preserve">Tobacco shop, Ybor City, keeps going </t>
   </si>
   <si>
-    <t>Astier de Villatte</t>
+    <t>Mantes La Jolie</t>
+  </si>
+  <si>
+    <t>Luckyscent</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
   </si>
   <si>
     <t>Signature</t>
   </si>
   <si>
-    <t>Mantes La Jolie</t>
-  </si>
-  <si>
-    <t>Luckyscent</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sharp rhubarb, loved at first but got less appealing the more I wore </t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
-  </si>
-  <si>
     <t>Sueño Latino</t>
   </si>
   <si>
@@ -158,6 +158,18 @@
     <t xml:space="preserve">Way too smoky </t>
   </si>
   <si>
+    <t>Price shows when you select the size, usually $5-10.</t>
+  </si>
+  <si>
+    <t>Azzaro</t>
+  </si>
+  <si>
+    <t>Azzaro pour Homme</t>
+  </si>
+  <si>
+    <t>The Perfumed Court</t>
+  </si>
+  <si>
     <t>Agar Olfactory</t>
   </si>
   <si>
@@ -167,27 +179,15 @@
     <t xml:space="preserve">Wow! Hot fax machine for real tho. </t>
   </si>
   <si>
-    <t>Price shows when you select the size, usually $5-10.</t>
-  </si>
-  <si>
     <t>Damp</t>
   </si>
   <si>
+    <t>https://theperfumedcourt.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Duplicative realistic earth and wet </t>
   </si>
   <si>
-    <t>Azzaro</t>
-  </si>
-  <si>
-    <t>Azzaro pour Homme</t>
-  </si>
-  <si>
-    <t>The Perfumed Court</t>
-  </si>
-  <si>
-    <t>https://theperfumedcourt.com</t>
-  </si>
-  <si>
     <t>Cereale</t>
   </si>
   <si>
@@ -197,15 +197,30 @@
     <t>Matsu Musk</t>
   </si>
   <si>
+    <t>Cheapest sample on the list.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Uncooked grocery store button mushrooms </t>
   </si>
   <si>
     <t>Rushlight</t>
   </si>
   <si>
+    <t>Bvlgari</t>
+  </si>
+  <si>
     <t>Yellow floral, really compelling, honeycomb and honesuckle, kinda Moon Bloom, stinks a lot but I like the stink</t>
   </si>
   <si>
+    <t>Rose Goldea Blossom Delight</t>
+  </si>
+  <si>
+    <t>Maple Prime</t>
+  </si>
+  <si>
+    <t>https://mapleprime.com/products/bvlgari-rose-goldea-blossom-delight-eau-de-parfum-for-women</t>
+  </si>
+  <si>
     <t>Amouage</t>
   </si>
   <si>
@@ -215,30 +230,15 @@
     <t xml:space="preserve">Mint forward, has kind of a gross cantaloupe vibe. </t>
   </si>
   <si>
-    <t>Cheapest sample on the list.</t>
-  </si>
-  <si>
     <t>Honour Man</t>
   </si>
   <si>
     <t xml:space="preserve">Not sure what I don't like in here. Geranium? Pepper is nice. Feels boring, but something wrong in there. </t>
   </si>
   <si>
-    <t>Bvlgari</t>
-  </si>
-  <si>
-    <t>Rose Goldea Blossom Delight</t>
-  </si>
-  <si>
-    <t>Maple Prime</t>
-  </si>
-  <si>
     <t>Interlude Woman</t>
   </si>
   <si>
-    <t>https://mapleprime.com/products/bvlgari-rose-goldea-blossom-delight-eau-de-parfum-for-women</t>
-  </si>
-  <si>
     <t>Lotsa stuff I like, reviews said kiwi, my vibe was just a mild no</t>
   </si>
   <si>
@@ -251,27 +251,33 @@
     <t xml:space="preserve">Hay, orris, green, very good version of this. Skin scent. Ultimately too feminine and boring. </t>
   </si>
   <si>
+    <t>All three decant sizes out of stock. Re-check.</t>
+  </si>
+  <si>
     <t>Cool but ultimately a watery mess</t>
   </si>
   <si>
-    <t>All three decant sizes out of stock. Re-check.</t>
+    <t>Caron</t>
+  </si>
+  <si>
+    <t>Coup de Fouet</t>
+  </si>
+  <si>
+    <t>Vintage market only.</t>
+  </si>
+  <si>
+    <t>Poivre</t>
   </si>
   <si>
     <t>Brioche</t>
   </si>
   <si>
+    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
+  </si>
+  <si>
     <t>Bread and bran, sweet honey, a nice and not gourmand fragrance</t>
   </si>
   <si>
-    <t>Caron</t>
-  </si>
-  <si>
-    <t>Coup de Fouet</t>
-  </si>
-  <si>
-    <t>Vintage market only.</t>
-  </si>
-  <si>
     <t>Andrea Maack</t>
   </si>
   <si>
@@ -281,10 +287,13 @@
     <t xml:space="preserve">Try this again? Says it's marine but I got a big food vibe of something savory </t>
   </si>
   <si>
-    <t>Poivre</t>
-  </si>
-  <si>
-    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
+    <t>Chanel</t>
+  </si>
+  <si>
+    <t>No. 19</t>
+  </si>
+  <si>
+    <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
   </si>
   <si>
     <t>Solstice</t>
@@ -293,33 +302,24 @@
     <t xml:space="preserve">Mr Bubble watermelon </t>
   </si>
   <si>
-    <t>Chanel</t>
-  </si>
-  <si>
-    <t>No. 19</t>
-  </si>
-  <si>
-    <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
+    <t>Coach</t>
+  </si>
+  <si>
+    <t>Coach Green</t>
+  </si>
+  <si>
+    <t>DecantX</t>
   </si>
   <si>
     <t>Coven</t>
   </si>
   <si>
-    <t>Coach</t>
-  </si>
-  <si>
-    <t>Coach Green</t>
-  </si>
-  <si>
-    <t>DecantX</t>
+    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
   </si>
   <si>
     <t xml:space="preserve">Dirt. Probably great layered with something. </t>
   </si>
   <si>
-    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
-  </si>
-  <si>
     <t>Dual</t>
   </si>
   <si>
@@ -341,13 +341,22 @@
     <t>Bleh I don't like this dude I will die on this hill</t>
   </si>
   <si>
+    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+  </si>
+  <si>
     <t>Sundowner</t>
   </si>
   <si>
     <t>Scrubber. Chocolate note disgusted me</t>
   </si>
   <si>
-    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+    <t>Comme des Garçons</t>
+  </si>
+  <si>
+    <t>Series 2 Red: Carnation</t>
+  </si>
+  <si>
+    <t>Discontinued Red series. Vintage market.</t>
   </si>
   <si>
     <t>L'Air du Désert Marocain</t>
@@ -356,13 +365,10 @@
     <t xml:space="preserve">Wanted to love, didn't </t>
   </si>
   <si>
-    <t>Comme des Garçons</t>
-  </si>
-  <si>
-    <t>Series 2 Red: Carnation</t>
-  </si>
-  <si>
-    <t>Discontinued Red series. Vintage market.</t>
+    <t>Dolce &amp; Gabbana</t>
+  </si>
+  <si>
+    <t>D&amp;G Anthology L'Amoureux 6</t>
   </si>
   <si>
     <t>Sandalo</t>
@@ -371,10 +377,7 @@
     <t xml:space="preserve">Cheap soap started great but then muddy cleaning product, huge bummer </t>
   </si>
   <si>
-    <t>Dolce &amp; Gabbana</t>
-  </si>
-  <si>
-    <t>D&amp;G Anthology L'Amoureux 6</t>
+    <t>DSH Perfumes</t>
   </si>
   <si>
     <t>Argos</t>
@@ -386,9 +389,6 @@
     <t xml:space="preserve">Rose, great at first but ultimately dries down too candy-like </t>
   </si>
   <si>
-    <t>DSH Perfumes</t>
-  </si>
-  <si>
     <t>Rubis Rose</t>
   </si>
   <si>
@@ -410,6 +410,9 @@
     <t>Armani Privé</t>
   </si>
   <si>
+    <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
+  </si>
+  <si>
     <t>Rose Alexandrie</t>
   </si>
   <si>
@@ -422,13 +425,25 @@
     <t xml:space="preserve">Simple and duplicative but rare I like it at this degree </t>
   </si>
   <si>
+    <t>Ensar Oud</t>
+  </si>
+  <si>
+    <t>Japanese Red Rose oil</t>
+  </si>
+  <si>
+    <t>Sells direct only.</t>
+  </si>
+  <si>
     <t>Rose d'Arabie</t>
   </si>
   <si>
     <t xml:space="preserve">A great rose but not my favorite. Deep. </t>
   </si>
   <si>
-    <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
+    <t>Eris Parfums</t>
+  </si>
+  <si>
+    <t>Green Spell</t>
   </si>
   <si>
     <t>Musc Shamal</t>
@@ -437,61 +452,85 @@
     <t xml:space="preserve">Slightly more interesting than a plain musk, tips a bit sweet resin </t>
   </si>
   <si>
-    <t>Ensar Oud</t>
+    <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
   </si>
   <si>
     <t>Cuir Nu</t>
   </si>
   <si>
-    <t>Japanese Red Rose oil</t>
-  </si>
-  <si>
     <t xml:space="preserve">Insane </t>
   </si>
   <si>
-    <t>Sells direct only.</t>
-  </si>
-  <si>
-    <t>Eris Parfums</t>
-  </si>
-  <si>
-    <t>Green Spell</t>
-  </si>
-  <si>
     <t>Rouge Malachite</t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gourmand </t>
   </si>
   <si>
+    <t>Indigo Perfumery has the 50ml bottle.</t>
+  </si>
+  <si>
     <t>Pivoine Suzhou</t>
   </si>
   <si>
+    <t>Floris</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>Scent Split</t>
+  </si>
+  <si>
+    <t>https://scentsplit.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Raspberry rose </t>
   </si>
   <si>
     <t>Orangerie Venise</t>
   </si>
   <si>
+    <t>DecantX sample sold out.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shouldn't like this, neroli and plain orange, but it's got something special </t>
   </si>
   <si>
+    <t>Goutal</t>
+  </si>
+  <si>
+    <t>Gardenia Passion</t>
+  </si>
+  <si>
+    <t>Parfums Raffy</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
+  </si>
+  <si>
     <t>Jasmin Kusamono</t>
   </si>
   <si>
     <t xml:space="preserve">Plain non-indolic jasmine, lovely basic floral </t>
   </si>
   <si>
+    <t>Listed, out of stock. Re-check.</t>
+  </si>
+  <si>
     <t>Thé Yulong</t>
   </si>
   <si>
     <t>Same old tea</t>
   </si>
   <si>
-    <t>Indigo Perfumery has the 50ml bottle.</t>
+    <t>Un Matin d'Orage</t>
+  </si>
+  <si>
+    <t>DecantX / Maple Prime</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
   </si>
   <si>
     <t>Santal Dan Sha</t>
@@ -500,13 +539,7 @@
     <t xml:space="preserve">So generic, can't smell any notes? </t>
   </si>
   <si>
-    <t>Floris</t>
-  </si>
-  <si>
-    <t>Elite</t>
-  </si>
-  <si>
-    <t>Scent Split</t>
+    <t>Decants listed at both, sold out at both.</t>
   </si>
   <si>
     <t>Vert Malachite</t>
@@ -515,7 +548,13 @@
     <t xml:space="preserve">Tuberose? Tube much. </t>
   </si>
   <si>
-    <t>https://scentsplit.com</t>
+    <t>Guerlain</t>
+  </si>
+  <si>
+    <t>Cuir Intense</t>
+  </si>
+  <si>
+    <t>DecantX has 2ml at $8.79.</t>
   </si>
   <si>
     <t>Bleu Lazuli</t>
@@ -524,12 +563,21 @@
     <t xml:space="preserve">Not at all </t>
   </si>
   <si>
+    <t>Santal Pao Rosa</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
+  </si>
+  <si>
     <t>Bois d'Encens</t>
   </si>
   <si>
     <t xml:space="preserve">Starts promising, ends nice basic wood </t>
   </si>
   <si>
+    <t>Only source found.</t>
+  </si>
+  <si>
     <t>Arquiste</t>
   </si>
   <si>
@@ -539,6 +587,12 @@
     <t>Salty and oily, olive and trees? Need to try again, maybe don't like the dry down</t>
   </si>
   <si>
+    <t>Jasmin Grandiflorum Extrait 30</t>
+  </si>
+  <si>
+    <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
+  </si>
+  <si>
     <t>Astrophil &amp; Stella</t>
   </si>
   <si>
@@ -548,37 +602,52 @@
     <t xml:space="preserve">Tuberose and magnolia, or green tea and plum. Optical illusion for noses. </t>
   </si>
   <si>
-    <t>DecantX sample sold out.</t>
+    <t>Eau de Guerlain</t>
+  </si>
+  <si>
+    <t>A vintage version is also listed at $6.99, likely the one you want.</t>
+  </si>
+  <si>
+    <t>Hermès</t>
   </si>
   <si>
     <t>Chloé Atelier des Fleurs</t>
   </si>
   <si>
+    <t>Hermessence Poivre Samarcande</t>
+  </si>
+  <si>
     <t>Magnolia Alba</t>
   </si>
   <si>
     <t>The perfect white floral, lasts forever, doesn't smell girly</t>
   </si>
   <si>
-    <t>Goutal</t>
-  </si>
-  <si>
-    <t>Gardenia Passion</t>
+    <t>Perfumeniche has the full bottle.</t>
+  </si>
+  <si>
+    <t>Universal Flowering</t>
+  </si>
+  <si>
+    <t>Holy Hell</t>
+  </si>
+  <si>
+    <t>Sells direct.</t>
   </si>
   <si>
     <t>Atelier des Ors</t>
   </si>
   <si>
-    <t>Parfums Raffy</t>
-  </si>
-  <si>
     <t>Rose Omeyyade</t>
   </si>
   <si>
     <t xml:space="preserve">Kinda useless. Great bottle tho </t>
   </si>
   <si>
-    <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
+    <t>(note row)</t>
+  </si>
+  <si>
+    <t>Isabelle Larignon</t>
   </si>
   <si>
     <t>Balmain</t>
@@ -587,40 +656,100 @@
     <t>Vent Vert</t>
   </si>
   <si>
+    <t>Le Flocon de Johann K</t>
+  </si>
+  <si>
     <t>I love this. It's a lot and kinda wears me, but very good green.</t>
   </si>
   <si>
+    <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
+  </si>
+  <si>
+    <t>J.F. Schwarzlose Berlin</t>
+  </si>
+  <si>
+    <t>Trance</t>
+  </si>
+  <si>
     <t>Baruti</t>
   </si>
   <si>
+    <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
+  </si>
+  <si>
     <t>Hot Cotton</t>
   </si>
   <si>
     <t xml:space="preserve">Wow, metallic and starched shirts. No reason to wear it but very cool. </t>
   </si>
   <si>
+    <t>Joop</t>
+  </si>
+  <si>
+    <t>Homme Absolute</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com</t>
+  </si>
+  <si>
+    <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
+  </si>
+  <si>
+    <t>L'Occitane</t>
+  </si>
+  <si>
+    <t>Eau du Val (Magnolia)</t>
+  </si>
+  <si>
+    <t>Perfumed Court has Eau des Baux only.</t>
+  </si>
+  <si>
+    <t>Lancôme</t>
+  </si>
+  <si>
+    <t>Cuir de Lancôme</t>
+  </si>
+  <si>
+    <t>Loewe</t>
+  </si>
+  <si>
+    <t>Pour Homme</t>
+  </si>
+  <si>
+    <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
+  </si>
+  <si>
     <t>BeauFort London</t>
   </si>
   <si>
     <t>Fathom V</t>
   </si>
   <si>
+    <t>Maison Margiela</t>
+  </si>
+  <si>
     <t xml:space="preserve">Probably a no. Eirik says vase water. Cumin? </t>
   </si>
   <si>
-    <t>Listed, out of stock. Re-check.</t>
-  </si>
-  <si>
-    <t>Un Matin d'Orage</t>
+    <t>(untitled)</t>
+  </si>
+  <si>
+    <t>Perfumeniche</t>
+  </si>
+  <si>
+    <t>https://perfumeniche.com</t>
+  </si>
+  <si>
+    <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
   </si>
   <si>
     <t>The Grudge</t>
   </si>
   <si>
-    <t>DecantX / Maple Prime</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
+    <t>Marc Jacobs</t>
+  </si>
+  <si>
+    <t>Bang</t>
   </si>
   <si>
     <t>Billie Eilish</t>
@@ -629,9 +758,18 @@
     <t>Eilish No. 2</t>
   </si>
   <si>
+    <t>Maya Njie</t>
+  </si>
+  <si>
+    <t>Nordic Cedar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Opened great, weird middle, interesting end. Worth another visit. </t>
   </si>
   <si>
+    <t>https://mayanjie.com/products/discovery-set</t>
+  </si>
+  <si>
     <t>Bohoboco</t>
   </si>
   <si>
@@ -641,12 +779,27 @@
     <t>Yeesh. I think it's very well crafted but 2 MUCH</t>
   </si>
   <si>
+    <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
+  </si>
+  <si>
     <t>Mango Yuzu Gasoline</t>
   </si>
   <si>
+    <t>Miller Harris</t>
+  </si>
+  <si>
+    <t>Le Cèdre</t>
+  </si>
+  <si>
     <t>Points for realism and saying what it is, but too strong on all counts</t>
   </si>
   <si>
+    <t>Miller Harris direct</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
+  </si>
+  <si>
     <t>Boka</t>
   </si>
   <si>
@@ -656,22 +809,28 @@
     <t>Great zesty citrus opening but goes away immediately</t>
   </si>
   <si>
-    <t>Decants listed at both, sold out at both.</t>
+    <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
+  </si>
+  <si>
+    <t>Wander Through the Parks</t>
   </si>
   <si>
     <t>Živeli</t>
   </si>
   <si>
-    <t>Guerlain</t>
-  </si>
-  <si>
-    <t>Cuir Intense</t>
+    <t>https://www.millerharris.com</t>
   </si>
   <si>
     <t>Absolute scrubber omG</t>
   </si>
   <si>
-    <t>DecantX has 2ml at $8.79.</t>
+    <t>50ml sold out, no sample listing.</t>
+  </si>
+  <si>
+    <t>Feuilles de Tabac</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
   </si>
   <si>
     <t>Bon Parfumeur</t>
@@ -683,12 +842,6 @@
     <t xml:space="preserve">A similar thing I don't like from something else idk </t>
   </si>
   <si>
-    <t>Santal Pao Rosa</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
-  </si>
-  <si>
     <t>BORNTOSTANDOUT</t>
   </si>
   <si>
@@ -698,6 +851,18 @@
     <t xml:space="preserve">Organic cherry cough drop </t>
   </si>
   <si>
+    <t>Montale</t>
+  </si>
+  <si>
+    <t>Intense Pepper</t>
+  </si>
+  <si>
+    <t>Twisted Lily</t>
+  </si>
+  <si>
+    <t>https://twistedlily.com/products/intense-pepper-sample</t>
+  </si>
+  <si>
     <t>Dirty Rice</t>
   </si>
   <si>
@@ -716,7 +881,7 @@
     <t>Banana bread no thank you</t>
   </si>
   <si>
-    <t>Only source found.</t>
+    <t>DecantX and Maple Prime have no sample in stock.</t>
   </si>
   <si>
     <t>Bortnikoff</t>
@@ -728,7 +893,13 @@
     <t xml:space="preserve">Oh wow, the blue toothpaste I used as a child </t>
   </si>
   <si>
-    <t>Jasmin Grandiflorum Extrait 30</t>
+    <t>Prissana</t>
+  </si>
+  <si>
+    <t>Nefer</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
   </si>
   <si>
     <t>Boy Smells</t>
@@ -740,70 +911,64 @@
     <t xml:space="preserve">Another rose, nice green but sour </t>
   </si>
   <si>
-    <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
-  </si>
-  <si>
     <t>Gyan</t>
   </si>
   <si>
     <t xml:space="preserve">Very not my normal thing but I'm really digging it thus far. </t>
   </si>
   <si>
-    <t>Eau de Guerlain</t>
+    <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
   </si>
   <si>
     <t>Le Gemme Tygar</t>
   </si>
   <si>
-    <t>A vintage version is also listed at $6.99, likely the one you want.</t>
-  </si>
-  <si>
     <t>Wow. Crazy grapefruit opening, deep ambroxan base, lasts forever. Maybe too beast but really compelling, I want to try all of them</t>
   </si>
   <si>
+    <t>Nest</t>
+  </si>
+  <si>
+    <t>Black Tulip</t>
+  </si>
+  <si>
     <t>Kilian</t>
   </si>
   <si>
-    <t>Hermès</t>
-  </si>
-  <si>
-    <t>Hermessence Poivre Samarcande</t>
-  </si>
-  <si>
     <t>Imperial Tea</t>
   </si>
   <si>
     <t>Smells like Nestea to me but Eirik loves it</t>
   </si>
   <si>
-    <t>Perfumeniche has the full bottle.</t>
-  </si>
-  <si>
-    <t>Universal Flowering</t>
-  </si>
-  <si>
-    <t>Holy Hell</t>
+    <t>Olfactive Studio</t>
+  </si>
+  <si>
+    <t>Flash Back</t>
   </si>
   <si>
     <t>Kologne, Shield of Protection</t>
   </si>
   <si>
-    <t>Sells direct.</t>
-  </si>
-  <si>
-    <t>(note row)</t>
+    <t>Listed as Flashback in New York.</t>
   </si>
   <si>
     <t>Not remembering why it was a no, but it was a no</t>
   </si>
   <si>
-    <t>Isabelle Larignon</t>
-  </si>
-  <si>
-    <t>Le Flocon de Johann K</t>
-  </si>
-  <si>
-    <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
+    <t>One Day</t>
+  </si>
+  <si>
+    <t>Taipei</t>
+  </si>
+  <si>
+    <t>Ministry of Scent sample sold out.</t>
+  </si>
+  <si>
+    <t>Ormonde Jayne</t>
+  </si>
+  <si>
+    <t>Montabaco Intensivo</t>
   </si>
   <si>
     <t>L'Heure Verte</t>
@@ -812,34 +977,28 @@
     <t xml:space="preserve">No idea what people are saying with absinthe and licorice. It smells fine, dna of that Angel's Share sweetness. </t>
   </si>
   <si>
-    <t>J.F. Schwarzlose Berlin</t>
-  </si>
-  <si>
-    <t>Trance</t>
+    <t>Bloom has standard Montabaco at $10, not Intensivo.</t>
   </si>
   <si>
     <t>Roses on Ice</t>
   </si>
   <si>
-    <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
+    <t>Paco Rabanne</t>
   </si>
   <si>
     <t xml:space="preserve">Ozonic cucumber, so strange. Maybe smells like cheap body spray but I don't know, I like smelling it.  </t>
   </si>
   <si>
+    <t>Maple Prime has full bottles from $38.99, no small size anywhere.</t>
+  </si>
+  <si>
     <t>Rolling in Love</t>
   </si>
   <si>
-    <t>Joop</t>
-  </si>
-  <si>
-    <t>Homme Absolute</t>
-  </si>
-  <si>
     <t>Almond, nice, too sweet to wear</t>
   </si>
   <si>
-    <t>https://parfumsraffy.com</t>
+    <t>Duplicate of the row above.</t>
   </si>
   <si>
     <t>Byredo</t>
@@ -851,67 +1010,73 @@
     <t>Floral and HONEY this is irresistable</t>
   </si>
   <si>
+    <t>Papillon Artisan</t>
+  </si>
+  <si>
+    <t>Tobacco Rose</t>
+  </si>
+  <si>
+    <t>Perfumed Court $10.94. Papillon's own site sells full bottles only.</t>
+  </si>
+  <si>
     <t>La Tulipe</t>
   </si>
   <si>
     <t xml:space="preserve">A familiar flower I've never smelled before, surprised I love this </t>
   </si>
   <si>
+    <t>Parfumerie Particulière</t>
+  </si>
+  <si>
+    <t>Black Tar</t>
+  </si>
+  <si>
     <t>Open Sky</t>
   </si>
   <si>
+    <t>Ministry of Scent has 2ml at $7.00.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pot and pomelo, addictive </t>
   </si>
   <si>
-    <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
+    <t>Penhaligon's</t>
+  </si>
+  <si>
+    <t>Blenheim Bouquet</t>
   </si>
   <si>
     <t>Cuir Obscur</t>
   </si>
   <si>
+    <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
+  </si>
+  <si>
     <t>Amaretto to rose and leather, probably many like it but I'm into this combination</t>
   </si>
   <si>
-    <t>L'Occitane</t>
-  </si>
-  <si>
-    <t>Eau du Val (Magnolia)</t>
-  </si>
-  <si>
     <t>Mojave Ghost</t>
   </si>
   <si>
-    <t>Perfumed Court has Eau des Baux only.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subtle as to be almost indistinguishable, but nice? Not getting the hype but might try the candle or something. </t>
   </si>
   <si>
-    <t>Lancôme</t>
-  </si>
-  <si>
     <t>Inflorescence</t>
   </si>
   <si>
-    <t>Cuir de Lancôme</t>
-  </si>
-  <si>
     <t xml:space="preserve">Very white floral, less babysitter than la tulipe </t>
   </si>
   <si>
     <t>Pulp</t>
   </si>
   <si>
-    <t>Loewe</t>
-  </si>
-  <si>
-    <t>Pour Homme</t>
-  </si>
-  <si>
     <t xml:space="preserve">Don't like this fig, way too something. Coats the nose and throat </t>
   </si>
   <si>
-    <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
+    <t>Liquid Love</t>
+  </si>
+  <si>
+    <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
   </si>
   <si>
     <t>Space Rage Travx</t>
@@ -920,16 +1085,10 @@
     <t xml:space="preserve">Pulp again </t>
   </si>
   <si>
-    <t>Maison Margiela</t>
-  </si>
-  <si>
-    <t>(untitled)</t>
-  </si>
-  <si>
-    <t>Perfumeniche</t>
-  </si>
-  <si>
-    <t>https://perfumeniche.com</t>
+    <t>Parfums Quartana</t>
+  </si>
+  <si>
+    <t>Forest of the Golden Dream</t>
   </si>
   <si>
     <t>Oud Immortel</t>
@@ -938,52 +1097,55 @@
     <t xml:space="preserve">Dry down pretty gross. </t>
   </si>
   <si>
+    <t>Their own site would not load when I tried.</t>
+  </si>
+  <si>
     <t>Young Rose</t>
   </si>
   <si>
     <t xml:space="preserve">Insane citrus blast, very bad </t>
   </si>
   <si>
+    <t>Ierofante</t>
+  </si>
+  <si>
+    <t>Worth confirming the spelling.</t>
+  </si>
+  <si>
     <t>Bal d'Afrique</t>
   </si>
   <si>
     <t xml:space="preserve">Good and interesting but hits me as pineapple and coconut so no </t>
   </si>
   <si>
+    <t>Robert Piguet</t>
+  </si>
+  <si>
+    <t>Bandit</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
+  </si>
+  <si>
     <t>Desert Dawn</t>
   </si>
   <si>
     <t xml:space="preserve">Boring powdery sandalwood </t>
   </si>
   <si>
-    <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
-  </si>
-  <si>
-    <t>Marc Jacobs</t>
-  </si>
-  <si>
     <t>Gypsy Water</t>
   </si>
   <si>
-    <t>Bang</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lemon creamsicle, utterly gone after 15 mins </t>
   </si>
   <si>
-    <t>Maya Njie</t>
-  </si>
-  <si>
-    <t>Nordic Cedar</t>
-  </si>
-  <si>
     <t>Blanche</t>
   </si>
   <si>
     <t xml:space="preserve">Fabric softener </t>
   </si>
   <si>
-    <t>https://mayanjie.com/products/discovery-set</t>
+    <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
   </si>
   <si>
     <t>Pour Un Homme de Caron</t>
@@ -992,39 +1154,45 @@
     <t xml:space="preserve">Beautiful lavender Fougeres, more subtle than Lav Extreme, dumb reach </t>
   </si>
   <si>
+    <t>Rogue Perfumery</t>
+  </si>
+  <si>
+    <t>(discovery set)</t>
+  </si>
+  <si>
     <t>Yatagan</t>
   </si>
   <si>
+    <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
+  </si>
+  <si>
     <t>Like Un Homme but more animalic</t>
   </si>
   <si>
+    <t>Rogue's own discovery set is sold out and most of their line with it.</t>
+  </si>
+  <si>
     <t>Tabac Blond</t>
   </si>
   <si>
     <t xml:space="preserve">Not for me, Grandma Doris, but great on Eirik </t>
   </si>
   <si>
-    <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
+    <t>Romeo Gigli</t>
+  </si>
+  <si>
+    <t>Romeo di Romeo Gigli</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
   </si>
   <si>
     <t>Tabac Noir</t>
   </si>
   <si>
-    <t>Miller Harris</t>
-  </si>
-  <si>
     <t>Sweet</t>
   </si>
   <si>
-    <t>Le Cèdre</t>
-  </si>
-  <si>
-    <t>Miller Harris direct</t>
-  </si>
-  <si>
-    <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
-  </si>
-  <si>
     <t>Pour Un Homme de Caron Le Matin</t>
   </si>
   <si>
@@ -1037,6 +1205,9 @@
     <t xml:space="preserve">Pretty good not great, not better than original </t>
   </si>
   <si>
+    <t>Cheapest on the list.</t>
+  </si>
+  <si>
     <t>Caswell-Massey</t>
   </si>
   <si>
@@ -1046,13 +1217,28 @@
     <t xml:space="preserve">Perfect perfect perfect. Doesn't last. </t>
   </si>
   <si>
+    <t>Sanctuary</t>
+  </si>
+  <si>
+    <t>Javan Rhino</t>
+  </si>
+  <si>
+    <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
+  </si>
+  <si>
     <t>Orchid</t>
   </si>
   <si>
     <t xml:space="preserve">Pure floral, old lady but not powdery. I like it! </t>
   </si>
   <si>
-    <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
+    <t>Senyokô</t>
+  </si>
+  <si>
+    <t>Indigo Perfumery</t>
+  </si>
+  <si>
+    <t>https://indigoperfumery.com</t>
   </si>
   <si>
     <t>Rose</t>
@@ -1061,12 +1247,6 @@
     <t>Classic, linear, I really like florals from this house but not a standout rose</t>
   </si>
   <si>
-    <t>Wander Through the Parks</t>
-  </si>
-  <si>
-    <t>https://www.millerharris.com</t>
-  </si>
-  <si>
     <t>Jockey Club</t>
   </si>
   <si>
@@ -1079,13 +1259,22 @@
     <t xml:space="preserve">Simple old man + lemon, but nice enough. Weak. </t>
   </si>
   <si>
+    <t>Indigo carries the line, no samples listed.</t>
+  </si>
+  <si>
     <t>Almond</t>
   </si>
   <si>
     <t xml:space="preserve">Probably fine but I barely smell it </t>
   </si>
   <si>
-    <t>50ml sold out, no sample listing.</t>
+    <t>Serge Lutens</t>
+  </si>
+  <si>
+    <t>Poivre Noir</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/serge-lutens-poivre-noir-eau-de-parfum-unisex</t>
   </si>
   <si>
     <t>Marem</t>
@@ -1094,12 +1283,6 @@
     <t xml:space="preserve">Red currant, citrus and rose. Not sure what I think. </t>
   </si>
   <si>
-    <t>Feuilles de Tabac</t>
-  </si>
-  <si>
-    <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
-  </si>
-  <si>
     <t>CB I Hate Perfume</t>
   </si>
   <si>
@@ -1109,34 +1292,37 @@
     <t xml:space="preserve">Love this dirt and sunshine </t>
   </si>
   <si>
+    <t>Sample listed, sold out. Maple Prime has 100ml at $76.99.</t>
+  </si>
+  <si>
     <t>A Room with a View</t>
   </si>
   <si>
     <t xml:space="preserve">Very intriguing, try the non water extrait. Soapy. </t>
   </si>
   <si>
+    <t>Vitriol d'Œillet</t>
+  </si>
+  <si>
     <t>At the Beach 1966</t>
   </si>
   <si>
     <t xml:space="preserve">Lovely, summer, not sunscreen but not NOT sunscreen </t>
   </si>
   <si>
+    <t>Not at any of the three retailers that carry Serge Lutens.</t>
+  </si>
+  <si>
     <t>Black March</t>
   </si>
   <si>
     <t xml:space="preserve">Probably very good but I've smelled too many similar dirt and rain and moss ones </t>
   </si>
   <si>
-    <t>Montale</t>
-  </si>
-  <si>
-    <t>Intense Pepper</t>
-  </si>
-  <si>
-    <t>Twisted Lily</t>
-  </si>
-  <si>
-    <t>https://twistedlily.com/products/intense-pepper-sample</t>
+    <t>Fils de Joie</t>
+  </si>
+  <si>
+    <t>https://theperfumedcourt.com/products/serge-lutens-fils-de-joie-edp-decant-sample</t>
   </si>
   <si>
     <t>In the Library</t>
@@ -1154,28 +1340,34 @@
     <t>Paris – Paris</t>
   </si>
   <si>
+    <t>1ml is $9.99. Discontinued from the Noire collection.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nice rose </t>
   </si>
   <si>
+    <t>SJP</t>
+  </si>
+  <si>
+    <t>Stash SJP</t>
+  </si>
+  <si>
+    <t>MicroPerfumes / Maple Prime</t>
+  </si>
+  <si>
+    <t>https://microperfumes.com/products/stash-edp-sample-vial</t>
+  </si>
+  <si>
     <t>Le Lion</t>
   </si>
   <si>
     <t xml:space="preserve">No thanks </t>
   </si>
   <si>
-    <t>DecantX and Maple Prime have no sample in stock.</t>
-  </si>
-  <si>
     <t>Sycomore</t>
   </si>
   <si>
-    <t>Prissana</t>
-  </si>
-  <si>
-    <t>Nefer</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
+    <t>Sample and 10ml both sold out.</t>
   </si>
   <si>
     <t>31 Rue Cambon</t>
@@ -1184,19 +1376,34 @@
     <t xml:space="preserve">Apparently a masterpiece. Giving it too many chances. It's diaper and sour underneath all the great stuff I smell. Drydown is better. </t>
   </si>
   <si>
+    <t>The 7 Virtues</t>
+  </si>
+  <si>
+    <t>Vetiver Elemi</t>
+  </si>
+  <si>
+    <t>Perfumed Court carries the brand, only three other scents.</t>
+  </si>
+  <si>
     <t>Coromandel</t>
   </si>
   <si>
     <t xml:space="preserve">Magic </t>
   </si>
   <si>
+    <t>The House of Oud</t>
+  </si>
+  <si>
+    <t>Almond Harmony</t>
+  </si>
+  <si>
     <t>1957</t>
   </si>
   <si>
     <t xml:space="preserve">Musky white, surprisingly great, simple </t>
   </si>
   <si>
-    <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
+    <t>Maple Prime has 75ml at $127.99.</t>
   </si>
   <si>
     <t>Bleu de Chanel</t>
@@ -1205,10 +1412,10 @@
     <t xml:space="preserve">Nice, basic cologne </t>
   </si>
   <si>
-    <t>Nest</t>
-  </si>
-  <si>
-    <t>Black Tulip</t>
+    <t>Une Nuit Nomade</t>
+  </si>
+  <si>
+    <t>Chemin d'Amande</t>
   </si>
   <si>
     <t>Chasing Scents</t>
@@ -1220,13 +1427,13 @@
     <t xml:space="preserve">Sweet tea in a rubber </t>
   </si>
   <si>
-    <t>Olfactive Studio</t>
-  </si>
-  <si>
-    <t>Flash Back</t>
-  </si>
-  <si>
-    <t>Listed as Flashback in New York.</t>
+    <t>Vilhelm Parfumerie</t>
+  </si>
+  <si>
+    <t>Fleur Burlesque</t>
+  </si>
+  <si>
+    <t>https://twistedlily.com/products/fleur-burlesque-sample</t>
   </si>
   <si>
     <t>Weeping Rose</t>
@@ -1235,15 +1442,6 @@
     <t xml:space="preserve">Dastardly. Nice for a literal minute then gross amber maple syrup </t>
   </si>
   <si>
-    <t>One Day</t>
-  </si>
-  <si>
-    <t>Taipei</t>
-  </si>
-  <si>
-    <t>Ministry of Scent sample sold out.</t>
-  </si>
-  <si>
     <t>Chloé</t>
   </si>
   <si>
@@ -1253,25 +1451,22 @@
     <t xml:space="preserve">Sparkly and bright and rose, it's good. I think I like Chloe in general. </t>
   </si>
   <si>
-    <t>Ormonde Jayne</t>
-  </si>
-  <si>
-    <t>Montabaco Intensivo</t>
+    <t>Scent Split lists it sold out.</t>
   </si>
   <si>
     <t>Sous les Pins</t>
   </si>
   <si>
-    <t>Bloom has standard Montabaco at $10, not Intensivo.</t>
-  </si>
-  <si>
     <t>Something underneath that I hate</t>
   </si>
   <si>
-    <t>Paco Rabanne</t>
-  </si>
-  <si>
-    <t>Maple Prime has full bottles from $38.99, no small size anywhere.</t>
+    <t>YSL</t>
+  </si>
+  <si>
+    <t>Rive Gauche Pour Homme</t>
+  </si>
+  <si>
+    <t>Only the women's Rive Gauche turns up.</t>
   </si>
   <si>
     <t>Chloé Eau de Parfum</t>
@@ -1280,9 +1475,6 @@
     <t xml:space="preserve">So classic and good, not old lady, easy to wear but very feminine </t>
   </si>
   <si>
-    <t>Duplicate of the row above.</t>
-  </si>
-  <si>
     <t>Clue Perfumery</t>
   </si>
   <si>
@@ -1292,88 +1484,73 @@
     <t xml:space="preserve">Weeds with fat, as advertised. It's really nice. Doesn't last long. </t>
   </si>
   <si>
-    <t>Papillon Artisan</t>
-  </si>
-  <si>
-    <t>Tobacco Rose</t>
+    <t>Kouros</t>
   </si>
   <si>
     <t>Amy</t>
   </si>
   <si>
-    <t>Perfumed Court $10.94. Papillon's own site sells full bottles only.</t>
-  </si>
-  <si>
-    <t>Parfumerie Particulière</t>
-  </si>
-  <si>
-    <t>Black Tar</t>
-  </si>
-  <si>
-    <t>Ministry of Scent has 2ml at $7.00.</t>
+    <t>Maple Prime has 100ml at $80.99, no sample anywhere.</t>
+  </si>
+  <si>
+    <t>Frédéric Malle</t>
+  </si>
+  <si>
+    <t>French Lover</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/frederic-malle-french-lover-eau-de-parfum-for-men</t>
   </si>
   <si>
     <t>Morel Map</t>
   </si>
   <si>
-    <t>Penhaligon's</t>
-  </si>
-  <si>
-    <t>Blenheim Bouquet</t>
-  </si>
-  <si>
     <t xml:space="preserve">Damp mossy forest floor, beautiful </t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
-  </si>
-  <si>
     <t>Warm Bulb</t>
   </si>
   <si>
     <t xml:space="preserve">I like it but I don't love it on. More of a novelty. </t>
   </si>
   <si>
+    <t>Also in your Maple Prime cart at 1.2ml for $12.99.</t>
+  </si>
+  <si>
     <t>With the Candlestick</t>
   </si>
   <si>
     <t>Bad candy? Clumsy</t>
   </si>
   <si>
+    <t>Viktor &amp; Rolf</t>
+  </si>
+  <si>
+    <t>Spicebomb Metallic Musk</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/viktor-rolf-spicebomb-metallic-musk-eau-de-parfum-for-men</t>
+  </si>
+  <si>
     <t>Need to try on my skin but so nice</t>
   </si>
   <si>
-    <t>Liquid Love</t>
-  </si>
-  <si>
     <t>Monocle Scent Three: Sugi</t>
   </si>
   <si>
-    <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Similar to Setchu but leaves me wanting more </t>
   </si>
   <si>
-    <t>Parfums Quartana</t>
-  </si>
-  <si>
-    <t>Forest of the Golden Dream</t>
-  </si>
-  <si>
-    <t>Their own site would not load when I tried.</t>
-  </si>
-  <si>
     <t>Series 1 Leaves: Lily</t>
   </si>
   <si>
+    <t>This is Viktor &amp; Rolf Spicebomb Metallic Musk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Simple white floral but a flower I'm not that familiar with </t>
   </si>
   <si>
-    <t>Ierofante</t>
-  </si>
-  <si>
-    <t>Worth confirming the spelling.</t>
+    <t>Buongiorno</t>
   </si>
   <si>
     <t>Serpentine</t>
@@ -1382,13 +1559,13 @@
     <t>Nice! Probably duplicative but I could wear this.</t>
   </si>
   <si>
-    <t>Robert Piguet</t>
-  </si>
-  <si>
-    <t>Bandit</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
+    <t>DecantX has it at $13.29.</t>
+  </si>
+  <si>
+    <t>Moss Cologne</t>
+  </si>
+  <si>
+    <t>Luckyscent carries Bortnikoff too.</t>
   </si>
   <si>
     <t>Amazingreen</t>
@@ -1397,7 +1574,13 @@
     <t xml:space="preserve">Not a favorite. </t>
   </si>
   <si>
-    <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
+    <t>Vanilla Black Pepper</t>
+  </si>
+  <si>
+    <t>Ministry of Scent</t>
+  </si>
+  <si>
+    <t>https://ministryofscent.com/products/vanilla-black-pepper</t>
   </si>
   <si>
     <t>Incense: Kyoto</t>
@@ -1412,34 +1595,43 @@
     <t>I can't tell if this is tricking me? Apparently it smells like 90s A&amp;F mall scent, but I love it. Floral but tomato leaf but something spicy? Could turn terrible, but we will see</t>
   </si>
   <si>
-    <t>Rogue Perfumery</t>
-  </si>
-  <si>
-    <t>(discovery set)</t>
+    <t>Formerly Tigerlily Perfumery, San Francisco.</t>
   </si>
   <si>
     <t>Cologne: Anbar</t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
-  </si>
-  <si>
     <t xml:space="preserve">Citrus, then warm spice. Clove? I shouldn't like this but it feels like an easy summer splash on cologne that isn't basic </t>
   </si>
   <si>
+    <t>Les Bains Guerbois</t>
+  </si>
+  <si>
+    <t>Rose Graffiti</t>
+  </si>
+  <si>
     <t>Ganja</t>
   </si>
   <si>
+    <t>No 1ml listed for this one.</t>
+  </si>
+  <si>
     <t>I liked it then didn't then did then didn't then DID!</t>
   </si>
   <si>
+    <t>Angelos Creations Olfactives</t>
+  </si>
+  <si>
+    <t>Pothos</t>
+  </si>
+  <si>
     <t>Odeur 10</t>
   </si>
   <si>
     <t>Like a row of washing machines in action. Metal, clean, not detergent but very soapy, don't want to wear but very good</t>
   </si>
   <si>
-    <t>Rogue's own discovery set is sold out and most of their line with it.</t>
+    <t>https://www.luckyscent.com/products/pothos-by-angelos-creations-olfactives</t>
   </si>
   <si>
     <t>Monocle Scent Four: Yoyogi</t>
@@ -1448,21 +1640,21 @@
     <t>Pleasant wood, just kind of a watered down Laurel</t>
   </si>
   <si>
-    <t>Romeo Gigli</t>
-  </si>
-  <si>
-    <t>Romeo di Romeo Gigli</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
-  </si>
-  <si>
     <t>Dot</t>
   </si>
   <si>
     <t xml:space="preserve">Sweet and maybe well crafted but no </t>
   </si>
   <si>
+    <t>CBCB Fragrances</t>
+  </si>
+  <si>
+    <t>Comrade</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/comrade-by-cbcb-fragrances</t>
+  </si>
+  <si>
     <t>Incense: Ouarzazate</t>
   </si>
   <si>
@@ -1475,39 +1667,18 @@
     <t xml:space="preserve">Amber pepper wood, doesn't last for shit </t>
   </si>
   <si>
-    <t>Cheapest on the list.</t>
-  </si>
-  <si>
-    <t>Sanctuary</t>
-  </si>
-  <si>
     <t>Incense: Zagorsk</t>
   </si>
   <si>
-    <t>Javan Rhino</t>
-  </si>
-  <si>
     <t>Not into this one</t>
   </si>
   <si>
-    <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
-  </si>
-  <si>
-    <t>Senyokô</t>
-  </si>
-  <si>
     <t>Artek: Standard</t>
   </si>
   <si>
-    <t>Indigo Perfumery</t>
-  </si>
-  <si>
     <t xml:space="preserve">Factory smells a bit. But not very interesting </t>
   </si>
   <si>
-    <t>https://indigoperfumery.com</t>
-  </si>
-  <si>
     <t>Marseille</t>
   </si>
   <si>
@@ -1517,39 +1688,12 @@
     <t xml:space="preserve">Photorealistic pot smell. Amazing. Absolutely not. </t>
   </si>
   <si>
-    <t>Indigo carries the line, no samples listed.</t>
-  </si>
-  <si>
-    <t>Serge Lutens</t>
-  </si>
-  <si>
-    <t>Poivre Noir</t>
-  </si>
-  <si>
     <t>Incense: Jaisalmer</t>
   </si>
   <si>
-    <t>https://www.decantx.com/products/serge-lutens-poivre-noir-eau-de-parfum-unisex</t>
-  </si>
-  <si>
     <t>Incense: Avignon</t>
   </si>
   <si>
-    <t>Sample listed, sold out. Maple Prime has 100ml at $76.99.</t>
-  </si>
-  <si>
-    <t>Vitriol d'Œillet</t>
-  </si>
-  <si>
-    <t>Not at any of the three retailers that carry Serge Lutens.</t>
-  </si>
-  <si>
-    <t>Fils de Joie</t>
-  </si>
-  <si>
-    <t>https://theperfumedcourt.com/products/serge-lutens-fils-de-joie-edp-decant-sample</t>
-  </si>
-  <si>
     <t>Monocle Scent Two: Laurel</t>
   </si>
   <si>
@@ -1562,27 +1706,12 @@
     <t xml:space="preserve">Perfect white floral with a hint of Ziplock bags, not overly tuberose </t>
   </si>
   <si>
-    <t>1ml is $9.99. Discontinued from the Noire collection.</t>
-  </si>
-  <si>
     <t>Chlorophyll Gardenia</t>
   </si>
   <si>
-    <t>SJP</t>
-  </si>
-  <si>
-    <t>Stash SJP</t>
-  </si>
-  <si>
-    <t>MicroPerfumes / Maple Prime</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
   </si>
   <si>
-    <t>https://microperfumes.com/products/stash-edp-sample-vial</t>
-  </si>
-  <si>
     <t>Odeur 53</t>
   </si>
   <si>
@@ -1598,66 +1727,30 @@
     <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
   </si>
   <si>
-    <t>Sample and 10ml both sold out.</t>
-  </si>
-  <si>
     <t>Blackpepper</t>
   </si>
   <si>
     <t xml:space="preserve">Black pepper for sure. Doesn't last. I'd definitely spray this on if it were around. </t>
   </si>
   <si>
-    <t>The 7 Virtues</t>
-  </si>
-  <si>
-    <t>Vetiver Elemi</t>
-  </si>
-  <si>
-    <t>Perfumed Court carries the brand, only three other scents.</t>
-  </si>
-  <si>
     <t>Monocle Scent One: Hinoki</t>
   </si>
   <si>
     <t xml:space="preserve">Balanced and beautiful wood, but a sourness makes me not want to wear it </t>
   </si>
   <si>
-    <t>The House of Oud</t>
-  </si>
-  <si>
-    <t>Almond Harmony</t>
-  </si>
-  <si>
-    <t>Maple Prime has 75ml at $127.99.</t>
-  </si>
-  <si>
     <t>Grace</t>
   </si>
   <si>
     <t xml:space="preserve">Pleasant floral, not to special </t>
   </si>
   <si>
-    <t>Une Nuit Nomade</t>
-  </si>
-  <si>
-    <t>Chemin d'Amande</t>
-  </si>
-  <si>
     <t>Cologne: Citrico</t>
   </si>
   <si>
     <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
   </si>
   <si>
-    <t>Vilhelm Parfumerie</t>
-  </si>
-  <si>
-    <t>Fleur Burlesque</t>
-  </si>
-  <si>
-    <t>https://twistedlily.com/products/fleur-burlesque-sample</t>
-  </si>
-  <si>
     <t>Cologne: Vettiveru</t>
   </si>
   <si>
@@ -1676,9 +1769,6 @@
     <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
   </si>
   <si>
-    <t>Scent Split lists it sold out.</t>
-  </si>
-  <si>
     <t>Coqui Coqui</t>
   </si>
   <si>
@@ -1688,42 +1778,18 @@
     <t>Very brash eucalyptus and cedar. I like it?</t>
   </si>
   <si>
-    <t>YSL</t>
-  </si>
-  <si>
-    <t>Rive Gauche Pour Homme</t>
-  </si>
-  <si>
-    <t>Only the women's Rive Gauche turns up.</t>
-  </si>
-  <si>
     <t>Rosas Secas</t>
   </si>
   <si>
     <t xml:space="preserve">Tart rose but dried roses, nice! </t>
   </si>
   <si>
-    <t>Kouros</t>
-  </si>
-  <si>
-    <t>Maple Prime has 100ml at $80.99, no sample anywhere.</t>
-  </si>
-  <si>
     <t>Maderas</t>
   </si>
   <si>
     <t xml:space="preserve">Hard to describe. Warm spice underneath </t>
   </si>
   <si>
-    <t>Frédéric Malle</t>
-  </si>
-  <si>
-    <t>French Lover</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/frederic-malle-french-lover-eau-de-parfum-for-men</t>
-  </si>
-  <si>
     <t>Coqui coqui</t>
   </si>
   <si>
@@ -1751,27 +1817,15 @@
     <t>Silver Mountain Water</t>
   </si>
   <si>
-    <t>Also in your Maple Prime cart at 1.2ml for $12.99.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fine, subtle, freshie, eh </t>
   </si>
   <si>
-    <t>Viktor &amp; Rolf</t>
-  </si>
-  <si>
-    <t>Spicebomb Metallic Musk</t>
-  </si>
-  <si>
     <t>White Flowers</t>
   </si>
   <si>
     <t>Weirdly bad, I don't get it</t>
   </si>
   <si>
-    <t>https://www.decantx.com/products/viktor-rolf-spicebomb-metallic-musk-eau-de-parfum-for-men</t>
-  </si>
-  <si>
     <t>Czech &amp; Speake</t>
   </si>
   <si>
@@ -1790,21 +1844,12 @@
     <t>White floral, lovely, duplicative but maybe...?</t>
   </si>
   <si>
-    <t>This is Viktor &amp; Rolf Spicebomb Metallic Musk.</t>
-  </si>
-  <si>
     <t>Da Lat</t>
   </si>
   <si>
     <t xml:space="preserve">Complex rose, liking it less the more I try it. </t>
   </si>
   <si>
-    <t>Buongiorno</t>
-  </si>
-  <si>
-    <t>DecantX has it at $13.29.</t>
-  </si>
-  <si>
     <t>D'Orsay</t>
   </si>
   <si>
@@ -1814,12 +1859,6 @@
     <t>Too minty</t>
   </si>
   <si>
-    <t>Moss Cologne</t>
-  </si>
-  <si>
-    <t>Luckyscent carries Bortnikoff too.</t>
-  </si>
-  <si>
     <t>D&amp;Scent Studios</t>
   </si>
   <si>
@@ -1829,15 +1868,6 @@
     <t>Green and dry and bitter, could try again</t>
   </si>
   <si>
-    <t>Vanilla Black Pepper</t>
-  </si>
-  <si>
-    <t>Ministry of Scent</t>
-  </si>
-  <si>
-    <t>https://ministryofscent.com/products/vanilla-black-pepper</t>
-  </si>
-  <si>
     <t>Der Duft</t>
   </si>
   <si>
@@ -1853,42 +1883,21 @@
     <t xml:space="preserve">Interesting but no </t>
   </si>
   <si>
-    <t>Formerly Tigerlily Perfumery, San Francisco.</t>
-  </si>
-  <si>
     <t>Match</t>
   </si>
   <si>
     <t xml:space="preserve">Super subtle, burnt match I guess </t>
   </si>
   <si>
-    <t>Les Bains Guerbois</t>
-  </si>
-  <si>
-    <t>Rose Graffiti</t>
-  </si>
-  <si>
     <t>Dior</t>
   </si>
   <si>
-    <t>No 1ml listed for this one.</t>
-  </si>
-  <si>
     <t>Thé Cachemire</t>
   </si>
   <si>
     <t xml:space="preserve">Tea and floral, citrus at the upfront, well crafted and I enjoy smelling it. Got better over time too. Duplicative but great. </t>
   </si>
   <si>
-    <t>Angelos Creations Olfactives</t>
-  </si>
-  <si>
-    <t>Pothos</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/pothos-by-angelos-creations-olfactives</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nice rose. Didn't get to wear on skin tho </t>
   </si>
   <si>
@@ -1913,16 +1922,7 @@
     <t>Dior Addict Eau de Toilette</t>
   </si>
   <si>
-    <t>CBCB Fragrances</t>
-  </si>
-  <si>
-    <t>Comrade</t>
-  </si>
-  <si>
     <t xml:space="preserve">Intriguing and layered, don't think I want to smell like it but I'm still sniffing? </t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/comrade-by-cbcb-fragrances</t>
   </si>
   <si>
     <t>Bois d'Argent</t>
@@ -5550,10 +5550,10 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -5599,10 +5599,10 @@
     <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -6012,14 +6012,14 @@
       <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="11">
         <v>71.0</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -6191,16 +6191,16 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="11">
         <v>85.0</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="12"/>
@@ -6227,16 +6227,16 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="11">
         <v>80.0</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="12"/>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>43</v>
@@ -6335,16 +6335,16 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C10" s="11">
         <v>89.0</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="12"/>
@@ -6371,16 +6371,16 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" s="11">
         <v>85.0</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="12"/>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>58</v>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>60</v>
@@ -6452,7 +6452,7 @@
         <v>75.0</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="12"/>
@@ -6479,16 +6479,16 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="11">
         <v>90.0</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="12"/>
@@ -6515,16 +6515,16 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C15" s="11">
         <v>40.0</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="12"/>
@@ -6551,16 +6551,16 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C16" s="11">
         <v>40.0</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E16" s="17"/>
       <c r="F16" s="12"/>
@@ -6587,10 +6587,10 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" s="11">
         <v>40.0</v>
@@ -6668,11 +6668,11 @@
         <v>82.0</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="30"/>
-      <c r="G19" s="24"/>
+      <c r="G19" s="25"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
@@ -6698,13 +6698,13 @@
         <v>76</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C20" s="11">
         <v>87.0</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
@@ -6731,16 +6731,16 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C21" s="11">
         <v>70.0</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="12"/>
@@ -6767,16 +6767,16 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C22" s="11">
         <v>50.0</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="12"/>
@@ -6803,16 +6803,16 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C23" s="11">
         <v>88.0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="12"/>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" s="33" t="s">
         <v>102</v>
@@ -6875,7 +6875,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>104</v>
@@ -6950,13 +6950,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="11">
         <v>35.0</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="27"/>
@@ -6986,13 +6986,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C28" s="11">
         <v>50.0</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="12"/>
@@ -7022,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C29" s="11">
         <v>82.0</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="27"/>
@@ -7055,16 +7055,16 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="11">
         <v>60.0</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="12"/>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>127</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>129</v>
@@ -7166,13 +7166,13 @@
         <v>131</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C33" s="11">
         <v>83.0</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="12"/>
@@ -7202,13 +7202,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C34" s="11">
         <v>88.0</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="12"/>
@@ -7238,13 +7238,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C35" s="11">
         <v>86.0</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="12"/>
@@ -7274,13 +7274,13 @@
         <v>131</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C36" s="11">
         <v>87.0</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="12"/>
@@ -7310,13 +7310,13 @@
         <v>131</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C37" s="11">
         <v>60.0</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="12"/>
@@ -7346,7 +7346,7 @@
         <v>131</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="11">
         <v>60.0</v>
@@ -7382,13 +7382,13 @@
         <v>131</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" s="11">
         <v>85.0</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="12"/>
@@ -7418,13 +7418,13 @@
         <v>131</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C40" s="11">
         <v>89.0</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="12"/>
@@ -7454,13 +7454,13 @@
         <v>131</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C41" s="11">
         <v>90.0</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="12"/>
@@ -7490,13 +7490,13 @@
         <v>131</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C42" s="11">
         <v>82.0</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="12"/>
@@ -7526,13 +7526,13 @@
         <v>131</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C43" s="11">
         <v>82.0</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="12"/>
@@ -7562,13 +7562,13 @@
         <v>131</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C44" s="11">
         <v>84.0</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="12"/>
@@ -7598,13 +7598,13 @@
         <v>131</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C45" s="11">
         <v>78.0</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="12"/>
@@ -7634,13 +7634,13 @@
         <v>131</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C46" s="11">
         <v>87.0</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="12"/>
@@ -7667,16 +7667,16 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="C47" s="11">
         <v>65.0</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="12"/>
@@ -7703,16 +7703,16 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C48" s="11">
         <v>82.0</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="12"/>
@@ -7739,16 +7739,16 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C49" s="11">
         <v>87.0</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="12"/>
@@ -7775,16 +7775,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C50" s="11">
         <v>60.0</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="12"/>
@@ -7811,16 +7811,16 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="10" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C51" s="11">
         <v>90.0</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="12"/>
@@ -7847,16 +7847,16 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C52" s="11">
         <v>88.0</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="36"/>
@@ -7883,16 +7883,16 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="27" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="C53" s="11">
         <v>82.0</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="E53" s="27"/>
       <c r="F53" s="27"/>
@@ -7919,10 +7919,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="37" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="27"/>
@@ -7951,16 +7951,16 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="C55" s="11">
         <v>69.0</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="12"/>
@@ -7987,16 +7987,16 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="27" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="C56" s="11">
         <v>81.0</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="E56" s="17"/>
       <c r="F56" s="12"/>
@@ -8023,16 +8023,16 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="27" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="C57" s="11">
         <v>88.0</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="E57" s="27"/>
       <c r="F57" s="27"/>
@@ -8059,16 +8059,16 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="27" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="C58" s="11">
         <v>87.0</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="E58" s="27"/>
       <c r="F58" s="27"/>
@@ -8095,16 +8095,16 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="27" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="C59" s="38">
         <v>40.0</v>
       </c>
       <c r="D59" s="39" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="E59" s="27"/>
       <c r="F59" s="27"/>
@@ -8131,16 +8131,16 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="C60" s="11">
         <v>80.0</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="27"/>
@@ -8167,16 +8167,16 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="26" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="C61" s="11">
         <v>50.0</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
@@ -8203,16 +8203,16 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="26" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="C62" s="11">
         <v>40.0</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="E62" s="17"/>
       <c r="F62" s="12"/>
@@ -8239,16 +8239,16 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="10" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="C63" s="11">
         <v>40.0</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="12"/>
@@ -8275,16 +8275,16 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="19" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="C64" s="20">
         <v>40.0</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="23"/>
@@ -8311,16 +8311,16 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>236</v>
+        <v>291</v>
       </c>
       <c r="C65" s="11">
         <v>65.0</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
@@ -8347,16 +8347,16 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="10" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="C66" s="11">
         <v>85.0</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="E66" s="10"/>
       <c r="F66" s="12"/>
@@ -8383,16 +8383,16 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="C67" s="11">
         <v>88.0</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
@@ -8419,16 +8419,16 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="C68" s="11">
         <v>88.0</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>248</v>
+        <v>303</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="12"/>
@@ -8455,16 +8455,16 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>252</v>
+        <v>307</v>
       </c>
       <c r="C69" s="11">
         <v>50.0</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="E69" s="26"/>
       <c r="F69" s="12"/>
@@ -8491,16 +8491,16 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="C70" s="41">
         <v>50.0</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="42"/>
@@ -8527,16 +8527,16 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="C71" s="11">
         <v>50.0</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="12"/>
@@ -8563,16 +8563,16 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="C72" s="11">
         <v>84.0</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="12"/>
@@ -8599,16 +8599,16 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="C73" s="11">
         <v>60.0</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="E73" s="17"/>
       <c r="F73" s="12"/>
@@ -8635,16 +8635,16 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>277</v>
+        <v>330</v>
       </c>
       <c r="C74" s="11">
         <v>99.0</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="12"/>
@@ -8671,16 +8671,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="C75" s="11">
         <v>90.0</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="12"/>
@@ -8707,16 +8707,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>281</v>
+        <v>339</v>
       </c>
       <c r="C76" s="11">
         <v>89.0</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="E76" s="17"/>
       <c r="F76" s="12"/>
@@ -8743,16 +8743,16 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="C77" s="11">
         <v>86.0</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="E77" s="10"/>
       <c r="F77" s="12"/>
@@ -8779,16 +8779,16 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="C78" s="11">
         <v>84.0</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="12"/>
@@ -8815,16 +8815,16 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="C79" s="11">
         <v>83.0</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>294</v>
+        <v>350</v>
       </c>
       <c r="E79" s="10"/>
       <c r="F79" s="12"/>
@@ -8851,16 +8851,16 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="C80" s="11">
         <v>83.0</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="12"/>
@@ -8887,16 +8887,16 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="C81" s="11">
         <v>82.0</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="E81" s="10"/>
       <c r="F81" s="12"/>
@@ -8923,16 +8923,16 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B82" s="29" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="C82" s="11">
         <v>81.0</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="12"/>
@@ -8959,16 +8959,16 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="C83" s="11">
         <v>80.0</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="E83" s="10"/>
       <c r="F83" s="12"/>
@@ -8995,16 +8995,16 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>310</v>
+        <v>366</v>
       </c>
       <c r="C84" s="11">
         <v>79.0</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="E84" s="10"/>
       <c r="F84" s="12"/>
@@ -9031,16 +9031,16 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="C85" s="11">
         <v>74.0</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="12"/>
@@ -9067,16 +9067,16 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="C86" s="11">
         <v>71.0</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>318</v>
+        <v>374</v>
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="12"/>
@@ -9103,16 +9103,16 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="10" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>321</v>
+        <v>375</v>
       </c>
       <c r="C87" s="11">
         <v>70.0</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="E87" s="10"/>
       <c r="F87" s="12"/>
@@ -9139,16 +9139,16 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="C88" s="11">
         <v>96.0</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="E88" s="10"/>
       <c r="F88" s="12"/>
@@ -9175,16 +9175,16 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>326</v>
+        <v>382</v>
       </c>
       <c r="C89" s="11">
         <v>89.0</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="E89" s="10"/>
       <c r="F89" s="12"/>
@@ -9211,16 +9211,16 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="C90" s="11">
         <v>86.0</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="E90" s="10"/>
       <c r="F90" s="12"/>
@@ -9247,16 +9247,16 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="C91" s="11">
         <v>84.0</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="12"/>
@@ -9283,16 +9283,16 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="C92" s="11">
         <v>83.0</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="12"/>
@@ -9319,16 +9319,16 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="C93" s="11">
         <v>83.0</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>340</v>
+        <v>396</v>
       </c>
       <c r="E93" s="10"/>
       <c r="F93" s="12"/>
@@ -9355,16 +9355,16 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="C94" s="11">
         <v>93.0</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="12"/>
@@ -9391,16 +9391,16 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="C95" s="11">
         <v>91.0</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="E95" s="10"/>
       <c r="F95" s="12"/>
@@ -9427,16 +9427,16 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="C96" s="11">
         <v>87.0</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="12"/>
@@ -9463,16 +9463,16 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="C97" s="11">
         <v>85.0</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="E97" s="10"/>
       <c r="F97" s="12"/>
@@ -9499,16 +9499,16 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="C98" s="11">
         <v>82.0</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="12"/>
@@ -9535,16 +9535,16 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="C99" s="11">
         <v>80.0</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>356</v>
+        <v>417</v>
       </c>
       <c r="E99" s="10"/>
       <c r="F99" s="12"/>
@@ -9571,14 +9571,14 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="10" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="12"/>
@@ -9605,16 +9605,16 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="10" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>363</v>
+        <v>424</v>
       </c>
       <c r="C101" s="11">
         <v>89.0</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="12"/>
@@ -9641,16 +9641,16 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="10" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="C102" s="11">
         <v>85.0</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="E102" s="17"/>
       <c r="F102" s="12"/>
@@ -9677,16 +9677,16 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="10" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="C103" s="11">
         <v>84.0</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="E103" s="10"/>
       <c r="F103" s="12"/>
@@ -9713,16 +9713,16 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="10" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>369</v>
+        <v>433</v>
       </c>
       <c r="C104" s="11">
         <v>82.0</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="E104" s="10"/>
       <c r="F104" s="12"/>
@@ -9749,16 +9749,16 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="10" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>375</v>
+        <v>437</v>
       </c>
       <c r="C105" s="11">
         <v>70.0</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>376</v>
+        <v>438</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="12"/>
@@ -9785,16 +9785,16 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>377</v>
+        <v>439</v>
       </c>
       <c r="C106" s="11">
         <v>88.0</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>378</v>
+        <v>440</v>
       </c>
       <c r="E106" s="10"/>
       <c r="F106" s="12"/>
@@ -9821,16 +9821,16 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>379</v>
+        <v>441</v>
       </c>
       <c r="C107" s="11">
         <v>82.0</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="E107" s="10"/>
       <c r="F107" s="12"/>
@@ -9857,16 +9857,16 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>381</v>
+        <v>448</v>
       </c>
       <c r="C108" s="11">
         <v>74.0</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="E108" s="10"/>
       <c r="F108" s="12"/>
@@ -9893,16 +9893,16 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>384</v>
+        <v>450</v>
       </c>
       <c r="C109" s="11">
         <v>74.0</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="E109" s="10"/>
       <c r="F109" s="12"/>
@@ -9929,16 +9929,16 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>388</v>
+        <v>452</v>
       </c>
       <c r="C110" s="11">
         <v>71.0</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>389</v>
+        <v>453</v>
       </c>
       <c r="E110" s="10"/>
       <c r="F110" s="12"/>
@@ -9965,16 +9965,16 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="C111" s="11">
         <v>90.0</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>391</v>
+        <v>458</v>
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="12"/>
@@ -10001,16 +10001,16 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
       <c r="C112" s="11">
         <v>81.0</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>393</v>
+        <v>462</v>
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="12"/>
@@ -10037,16 +10037,16 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>395</v>
+        <v>464</v>
       </c>
       <c r="C113" s="11">
         <v>80.0</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>396</v>
+        <v>465</v>
       </c>
       <c r="E113" s="10"/>
       <c r="F113" s="12"/>
@@ -10073,16 +10073,16 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="27" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>400</v>
+        <v>469</v>
       </c>
       <c r="C114" s="11">
         <v>74.0</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>401</v>
+        <v>470</v>
       </c>
       <c r="E114" s="27"/>
       <c r="F114" s="27"/>
@@ -10109,16 +10109,16 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="27" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="B115" s="27" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="C115" s="11">
         <v>71.0</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>406</v>
+        <v>475</v>
       </c>
       <c r="E115" s="27"/>
       <c r="F115" s="27"/>
@@ -10145,16 +10145,16 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="10" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
       <c r="C116" s="11">
         <v>89.0</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="E116" s="10"/>
       <c r="F116" s="12"/>
@@ -10181,16 +10181,16 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="10" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="C117" s="11">
         <v>79.0</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="E117" s="17"/>
       <c r="F117" s="12"/>
@@ -10217,16 +10217,16 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="10" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>420</v>
+        <v>485</v>
       </c>
       <c r="C118" s="11">
         <v>91.0</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>421</v>
+        <v>486</v>
       </c>
       <c r="E118" s="17"/>
       <c r="F118" s="12"/>
@@ -10253,19 +10253,19 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="21" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="C119" s="41">
         <v>90.0</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>425</v>
+        <v>489</v>
       </c>
       <c r="E119" s="45" t="s">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="F119" s="10"/>
       <c r="G119" s="46"/>
@@ -10291,16 +10291,16 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>433</v>
+        <v>496</v>
       </c>
       <c r="C120" s="11">
         <v>90.0</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>436</v>
+        <v>497</v>
       </c>
       <c r="E120" s="10"/>
       <c r="F120" s="12"/>
@@ -10327,16 +10327,16 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="36" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="C121" s="11">
         <v>70.0</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>439</v>
+        <v>499</v>
       </c>
       <c r="E121" s="27"/>
       <c r="F121" s="36"/>
@@ -10363,16 +10363,16 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="C122" s="11">
         <v>55.0</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>441</v>
+        <v>502</v>
       </c>
       <c r="E122" s="10"/>
       <c r="F122" s="27"/>
@@ -10399,16 +10399,16 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="C123" s="11">
         <v>88.0</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>442</v>
+        <v>506</v>
       </c>
       <c r="E123" s="10"/>
       <c r="F123" s="12"/>
@@ -10435,16 +10435,16 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>444</v>
+        <v>507</v>
       </c>
       <c r="C124" s="11">
         <v>87.0</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>446</v>
+        <v>508</v>
       </c>
       <c r="E124" s="27"/>
       <c r="F124" s="27"/>
@@ -10471,16 +10471,16 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>450</v>
+        <v>509</v>
       </c>
       <c r="C125" s="11">
         <v>91.0</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="E125" s="27"/>
       <c r="F125" s="27"/>
@@ -10507,20 +10507,20 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>454</v>
+        <v>513</v>
       </c>
       <c r="C126" s="20">
         <v>89.0</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>455</v>
+        <v>514</v>
       </c>
       <c r="E126" s="22"/>
       <c r="F126" s="47"/>
-      <c r="G126" s="24"/>
+      <c r="G126" s="25"/>
       <c r="H126" s="48"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
@@ -10543,16 +10543,16 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>459</v>
+        <v>518</v>
       </c>
       <c r="C127" s="11">
         <v>50.0</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>460</v>
+        <v>519</v>
       </c>
       <c r="E127" s="10"/>
       <c r="F127" s="12"/>
@@ -10579,16 +10579,16 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>462</v>
+        <v>523</v>
       </c>
       <c r="C128" s="11">
         <v>91.0</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>463</v>
+        <v>524</v>
       </c>
       <c r="E128" s="27"/>
       <c r="F128" s="27"/>
@@ -10615,16 +10615,16 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>464</v>
+        <v>525</v>
       </c>
       <c r="C129" s="11">
         <v>91.0</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>465</v>
+        <v>526</v>
       </c>
       <c r="E129" s="27"/>
       <c r="F129" s="27"/>
@@ -10651,16 +10651,16 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>468</v>
+        <v>528</v>
       </c>
       <c r="C130" s="11">
         <v>90.0</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>470</v>
+        <v>529</v>
       </c>
       <c r="E130" s="27"/>
       <c r="F130" s="27"/>
@@ -10687,16 +10687,16 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>471</v>
+        <v>532</v>
       </c>
       <c r="C131" s="11">
         <v>89.0</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>472</v>
+        <v>534</v>
       </c>
       <c r="E131" s="27"/>
       <c r="F131" s="27"/>
@@ -10723,16 +10723,16 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>473</v>
+        <v>537</v>
       </c>
       <c r="C132" s="11">
         <v>88.0</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>474</v>
+        <v>538</v>
       </c>
       <c r="E132" s="27"/>
       <c r="F132" s="27"/>
@@ -10759,16 +10759,16 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="C133" s="11">
         <v>87.0</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>477</v>
+        <v>541</v>
       </c>
       <c r="E133" s="27"/>
       <c r="F133" s="27"/>
@@ -10795,16 +10795,16 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>481</v>
+        <v>542</v>
       </c>
       <c r="C134" s="11">
         <v>86.0</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>482</v>
+        <v>543</v>
       </c>
       <c r="E134" s="27"/>
       <c r="F134" s="27"/>
@@ -10831,16 +10831,16 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>483</v>
+        <v>547</v>
       </c>
       <c r="C135" s="11">
         <v>85.0</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>484</v>
+        <v>548</v>
       </c>
       <c r="E135" s="27"/>
       <c r="F135" s="27"/>
@@ -10867,16 +10867,16 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>485</v>
+        <v>549</v>
       </c>
       <c r="C136" s="11">
         <v>83.0</v>
       </c>
       <c r="D136" s="27" t="s">
-        <v>486</v>
+        <v>550</v>
       </c>
       <c r="E136" s="27"/>
       <c r="F136" s="27"/>
@@ -10903,16 +10903,16 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>489</v>
+        <v>551</v>
       </c>
       <c r="C137" s="11">
         <v>83.0</v>
       </c>
       <c r="D137" s="27" t="s">
-        <v>491</v>
+        <v>552</v>
       </c>
       <c r="E137" s="27"/>
       <c r="F137" s="27"/>
@@ -10939,16 +10939,16 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B138" s="36" t="s">
-        <v>494</v>
+        <v>553</v>
       </c>
       <c r="C138" s="11">
         <v>82.0</v>
       </c>
       <c r="D138" s="27" t="s">
-        <v>496</v>
+        <v>554</v>
       </c>
       <c r="E138" s="27"/>
       <c r="F138" s="27"/>
@@ -10975,16 +10975,16 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>498</v>
+        <v>555</v>
       </c>
       <c r="C139" s="11">
         <v>82.0</v>
       </c>
       <c r="D139" s="27" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="E139" s="27"/>
       <c r="F139" s="27"/>
@@ -11011,16 +11011,16 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B140" s="26" t="s">
-        <v>471</v>
+        <v>532</v>
       </c>
       <c r="C140" s="11">
         <v>70.0</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>500</v>
+        <v>557</v>
       </c>
       <c r="E140" s="26"/>
       <c r="F140" s="12"/>
@@ -11047,10 +11047,10 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B141" s="50" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="27"/>
@@ -11079,10 +11079,10 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B142" s="50" t="s">
-        <v>506</v>
+        <v>559</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="27"/>
@@ -11111,16 +11111,16 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B143" s="52" t="s">
-        <v>512</v>
+        <v>560</v>
       </c>
       <c r="C143" s="11">
         <v>96.0</v>
       </c>
       <c r="D143" s="27" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
       <c r="E143" s="27"/>
       <c r="F143" s="27"/>
@@ -11147,16 +11147,16 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="53" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>514</v>
+        <v>562</v>
       </c>
       <c r="C144" s="11">
         <v>94.0</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="12"/>
@@ -11183,16 +11183,16 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>517</v>
+        <v>564</v>
       </c>
       <c r="C145" s="11">
         <v>91.0</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>521</v>
+        <v>565</v>
       </c>
       <c r="E145" s="10"/>
       <c r="F145" s="12"/>
@@ -11219,16 +11219,16 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B146" s="36" t="s">
-        <v>523</v>
+        <v>566</v>
       </c>
       <c r="C146" s="11">
         <v>90.0</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>524</v>
+        <v>567</v>
       </c>
       <c r="E146" s="10"/>
       <c r="F146" s="12"/>
@@ -11255,16 +11255,16 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>525</v>
+        <v>568</v>
       </c>
       <c r="C147" s="11">
         <v>89.0</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>526</v>
+        <v>569</v>
       </c>
       <c r="E147" s="10"/>
       <c r="F147" s="12"/>
@@ -11291,16 +11291,16 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="C148" s="11">
         <v>88.0</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>527</v>
+        <v>570</v>
       </c>
       <c r="E148" s="10"/>
       <c r="F148" s="12"/>
@@ -11327,16 +11327,16 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B149" s="27" t="s">
-        <v>529</v>
+        <v>571</v>
       </c>
       <c r="C149" s="11">
         <v>87.0</v>
       </c>
       <c r="D149" s="27" t="s">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="E149" s="27"/>
       <c r="F149" s="27"/>
@@ -11363,16 +11363,16 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="C150" s="11">
         <v>86.0</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="E150" s="10"/>
       <c r="F150" s="12"/>
@@ -11399,16 +11399,16 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>539</v>
+        <v>575</v>
       </c>
       <c r="C151" s="11">
         <v>86.0</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>540</v>
+        <v>576</v>
       </c>
       <c r="E151" s="10"/>
       <c r="F151" s="12"/>
@@ -11435,16 +11435,16 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="C152" s="11">
         <v>85.0</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="E152" s="10"/>
       <c r="F152" s="12"/>
@@ -11471,16 +11471,16 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>548</v>
+        <v>579</v>
       </c>
       <c r="C153" s="11">
         <v>85.0</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
       <c r="E153" s="10"/>
       <c r="F153" s="12"/>
@@ -11507,16 +11507,16 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B154" s="36" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="C154" s="11">
         <v>84.0</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="E154" s="10"/>
       <c r="F154" s="12"/>
@@ -11543,16 +11543,16 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="C155" s="11">
         <v>83.0</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="E155" s="10"/>
       <c r="F155" s="12"/>
@@ -11579,16 +11579,16 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="10" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="C156" s="11">
         <v>89.0</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="E156" s="10"/>
       <c r="F156" s="12"/>
@@ -11615,16 +11615,16 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="27" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="B157" s="36" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="C157" s="11">
         <v>89.0</v>
       </c>
       <c r="D157" s="27" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="E157" s="27"/>
       <c r="F157" s="27"/>
@@ -11651,16 +11651,16 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="10" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="C158" s="11">
         <v>85.0</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="E158" s="10"/>
       <c r="F158" s="12"/>
@@ -11687,16 +11687,16 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="10" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="C159" s="11">
         <v>65.0</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="E159" s="10"/>
       <c r="F159" s="12"/>
@@ -11723,16 +11723,16 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="16" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="B160" s="54" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
       <c r="C160" s="11">
         <v>92.0</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="E160" s="10"/>
       <c r="F160" s="12"/>
@@ -11759,16 +11759,16 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="10" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="C161" s="11">
         <v>70.0</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="E161" s="10"/>
       <c r="F161" s="12"/>
@@ -11795,16 +11795,16 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="10" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="B162" s="26" t="s">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="C162" s="11">
         <v>68.0</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="E162" s="26"/>
       <c r="F162" s="12"/>
@@ -11831,16 +11831,16 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="10" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="C163" s="11">
         <v>35.0</v>
       </c>
       <c r="D163" s="26" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="E163" s="10"/>
       <c r="F163" s="27"/>
@@ -11867,16 +11867,16 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="55" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="C164" s="11">
         <v>79.0</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="E164" s="17"/>
       <c r="F164" s="12"/>
@@ -11903,16 +11903,16 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="10" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="C165" s="11">
         <v>88.0</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
       <c r="E165" s="17"/>
       <c r="F165" s="12"/>
@@ -11939,16 +11939,16 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="10" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="C166" s="11">
         <v>65.0</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="E166" s="17"/>
       <c r="F166" s="12"/>
@@ -11975,20 +11975,20 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="19" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="B167" s="19" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="C167" s="20">
         <v>80.0</v>
       </c>
       <c r="D167" s="21" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="E167" s="22"/>
       <c r="F167" s="30"/>
-      <c r="G167" s="24"/>
+      <c r="G167" s="25"/>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
@@ -12011,16 +12011,16 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="27" t="s">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="C168" s="20">
         <v>86.0</v>
       </c>
       <c r="D168" s="56" t="s">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="E168" s="27"/>
       <c r="F168" s="27"/>
@@ -12047,16 +12047,16 @@
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="36" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="B169" s="36" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="C169" s="11">
         <v>77.0</v>
       </c>
       <c r="D169" s="57" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="E169" s="27"/>
       <c r="F169" s="36"/>
@@ -12083,16 +12083,16 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="10" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="C170" s="11">
         <v>68.0</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="E170" s="10"/>
       <c r="F170" s="12"/>
@@ -12119,16 +12119,16 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="10" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="C171" s="11">
         <v>64.0</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="E171" s="10"/>
       <c r="F171" s="12"/>
@@ -12155,16 +12155,16 @@
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="27" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B172" s="57" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="C172" s="11">
         <v>89.0</v>
       </c>
       <c r="D172" s="27" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="E172" s="27"/>
       <c r="F172" s="27"/>
@@ -12191,14 +12191,14 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="10" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B173" s="10"/>
       <c r="C173" s="11">
         <v>87.0</v>
       </c>
       <c r="D173" s="10" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E173" s="10"/>
       <c r="F173" s="12"/>
@@ -12225,16 +12225,16 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="27" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B174" s="27" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C174" s="11">
         <v>87.0</v>
       </c>
       <c r="D174" s="27" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E174" s="27"/>
       <c r="F174" s="27"/>
@@ -12261,16 +12261,16 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="27" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B175" s="27" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C175" s="11">
         <v>86.0</v>
       </c>
       <c r="D175" s="27" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E175" s="27"/>
       <c r="F175" s="27"/>
@@ -12297,16 +12297,16 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="10" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B176" s="34" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C176" s="11">
         <v>84.0</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E176" s="34"/>
       <c r="F176" s="12"/>
@@ -12333,16 +12333,16 @@
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="10" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C177" s="11">
         <v>81.0</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E177" s="17"/>
       <c r="F177" s="12"/>
@@ -12369,7 +12369,7 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="10" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B178" s="10" t="s">
         <v>637</v>
@@ -12405,7 +12405,7 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="27" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B179" s="27" t="s">
         <v>639</v>
@@ -12441,7 +12441,7 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="10" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>641</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="21" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="C187" s="41">
         <v>78.0</v>
@@ -12705,7 +12705,7 @@
         <v>656</v>
       </c>
       <c r="E187" s="45" t="s">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="F187" s="10"/>
       <c r="G187" s="46"/>
@@ -13411,7 +13411,7 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>697</v>
@@ -13447,7 +13447,7 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>699</v>
@@ -13483,7 +13483,7 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B209" s="56" t="s">
         <v>701</v>
@@ -13519,7 +13519,7 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>703</v>
@@ -13555,7 +13555,7 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>705</v>
@@ -13591,7 +13591,7 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B212" s="17" t="s">
         <v>707</v>
@@ -13627,7 +13627,7 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>709</v>
@@ -13663,7 +13663,7 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B214" s="62" t="s">
         <v>711</v>
@@ -13695,7 +13695,7 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B215" s="62" t="s">
         <v>712</v>
@@ -13727,7 +13727,7 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B216" s="62" t="s">
         <v>713</v>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B217" s="62" t="s">
         <v>714</v>
@@ -13791,7 +13791,7 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B218" s="62" t="s">
         <v>715</v>
@@ -13823,7 +13823,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B219" s="62" t="s">
         <v>716</v>
@@ -13855,7 +13855,7 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B220" s="62" t="s">
         <v>717</v>
@@ -13887,7 +13887,7 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B221" s="62" t="s">
         <v>718</v>
@@ -13919,7 +13919,7 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B222" s="62" t="s">
         <v>719</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B223" s="62" t="s">
         <v>720</v>
@@ -13983,7 +13983,7 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B224" s="62" t="s">
         <v>721</v>
@@ -14015,7 +14015,7 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B225" s="63" t="s">
         <v>722</v>
@@ -14047,7 +14047,7 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B226" s="62" t="s">
         <v>723</v>
@@ -14079,7 +14079,7 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B227" s="62" t="s">
         <v>724</v>
@@ -14111,7 +14111,7 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B228" s="62" t="s">
         <v>725</v>
@@ -14143,7 +14143,7 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B229" s="62" t="s">
         <v>726</v>
@@ -14175,7 +14175,7 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B230" s="62" t="s">
         <v>727</v>
@@ -14207,7 +14207,7 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B231" s="62" t="s">
         <v>728</v>
@@ -14239,7 +14239,7 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B232" s="62" t="s">
         <v>729</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B233" s="62" t="s">
         <v>730</v>
@@ -14303,7 +14303,7 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B234" s="62" t="s">
         <v>731</v>
@@ -14335,7 +14335,7 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B235" s="62" t="s">
         <v>732</v>
@@ -14367,7 +14367,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B236" s="62" t="s">
         <v>733</v>
@@ -14399,7 +14399,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B237" s="62" t="s">
         <v>734</v>
@@ -14431,7 +14431,7 @@
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B238" s="62" t="s">
         <v>735</v>
@@ -15183,7 +15183,7 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="36" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B259" s="36" t="s">
         <v>784</v>
@@ -15219,7 +15219,7 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="67" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B260" s="67" t="s">
         <v>786</v>
@@ -15253,7 +15253,7 @@
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="67" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B261" s="67" t="s">
         <v>788</v>
@@ -15459,7 +15459,7 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>801</v>
@@ -15495,7 +15495,7 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="27" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B268" s="27" t="s">
         <v>803</v>
@@ -15531,7 +15531,7 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="27" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B269" s="27" t="s">
         <v>805</v>
@@ -15567,7 +15567,7 @@
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>807</v>
@@ -15603,7 +15603,7 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>809</v>
@@ -15639,7 +15639,7 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>811</v>
@@ -15675,7 +15675,7 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>813</v>
@@ -15711,7 +15711,7 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>815</v>
@@ -15747,7 +15747,7 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B275" s="17" t="s">
         <v>817</v>
@@ -15783,7 +15783,7 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>819</v>
@@ -15819,10 +15819,10 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>568</v>
+        <v>494</v>
       </c>
       <c r="C277" s="11"/>
       <c r="D277" s="10"/>
@@ -15851,7 +15851,7 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>821</v>
@@ -15887,7 +15887,7 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B279" s="17" t="s">
         <v>823</v>
@@ -15923,7 +15923,7 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B280" s="34" t="s">
         <v>825</v>
@@ -15959,7 +15959,7 @@
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="10" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>813</v>
@@ -16427,7 +16427,7 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="16" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B294" s="16" t="s">
         <v>856</v>
@@ -16463,7 +16463,7 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B295" s="27" t="s">
         <v>858</v>
@@ -16499,7 +16499,7 @@
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>860</v>
@@ -16535,7 +16535,7 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B297" s="27" t="s">
         <v>862</v>
@@ -16571,10 +16571,10 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B298" s="27" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="C298" s="11">
         <v>87.0</v>
@@ -16607,7 +16607,7 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B299" s="27" t="s">
         <v>865</v>
@@ -16643,7 +16643,7 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B300" s="27" t="s">
         <v>867</v>
@@ -16679,7 +16679,7 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B301" s="27" t="s">
         <v>869</v>
@@ -16715,7 +16715,7 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B302" s="27" t="s">
         <v>871</v>
@@ -16751,7 +16751,7 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B303" s="36" t="s">
         <v>873</v>
@@ -16787,7 +16787,7 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B304" s="27" t="s">
         <v>875</v>
@@ -16823,7 +16823,7 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B305" s="27" t="s">
         <v>877</v>
@@ -16859,7 +16859,7 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B306" s="27" t="s">
         <v>878</v>
@@ -16895,7 +16895,7 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B307" s="27" t="s">
         <v>879</v>
@@ -16931,7 +16931,7 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B308" s="27" t="s">
         <v>880</v>
@@ -16967,10 +16967,10 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B309" s="27" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="C309" s="11">
         <v>83.0</v>
@@ -17003,7 +17003,7 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="36" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B310" s="36" t="s">
         <v>883</v>
@@ -17039,7 +17039,7 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>885</v>
@@ -17075,7 +17075,7 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>887</v>
@@ -17111,7 +17111,7 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B313" s="26" t="s">
         <v>889</v>
@@ -17147,7 +17147,7 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B314" s="26" t="s">
         <v>891</v>
@@ -17183,7 +17183,7 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B315" s="26" t="s">
         <v>893</v>
@@ -17219,7 +17219,7 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B316" s="64" t="s">
         <v>895</v>
@@ -17255,7 +17255,7 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B317" s="17" t="s">
         <v>897</v>
@@ -17291,7 +17291,7 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B318" s="17" t="s">
         <v>899</v>
@@ -17327,7 +17327,7 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>901</v>
@@ -17363,7 +17363,7 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B320" s="17" t="s">
         <v>903</v>
@@ -17399,7 +17399,7 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>905</v>
@@ -17435,7 +17435,7 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>907</v>
@@ -17831,7 +17831,7 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="16" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B333" s="16" t="s">
         <v>931</v>
@@ -17867,7 +17867,7 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B334" s="26" t="s">
         <v>933</v>
@@ -17903,7 +17903,7 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B335" s="17" t="s">
         <v>935</v>
@@ -17939,7 +17939,7 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B336" s="10" t="s">
         <v>937</v>
@@ -17975,7 +17975,7 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="27" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B337" s="57" t="s">
         <v>939</v>
@@ -18011,7 +18011,7 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B338" s="17" t="s">
         <v>941</v>
@@ -18047,7 +18047,7 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B339" s="34" t="s">
         <v>943</v>
@@ -18083,7 +18083,7 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B340" s="26" t="s">
         <v>945</v>
@@ -18119,7 +18119,7 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>947</v>
@@ -18155,7 +18155,7 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>949</v>
@@ -18191,7 +18191,7 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B343" s="10" t="s">
         <v>951</v>
@@ -18227,7 +18227,7 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="27" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B344" s="57" t="s">
         <v>953</v>
@@ -18263,7 +18263,7 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="27" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B345" s="27" t="s">
         <v>955</v>
@@ -20095,7 +20095,7 @@
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>1071</v>
@@ -20131,7 +20131,7 @@
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="10" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>1073</v>
@@ -20419,7 +20419,7 @@
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="73" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="B405" s="27" t="s">
         <v>1094</v>
@@ -20455,7 +20455,7 @@
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="26" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>1096</v>
@@ -20599,7 +20599,7 @@
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="10" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>1106</v>
@@ -20635,7 +20635,7 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="10" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>1108</v>
@@ -20671,7 +20671,7 @@
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="10" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>1110</v>
@@ -20995,7 +20995,7 @@
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B421" s="10" t="s">
         <v>1130</v>
@@ -21787,7 +21787,7 @@
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="10" t="s">
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="B443" s="77" t="s">
         <v>1176</v>
@@ -21823,7 +21823,7 @@
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="10" t="s">
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>1178</v>
@@ -21859,7 +21859,7 @@
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="10" t="s">
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="B445" s="10" t="s">
         <v>1180</v>
@@ -22255,7 +22255,7 @@
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>1207</v>
@@ -22603,7 +22603,7 @@
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="36" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B466" s="36" t="s">
         <v>1226</v>
@@ -22639,7 +22639,7 @@
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>1228</v>
@@ -22675,7 +22675,7 @@
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>1230</v>
@@ -22711,7 +22711,7 @@
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>1232</v>
@@ -22747,7 +22747,7 @@
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>1234</v>
@@ -22783,7 +22783,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>1236</v>
@@ -22819,7 +22819,7 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>1238</v>
@@ -22855,7 +22855,7 @@
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>1240</v>
@@ -22891,7 +22891,7 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="10" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>1242</v>
@@ -23395,7 +23395,7 @@
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="10" t="s">
-        <v>371</v>
+        <v>279</v>
       </c>
       <c r="B488" s="17" t="s">
         <v>1276</v>
@@ -23503,7 +23503,7 @@
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="21" t="s">
-        <v>545</v>
+        <v>471</v>
       </c>
       <c r="B491" s="21" t="s">
         <v>1283</v>
@@ -23515,7 +23515,7 @@
         <v>1284</v>
       </c>
       <c r="E491" s="45" t="s">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="F491" s="10"/>
       <c r="G491" s="46"/>
@@ -23685,7 +23685,7 @@
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B496" s="21" t="s">
         <v>1295</v>
@@ -24891,7 +24891,7 @@
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="10" t="s">
-        <v>402</v>
+        <v>309</v>
       </c>
       <c r="B530" s="10" t="s">
         <v>1366</v>
@@ -24927,7 +24927,7 @@
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="27" t="s">
-        <v>402</v>
+        <v>309</v>
       </c>
       <c r="B531" s="27" t="s">
         <v>1368</v>
@@ -25143,7 +25143,7 @@
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="27" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B537" s="36" t="s">
         <v>1381</v>
@@ -25179,7 +25179,7 @@
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="27" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B538" s="36" t="s">
         <v>1383</v>
@@ -25215,7 +25215,7 @@
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="27" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B539" s="36" t="s">
         <v>1385</v>
@@ -25251,7 +25251,7 @@
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="27" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B540" s="36" t="s">
         <v>1387</v>
@@ -25287,7 +25287,7 @@
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="8" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B541" s="36" t="s">
         <v>1389</v>
@@ -25323,7 +25323,7 @@
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="27" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B542" s="36" t="s">
         <v>1391</v>
@@ -25359,7 +25359,7 @@
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="8" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="B543" s="27" t="s">
         <v>1393</v>
@@ -25395,7 +25395,7 @@
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="18" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="B544" s="10" t="s">
         <v>1395</v>
@@ -25431,7 +25431,7 @@
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="18" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="B545" s="10" t="s">
         <v>1397</v>
@@ -25575,7 +25575,7 @@
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="29" t="s">
-        <v>426</v>
+        <v>332</v>
       </c>
       <c r="B549" s="10" t="s">
         <v>1407</v>
@@ -25863,7 +25863,7 @@
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="84" t="s">
-        <v>430</v>
+        <v>337</v>
       </c>
       <c r="B557" s="27" t="s">
         <v>1425</v>
@@ -26007,7 +26007,7 @@
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="10" t="s">
-        <v>434</v>
+        <v>342</v>
       </c>
       <c r="B561" s="10" t="s">
         <v>1434</v>
@@ -26043,7 +26043,7 @@
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="10" t="s">
-        <v>434</v>
+        <v>342</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>1012</v>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="E566" s="22"/>
       <c r="F566" s="47"/>
-      <c r="G566" s="24"/>
+      <c r="G566" s="25"/>
       <c r="H566" s="48"/>
       <c r="I566" s="5"/>
       <c r="J566" s="5"/>
@@ -27013,7 +27013,7 @@
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="10" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B589" s="17" t="s">
         <v>1505</v>
@@ -27049,7 +27049,7 @@
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="10" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B590" s="17" t="s">
         <v>1507</v>
@@ -27085,7 +27085,7 @@
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="58" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B591" s="58" t="s">
         <v>1509</v>
@@ -27121,7 +27121,7 @@
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="10" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B592" s="10" t="s">
         <v>1511</v>
@@ -27265,7 +27265,7 @@
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="31" t="s">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="B596" s="26" t="s">
         <v>1521</v>
@@ -27517,7 +27517,7 @@
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="10" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B603" s="26" t="s">
         <v>1536</v>
@@ -27553,7 +27553,7 @@
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="10" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B604" s="26" t="s">
         <v>1538</v>
@@ -27589,7 +27589,7 @@
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="10" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>1540</v>
@@ -27625,7 +27625,7 @@
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="10" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B606" s="64" t="s">
         <v>1542</v>
@@ -27661,7 +27661,7 @@
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="10" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B607" s="10" t="s">
         <v>1544</v>
@@ -27748,7 +27748,7 @@
       </c>
       <c r="E609" s="22"/>
       <c r="F609" s="30"/>
-      <c r="G609" s="24"/>
+      <c r="G609" s="25"/>
       <c r="H609" s="48"/>
       <c r="I609" s="5"/>
       <c r="J609" s="5"/>
@@ -27807,7 +27807,7 @@
     </row>
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="21" t="s">
-        <v>518</v>
+        <v>444</v>
       </c>
       <c r="B611" s="21" t="s">
         <v>1554</v>
@@ -27843,7 +27843,7 @@
     </row>
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B612" s="21" t="s">
         <v>1556</v>
@@ -30155,7 +30155,7 @@
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="10" t="s">
-        <v>541</v>
+        <v>466</v>
       </c>
       <c r="B676" s="10" t="s">
         <v>1693</v>
@@ -30191,7 +30191,7 @@
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="27" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B677" s="27" t="s">
         <v>1695</v>
@@ -30227,7 +30227,7 @@
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="19" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B678" s="19" t="s">
         <v>1697</v>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="E678" s="22"/>
       <c r="F678" s="47"/>
-      <c r="G678" s="24"/>
+      <c r="G678" s="25"/>
       <c r="H678" s="5"/>
       <c r="I678" s="5"/>
       <c r="J678" s="5"/>
@@ -30263,7 +30263,7 @@
     </row>
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="19" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B679" s="27" t="s">
         <v>1699</v>
@@ -30371,7 +30371,7 @@
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="10" t="s">
-        <v>581</v>
+        <v>503</v>
       </c>
       <c r="B682" s="10" t="s">
         <v>1706</v>
@@ -30407,7 +30407,7 @@
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="10" t="s">
-        <v>581</v>
+        <v>503</v>
       </c>
       <c r="B683" s="17" t="s">
         <v>1708</v>
@@ -30443,7 +30443,7 @@
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="74" t="s">
-        <v>545</v>
+        <v>471</v>
       </c>
       <c r="B684" s="10" t="s">
         <v>1710</v>
@@ -30479,7 +30479,7 @@
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="10" t="s">
-        <v>545</v>
+        <v>471</v>
       </c>
       <c r="B685" s="34" t="s">
         <v>1712</v>
@@ -30515,7 +30515,7 @@
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="10" t="s">
-        <v>545</v>
+        <v>471</v>
       </c>
       <c r="B686" s="10" t="s">
         <v>1714</v>
@@ -30767,7 +30767,7 @@
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B693" s="27" t="s">
         <v>1731</v>
@@ -30803,7 +30803,7 @@
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B694" s="27" t="s">
         <v>1733</v>
@@ -30839,7 +30839,7 @@
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B695" s="27" t="s">
         <v>1735</v>
@@ -30875,7 +30875,7 @@
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B696" s="27" t="s">
         <v>1737</v>
@@ -30911,7 +30911,7 @@
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B697" s="27" t="s">
         <v>1739</v>
@@ -30947,7 +30947,7 @@
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B698" s="27" t="s">
         <v>1741</v>
@@ -30983,7 +30983,7 @@
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="27" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B699" s="27" t="s">
         <v>1743</v>
@@ -31019,7 +31019,7 @@
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="10" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B700" s="10" t="s">
         <v>1745</v>
@@ -31055,7 +31055,7 @@
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="49" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B701" s="49" t="s">
         <v>1747</v>
@@ -31125,7 +31125,7 @@
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="93" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B703" s="93" t="s">
         <v>1751</v>
@@ -38008,11 +38008,11 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="3"/>
+      <c r="Y1" s="4"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>11</v>
@@ -38078,15 +38078,15 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -38119,11 +38119,11 @@
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="24" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -38148,19 +38148,19 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>42</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -38185,19 +38185,19 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -38222,19 +38222,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -38259,15 +38259,15 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -38292,15 +38292,15 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -38325,15 +38325,15 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -38358,19 +38358,19 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>101</v>
+      <c r="D12" s="24" t="s">
+        <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -38395,15 +38395,15 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -38428,10 +38428,10 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -38459,19 +38459,19 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>126</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -38496,15 +38496,15 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -38529,19 +38529,19 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>149</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -38566,19 +38566,19 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -38603,19 +38603,19 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>188</v>
+        <v>163</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>164</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -38640,19 +38640,19 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>202</v>
+        <v>171</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>172</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -38677,19 +38677,19 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="E21" s="5" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -38714,19 +38714,19 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>224</v>
+        <v>98</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -38751,19 +38751,19 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="E23" s="5" t="s">
-        <v>242</v>
+        <v>192</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -38787,19 +38787,19 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>247</v>
+        <v>197</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -38824,19 +38824,19 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -38861,15 +38861,15 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -38894,7 +38894,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -38923,19 +38923,19 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -38960,15 +38960,15 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -38993,19 +38993,19 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>275</v>
+        <v>163</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>225</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -39030,15 +39030,15 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -39063,10 +39063,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -39094,15 +39094,15 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>297</v>
+        <v>233</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -39127,19 +39127,19 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>303</v>
+        <v>239</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>305</v>
+        <v>240</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>241</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>314</v>
+        <v>242</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -39164,10 +39164,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>315</v>
+        <v>244</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>317</v>
+        <v>245</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -39195,19 +39195,19 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>319</v>
+        <v>248</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>320</v>
+        <v>249</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>323</v>
+        <v>248</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>251</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -39232,19 +39232,19 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>332</v>
+        <v>257</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>334</v>
+        <v>258</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>336</v>
+        <v>260</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>261</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>346</v>
+        <v>265</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -39269,19 +39269,19 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>332</v>
+        <v>257</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>350</v>
+        <v>260</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>268</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>357</v>
+        <v>270</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -39306,16 +39306,16 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>332</v>
+        <v>257</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>361</v>
+        <v>260</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>272</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -39341,19 +39341,19 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>371</v>
+        <v>279</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>372</v>
+        <v>280</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>374</v>
+        <v>281</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>282</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>383</v>
+        <v>289</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -39378,19 +39378,19 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>385</v>
+        <v>293</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>386</v>
+        <v>294</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>387</v>
+        <v>39</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>295</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>394</v>
+        <v>301</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -39415,15 +39415,15 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>397</v>
+        <v>304</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>398</v>
+        <v>305</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -39448,19 +39448,19 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>402</v>
+        <v>309</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>403</v>
+        <v>310</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>404</v>
+        <v>312</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -39485,19 +39485,19 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>408</v>
+        <v>315</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="E44" s="5" t="s">
-        <v>409</v>
+        <v>316</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -39522,19 +39522,19 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>414</v>
+        <v>318</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -39559,15 +39559,15 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>297</v>
+        <v>233</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>419</v>
+        <v>325</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -39592,15 +39592,15 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>297</v>
+        <v>233</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -39625,19 +39625,19 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="5" t="s">
-        <v>426</v>
+        <v>332</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>427</v>
+        <v>333</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>429</v>
+        <v>334</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -39662,19 +39662,19 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>430</v>
+        <v>337</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>431</v>
+        <v>338</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>432</v>
+        <v>340</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -39699,16 +39699,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>434</v>
+        <v>342</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>435</v>
+        <v>343</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>437</v>
+        <v>39</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>345</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -39734,15 +39734,15 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>434</v>
+        <v>342</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>445</v>
+        <v>354</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -39767,15 +39767,15 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>447</v>
+        <v>357</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>448</v>
+        <v>358</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>449</v>
+        <v>361</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -39800,15 +39800,15 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>447</v>
+        <v>357</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>452</v>
+        <v>364</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>453</v>
+        <v>365</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -39833,19 +39833,19 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>456</v>
+        <v>368</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>457</v>
+        <v>369</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>458</v>
+        <v>163</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>370</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>461</v>
+        <v>377</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -39870,19 +39870,19 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>467</v>
+        <v>381</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>469</v>
+        <v>39</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>383</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -39907,19 +39907,19 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>478</v>
+        <v>388</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>479</v>
+        <v>389</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>480</v>
+        <v>163</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>390</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>487</v>
+        <v>397</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -39944,15 +39944,15 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>488</v>
+        <v>401</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>492</v>
+        <v>403</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -39977,19 +39977,19 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>467</v>
+        <v>381</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>497</v>
+        <v>407</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>408</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -40014,19 +40014,19 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>503</v>
+        <v>419</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D59" s="25" t="s">
-        <v>505</v>
+        <v>98</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>420</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>507</v>
+        <v>426</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -40051,15 +40051,15 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>508</v>
+        <v>429</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>509</v>
+        <v>432</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -40084,19 +40084,19 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>510</v>
+        <v>435</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>511</v>
+        <v>51</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>436</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>516</v>
+        <v>442</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -40121,19 +40121,19 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="s">
-        <v>518</v>
+        <v>444</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>522</v>
+        <v>446</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>447</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>528</v>
+        <v>451</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -40158,15 +40158,15 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>531</v>
+        <v>454</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>532</v>
+        <v>455</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>533</v>
+        <v>456</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -40191,19 +40191,19 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="s">
-        <v>536</v>
+        <v>459</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>537</v>
+        <v>460</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>538</v>
+        <v>463</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -40228,10 +40228,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>541</v>
+        <v>466</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>542</v>
+        <v>467</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -40259,19 +40259,19 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="s">
-        <v>545</v>
+        <v>471</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>546</v>
+        <v>472</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>547</v>
+        <v>281</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>473</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -40296,15 +40296,15 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>559</v>
+        <v>483</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>560</v>
+        <v>484</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -40329,15 +40329,15 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>563</v>
+        <v>490</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>564</v>
+        <v>492</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -40362,19 +40362,19 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>568</v>
+        <v>494</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>569</v>
+        <v>98</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>495</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>579</v>
+        <v>500</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -40399,19 +40399,19 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>581</v>
+        <v>503</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>585</v>
+        <v>98</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>505</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>592</v>
+        <v>510</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -40439,16 +40439,16 @@
         <v>26</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>595</v>
+        <v>512</v>
       </c>
       <c r="C71" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="E71" s="5" t="s">
-        <v>596</v>
+        <v>515</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -40473,19 +40473,19 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>600</v>
+        <v>516</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>601</v>
+        <v>517</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -40510,19 +40510,19 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>605</v>
+        <v>520</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>607</v>
+        <v>521</v>
+      </c>
+      <c r="D73" s="24" t="s">
+        <v>522</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>613</v>
+        <v>527</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -40547,19 +40547,19 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>616</v>
+        <v>530</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>617</v>
+        <v>531</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D74" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>619</v>
+        <v>533</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -40584,16 +40584,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>622</v>
+        <v>535</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>623</v>
+        <v>536</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>624</v>
+        <v>39</v>
+      </c>
+      <c r="D75" s="24" t="s">
+        <v>539</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -40619,16 +40619,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="5" t="s">
-        <v>633</v>
+        <v>544</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>634</v>
+        <v>545</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>636</v>
+        <v>39</v>
+      </c>
+      <c r="D76" s="24" t="s">
+        <v>546</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>

--- a/data/FRAGRANCES.xlsx
+++ b/data/FRAGRANCES.xlsx
@@ -38,18 +38,18 @@
     <t>Rating</t>
   </si>
   <si>
+    <t>Facts</t>
+  </si>
+  <si>
+    <t>Date tried</t>
+  </si>
+  <si>
     <t>100 Bon</t>
   </si>
   <si>
-    <t>Facts</t>
-  </si>
-  <si>
     <t>Rose &amp; Black Pepper</t>
   </si>
   <si>
-    <t>Date tried</t>
-  </si>
-  <si>
     <t>Not carried by any of the 12 retailers checked.</t>
   </si>
   <si>
@@ -62,21 +62,24 @@
     <t>Brand carried by Scent Split and The Perfumed Court, this one not.</t>
   </si>
   <si>
+    <t>19-69</t>
+  </si>
+  <si>
     <t>American Perfumer</t>
   </si>
   <si>
     <t>Black Walnut</t>
   </si>
   <si>
-    <t>19-69</t>
-  </si>
-  <si>
     <t>House brand of the Chicago shop. Buy direct.</t>
   </si>
   <si>
     <t>Miami Blue</t>
   </si>
   <si>
+    <t xml:space="preserve">Disappointing, smells nothing like cocaine </t>
+  </si>
+  <si>
     <t>Akro</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
     <t>Bloom Perfumery</t>
   </si>
   <si>
-    <t xml:space="preserve">Disappointing, smells nothing like cocaine </t>
-  </si>
-  <si>
     <t>https://bloomperfume.co.uk/products/ink</t>
   </si>
   <si>
@@ -101,31 +101,46 @@
     <t>Sweet rose, simple and nice. Not jammy, not "fresh," not soapy, just very rose</t>
   </si>
   <si>
+    <t>Spelled Akro. Ministry of Scent sample sold out.</t>
+  </si>
+  <si>
     <t>Oud &amp; Spice</t>
   </si>
   <si>
+    <t>Astier de Villatte</t>
+  </si>
+  <si>
     <t xml:space="preserve">A smokers sweatshirt in the back of a car </t>
   </si>
   <si>
+    <t>Mantes La Jolie</t>
+  </si>
+  <si>
+    <t>Luckyscent</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
+  </si>
+  <si>
     <t>Mandorlo di Sicilia</t>
   </si>
   <si>
     <t>So gross what is the deal with this hot and cold brand?</t>
   </si>
   <si>
-    <t>Spelled Akro. Ministry of Scent sample sold out.</t>
-  </si>
-  <si>
-    <t>Astier de Villatte</t>
-  </si>
-  <si>
-    <t>Mantes La Jolie</t>
-  </si>
-  <si>
-    <t>Luckyscent</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
+    <t>Price shows when you select the size, usually $5-10.</t>
+  </si>
+  <si>
+    <t>Azzaro</t>
+  </si>
+  <si>
+    <t>Azzaro pour Homme</t>
+  </si>
+  <si>
+    <t>The Perfumed Court</t>
+  </si>
+  <si>
+    <t>https://theperfumedcourt.com</t>
   </si>
   <si>
     <t>Aedes de Venustas</t>
@@ -152,25 +167,25 @@
     <t>Aesop</t>
   </si>
   <si>
+    <t>Cheapest sample on the list.</t>
+  </si>
+  <si>
     <t>Hwyl</t>
   </si>
   <si>
     <t xml:space="preserve">Way too smoky </t>
   </si>
   <si>
-    <t>Price shows when you select the size, usually $5-10.</t>
-  </si>
-  <si>
-    <t>Azzaro</t>
-  </si>
-  <si>
-    <t>Azzaro pour Homme</t>
-  </si>
-  <si>
-    <t>The Perfumed Court</t>
-  </si>
-  <si>
-    <t>https://theperfumedcourt.com</t>
+    <t>Bvlgari</t>
+  </si>
+  <si>
+    <t>Rose Goldea Blossom Delight</t>
+  </si>
+  <si>
+    <t>Maple Prime</t>
+  </si>
+  <si>
+    <t>https://mapleprime.com/products/bvlgari-rose-goldea-blossom-delight-eau-de-parfum-for-women</t>
   </si>
   <si>
     <t>Agar Olfactory</t>
@@ -191,51 +206,75 @@
     <t>Cereale</t>
   </si>
   <si>
+    <t>All three decant sizes out of stock. Re-check.</t>
+  </si>
+  <si>
     <t xml:space="preserve">?? Toothpaste </t>
   </si>
   <si>
+    <t>Caron</t>
+  </si>
+  <si>
+    <t>Coup de Fouet</t>
+  </si>
+  <si>
     <t>Matsu Musk</t>
   </si>
   <si>
     <t xml:space="preserve">Uncooked grocery store button mushrooms </t>
   </si>
   <si>
+    <t>Vintage market only.</t>
+  </si>
+  <si>
     <t>Rushlight</t>
   </si>
   <si>
-    <t>Cheapest sample on the list.</t>
+    <t>Poivre</t>
   </si>
   <si>
     <t>Yellow floral, really compelling, honeycomb and honesuckle, kinda Moon Bloom, stinks a lot but I like the stink</t>
   </si>
   <si>
-    <t>Bvlgari</t>
-  </si>
-  <si>
-    <t>Rose Goldea Blossom Delight</t>
+    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
   </si>
   <si>
     <t>Amouage</t>
   </si>
   <si>
-    <t>Maple Prime</t>
+    <t>Chanel</t>
   </si>
   <si>
     <t>Beach Hut Man</t>
   </si>
   <si>
-    <t>https://mapleprime.com/products/bvlgari-rose-goldea-blossom-delight-eau-de-parfum-for-women</t>
+    <t>No. 19</t>
   </si>
   <si>
     <t xml:space="preserve">Mint forward, has kind of a gross cantaloupe vibe. </t>
   </si>
   <si>
+    <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
+  </si>
+  <si>
     <t>Honour Man</t>
   </si>
   <si>
+    <t>Coach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not sure what I don't like in here. Geranium? Pepper is nice. Feels boring, but something wrong in there. </t>
   </si>
   <si>
+    <t>Coach Green</t>
+  </si>
+  <si>
+    <t>DecantX</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
+  </si>
+  <si>
     <t>Interlude Woman</t>
   </si>
   <si>
@@ -251,25 +290,19 @@
     <t xml:space="preserve">Hay, orris, green, very good version of this. Skin scent. Ultimately too feminine and boring. </t>
   </si>
   <si>
-    <t>All three decant sizes out of stock. Re-check.</t>
-  </si>
-  <si>
     <t>Cool but ultimately a watery mess</t>
   </si>
   <si>
-    <t>Caron</t>
-  </si>
-  <si>
-    <t>Coup de Fouet</t>
-  </si>
-  <si>
-    <t>Vintage market only.</t>
-  </si>
-  <si>
-    <t>Poivre</t>
-  </si>
-  <si>
-    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
+    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+  </si>
+  <si>
+    <t>Comme des Garçons</t>
+  </si>
+  <si>
+    <t>Series 2 Red: Carnation</t>
+  </si>
+  <si>
+    <t>Discontinued Red series. Vintage market.</t>
   </si>
   <si>
     <t>Brioche</t>
@@ -278,13 +311,19 @@
     <t>Bread and bran, sweet honey, a nice and not gourmand fragrance</t>
   </si>
   <si>
-    <t>Chanel</t>
-  </si>
-  <si>
-    <t>No. 19</t>
-  </si>
-  <si>
-    <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
+    <t>Dolce &amp; Gabbana</t>
+  </si>
+  <si>
+    <t>D&amp;G Anthology L'Amoureux 6</t>
+  </si>
+  <si>
+    <t>DSH Perfumes</t>
+  </si>
+  <si>
+    <t>Rubis Rose</t>
+  </si>
+  <si>
+    <t>https://www.dshperfumes.com</t>
   </si>
   <si>
     <t>Andrea Maack</t>
@@ -296,18 +335,6 @@
     <t xml:space="preserve">Try this again? Says it's marine but I got a big food vibe of something savory </t>
   </si>
   <si>
-    <t>Coach</t>
-  </si>
-  <si>
-    <t>Coach Green</t>
-  </si>
-  <si>
-    <t>DecantX</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
-  </si>
-  <si>
     <t>Solstice</t>
   </si>
   <si>
@@ -317,16 +344,34 @@
     <t>Coven</t>
   </si>
   <si>
+    <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dirt. Probably great layered with something. </t>
   </si>
   <si>
+    <t>Ensar Oud</t>
+  </si>
+  <si>
+    <t>Japanese Red Rose oil</t>
+  </si>
+  <si>
+    <t>Sells direct only.</t>
+  </si>
+  <si>
     <t>Dual</t>
   </si>
   <si>
     <t xml:space="preserve">Lemon cookie for some reason but some pencil shavings </t>
   </si>
   <si>
-    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+    <t>Eris Parfums</t>
+  </si>
+  <si>
+    <t>Green Spell</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
   </si>
   <si>
     <t>Ceramic</t>
@@ -335,15 +380,6 @@
     <t xml:space="preserve">Powder and nice but hits a truck stop soap after a minute </t>
   </si>
   <si>
-    <t>Comme des Garçons</t>
-  </si>
-  <si>
-    <t>Series 2 Red: Carnation</t>
-  </si>
-  <si>
-    <t>Discontinued Red series. Vintage market.</t>
-  </si>
-  <si>
     <t>Tauer Perfumes</t>
   </si>
   <si>
@@ -353,33 +389,33 @@
     <t>Bleh I don't like this dude I will die on this hill</t>
   </si>
   <si>
-    <t>Dolce &amp; Gabbana</t>
-  </si>
-  <si>
-    <t>D&amp;G Anthology L'Amoureux 6</t>
-  </si>
-  <si>
     <t>Sundowner</t>
   </si>
   <si>
     <t>Scrubber. Chocolate note disgusted me</t>
   </si>
   <si>
-    <t>DSH Perfumes</t>
-  </si>
-  <si>
-    <t>Rubis Rose</t>
-  </si>
-  <si>
-    <t>https://www.dshperfumes.com</t>
+    <t>Indigo Perfumery has the 50ml bottle.</t>
+  </si>
+  <si>
+    <t>Floris</t>
   </si>
   <si>
     <t>L'Air du Désert Marocain</t>
   </si>
   <si>
+    <t>Elite</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wanted to love, didn't </t>
   </si>
   <si>
+    <t>Scent Split</t>
+  </si>
+  <si>
+    <t>https://scentsplit.com</t>
+  </si>
+  <si>
     <t>Sandalo</t>
   </si>
   <si>
@@ -395,42 +431,36 @@
     <t xml:space="preserve">Rose, great at first but ultimately dries down too candy-like </t>
   </si>
   <si>
+    <t>DecantX sample sold out.</t>
+  </si>
+  <si>
     <t>Pallas Athene</t>
   </si>
   <si>
-    <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
+    <t>Goutal</t>
+  </si>
+  <si>
+    <t>Gardenia Passion</t>
+  </si>
+  <si>
+    <t>Parfums Raffy</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
   </si>
   <si>
     <t>Rose, good at first but ultimately dries down too candy-like</t>
   </si>
   <si>
-    <t>Ensar Oud</t>
-  </si>
-  <si>
-    <t>Japanese Red Rose oil</t>
-  </si>
-  <si>
-    <t>Sells direct only.</t>
-  </si>
-  <si>
     <t>Triumph Of Bacchus</t>
   </si>
   <si>
     <t xml:space="preserve">Too sweet kinda gay nah </t>
   </si>
   <si>
-    <t>Eris Parfums</t>
-  </si>
-  <si>
-    <t>Green Spell</t>
-  </si>
-  <si>
     <t>Armani Privé</t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
-  </si>
-  <si>
     <t>Rose Alexandrie</t>
   </si>
   <si>
@@ -440,130 +470,142 @@
     <t>Rose Milano</t>
   </si>
   <si>
+    <t>Listed, out of stock. Re-check.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Simple and duplicative but rare I like it at this degree </t>
   </si>
   <si>
+    <t>Un Matin d'Orage</t>
+  </si>
+  <si>
+    <t>DecantX / Maple Prime</t>
+  </si>
+  <si>
     <t>Rose d'Arabie</t>
   </si>
   <si>
     <t xml:space="preserve">A great rose but not my favorite. Deep. </t>
   </si>
   <si>
+    <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
+  </si>
+  <si>
     <t>Musc Shamal</t>
   </si>
   <si>
     <t xml:space="preserve">Slightly more interesting than a plain musk, tips a bit sweet resin </t>
   </si>
   <si>
-    <t>Indigo Perfumery has the 50ml bottle.</t>
-  </si>
-  <si>
     <t>Cuir Nu</t>
   </si>
   <si>
     <t xml:space="preserve">Insane </t>
   </si>
   <si>
-    <t>Floris</t>
-  </si>
-  <si>
-    <t>Elite</t>
-  </si>
-  <si>
-    <t>Scent Split</t>
-  </si>
-  <si>
     <t>Rouge Malachite</t>
   </si>
   <si>
-    <t>https://scentsplit.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gourmand </t>
   </si>
   <si>
+    <t>Decants listed at both, sold out at both.</t>
+  </si>
+  <si>
+    <t>Guerlain</t>
+  </si>
+  <si>
     <t>Pivoine Suzhou</t>
   </si>
   <si>
+    <t>Cuir Intense</t>
+  </si>
+  <si>
     <t xml:space="preserve">Raspberry rose </t>
   </si>
   <si>
+    <t>DecantX has 2ml at $8.79.</t>
+  </si>
+  <si>
     <t>Orangerie Venise</t>
   </si>
   <si>
+    <t>Santal Pao Rosa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shouldn't like this, neroli and plain orange, but it's got something special </t>
   </si>
   <si>
+    <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
+  </si>
+  <si>
     <t>Jasmin Kusamono</t>
   </si>
   <si>
     <t xml:space="preserve">Plain non-indolic jasmine, lovely basic floral </t>
   </si>
   <si>
-    <t>DecantX sample sold out.</t>
-  </si>
-  <si>
     <t>Thé Yulong</t>
   </si>
   <si>
-    <t>Goutal</t>
-  </si>
-  <si>
-    <t>Gardenia Passion</t>
-  </si>
-  <si>
     <t>Same old tea</t>
   </si>
   <si>
-    <t>Parfums Raffy</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
-  </si>
-  <si>
     <t>Santal Dan Sha</t>
   </si>
   <si>
     <t xml:space="preserve">So generic, can't smell any notes? </t>
   </si>
   <si>
+    <t>Only source found.</t>
+  </si>
+  <si>
     <t>Vert Malachite</t>
   </si>
   <si>
     <t xml:space="preserve">Tuberose? Tube much. </t>
   </si>
   <si>
+    <t>Jasmin Grandiflorum Extrait 30</t>
+  </si>
+  <si>
+    <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
+  </si>
+  <si>
     <t>Bleu Lazuli</t>
   </si>
   <si>
     <t xml:space="preserve">Not at all </t>
   </si>
   <si>
+    <t>Eau de Guerlain</t>
+  </si>
+  <si>
     <t>Bois d'Encens</t>
   </si>
   <si>
     <t xml:space="preserve">Starts promising, ends nice basic wood </t>
   </si>
   <si>
-    <t>Listed, out of stock. Re-check.</t>
+    <t>A vintage version is also listed at $6.99, likely the one you want.</t>
   </si>
   <si>
     <t>Arquiste</t>
   </si>
   <si>
+    <t>Hermès</t>
+  </si>
+  <si>
     <t>A Grove by the Sea</t>
   </si>
   <si>
+    <t>Hermessence Poivre Samarcande</t>
+  </si>
+  <si>
     <t>Salty and oily, olive and trees? Need to try again, maybe don't like the dry down</t>
   </si>
   <si>
-    <t>Un Matin d'Orage</t>
-  </si>
-  <si>
-    <t>DecantX / Maple Prime</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
+    <t>Perfumeniche has the full bottle.</t>
   </si>
   <si>
     <t>Astrophil &amp; Stella</t>
@@ -575,6 +617,15 @@
     <t xml:space="preserve">Tuberose and magnolia, or green tea and plum. Optical illusion for noses. </t>
   </si>
   <si>
+    <t>Universal Flowering</t>
+  </si>
+  <si>
+    <t>Holy Hell</t>
+  </si>
+  <si>
+    <t>Sells direct.</t>
+  </si>
+  <si>
     <t>Chloé Atelier des Fleurs</t>
   </si>
   <si>
@@ -584,6 +635,9 @@
     <t>The perfect white floral, lasts forever, doesn't smell girly</t>
   </si>
   <si>
+    <t>(note row)</t>
+  </si>
+  <si>
     <t>Atelier des Ors</t>
   </si>
   <si>
@@ -593,7 +647,13 @@
     <t xml:space="preserve">Kinda useless. Great bottle tho </t>
   </si>
   <si>
-    <t>Decants listed at both, sold out at both.</t>
+    <t>Isabelle Larignon</t>
+  </si>
+  <si>
+    <t>Le Flocon de Johann K</t>
+  </si>
+  <si>
+    <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
   </si>
   <si>
     <t>Balmain</t>
@@ -605,16 +665,16 @@
     <t>I love this. It's a lot and kinda wears me, but very good green.</t>
   </si>
   <si>
-    <t>Guerlain</t>
-  </si>
-  <si>
-    <t>Cuir Intense</t>
+    <t>J.F. Schwarzlose Berlin</t>
+  </si>
+  <si>
+    <t>Trance</t>
   </si>
   <si>
     <t>Baruti</t>
   </si>
   <si>
-    <t>DecantX has 2ml at $8.79.</t>
+    <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
   </si>
   <si>
     <t>Hot Cotton</t>
@@ -623,10 +683,13 @@
     <t xml:space="preserve">Wow, metallic and starched shirts. No reason to wear it but very cool. </t>
   </si>
   <si>
-    <t>Santal Pao Rosa</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
+    <t>Joop</t>
+  </si>
+  <si>
+    <t>Homme Absolute</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com</t>
   </si>
   <si>
     <t>BeauFort London</t>
@@ -638,22 +701,43 @@
     <t xml:space="preserve">Probably a no. Eirik says vase water. Cumin? </t>
   </si>
   <si>
+    <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
+  </si>
+  <si>
     <t>The Grudge</t>
   </si>
   <si>
-    <t>Only source found.</t>
+    <t>L'Occitane</t>
+  </si>
+  <si>
+    <t>Eau du Val (Magnolia)</t>
+  </si>
+  <si>
+    <t>Perfumed Court has Eau des Baux only.</t>
+  </si>
+  <si>
+    <t>Lancôme</t>
   </si>
   <si>
     <t>Billie Eilish</t>
   </si>
   <si>
+    <t>Cuir de Lancôme</t>
+  </si>
+  <si>
     <t>Eilish No. 2</t>
   </si>
   <si>
     <t xml:space="preserve">Opened great, weird middle, interesting end. Worth another visit. </t>
   </si>
   <si>
-    <t>Jasmin Grandiflorum Extrait 30</t>
+    <t>Loewe</t>
+  </si>
+  <si>
+    <t>Pour Homme</t>
+  </si>
+  <si>
+    <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
   </si>
   <si>
     <t>Bohoboco</t>
@@ -662,13 +746,19 @@
     <t>Wild Carrot Oud</t>
   </si>
   <si>
-    <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
-  </si>
-  <si>
     <t>Yeesh. I think it's very well crafted but 2 MUCH</t>
   </si>
   <si>
-    <t>Eau de Guerlain</t>
+    <t>Maison Margiela</t>
+  </si>
+  <si>
+    <t>(untitled)</t>
+  </si>
+  <si>
+    <t>Perfumeniche</t>
+  </si>
+  <si>
+    <t>https://perfumeniche.com</t>
   </si>
   <si>
     <t>Mango Yuzu Gasoline</t>
@@ -677,49 +767,37 @@
     <t>Points for realism and saying what it is, but too strong on all counts</t>
   </si>
   <si>
-    <t>A vintage version is also listed at $6.99, likely the one you want.</t>
-  </si>
-  <si>
-    <t>Hermès</t>
-  </si>
-  <si>
     <t>Boka</t>
   </si>
   <si>
-    <t>Hermessence Poivre Samarcande</t>
-  </si>
-  <si>
     <t>Zelen</t>
   </si>
   <si>
     <t>Great zesty citrus opening but goes away immediately</t>
   </si>
   <si>
-    <t>Perfumeniche has the full bottle.</t>
-  </si>
-  <si>
-    <t>Universal Flowering</t>
-  </si>
-  <si>
-    <t>Holy Hell</t>
-  </si>
-  <si>
     <t>Živeli</t>
   </si>
   <si>
-    <t>Sells direct.</t>
+    <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
+  </si>
+  <si>
+    <t>Marc Jacobs</t>
   </si>
   <si>
     <t>Absolute scrubber omG</t>
   </si>
   <si>
-    <t>(note row)</t>
-  </si>
-  <si>
-    <t>Isabelle Larignon</t>
-  </si>
-  <si>
-    <t>Le Flocon de Johann K</t>
+    <t>Bang</t>
+  </si>
+  <si>
+    <t>Maya Njie</t>
+  </si>
+  <si>
+    <t>Nordic Cedar</t>
+  </si>
+  <si>
+    <t>https://mayanjie.com/products/discovery-set</t>
   </si>
   <si>
     <t>Bon Parfumeur</t>
@@ -728,21 +806,9 @@
     <t>801</t>
   </si>
   <si>
-    <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
-  </si>
-  <si>
     <t xml:space="preserve">A similar thing I don't like from something else idk </t>
   </si>
   <si>
-    <t>J.F. Schwarzlose Berlin</t>
-  </si>
-  <si>
-    <t>Trance</t>
-  </si>
-  <si>
-    <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
-  </si>
-  <si>
     <t>BORNTOSTANDOUT</t>
   </si>
   <si>
@@ -752,36 +818,39 @@
     <t xml:space="preserve">Organic cherry cough drop </t>
   </si>
   <si>
-    <t>Joop</t>
-  </si>
-  <si>
-    <t>Homme Absolute</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com</t>
-  </si>
-  <si>
     <t>Dirty Rice</t>
   </si>
   <si>
     <t>Neither dirty nor rice</t>
   </si>
   <si>
+    <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
+  </si>
+  <si>
     <t>Warm Air</t>
   </si>
   <si>
     <t xml:space="preserve">Thought it was good but NO! </t>
   </si>
   <si>
+    <t>Miller Harris</t>
+  </si>
+  <si>
+    <t>Le Cèdre</t>
+  </si>
+  <si>
+    <t>Miller Harris direct</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
+  </si>
+  <si>
     <t>Nanatopia</t>
   </si>
   <si>
     <t>Banana bread no thank you</t>
   </si>
   <si>
-    <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
-  </si>
-  <si>
     <t>Bortnikoff</t>
   </si>
   <si>
@@ -791,15 +860,6 @@
     <t xml:space="preserve">Oh wow, the blue toothpaste I used as a child </t>
   </si>
   <si>
-    <t>L'Occitane</t>
-  </si>
-  <si>
-    <t>Eau du Val (Magnolia)</t>
-  </si>
-  <si>
-    <t>Perfumed Court has Eau des Baux only.</t>
-  </si>
-  <si>
     <t>Boy Smells</t>
   </si>
   <si>
@@ -809,10 +869,7 @@
     <t xml:space="preserve">Another rose, nice green but sour </t>
   </si>
   <si>
-    <t>Lancôme</t>
-  </si>
-  <si>
-    <t>Cuir de Lancôme</t>
+    <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
   </si>
   <si>
     <t>Gyan</t>
@@ -821,13 +878,10 @@
     <t xml:space="preserve">Very not my normal thing but I'm really digging it thus far. </t>
   </si>
   <si>
-    <t>Loewe</t>
-  </si>
-  <si>
-    <t>Pour Homme</t>
-  </si>
-  <si>
-    <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
+    <t>Wander Through the Parks</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com</t>
   </si>
   <si>
     <t>Le Gemme Tygar</t>
@@ -836,18 +890,6 @@
     <t>Wow. Crazy grapefruit opening, deep ambroxan base, lasts forever. Maybe too beast but really compelling, I want to try all of them</t>
   </si>
   <si>
-    <t>Maison Margiela</t>
-  </si>
-  <si>
-    <t>(untitled)</t>
-  </si>
-  <si>
-    <t>Perfumeniche</t>
-  </si>
-  <si>
-    <t>https://perfumeniche.com</t>
-  </si>
-  <si>
     <t>Kilian</t>
   </si>
   <si>
@@ -857,30 +899,30 @@
     <t>Smells like Nestea to me but Eirik loves it</t>
   </si>
   <si>
+    <t>50ml sold out, no sample listing.</t>
+  </si>
+  <si>
     <t>Kologne, Shield of Protection</t>
   </si>
   <si>
     <t>Not remembering why it was a no, but it was a no</t>
   </si>
   <si>
+    <t>Feuilles de Tabac</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
+  </si>
+  <si>
     <t>L'Heure Verte</t>
   </si>
   <si>
     <t xml:space="preserve">No idea what people are saying with absinthe and licorice. It smells fine, dna of that Angel's Share sweetness. </t>
   </si>
   <si>
-    <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
-  </si>
-  <si>
     <t>Roses on Ice</t>
   </si>
   <si>
-    <t>Marc Jacobs</t>
-  </si>
-  <si>
-    <t>Bang</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ozonic cucumber, so strange. Maybe smells like cheap body spray but I don't know, I like smelling it.  </t>
   </si>
   <si>
@@ -890,24 +932,27 @@
     <t>Almond, nice, too sweet to wear</t>
   </si>
   <si>
-    <t>Maya Njie</t>
-  </si>
-  <si>
-    <t>Nordic Cedar</t>
-  </si>
-  <si>
-    <t>https://mayanjie.com/products/discovery-set</t>
-  </si>
-  <si>
     <t>Byredo</t>
   </si>
   <si>
+    <t>Montale</t>
+  </si>
+  <si>
     <t>Casablanca Lily</t>
   </si>
   <si>
+    <t>Intense Pepper</t>
+  </si>
+  <si>
     <t>Floral and HONEY this is irresistable</t>
   </si>
   <si>
+    <t>Twisted Lily</t>
+  </si>
+  <si>
+    <t>https://twistedlily.com/products/intense-pepper-sample</t>
+  </si>
+  <si>
     <t>La Tulipe</t>
   </si>
   <si>
@@ -920,33 +965,21 @@
     <t xml:space="preserve">Pot and pomelo, addictive </t>
   </si>
   <si>
-    <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
-  </si>
-  <si>
     <t>Cuir Obscur</t>
   </si>
   <si>
     <t>Amaretto to rose and leather, probably many like it but I'm into this combination</t>
   </si>
   <si>
-    <t>Miller Harris</t>
-  </si>
-  <si>
-    <t>Le Cèdre</t>
-  </si>
-  <si>
-    <t>Miller Harris direct</t>
-  </si>
-  <si>
     <t>Mojave Ghost</t>
   </si>
   <si>
-    <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subtle as to be almost indistinguishable, but nice? Not getting the hype but might try the candle or something. </t>
   </si>
   <si>
+    <t>DecantX and Maple Prime have no sample in stock.</t>
+  </si>
+  <si>
     <t>Inflorescence</t>
   </si>
   <si>
@@ -965,27 +998,27 @@
     <t xml:space="preserve">Pulp again </t>
   </si>
   <si>
+    <t>Prissana</t>
+  </si>
+  <si>
+    <t>Nefer</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
+  </si>
+  <si>
     <t>Oud Immortel</t>
   </si>
   <si>
     <t xml:space="preserve">Dry down pretty gross. </t>
   </si>
   <si>
-    <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
-  </si>
-  <si>
     <t>Young Rose</t>
   </si>
   <si>
     <t xml:space="preserve">Insane citrus blast, very bad </t>
   </si>
   <si>
-    <t>Wander Through the Parks</t>
-  </si>
-  <si>
-    <t>https://www.millerharris.com</t>
-  </si>
-  <si>
     <t>Bal d'Afrique</t>
   </si>
   <si>
@@ -995,54 +1028,90 @@
     <t>Desert Dawn</t>
   </si>
   <si>
+    <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Boring powdery sandalwood </t>
   </si>
   <si>
+    <t>Nest</t>
+  </si>
+  <si>
+    <t>Black Tulip</t>
+  </si>
+  <si>
     <t>Gypsy Water</t>
   </si>
   <si>
     <t xml:space="preserve">Lemon creamsicle, utterly gone after 15 mins </t>
   </si>
   <si>
+    <t>Olfactive Studio</t>
+  </si>
+  <si>
+    <t>Flash Back</t>
+  </si>
+  <si>
     <t>Blanche</t>
   </si>
   <si>
     <t xml:space="preserve">Fabric softener </t>
   </si>
   <si>
-    <t>50ml sold out, no sample listing.</t>
+    <t>Listed as Flashback in New York.</t>
+  </si>
+  <si>
+    <t>One Day</t>
   </si>
   <si>
     <t>Pour Un Homme de Caron</t>
   </si>
   <si>
+    <t>Taipei</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beautiful lavender Fougeres, more subtle than Lav Extreme, dumb reach </t>
   </si>
   <si>
+    <t>Ministry of Scent sample sold out.</t>
+  </si>
+  <si>
+    <t>Ormonde Jayne</t>
+  </si>
+  <si>
     <t>Yatagan</t>
   </si>
   <si>
+    <t>Montabaco Intensivo</t>
+  </si>
+  <si>
     <t>Like Un Homme but more animalic</t>
   </si>
   <si>
-    <t>Feuilles de Tabac</t>
+    <t>Bloom has standard Montabaco at $10, not Intensivo.</t>
   </si>
   <si>
     <t>Tabac Blond</t>
   </si>
   <si>
-    <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
+    <t>Paco Rabanne</t>
   </si>
   <si>
     <t xml:space="preserve">Not for me, Grandma Doris, but great on Eirik </t>
   </si>
   <si>
+    <t>Maple Prime has full bottles from $38.99, no small size anywhere.</t>
+  </si>
+  <si>
     <t>Tabac Noir</t>
   </si>
   <si>
     <t>Sweet</t>
   </si>
   <si>
+    <t>Duplicate of the row above.</t>
+  </si>
+  <si>
     <t>Pour Un Homme de Caron Le Matin</t>
   </si>
   <si>
@@ -1055,6 +1124,12 @@
     <t xml:space="preserve">Pretty good not great, not better than original </t>
   </si>
   <si>
+    <t>Papillon Artisan</t>
+  </si>
+  <si>
+    <t>Tobacco Rose</t>
+  </si>
+  <si>
     <t>Caswell-Massey</t>
   </si>
   <si>
@@ -1064,22 +1139,31 @@
     <t xml:space="preserve">Perfect perfect perfect. Doesn't last. </t>
   </si>
   <si>
+    <t>Perfumed Court $10.94. Papillon's own site sells full bottles only.</t>
+  </si>
+  <si>
+    <t>Parfumerie Particulière</t>
+  </si>
+  <si>
+    <t>Black Tar</t>
+  </si>
+  <si>
     <t>Orchid</t>
   </si>
   <si>
-    <t>Montale</t>
+    <t>Ministry of Scent has 2ml at $7.00.</t>
   </si>
   <si>
     <t xml:space="preserve">Pure floral, old lady but not powdery. I like it! </t>
   </si>
   <si>
-    <t>Intense Pepper</t>
-  </si>
-  <si>
-    <t>Twisted Lily</t>
-  </si>
-  <si>
-    <t>https://twistedlily.com/products/intense-pepper-sample</t>
+    <t>Penhaligon's</t>
+  </si>
+  <si>
+    <t>Blenheim Bouquet</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
   </si>
   <si>
     <t>Rose</t>
@@ -1100,13 +1184,25 @@
     <t xml:space="preserve">Simple old man + lemon, but nice enough. Weak. </t>
   </si>
   <si>
+    <t>Liquid Love</t>
+  </si>
+  <si>
+    <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
+  </si>
+  <si>
     <t>Almond</t>
   </si>
   <si>
     <t xml:space="preserve">Probably fine but I barely smell it </t>
   </si>
   <si>
-    <t>DecantX and Maple Prime have no sample in stock.</t>
+    <t>Parfums Quartana</t>
+  </si>
+  <si>
+    <t>Forest of the Golden Dream</t>
+  </si>
+  <si>
+    <t>Their own site would not load when I tried.</t>
   </si>
   <si>
     <t>Marem</t>
@@ -1115,13 +1211,10 @@
     <t xml:space="preserve">Red currant, citrus and rose. Not sure what I think. </t>
   </si>
   <si>
-    <t>Prissana</t>
-  </si>
-  <si>
-    <t>Nefer</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
+    <t>Ierofante</t>
+  </si>
+  <si>
+    <t>Worth confirming the spelling.</t>
   </si>
   <si>
     <t>CB I Hate Perfume</t>
@@ -1133,6 +1226,15 @@
     <t xml:space="preserve">Love this dirt and sunshine </t>
   </si>
   <si>
+    <t>Robert Piguet</t>
+  </si>
+  <si>
+    <t>Bandit</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
+  </si>
+  <si>
     <t>A Room with a View</t>
   </si>
   <si>
@@ -1151,7 +1253,7 @@
     <t xml:space="preserve">Probably very good but I've smelled too many similar dirt and rain and moss ones </t>
   </si>
   <si>
-    <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
+    <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
   </si>
   <si>
     <t>In the Library</t>
@@ -1160,73 +1262,52 @@
     <t xml:space="preserve">Can't smell nothin, doesn't smell like a library tho </t>
   </si>
   <si>
-    <t>Nest</t>
-  </si>
-  <si>
-    <t>Black Tulip</t>
+    <t>Rogue Perfumery</t>
+  </si>
+  <si>
+    <t>(discovery set)</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
   </si>
   <si>
     <t>Boy</t>
   </si>
   <si>
-    <t>Olfactive Studio</t>
-  </si>
-  <si>
-    <t>Flash Back</t>
-  </si>
-  <si>
     <t>As beautiful and complex and wearable as I could hope, not too feminine but still real Chanel</t>
   </si>
   <si>
-    <t>Listed as Flashback in New York.</t>
-  </si>
-  <si>
     <t>Paris – Paris</t>
   </si>
   <si>
     <t xml:space="preserve">Nice rose </t>
   </si>
   <si>
-    <t>One Day</t>
-  </si>
-  <si>
-    <t>Taipei</t>
-  </si>
-  <si>
-    <t>Ministry of Scent sample sold out.</t>
-  </si>
-  <si>
     <t>Le Lion</t>
   </si>
   <si>
     <t xml:space="preserve">No thanks </t>
   </si>
   <si>
-    <t>Ormonde Jayne</t>
-  </si>
-  <si>
-    <t>Montabaco Intensivo</t>
-  </si>
-  <si>
-    <t>Bloom has standard Montabaco at $10, not Intensivo.</t>
-  </si>
-  <si>
     <t>Sycomore</t>
   </si>
   <si>
-    <t>Paco Rabanne</t>
-  </si>
-  <si>
-    <t>Maple Prime has full bottles from $38.99, no small size anywhere.</t>
+    <t>Rogue's own discovery set is sold out and most of their line with it.</t>
+  </si>
+  <si>
+    <t>Romeo Gigli</t>
   </si>
   <si>
     <t>31 Rue Cambon</t>
   </si>
   <si>
+    <t>Romeo di Romeo Gigli</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apparently a masterpiece. Giving it too many chances. It's diaper and sour underneath all the great stuff I smell. Drydown is better. </t>
   </si>
   <si>
-    <t>Duplicate of the row above.</t>
+    <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
   </si>
   <si>
     <t>Coromandel</t>
@@ -1235,52 +1316,46 @@
     <t xml:space="preserve">Magic </t>
   </si>
   <si>
-    <t>Papillon Artisan</t>
-  </si>
-  <si>
-    <t>Tobacco Rose</t>
-  </si>
-  <si>
     <t>1957</t>
   </si>
   <si>
     <t xml:space="preserve">Musky white, surprisingly great, simple </t>
   </si>
   <si>
-    <t>Perfumed Court $10.94. Papillon's own site sells full bottles only.</t>
-  </si>
-  <si>
     <t>Bleu de Chanel</t>
   </si>
   <si>
-    <t>Parfumerie Particulière</t>
-  </si>
-  <si>
-    <t>Black Tar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nice, basic cologne </t>
   </si>
   <si>
-    <t>Ministry of Scent has 2ml at $7.00.</t>
+    <t>Cheapest on the list.</t>
   </si>
   <si>
     <t>Chasing Scents</t>
   </si>
   <si>
+    <t>Sanctuary</t>
+  </si>
+  <si>
+    <t>Javan Rhino</t>
+  </si>
+  <si>
     <t>Tea Service</t>
   </si>
   <si>
+    <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sweet tea in a rubber </t>
   </si>
   <si>
-    <t>Penhaligon's</t>
-  </si>
-  <si>
-    <t>Blenheim Bouquet</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
+    <t>Senyokô</t>
+  </si>
+  <si>
+    <t>Indigo Perfumery</t>
+  </si>
+  <si>
+    <t>https://indigoperfumery.com</t>
   </si>
   <si>
     <t>Weeping Rose</t>
@@ -1310,66 +1385,63 @@
     <t xml:space="preserve">So classic and good, not old lady, easy to wear but very feminine </t>
   </si>
   <si>
+    <t>Indigo carries the line, no samples listed.</t>
+  </si>
+  <si>
     <t>Clue Perfumery</t>
   </si>
   <si>
-    <t>Liquid Love</t>
+    <t>Serge Lutens</t>
+  </si>
+  <si>
+    <t>Poivre Noir</t>
   </si>
   <si>
     <t>Dandelion Butter</t>
   </si>
   <si>
-    <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Weeds with fat, as advertised. It's really nice. Doesn't last long. </t>
   </si>
   <si>
+    <t>https://www.decantx.com/products/serge-lutens-poivre-noir-eau-de-parfum-unisex</t>
+  </si>
+  <si>
     <t>Amy</t>
   </si>
   <si>
-    <t>Parfums Quartana</t>
-  </si>
-  <si>
-    <t>Forest of the Golden Dream</t>
-  </si>
-  <si>
-    <t>Their own site would not load when I tried.</t>
-  </si>
-  <si>
-    <t>Ierofante</t>
-  </si>
-  <si>
     <t>Morel Map</t>
   </si>
   <si>
-    <t>Worth confirming the spelling.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Damp mossy forest floor, beautiful </t>
   </si>
   <si>
-    <t>Robert Piguet</t>
-  </si>
-  <si>
-    <t>Bandit</t>
+    <t>Sample listed, sold out. Maple Prime has 100ml at $76.99.</t>
   </si>
   <si>
     <t>Warm Bulb</t>
   </si>
   <si>
-    <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
-  </si>
-  <si>
     <t xml:space="preserve">I like it but I don't love it on. More of a novelty. </t>
   </si>
   <si>
+    <t>Vitriol d'Œillet</t>
+  </si>
+  <si>
+    <t>Not at any of the three retailers that carry Serge Lutens.</t>
+  </si>
+  <si>
     <t>With the Candlestick</t>
   </si>
   <si>
     <t>Bad candy? Clumsy</t>
   </si>
   <si>
+    <t>Fils de Joie</t>
+  </si>
+  <si>
+    <t>https://theperfumedcourt.com/products/serge-lutens-fils-de-joie-edp-decant-sample</t>
+  </si>
+  <si>
     <t>Need to try on my skin but so nice</t>
   </si>
   <si>
@@ -1379,108 +1451,48 @@
     <t xml:space="preserve">Similar to Setchu but leaves me wanting more </t>
   </si>
   <si>
-    <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
-  </si>
-  <si>
-    <t>Rogue Perfumery</t>
-  </si>
-  <si>
-    <t>(discovery set)</t>
-  </si>
-  <si>
     <t>Series 1 Leaves: Lily</t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simple white floral but a flower I'm not that familiar with </t>
   </si>
   <si>
+    <t>1ml is $9.99. Discontinued from the Noire collection.</t>
+  </si>
+  <si>
     <t>Serpentine</t>
   </si>
   <si>
+    <t>SJP</t>
+  </si>
+  <si>
+    <t>Stash SJP</t>
+  </si>
+  <si>
     <t>Nice! Probably duplicative but I could wear this.</t>
   </si>
   <si>
-    <t>Rogue's own discovery set is sold out and most of their line with it.</t>
-  </si>
-  <si>
-    <t>Romeo Gigli</t>
-  </si>
-  <si>
-    <t>Romeo di Romeo Gigli</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
-  </si>
-  <si>
-    <t>Cheapest on the list.</t>
-  </si>
-  <si>
-    <t>Sanctuary</t>
-  </si>
-  <si>
-    <t>Javan Rhino</t>
-  </si>
-  <si>
-    <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
-  </si>
-  <si>
-    <t>Senyokô</t>
-  </si>
-  <si>
-    <t>Indigo Perfumery</t>
-  </si>
-  <si>
-    <t>https://indigoperfumery.com</t>
-  </si>
-  <si>
-    <t>Indigo carries the line, no samples listed.</t>
-  </si>
-  <si>
-    <t>Serge Lutens</t>
-  </si>
-  <si>
-    <t>Poivre Noir</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/serge-lutens-poivre-noir-eau-de-parfum-unisex</t>
-  </si>
-  <si>
-    <t>Sample listed, sold out. Maple Prime has 100ml at $76.99.</t>
-  </si>
-  <si>
-    <t>Vitriol d'Œillet</t>
-  </si>
-  <si>
-    <t>Not at any of the three retailers that carry Serge Lutens.</t>
-  </si>
-  <si>
-    <t>Fils de Joie</t>
-  </si>
-  <si>
-    <t>https://theperfumedcourt.com/products/serge-lutens-fils-de-joie-edp-decant-sample</t>
-  </si>
-  <si>
-    <t>1ml is $9.99. Discontinued from the Noire collection.</t>
-  </si>
-  <si>
-    <t>SJP</t>
-  </si>
-  <si>
-    <t>Stash SJP</t>
-  </si>
-  <si>
     <t>MicroPerfumes / Maple Prime</t>
   </si>
   <si>
     <t>https://microperfumes.com/products/stash-edp-sample-vial</t>
   </si>
   <si>
+    <t>Amazingreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not a favorite. </t>
+  </si>
+  <si>
     <t>Sample and 10ml both sold out.</t>
   </si>
   <si>
+    <t>Incense: Kyoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Really good, light and airy but incense. Wood but maybe the immortelle changes it? Could be a bottle. </t>
+  </si>
+  <si>
     <t>The 7 Virtues</t>
   </si>
   <si>
@@ -1490,6 +1502,12 @@
     <t>Perfumed Court carries the brand, only three other scents.</t>
   </si>
   <si>
+    <t>Vaquera: Classique Perdu</t>
+  </si>
+  <si>
+    <t>I can't tell if this is tricking me? Apparently it smells like 90s A&amp;F mall scent, but I love it. Floral but tomato leaf but something spicy? Could turn terrible, but we will see</t>
+  </si>
+  <si>
     <t>The House of Oud</t>
   </si>
   <si>
@@ -1499,6 +1517,12 @@
     <t>Maple Prime has 75ml at $127.99.</t>
   </si>
   <si>
+    <t>Cologne: Anbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus, then warm spice. Clove? I shouldn't like this but it feels like an easy summer splash on cologne that isn't basic </t>
+  </si>
+  <si>
     <t>Une Nuit Nomade</t>
   </si>
   <si>
@@ -1508,15 +1532,39 @@
     <t>Vilhelm Parfumerie</t>
   </si>
   <si>
+    <t>Ganja</t>
+  </si>
+  <si>
     <t>Fleur Burlesque</t>
   </si>
   <si>
+    <t>I liked it then didn't then did then didn't then DID!</t>
+  </si>
+  <si>
     <t>https://twistedlily.com/products/fleur-burlesque-sample</t>
   </si>
   <si>
+    <t>Odeur 10</t>
+  </si>
+  <si>
+    <t>Like a row of washing machines in action. Metal, clean, not detergent but very soapy, don't want to wear but very good</t>
+  </si>
+  <si>
+    <t>Monocle Scent Four: Yoyogi</t>
+  </si>
+  <si>
+    <t>Pleasant wood, just kind of a watered down Laurel</t>
+  </si>
+  <si>
     <t>Scent Split lists it sold out.</t>
   </si>
   <si>
+    <t>Dot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweet and maybe well crafted but no </t>
+  </si>
+  <si>
     <t>YSL</t>
   </si>
   <si>
@@ -1526,12 +1574,24 @@
     <t>Only the women's Rive Gauche turns up.</t>
   </si>
   <si>
+    <t>Incense: Ouarzazate</t>
+  </si>
+  <si>
+    <t>Not as special as the others but a nice woody scent, dry down ends kinda sour</t>
+  </si>
+  <si>
     <t>Kouros</t>
   </si>
   <si>
     <t>Maple Prime has 100ml at $80.99, no sample anywhere.</t>
   </si>
   <si>
+    <t>Dia x Meg Webster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amber pepper wood, doesn't last for shit </t>
+  </si>
+  <si>
     <t>Frédéric Malle</t>
   </si>
   <si>
@@ -1541,9 +1601,27 @@
     <t>https://www.decantx.com/products/frederic-malle-french-lover-eau-de-parfum-for-men</t>
   </si>
   <si>
+    <t>Incense: Zagorsk</t>
+  </si>
+  <si>
+    <t>Not into this one</t>
+  </si>
+  <si>
+    <t>Artek: Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factory smells a bit. But not very interesting </t>
+  </si>
+  <si>
     <t>Also in your Maple Prime cart at 1.2ml for $12.99.</t>
   </si>
   <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is likely very beautiful but it is instantly a public bathroom after a cleaning. Maybe in Europe. </t>
+  </si>
+  <si>
     <t>Viktor &amp; Rolf</t>
   </si>
   <si>
@@ -1553,91 +1631,70 @@
     <t>https://www.decantx.com/products/viktor-rolf-spicebomb-metallic-musk-eau-de-parfum-for-men</t>
   </si>
   <si>
-    <t>Amazingreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not a favorite. </t>
-  </si>
-  <si>
-    <t>Incense: Kyoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Really good, light and airy but incense. Wood but maybe the immortelle changes it? Could be a bottle. </t>
-  </si>
-  <si>
-    <t>Vaquera: Classique Perdu</t>
-  </si>
-  <si>
-    <t>I can't tell if this is tricking me? Apparently it smells like 90s A&amp;F mall scent, but I love it. Floral but tomato leaf but something spicy? Could turn terrible, but we will see</t>
+    <t xml:space="preserve">Photorealistic pot smell. Amazing. Absolutely not. </t>
+  </si>
+  <si>
+    <t>Incense: Jaisalmer</t>
   </si>
   <si>
     <t>This is Viktor &amp; Rolf Spicebomb Metallic Musk.</t>
   </si>
   <si>
+    <t>Incense: Avignon</t>
+  </si>
+  <si>
     <t>Buongiorno</t>
   </si>
   <si>
-    <t>Cologne: Anbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citrus, then warm spice. Clove? I shouldn't like this but it feels like an easy summer splash on cologne that isn't basic </t>
-  </si>
-  <si>
     <t>DecantX has it at $13.29.</t>
   </si>
   <si>
     <t>Moss Cologne</t>
   </si>
   <si>
-    <t>Ganja</t>
-  </si>
-  <si>
-    <t>I liked it then didn't then did then didn't then DID!</t>
+    <t>Monocle Scent Two: Laurel</t>
   </si>
   <si>
     <t>Luckyscent carries Bortnikoff too.</t>
   </si>
   <si>
+    <t>Wow. The wood I've not been able to find.</t>
+  </si>
+  <si>
     <t>Vanilla Black Pepper</t>
   </si>
   <si>
     <t>Ministry of Scent</t>
   </si>
   <si>
-    <t>Odeur 10</t>
-  </si>
-  <si>
     <t>https://ministryofscent.com/products/vanilla-black-pepper</t>
   </si>
   <si>
-    <t>Like a row of washing machines in action. Metal, clean, not detergent but very soapy, don't want to wear but very good</t>
-  </si>
-  <si>
-    <t>Monocle Scent Four: Yoyogi</t>
-  </si>
-  <si>
-    <t>Pleasant wood, just kind of a watered down Laurel</t>
-  </si>
-  <si>
-    <t>Dot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweet and maybe well crafted but no </t>
-  </si>
-  <si>
-    <t>Incense: Ouarzazate</t>
-  </si>
-  <si>
-    <t>Not as special as the others but a nice woody scent, dry down ends kinda sour</t>
+    <t>Celluloid Galbanum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfect white floral with a hint of Ziplock bags, not overly tuberose </t>
+  </si>
+  <si>
+    <t>Chlorophyll Gardenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
+  </si>
+  <si>
+    <t>Odeur 53</t>
+  </si>
+  <si>
+    <t>Mineral and clay and hot bulb, so cool</t>
   </si>
   <si>
     <t>Formerly Tigerlily Perfumery, San Francisco.</t>
   </si>
   <si>
-    <t>Dia x Meg Webster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber pepper wood, doesn't last for shit </t>
+    <t>Radish Vetiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spicy, photorealistic. Maybe too odd to wear but very into it. </t>
   </si>
   <si>
     <t>Les Bains Guerbois</t>
@@ -1649,10 +1706,7 @@
     <t>No 1ml listed for this one.</t>
   </si>
   <si>
-    <t>Incense: Zagorsk</t>
-  </si>
-  <si>
-    <t>Not into this one</t>
+    <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
   </si>
   <si>
     <t>Angelos Creations Olfactives</t>
@@ -1664,19 +1718,28 @@
     <t>https://www.luckyscent.com/products/pothos-by-angelos-creations-olfactives</t>
   </si>
   <si>
-    <t>Artek: Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factory smells a bit. But not very interesting </t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is likely very beautiful but it is instantly a public bathroom after a cleaning. Maybe in Europe. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Photorealistic pot smell. Amazing. Absolutely not. </t>
+    <t>Blackpepper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black pepper for sure. Doesn't last. I'd definitely spray this on if it were around. </t>
+  </si>
+  <si>
+    <t>Monocle Scent One: Hinoki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced and beautiful wood, but a sourness makes me not want to wear it </t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleasant floral, not to special </t>
+  </si>
+  <si>
+    <t>Cologne: Citrico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
   </si>
   <si>
     <t>CBCB Fragrances</t>
@@ -1688,103 +1751,40 @@
     <t>https://www.luckyscent.com/products/comrade-by-cbcb-fragrances</t>
   </si>
   <si>
-    <t>Incense: Jaisalmer</t>
-  </si>
-  <si>
-    <t>Incense: Avignon</t>
+    <t>Cologne: Vettiveru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So straightforward, just vetiver </t>
+  </si>
+  <si>
+    <t>Monocle Scent Five: Syros</t>
+  </si>
+  <si>
+    <t>2 much turmeric 4 me</t>
+  </si>
+  <si>
+    <t>Wonderoud</t>
+  </si>
+  <si>
+    <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
+  </si>
+  <si>
+    <t>Coqui Coqui</t>
+  </si>
+  <si>
+    <t>Eucaced</t>
+  </si>
+  <si>
+    <t>Very brash eucalyptus and cedar. I like it?</t>
+  </si>
+  <si>
+    <t>Rosas Secas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tart rose but dried roses, nice! </t>
   </si>
   <si>
     <t>Geranium Absolue</t>
-  </si>
-  <si>
-    <t>Monocle Scent Two: Laurel</t>
-  </si>
-  <si>
-    <t>Wow. The wood I've not been able to find.</t>
-  </si>
-  <si>
-    <t>Celluloid Galbanum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfect white floral with a hint of Ziplock bags, not overly tuberose </t>
-  </si>
-  <si>
-    <t>Chlorophyll Gardenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
-  </si>
-  <si>
-    <t>Odeur 53</t>
-  </si>
-  <si>
-    <t>Mineral and clay and hot bulb, so cool</t>
-  </si>
-  <si>
-    <t>Radish Vetiver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spicy, photorealistic. Maybe too odd to wear but very into it. </t>
-  </si>
-  <si>
-    <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
-  </si>
-  <si>
-    <t>Blackpepper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black pepper for sure. Doesn't last. I'd definitely spray this on if it were around. </t>
-  </si>
-  <si>
-    <t>Monocle Scent One: Hinoki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balanced and beautiful wood, but a sourness makes me not want to wear it </t>
-  </si>
-  <si>
-    <t>Grace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pleasant floral, not to special </t>
-  </si>
-  <si>
-    <t>Cologne: Citrico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
-  </si>
-  <si>
-    <t>Cologne: Vettiveru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So straightforward, just vetiver </t>
-  </si>
-  <si>
-    <t>Monocle Scent Five: Syros</t>
-  </si>
-  <si>
-    <t>2 much turmeric 4 me</t>
-  </si>
-  <si>
-    <t>Wonderoud</t>
-  </si>
-  <si>
-    <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
-  </si>
-  <si>
-    <t>Coqui Coqui</t>
-  </si>
-  <si>
-    <t>Eucaced</t>
-  </si>
-  <si>
-    <t>Very brash eucalyptus and cedar. I like it?</t>
-  </si>
-  <si>
-    <t>Rosas Secas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tart rose but dried roses, nice! </t>
   </si>
   <si>
     <t>Maderas</t>
@@ -5401,13 +5401,13 @@
       <name val="Ui-sans-serif"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFF0000"/>
+      <u/>
+      <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <color rgb="FF1155CC"/>
+      <b/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -5553,10 +5553,10 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -5584,20 +5584,20 @@
     <xf borderId="1" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -5672,12 +5672,12 @@
     <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="6" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -6018,14 +6018,14 @@
       <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -6053,7 +6053,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>20</v>
@@ -6062,7 +6062,7 @@
         <v>71.0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="12"/>
@@ -6124,17 +6124,17 @@
       <c r="Z3" s="14"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="11">
         <v>73.0</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="12"/>
@@ -6160,17 +6160,17 @@
       <c r="Z4" s="14"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="20">
+      <c r="B5" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="21">
         <v>50.0</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>32</v>
+      <c r="D5" s="22" t="s">
+        <v>37</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="24"/>
@@ -6197,16 +6197,16 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C6" s="11">
         <v>85.0</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="12"/>
@@ -6233,16 +6233,16 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C7" s="11">
         <v>80.0</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="12"/>
@@ -6269,16 +6269,16 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C8" s="11">
         <v>70.0</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="12"/>
@@ -6305,16 +6305,16 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C9" s="11">
         <v>40.0</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="27"/>
@@ -6341,16 +6341,16 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C10" s="11">
         <v>89.0</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="12"/>
@@ -6377,16 +6377,16 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="11">
         <v>85.0</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="12"/>
@@ -6413,16 +6413,16 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C12" s="11">
         <v>75.0</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="12"/>
@@ -6449,16 +6449,16 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C13" s="11">
         <v>75.0</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="12"/>
@@ -6485,16 +6485,16 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C14" s="11">
         <v>90.0</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="12"/>
@@ -6521,16 +6521,16 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C15" s="11">
         <v>40.0</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="12"/>
@@ -6557,16 +6557,16 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C16" s="11">
         <v>40.0</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E16" s="17"/>
       <c r="F16" s="12"/>
@@ -6593,16 +6593,16 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C17" s="11">
         <v>40.0</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="12"/>
@@ -6629,16 +6629,16 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="29" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C18" s="11">
         <v>88.0</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="12"/>
@@ -6664,17 +6664,17 @@
       <c r="Z18" s="14"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="20">
+      <c r="A19" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="21">
         <v>82.0</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>80</v>
+      <c r="D19" s="22" t="s">
+        <v>92</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="30"/>
@@ -6701,16 +6701,16 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="31" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C20" s="11">
         <v>87.0</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
@@ -6737,16 +6737,16 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C21" s="11">
         <v>70.0</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="12"/>
@@ -6773,16 +6773,16 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C22" s="11">
         <v>50.0</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="12"/>
@@ -6809,16 +6809,16 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C23" s="11">
         <v>88.0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="12"/>
@@ -6844,17 +6844,17 @@
       <c r="Z23" s="14"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="21" t="s">
-        <v>91</v>
+      <c r="A24" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C24" s="11">
         <v>83.0</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
@@ -6880,17 +6880,17 @@
       <c r="Z24" s="8"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="18" t="s">
-        <v>91</v>
+      <c r="A25" s="19" t="s">
+        <v>104</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C25" s="11">
         <v>65.0</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="12"/>
@@ -6917,16 +6917,16 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C26" s="11">
         <v>45.0</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="27"/>
@@ -6953,16 +6953,16 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="26" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C27" s="11">
         <v>35.0</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="27"/>
@@ -6989,16 +6989,16 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="10" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C28" s="11">
         <v>50.0</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="12"/>
@@ -7028,13 +7028,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C29" s="11">
         <v>82.0</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="27"/>
@@ -7061,16 +7061,16 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C30" s="11">
         <v>60.0</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="12"/>
@@ -7097,16 +7097,16 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C31" s="11">
         <v>60.0</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E31" s="34"/>
       <c r="F31" s="12"/>
@@ -7133,16 +7133,16 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C32" s="11">
         <v>50.0</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="12"/>
@@ -7169,16 +7169,16 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C33" s="11">
         <v>83.0</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="12"/>
@@ -7205,16 +7205,16 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C34" s="11">
         <v>88.0</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="12"/>
@@ -7241,16 +7241,16 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C35" s="11">
         <v>86.0</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="12"/>
@@ -7277,16 +7277,16 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C36" s="11">
         <v>87.0</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="12"/>
@@ -7313,16 +7313,16 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C37" s="11">
         <v>60.0</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="12"/>
@@ -7349,16 +7349,16 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C38" s="11">
         <v>60.0</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="12"/>
@@ -7385,16 +7385,16 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C39" s="11">
         <v>85.0</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="12"/>
@@ -7421,16 +7421,16 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>171</v>
       </c>
       <c r="C40" s="11">
         <v>89.0</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="12"/>
@@ -7457,16 +7457,16 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>160</v>
+        <v>148</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="C41" s="11">
         <v>90.0</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="12"/>
@@ -7493,16 +7493,16 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C42" s="11">
         <v>82.0</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="12"/>
@@ -7529,16 +7529,16 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C43" s="11">
         <v>82.0</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="12"/>
@@ -7565,16 +7565,16 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C44" s="11">
         <v>84.0</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="12"/>
@@ -7601,16 +7601,16 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C45" s="11">
         <v>78.0</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="12"/>
@@ -7637,16 +7637,16 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C46" s="11">
         <v>87.0</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="12"/>
@@ -7673,16 +7673,16 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C47" s="11">
         <v>65.0</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="12"/>
@@ -7709,16 +7709,16 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C48" s="11">
         <v>82.0</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="12"/>
@@ -7745,16 +7745,16 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C49" s="11">
         <v>87.0</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="12"/>
@@ -7781,16 +7781,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C50" s="11">
         <v>60.0</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="12"/>
@@ -7817,16 +7817,16 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="10" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C51" s="11">
         <v>90.0</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="12"/>
@@ -7853,16 +7853,16 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C52" s="11">
         <v>88.0</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="36"/>
@@ -7889,16 +7889,16 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="27" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C53" s="11">
         <v>82.0</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="E53" s="27"/>
       <c r="F53" s="27"/>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="37" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="27"/>
@@ -7957,16 +7957,16 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C55" s="11">
         <v>69.0</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="12"/>
@@ -7993,16 +7993,16 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="27" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C56" s="11">
         <v>81.0</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="E56" s="17"/>
       <c r="F56" s="12"/>
@@ -8029,16 +8029,16 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="27" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="C57" s="11">
         <v>88.0</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E57" s="27"/>
       <c r="F57" s="27"/>
@@ -8065,16 +8065,16 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="27" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C58" s="11">
         <v>87.0</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="E58" s="27"/>
       <c r="F58" s="27"/>
@@ -8101,16 +8101,16 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="27" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C59" s="38">
         <v>40.0</v>
       </c>
       <c r="D59" s="39" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="E59" s="27"/>
       <c r="F59" s="27"/>
@@ -8136,17 +8136,17 @@
       <c r="Z59" s="8"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="21" t="s">
-        <v>236</v>
+      <c r="A60" s="22" t="s">
+        <v>262</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C60" s="11">
         <v>80.0</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="27"/>
@@ -8173,16 +8173,16 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="26" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C61" s="11">
         <v>50.0</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
@@ -8209,16 +8209,16 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="26" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C62" s="11">
         <v>40.0</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="E62" s="17"/>
       <c r="F62" s="12"/>
@@ -8245,16 +8245,16 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="10" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C63" s="11">
         <v>40.0</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="12"/>
@@ -8280,17 +8280,17 @@
       <c r="Z63" s="14"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="C64" s="20">
+      <c r="A64" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C64" s="21">
         <v>40.0</v>
       </c>
-      <c r="D64" s="21" t="s">
-        <v>254</v>
+      <c r="D64" s="22" t="s">
+        <v>278</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="24"/>
@@ -8317,16 +8317,16 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C65" s="11">
         <v>65.0</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
@@ -8353,16 +8353,16 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="10" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C66" s="11">
         <v>85.0</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="E66" s="10"/>
       <c r="F66" s="12"/>
@@ -8389,16 +8389,16 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C67" s="11">
         <v>88.0</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
@@ -8425,16 +8425,16 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="10" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="C68" s="11">
         <v>88.0</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="12"/>
@@ -8461,16 +8461,16 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C69" s="11">
         <v>50.0</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="E69" s="26"/>
       <c r="F69" s="12"/>
@@ -8497,16 +8497,16 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C70" s="41">
         <v>50.0</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="42"/>
@@ -8533,16 +8533,16 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C71" s="11">
         <v>50.0</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="12"/>
@@ -8569,16 +8569,16 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="C72" s="11">
         <v>84.0</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="12"/>
@@ -8605,16 +8605,16 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C73" s="11">
         <v>60.0</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E73" s="17"/>
       <c r="F73" s="12"/>
@@ -8641,16 +8641,16 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C74" s="11">
         <v>99.0</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="12"/>
@@ -8677,16 +8677,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C75" s="11">
         <v>90.0</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="12"/>
@@ -8713,16 +8713,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C76" s="11">
         <v>89.0</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="E76" s="17"/>
       <c r="F76" s="12"/>
@@ -8749,16 +8749,16 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C77" s="11">
         <v>86.0</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E77" s="10"/>
       <c r="F77" s="12"/>
@@ -8785,16 +8785,16 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="B78" s="18" t="s">
-        <v>308</v>
+        <v>306</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="C78" s="11">
         <v>84.0</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="12"/>
@@ -8821,16 +8821,16 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C79" s="11">
         <v>83.0</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="E79" s="10"/>
       <c r="F79" s="12"/>
@@ -8857,16 +8857,16 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C80" s="11">
         <v>83.0</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="12"/>
@@ -8893,16 +8893,16 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C81" s="11">
         <v>82.0</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="E81" s="10"/>
       <c r="F81" s="12"/>
@@ -8929,16 +8929,16 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B82" s="29" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C82" s="11">
         <v>81.0</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="12"/>
@@ -8965,16 +8965,16 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C83" s="11">
         <v>80.0</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="E83" s="10"/>
       <c r="F83" s="12"/>
@@ -9001,16 +9001,16 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C84" s="11">
         <v>79.0</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="E84" s="10"/>
       <c r="F84" s="12"/>
@@ -9037,16 +9037,16 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C85" s="11">
         <v>74.0</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="12"/>
@@ -9073,16 +9073,16 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C86" s="11">
         <v>71.0</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="12"/>
@@ -9109,16 +9109,16 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="C87" s="11">
         <v>70.0</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="E87" s="10"/>
       <c r="F87" s="12"/>
@@ -9145,16 +9145,16 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="C88" s="11">
         <v>96.0</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="E88" s="10"/>
       <c r="F88" s="12"/>
@@ -9181,16 +9181,16 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="16" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="C89" s="11">
         <v>89.0</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="E89" s="10"/>
       <c r="F89" s="12"/>
@@ -9217,16 +9217,16 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="10" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C90" s="11">
         <v>86.0</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="E90" s="10"/>
       <c r="F90" s="12"/>
@@ -9253,16 +9253,16 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="10" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C91" s="11">
         <v>84.0</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="12"/>
@@ -9289,16 +9289,16 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="10" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C92" s="11">
         <v>83.0</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="12"/>
@@ -9325,16 +9325,16 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="10" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C93" s="11">
         <v>83.0</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="E93" s="10"/>
       <c r="F93" s="12"/>
@@ -9361,16 +9361,16 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C94" s="11">
         <v>93.0</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="12"/>
@@ -9397,16 +9397,16 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="C95" s="11">
         <v>91.0</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="E95" s="10"/>
       <c r="F95" s="12"/>
@@ -9433,16 +9433,16 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="C96" s="11">
         <v>87.0</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="12"/>
@@ -9469,16 +9469,16 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="C97" s="11">
         <v>85.0</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="E97" s="10"/>
       <c r="F97" s="12"/>
@@ -9505,16 +9505,16 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="C98" s="11">
         <v>82.0</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="12"/>
@@ -9541,16 +9541,16 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="C99" s="11">
         <v>80.0</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="E99" s="10"/>
       <c r="F99" s="12"/>
@@ -9577,14 +9577,14 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="10" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="12"/>
@@ -9611,16 +9611,16 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="10" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="C101" s="11">
         <v>89.0</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="12"/>
@@ -9647,16 +9647,16 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="10" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="C102" s="11">
         <v>85.0</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="E102" s="17"/>
       <c r="F102" s="12"/>
@@ -9683,16 +9683,16 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="10" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="C103" s="11">
         <v>84.0</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="E103" s="10"/>
       <c r="F103" s="12"/>
@@ -9719,16 +9719,16 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="10" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="C104" s="11">
         <v>82.0</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="E104" s="10"/>
       <c r="F104" s="12"/>
@@ -9755,16 +9755,16 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="10" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C105" s="11">
         <v>70.0</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="12"/>
@@ -9791,16 +9791,16 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="C106" s="11">
         <v>88.0</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E106" s="10"/>
       <c r="F106" s="12"/>
@@ -9827,16 +9827,16 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="C107" s="11">
         <v>82.0</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="E107" s="10"/>
       <c r="F107" s="12"/>
@@ -9863,16 +9863,16 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="C108" s="11">
         <v>74.0</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="E108" s="10"/>
       <c r="F108" s="12"/>
@@ -9899,16 +9899,16 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="C109" s="11">
         <v>74.0</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="E109" s="10"/>
       <c r="F109" s="12"/>
@@ -9935,16 +9935,16 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="C110" s="11">
         <v>71.0</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="E110" s="10"/>
       <c r="F110" s="12"/>
@@ -9971,16 +9971,16 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="C111" s="11">
         <v>90.0</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="12"/>
@@ -10007,16 +10007,16 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="C112" s="11">
         <v>81.0</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="12"/>
@@ -10043,16 +10043,16 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C113" s="11">
         <v>80.0</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="E113" s="10"/>
       <c r="F113" s="12"/>
@@ -10079,16 +10079,16 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="27" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="C114" s="11">
         <v>74.0</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="E114" s="27"/>
       <c r="F114" s="27"/>
@@ -10115,16 +10115,16 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="27" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="B115" s="27" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="C115" s="11">
         <v>71.0</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="E115" s="27"/>
       <c r="F115" s="27"/>
@@ -10151,16 +10151,16 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="10" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C116" s="11">
         <v>89.0</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="E116" s="10"/>
       <c r="F116" s="12"/>
@@ -10187,16 +10187,16 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="10" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C117" s="11">
         <v>79.0</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="E117" s="17"/>
       <c r="F117" s="12"/>
@@ -10223,16 +10223,16 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="10" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C118" s="11">
         <v>91.0</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="E118" s="17"/>
       <c r="F118" s="12"/>
@@ -10258,55 +10258,55 @@
       <c r="Z118" s="14"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="B119" s="21" t="s">
-        <v>434</v>
+      <c r="A119" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>461</v>
       </c>
       <c r="C119" s="41">
         <v>90.0</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="E119" s="45" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="F119" s="10"/>
       <c r="G119" s="46"/>
-      <c r="H119" s="18"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="18"/>
-      <c r="K119" s="18"/>
-      <c r="L119" s="18"/>
-      <c r="M119" s="18"/>
-      <c r="N119" s="18"/>
-      <c r="O119" s="18"/>
-      <c r="P119" s="18"/>
-      <c r="Q119" s="18"/>
-      <c r="R119" s="18"/>
-      <c r="S119" s="18"/>
-      <c r="T119" s="18"/>
-      <c r="U119" s="18"/>
-      <c r="V119" s="18"/>
-      <c r="W119" s="18"/>
-      <c r="X119" s="18"/>
-      <c r="Y119" s="18"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="19"/>
+      <c r="K119" s="19"/>
+      <c r="L119" s="19"/>
+      <c r="M119" s="19"/>
+      <c r="N119" s="19"/>
+      <c r="O119" s="19"/>
+      <c r="P119" s="19"/>
+      <c r="Q119" s="19"/>
+      <c r="R119" s="19"/>
+      <c r="S119" s="19"/>
+      <c r="T119" s="19"/>
+      <c r="U119" s="19"/>
+      <c r="V119" s="19"/>
+      <c r="W119" s="19"/>
+      <c r="X119" s="19"/>
+      <c r="Y119" s="19"/>
       <c r="Z119" s="8"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="10" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C120" s="11">
         <v>90.0</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="E120" s="10"/>
       <c r="F120" s="12"/>
@@ -10333,16 +10333,16 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="36" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C121" s="11">
         <v>70.0</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="E121" s="27"/>
       <c r="F121" s="36"/>
@@ -10369,16 +10369,16 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="C122" s="11">
         <v>55.0</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="E122" s="10"/>
       <c r="F122" s="27"/>
@@ -10405,16 +10405,16 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="10" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="C123" s="11">
         <v>88.0</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="E123" s="10"/>
       <c r="F123" s="12"/>
@@ -10440,17 +10440,17 @@
       <c r="Z123" s="14"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B124" s="21" t="s">
-        <v>453</v>
+      <c r="A124" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>477</v>
       </c>
       <c r="C124" s="11">
         <v>87.0</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="E124" s="27"/>
       <c r="F124" s="27"/>
@@ -10477,16 +10477,16 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="C125" s="11">
         <v>91.0</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="E125" s="27"/>
       <c r="F125" s="27"/>
@@ -10512,17 +10512,17 @@
       <c r="Z125" s="8"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="C126" s="20">
+      <c r="A126" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B126" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="C126" s="21">
         <v>89.0</v>
       </c>
-      <c r="D126" s="21" t="s">
-        <v>462</v>
+      <c r="D126" s="22" t="s">
+        <v>485</v>
       </c>
       <c r="E126" s="23"/>
       <c r="F126" s="47"/>
@@ -10549,16 +10549,16 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="C127" s="11">
         <v>50.0</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="E127" s="10"/>
       <c r="F127" s="12"/>
@@ -10585,16 +10585,16 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="C128" s="11">
         <v>91.0</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="E128" s="27"/>
       <c r="F128" s="27"/>
@@ -10621,16 +10621,16 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="C129" s="11">
         <v>91.0</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="E129" s="27"/>
       <c r="F129" s="27"/>
@@ -10657,16 +10657,16 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="C130" s="11">
         <v>90.0</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="E130" s="27"/>
       <c r="F130" s="27"/>
@@ -10693,16 +10693,16 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="C131" s="11">
         <v>89.0</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="E131" s="27"/>
       <c r="F131" s="27"/>
@@ -10729,16 +10729,16 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C132" s="11">
         <v>88.0</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="E132" s="27"/>
       <c r="F132" s="27"/>
@@ -10765,16 +10765,16 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C133" s="11">
         <v>87.0</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="E133" s="27"/>
       <c r="F133" s="27"/>
@@ -10801,16 +10801,16 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="C134" s="11">
         <v>86.0</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E134" s="27"/>
       <c r="F134" s="27"/>
@@ -10837,16 +10837,16 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="C135" s="11">
         <v>85.0</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="E135" s="27"/>
       <c r="F135" s="27"/>
@@ -10873,16 +10873,16 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="C136" s="11">
         <v>83.0</v>
       </c>
       <c r="D136" s="27" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="E136" s="27"/>
       <c r="F136" s="27"/>
@@ -10909,16 +10909,16 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C137" s="11">
         <v>83.0</v>
       </c>
       <c r="D137" s="27" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="E137" s="27"/>
       <c r="F137" s="27"/>
@@ -10945,16 +10945,16 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B138" s="36" t="s">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="C138" s="11">
         <v>82.0</v>
       </c>
       <c r="D138" s="27" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="E138" s="27"/>
       <c r="F138" s="27"/>
@@ -10981,16 +10981,16 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="C139" s="11">
         <v>82.0</v>
       </c>
       <c r="D139" s="27" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="E139" s="27"/>
       <c r="F139" s="27"/>
@@ -11017,16 +11017,16 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B140" s="26" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="C140" s="11">
         <v>70.0</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="E140" s="26"/>
       <c r="F140" s="12"/>
@@ -11053,10 +11053,10 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="49" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B141" s="50" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="27"/>
@@ -11085,10 +11085,10 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="49" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B142" s="50" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="27"/>
@@ -11117,16 +11117,16 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="B143" s="53" t="s">
-        <v>561</v>
+        <v>94</v>
+      </c>
+      <c r="B143" s="52" t="s">
+        <v>546</v>
       </c>
       <c r="C143" s="11">
         <v>96.0</v>
       </c>
       <c r="D143" s="27" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="E143" s="27"/>
       <c r="F143" s="27"/>
@@ -11152,17 +11152,17 @@
       <c r="Z143" s="8"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="54" t="s">
-        <v>107</v>
+      <c r="A144" s="53" t="s">
+        <v>94</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="C144" s="11">
         <v>94.0</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="12"/>
@@ -11189,16 +11189,16 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="16" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C145" s="11">
         <v>91.0</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="E145" s="10"/>
       <c r="F145" s="12"/>
@@ -11225,16 +11225,16 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B146" s="36" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C146" s="11">
         <v>90.0</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="E146" s="10"/>
       <c r="F146" s="12"/>
@@ -11261,16 +11261,16 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="16" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C147" s="11">
         <v>89.0</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="E147" s="10"/>
       <c r="F147" s="12"/>
@@ -11297,16 +11297,16 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C148" s="11">
         <v>88.0</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="E148" s="10"/>
       <c r="F148" s="12"/>
@@ -11333,16 +11333,16 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B149" s="27" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C149" s="11">
         <v>87.0</v>
       </c>
       <c r="D149" s="27" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E149" s="27"/>
       <c r="F149" s="27"/>
@@ -11369,16 +11369,16 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C150" s="11">
         <v>86.0</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E150" s="10"/>
       <c r="F150" s="12"/>
@@ -11405,16 +11405,16 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C151" s="11">
         <v>86.0</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E151" s="10"/>
       <c r="F151" s="12"/>
@@ -11441,16 +11441,16 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C152" s="11">
         <v>85.0</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E152" s="10"/>
       <c r="F152" s="12"/>
@@ -11477,16 +11477,16 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C153" s="11">
         <v>85.0</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E153" s="10"/>
       <c r="F153" s="12"/>
@@ -11513,16 +11513,16 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="27" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B154" s="36" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C154" s="11">
         <v>84.0</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E154" s="10"/>
       <c r="F154" s="12"/>
@@ -11549,16 +11549,16 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C155" s="11">
         <v>83.0</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E155" s="10"/>
       <c r="F155" s="12"/>
@@ -11585,16 +11585,16 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B156" s="10" t="s">
         <v>586</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>587</v>
       </c>
       <c r="C156" s="11">
         <v>89.0</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E156" s="10"/>
       <c r="F156" s="12"/>
@@ -11621,16 +11621,16 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="27" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B157" s="36" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C157" s="11">
         <v>89.0</v>
       </c>
       <c r="D157" s="27" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E157" s="27"/>
       <c r="F157" s="27"/>
@@ -11657,7 +11657,7 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>591</v>
@@ -11980,16 +11980,16 @@
       <c r="Z166" s="14"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="19" t="s">
+      <c r="A167" s="20" t="s">
         <v>613</v>
       </c>
-      <c r="B167" s="19" t="s">
+      <c r="B167" s="20" t="s">
         <v>614</v>
       </c>
-      <c r="C167" s="20">
+      <c r="C167" s="21">
         <v>80.0</v>
       </c>
-      <c r="D167" s="21" t="s">
+      <c r="D167" s="22" t="s">
         <v>615</v>
       </c>
       <c r="E167" s="23"/>
@@ -12022,7 +12022,7 @@
       <c r="B168" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="C168" s="20">
+      <c r="C168" s="21">
         <v>86.0</v>
       </c>
       <c r="D168" s="57" t="s">
@@ -12698,11 +12698,11 @@
       <c r="Z186" s="14"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="B187" s="21" t="s">
-        <v>249</v>
+      <c r="A187" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="B187" s="22" t="s">
+        <v>268</v>
       </c>
       <c r="C187" s="41">
         <v>78.0</v>
@@ -12711,28 +12711,28 @@
         <v>657</v>
       </c>
       <c r="E187" s="45" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="F187" s="10"/>
       <c r="G187" s="46"/>
-      <c r="H187" s="18"/>
-      <c r="I187" s="18"/>
-      <c r="J187" s="18"/>
-      <c r="K187" s="18"/>
-      <c r="L187" s="18"/>
-      <c r="M187" s="18"/>
-      <c r="N187" s="18"/>
-      <c r="O187" s="18"/>
-      <c r="P187" s="18"/>
-      <c r="Q187" s="18"/>
-      <c r="R187" s="18"/>
-      <c r="S187" s="18"/>
-      <c r="T187" s="18"/>
-      <c r="U187" s="18"/>
-      <c r="V187" s="18"/>
-      <c r="W187" s="18"/>
-      <c r="X187" s="18"/>
-      <c r="Y187" s="18"/>
+      <c r="H187" s="19"/>
+      <c r="I187" s="19"/>
+      <c r="J187" s="19"/>
+      <c r="K187" s="19"/>
+      <c r="L187" s="19"/>
+      <c r="M187" s="19"/>
+      <c r="N187" s="19"/>
+      <c r="O187" s="19"/>
+      <c r="P187" s="19"/>
+      <c r="Q187" s="19"/>
+      <c r="R187" s="19"/>
+      <c r="S187" s="19"/>
+      <c r="T187" s="19"/>
+      <c r="U187" s="19"/>
+      <c r="V187" s="19"/>
+      <c r="W187" s="19"/>
+      <c r="X187" s="19"/>
+      <c r="Y187" s="19"/>
       <c r="Z187" s="8"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
@@ -13417,7 +13417,7 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>698</v>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>700</v>
@@ -13489,7 +13489,7 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="27" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B209" s="57" t="s">
         <v>702</v>
@@ -13525,7 +13525,7 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>704</v>
@@ -13561,7 +13561,7 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>706</v>
@@ -13572,7 +13572,7 @@
       <c r="D211" s="10" t="s">
         <v>707</v>
       </c>
-      <c r="E211" s="18"/>
+      <c r="E211" s="19"/>
       <c r="F211" s="14"/>
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
@@ -13597,7 +13597,7 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B212" s="17" t="s">
         <v>708</v>
@@ -13633,7 +13633,7 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>710</v>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B214" s="63" t="s">
         <v>712</v>
@@ -13701,7 +13701,7 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B215" s="63" t="s">
         <v>713</v>
@@ -13733,7 +13733,7 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B216" s="63" t="s">
         <v>714</v>
@@ -13765,7 +13765,7 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B217" s="63" t="s">
         <v>715</v>
@@ -13797,7 +13797,7 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B218" s="63" t="s">
         <v>716</v>
@@ -13829,7 +13829,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B219" s="63" t="s">
         <v>717</v>
@@ -13861,7 +13861,7 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B220" s="63" t="s">
         <v>718</v>
@@ -13893,7 +13893,7 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B221" s="63" t="s">
         <v>719</v>
@@ -13925,7 +13925,7 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B222" s="63" t="s">
         <v>720</v>
@@ -13957,7 +13957,7 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B223" s="63" t="s">
         <v>721</v>
@@ -13989,7 +13989,7 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B224" s="63" t="s">
         <v>722</v>
@@ -14021,7 +14021,7 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B225" s="64" t="s">
         <v>723</v>
@@ -14053,7 +14053,7 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B226" s="63" t="s">
         <v>724</v>
@@ -14085,7 +14085,7 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B227" s="63" t="s">
         <v>725</v>
@@ -14117,7 +14117,7 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B228" s="63" t="s">
         <v>726</v>
@@ -14149,7 +14149,7 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B229" s="63" t="s">
         <v>727</v>
@@ -14181,7 +14181,7 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B230" s="63" t="s">
         <v>728</v>
@@ -14213,7 +14213,7 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B231" s="63" t="s">
         <v>729</v>
@@ -14245,7 +14245,7 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B232" s="63" t="s">
         <v>730</v>
@@ -14277,7 +14277,7 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B233" s="63" t="s">
         <v>731</v>
@@ -14309,7 +14309,7 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B234" s="63" t="s">
         <v>732</v>
@@ -14341,7 +14341,7 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B235" s="63" t="s">
         <v>733</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B236" s="63" t="s">
         <v>734</v>
@@ -14405,7 +14405,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B237" s="63" t="s">
         <v>735</v>
@@ -14437,7 +14437,7 @@
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B238" s="63" t="s">
         <v>736</v>
@@ -14732,7 +14732,7 @@
       <c r="D246" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="E246" s="18"/>
+      <c r="E246" s="19"/>
       <c r="F246" s="14"/>
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
@@ -14768,7 +14768,7 @@
       <c r="D247" s="10" t="s">
         <v>758</v>
       </c>
-      <c r="E247" s="18"/>
+      <c r="E247" s="19"/>
       <c r="F247" s="14"/>
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
@@ -14804,7 +14804,7 @@
       <c r="D248" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="E248" s="18"/>
+      <c r="E248" s="19"/>
       <c r="F248" s="14"/>
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
@@ -14840,7 +14840,7 @@
       <c r="D249" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="E249" s="18"/>
+      <c r="E249" s="19"/>
       <c r="F249" s="14"/>
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
@@ -14984,7 +14984,7 @@
       <c r="D253" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="E253" s="18"/>
+      <c r="E253" s="19"/>
       <c r="F253" s="14"/>
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
@@ -15020,7 +15020,7 @@
       <c r="D254" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="E254" s="18"/>
+      <c r="E254" s="19"/>
       <c r="F254" s="14"/>
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
@@ -15044,16 +15044,16 @@
       <c r="Z254" s="14"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="19" t="s">
+      <c r="A255" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="B255" s="19" t="s">
+      <c r="B255" s="20" t="s">
         <v>774</v>
       </c>
-      <c r="C255" s="20">
+      <c r="C255" s="21">
         <v>89.0</v>
       </c>
-      <c r="D255" s="21" t="s">
+      <c r="D255" s="22" t="s">
         <v>775</v>
       </c>
       <c r="E255" s="23"/>
@@ -15189,7 +15189,7 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="36" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B259" s="36" t="s">
         <v>785</v>
@@ -15225,7 +15225,7 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="68" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B260" s="68" t="s">
         <v>787</v>
@@ -15259,7 +15259,7 @@
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="68" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B261" s="68" t="s">
         <v>789</v>
@@ -15465,7 +15465,7 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>802</v>
@@ -15501,7 +15501,7 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="27" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B268" s="27" t="s">
         <v>804</v>
@@ -15537,7 +15537,7 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="27" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B269" s="27" t="s">
         <v>806</v>
@@ -15573,7 +15573,7 @@
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>808</v>
@@ -15609,7 +15609,7 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>810</v>
@@ -15645,7 +15645,7 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>812</v>
@@ -15681,7 +15681,7 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>814</v>
@@ -15717,7 +15717,7 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>816</v>
@@ -15753,7 +15753,7 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B275" s="17" t="s">
         <v>818</v>
@@ -15789,7 +15789,7 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>820</v>
@@ -15825,10 +15825,10 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="C277" s="11"/>
       <c r="D277" s="10"/>
@@ -15857,7 +15857,7 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>822</v>
@@ -15893,7 +15893,7 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B279" s="17" t="s">
         <v>824</v>
@@ -15929,7 +15929,7 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B280" s="34" t="s">
         <v>826</v>
@@ -15965,7 +15965,7 @@
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="10" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>814</v>
@@ -16433,7 +16433,7 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="16" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B294" s="16" t="s">
         <v>857</v>
@@ -16469,7 +16469,7 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B295" s="27" t="s">
         <v>859</v>
@@ -16505,7 +16505,7 @@
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>861</v>
@@ -16541,7 +16541,7 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B297" s="27" t="s">
         <v>863</v>
@@ -16577,10 +16577,10 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B298" s="27" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="C298" s="11">
         <v>87.0</v>
@@ -16613,7 +16613,7 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B299" s="27" t="s">
         <v>866</v>
@@ -16649,7 +16649,7 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B300" s="27" t="s">
         <v>868</v>
@@ -16685,7 +16685,7 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B301" s="27" t="s">
         <v>870</v>
@@ -16721,7 +16721,7 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B302" s="27" t="s">
         <v>872</v>
@@ -16757,7 +16757,7 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B303" s="36" t="s">
         <v>874</v>
@@ -16793,7 +16793,7 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B304" s="27" t="s">
         <v>876</v>
@@ -16829,7 +16829,7 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B305" s="27" t="s">
         <v>878</v>
@@ -16865,7 +16865,7 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B306" s="27" t="s">
         <v>879</v>
@@ -16901,7 +16901,7 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B307" s="27" t="s">
         <v>880</v>
@@ -16937,7 +16937,7 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B308" s="27" t="s">
         <v>881</v>
@@ -16973,10 +16973,10 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="27" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B309" s="27" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="C309" s="11">
         <v>83.0</v>
@@ -17009,7 +17009,7 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="36" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B310" s="36" t="s">
         <v>884</v>
@@ -17045,7 +17045,7 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>886</v>
@@ -17081,7 +17081,7 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>888</v>
@@ -17117,7 +17117,7 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B313" s="26" t="s">
         <v>890</v>
@@ -17153,7 +17153,7 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B314" s="26" t="s">
         <v>892</v>
@@ -17189,7 +17189,7 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B315" s="26" t="s">
         <v>894</v>
@@ -17225,7 +17225,7 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B316" s="65" t="s">
         <v>896</v>
@@ -17261,7 +17261,7 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B317" s="17" t="s">
         <v>898</v>
@@ -17297,7 +17297,7 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B318" s="17" t="s">
         <v>900</v>
@@ -17333,7 +17333,7 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>902</v>
@@ -17369,7 +17369,7 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B320" s="17" t="s">
         <v>904</v>
@@ -17405,7 +17405,7 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>906</v>
@@ -17441,7 +17441,7 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="10" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>908</v>
@@ -17837,7 +17837,7 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="16" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B333" s="16" t="s">
         <v>932</v>
@@ -17873,7 +17873,7 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B334" s="26" t="s">
         <v>934</v>
@@ -17909,7 +17909,7 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B335" s="17" t="s">
         <v>936</v>
@@ -17945,7 +17945,7 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B336" s="10" t="s">
         <v>938</v>
@@ -17981,7 +17981,7 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="27" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B337" s="58" t="s">
         <v>940</v>
@@ -18017,7 +18017,7 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B338" s="17" t="s">
         <v>942</v>
@@ -18053,7 +18053,7 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B339" s="34" t="s">
         <v>944</v>
@@ -18089,7 +18089,7 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B340" s="26" t="s">
         <v>946</v>
@@ -18125,7 +18125,7 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>948</v>
@@ -18161,7 +18161,7 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>950</v>
@@ -18197,7 +18197,7 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B343" s="10" t="s">
         <v>952</v>
@@ -18233,7 +18233,7 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="27" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B344" s="58" t="s">
         <v>954</v>
@@ -18269,7 +18269,7 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="27" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B345" s="27" t="s">
         <v>956</v>
@@ -19176,7 +19176,7 @@
       <c r="D370" s="10" t="s">
         <v>1012</v>
       </c>
-      <c r="E370" s="18"/>
+      <c r="E370" s="19"/>
       <c r="F370" s="14"/>
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
@@ -19212,7 +19212,7 @@
       <c r="D371" s="10" t="s">
         <v>1014</v>
       </c>
-      <c r="E371" s="18"/>
+      <c r="E371" s="19"/>
       <c r="F371" s="8"/>
       <c r="G371" s="8"/>
       <c r="H371" s="8"/>
@@ -19704,10 +19704,10 @@
       <c r="Z384" s="14"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="21" t="s">
+      <c r="A385" s="22" t="s">
         <v>1042</v>
       </c>
-      <c r="B385" s="21" t="s">
+      <c r="B385" s="22" t="s">
         <v>1047</v>
       </c>
       <c r="C385" s="11">
@@ -20064,7 +20064,7 @@
       <c r="Z394" s="8"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="18" t="s">
+      <c r="A395" s="19" t="s">
         <v>1065</v>
       </c>
       <c r="B395" s="10" t="s">
@@ -20101,7 +20101,7 @@
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>1072</v>
@@ -20137,7 +20137,7 @@
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>1074</v>
@@ -20425,7 +20425,7 @@
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="74" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="B405" s="27" t="s">
         <v>1095</v>
@@ -20461,7 +20461,7 @@
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="26" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>1097</v>
@@ -20605,7 +20605,7 @@
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="10" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>1107</v>
@@ -20641,7 +20641,7 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="10" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>1109</v>
@@ -20677,7 +20677,7 @@
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="10" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>1111</v>
@@ -21001,7 +21001,7 @@
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="10" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B421" s="10" t="s">
         <v>1131</v>
@@ -21793,7 +21793,7 @@
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="10" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B443" s="78" t="s">
         <v>1177</v>
@@ -21829,7 +21829,7 @@
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="10" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>1179</v>
@@ -21865,7 +21865,7 @@
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="10" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B445" s="10" t="s">
         <v>1181</v>
@@ -22261,7 +22261,7 @@
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>1208</v>
@@ -22609,7 +22609,7 @@
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="36" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B466" s="36" t="s">
         <v>1227</v>
@@ -22645,7 +22645,7 @@
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>1229</v>
@@ -22681,7 +22681,7 @@
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>1231</v>
@@ -22717,7 +22717,7 @@
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>1233</v>
@@ -22753,7 +22753,7 @@
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>1235</v>
@@ -22789,7 +22789,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>1237</v>
@@ -22825,7 +22825,7 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>1239</v>
@@ -22861,7 +22861,7 @@
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>1241</v>
@@ -22897,7 +22897,7 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="10" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>1243</v>
@@ -22968,7 +22968,7 @@
       <c r="Z475" s="14"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="18" t="s">
+      <c r="A476" s="19" t="s">
         <v>1248</v>
       </c>
       <c r="B476" s="17" t="s">
@@ -23401,7 +23401,7 @@
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="10" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="B488" s="17" t="s">
         <v>1277</v>
@@ -23475,7 +23475,7 @@
       <c r="A490" s="10" t="s">
         <v>1279</v>
       </c>
-      <c r="B490" s="18" t="s">
+      <c r="B490" s="19" t="s">
         <v>1282</v>
       </c>
       <c r="C490" s="11">
@@ -23508,41 +23508,41 @@
       <c r="Z490" s="14"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="21" t="s">
-        <v>497</v>
-      </c>
-      <c r="B491" s="21" t="s">
+      <c r="A491" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="B491" s="22" t="s">
         <v>1284</v>
       </c>
       <c r="C491" s="11">
         <v>86.0</v>
       </c>
-      <c r="D491" s="21" t="s">
+      <c r="D491" s="22" t="s">
         <v>1285</v>
       </c>
       <c r="E491" s="45" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="F491" s="10"/>
       <c r="G491" s="46"/>
-      <c r="H491" s="18"/>
-      <c r="I491" s="18"/>
-      <c r="J491" s="18"/>
-      <c r="K491" s="18"/>
-      <c r="L491" s="18"/>
-      <c r="M491" s="18"/>
-      <c r="N491" s="18"/>
-      <c r="O491" s="18"/>
-      <c r="P491" s="18"/>
-      <c r="Q491" s="18"/>
-      <c r="R491" s="18"/>
-      <c r="S491" s="18"/>
-      <c r="T491" s="18"/>
-      <c r="U491" s="18"/>
-      <c r="V491" s="18"/>
-      <c r="W491" s="18"/>
-      <c r="X491" s="18"/>
-      <c r="Y491" s="18"/>
+      <c r="H491" s="19"/>
+      <c r="I491" s="19"/>
+      <c r="J491" s="19"/>
+      <c r="K491" s="19"/>
+      <c r="L491" s="19"/>
+      <c r="M491" s="19"/>
+      <c r="N491" s="19"/>
+      <c r="O491" s="19"/>
+      <c r="P491" s="19"/>
+      <c r="Q491" s="19"/>
+      <c r="R491" s="19"/>
+      <c r="S491" s="19"/>
+      <c r="T491" s="19"/>
+      <c r="U491" s="19"/>
+      <c r="V491" s="19"/>
+      <c r="W491" s="19"/>
+      <c r="X491" s="19"/>
+      <c r="Y491" s="19"/>
       <c r="Z491" s="8"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
@@ -23657,49 +23657,49 @@
       <c r="A495" s="10" t="s">
         <v>1289</v>
       </c>
-      <c r="B495" s="21" t="s">
+      <c r="B495" s="22" t="s">
         <v>1294</v>
       </c>
       <c r="C495" s="11">
         <v>79.0</v>
       </c>
-      <c r="D495" s="21" t="s">
+      <c r="D495" s="22" t="s">
         <v>1295</v>
       </c>
       <c r="E495" s="80"/>
       <c r="F495" s="10"/>
       <c r="G495" s="46"/>
-      <c r="H495" s="18"/>
-      <c r="I495" s="18"/>
-      <c r="J495" s="18"/>
-      <c r="K495" s="18"/>
-      <c r="L495" s="18"/>
-      <c r="M495" s="18"/>
-      <c r="N495" s="18"/>
-      <c r="O495" s="18"/>
-      <c r="P495" s="18"/>
-      <c r="Q495" s="18"/>
-      <c r="R495" s="18"/>
-      <c r="S495" s="18"/>
-      <c r="T495" s="18"/>
-      <c r="U495" s="18"/>
-      <c r="V495" s="18"/>
-      <c r="W495" s="18"/>
-      <c r="X495" s="18"/>
-      <c r="Y495" s="18"/>
+      <c r="H495" s="19"/>
+      <c r="I495" s="19"/>
+      <c r="J495" s="19"/>
+      <c r="K495" s="19"/>
+      <c r="L495" s="19"/>
+      <c r="M495" s="19"/>
+      <c r="N495" s="19"/>
+      <c r="O495" s="19"/>
+      <c r="P495" s="19"/>
+      <c r="Q495" s="19"/>
+      <c r="R495" s="19"/>
+      <c r="S495" s="19"/>
+      <c r="T495" s="19"/>
+      <c r="U495" s="19"/>
+      <c r="V495" s="19"/>
+      <c r="W495" s="19"/>
+      <c r="X495" s="19"/>
+      <c r="Y495" s="19"/>
       <c r="Z495" s="8"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B496" s="21" t="s">
+      <c r="A496" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B496" s="22" t="s">
         <v>1296</v>
       </c>
       <c r="C496" s="11">
         <v>84.0</v>
       </c>
-      <c r="D496" s="21" t="s">
+      <c r="D496" s="22" t="s">
         <v>1297</v>
       </c>
       <c r="E496" s="80" t="s">
@@ -23707,24 +23707,24 @@
       </c>
       <c r="F496" s="10"/>
       <c r="G496" s="46"/>
-      <c r="H496" s="18"/>
-      <c r="I496" s="18"/>
-      <c r="J496" s="18"/>
-      <c r="K496" s="18"/>
-      <c r="L496" s="18"/>
-      <c r="M496" s="18"/>
-      <c r="N496" s="18"/>
-      <c r="O496" s="18"/>
-      <c r="P496" s="18"/>
-      <c r="Q496" s="18"/>
-      <c r="R496" s="18"/>
-      <c r="S496" s="18"/>
-      <c r="T496" s="18"/>
-      <c r="U496" s="18"/>
-      <c r="V496" s="18"/>
-      <c r="W496" s="18"/>
-      <c r="X496" s="18"/>
-      <c r="Y496" s="18"/>
+      <c r="H496" s="19"/>
+      <c r="I496" s="19"/>
+      <c r="J496" s="19"/>
+      <c r="K496" s="19"/>
+      <c r="L496" s="19"/>
+      <c r="M496" s="19"/>
+      <c r="N496" s="19"/>
+      <c r="O496" s="19"/>
+      <c r="P496" s="19"/>
+      <c r="Q496" s="19"/>
+      <c r="R496" s="19"/>
+      <c r="S496" s="19"/>
+      <c r="T496" s="19"/>
+      <c r="U496" s="19"/>
+      <c r="V496" s="19"/>
+      <c r="W496" s="19"/>
+      <c r="X496" s="19"/>
+      <c r="Y496" s="19"/>
       <c r="Z496" s="8"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
@@ -24548,7 +24548,7 @@
       <c r="Z519" s="14"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="18" t="s">
+      <c r="A520" s="19" t="s">
         <v>1325</v>
       </c>
       <c r="B520" s="17" t="s">
@@ -24897,7 +24897,7 @@
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="10" t="s">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="B530" s="10" t="s">
         <v>1367</v>
@@ -24933,7 +24933,7 @@
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="27" t="s">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="B531" s="27" t="s">
         <v>1369</v>
@@ -25149,7 +25149,7 @@
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="27" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B537" s="36" t="s">
         <v>1382</v>
@@ -25185,7 +25185,7 @@
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="27" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B538" s="36" t="s">
         <v>1384</v>
@@ -25221,7 +25221,7 @@
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="27" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B539" s="36" t="s">
         <v>1386</v>
@@ -25257,7 +25257,7 @@
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="27" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B540" s="36" t="s">
         <v>1388</v>
@@ -25293,7 +25293,7 @@
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="8" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B541" s="36" t="s">
         <v>1390</v>
@@ -25329,7 +25329,7 @@
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="27" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B542" s="36" t="s">
         <v>1392</v>
@@ -25365,7 +25365,7 @@
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="8" t="s">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="B543" s="27" t="s">
         <v>1394</v>
@@ -25400,8 +25400,8 @@
       <c r="Z543" s="8"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="18" t="s">
-        <v>396</v>
+      <c r="A544" s="19" t="s">
+        <v>354</v>
       </c>
       <c r="B544" s="10" t="s">
         <v>1396</v>
@@ -25436,8 +25436,8 @@
       <c r="Z544" s="14"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="18" t="s">
-        <v>396</v>
+      <c r="A545" s="19" t="s">
+        <v>354</v>
       </c>
       <c r="B545" s="10" t="s">
         <v>1398</v>
@@ -25581,7 +25581,7 @@
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="29" t="s">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="B549" s="10" t="s">
         <v>1408</v>
@@ -25869,7 +25869,7 @@
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="85" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="B557" s="27" t="s">
         <v>1426</v>
@@ -26013,7 +26013,7 @@
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="10" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
       <c r="B561" s="10" t="s">
         <v>1435</v>
@@ -26049,7 +26049,7 @@
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="10" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>1013</v>
@@ -26198,8 +26198,8 @@
       <c r="B566" s="88" t="s">
         <v>1447</v>
       </c>
-      <c r="C566" s="20"/>
-      <c r="D566" s="21" t="s">
+      <c r="C566" s="21"/>
+      <c r="D566" s="22" t="s">
         <v>1448</v>
       </c>
       <c r="E566" s="23"/>
@@ -27019,7 +27019,7 @@
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="10" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="B589" s="17" t="s">
         <v>1506</v>
@@ -27055,7 +27055,7 @@
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="10" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="B590" s="17" t="s">
         <v>1508</v>
@@ -27091,7 +27091,7 @@
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="59" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="B591" s="59" t="s">
         <v>1510</v>
@@ -27127,7 +27127,7 @@
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="10" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="B592" s="10" t="s">
         <v>1512</v>
@@ -27271,7 +27271,7 @@
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="31" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="B596" s="26" t="s">
         <v>1522</v>
@@ -27459,7 +27459,7 @@
       <c r="C601" s="11">
         <v>83.0</v>
       </c>
-      <c r="D601" s="18" t="s">
+      <c r="D601" s="19" t="s">
         <v>1534</v>
       </c>
       <c r="E601" s="26"/>
@@ -27523,7 +27523,7 @@
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="10" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B603" s="26" t="s">
         <v>1537</v>
@@ -27559,7 +27559,7 @@
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="10" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B604" s="26" t="s">
         <v>1539</v>
@@ -27595,7 +27595,7 @@
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="10" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>1541</v>
@@ -27631,7 +27631,7 @@
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="10" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B606" s="65" t="s">
         <v>1543</v>
@@ -27667,7 +27667,7 @@
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="10" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B607" s="10" t="s">
         <v>1545</v>
@@ -27678,7 +27678,7 @@
       <c r="D607" s="10" t="s">
         <v>1546</v>
       </c>
-      <c r="E607" s="18"/>
+      <c r="E607" s="19"/>
       <c r="F607" s="14"/>
       <c r="G607" s="14"/>
       <c r="H607" s="14"/>
@@ -27702,54 +27702,54 @@
       <c r="Z607" s="14"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="21" t="s">
+      <c r="A608" s="22" t="s">
         <v>1547</v>
       </c>
-      <c r="B608" s="21" t="s">
+      <c r="B608" s="22" t="s">
         <v>1548</v>
       </c>
       <c r="C608" s="11">
         <v>78.0</v>
       </c>
-      <c r="D608" s="21" t="s">
+      <c r="D608" s="22" t="s">
         <v>1549</v>
       </c>
       <c r="E608" s="89" t="s">
         <v>1298</v>
       </c>
-      <c r="F608" s="18"/>
-      <c r="G608" s="18"/>
-      <c r="H608" s="18"/>
-      <c r="I608" s="18"/>
-      <c r="J608" s="18"/>
-      <c r="K608" s="18"/>
-      <c r="L608" s="18"/>
-      <c r="M608" s="18"/>
-      <c r="N608" s="18"/>
-      <c r="O608" s="18"/>
-      <c r="P608" s="18"/>
-      <c r="Q608" s="18"/>
-      <c r="R608" s="18"/>
-      <c r="S608" s="18"/>
-      <c r="T608" s="18"/>
-      <c r="U608" s="18"/>
-      <c r="V608" s="18"/>
-      <c r="W608" s="18"/>
-      <c r="X608" s="18"/>
-      <c r="Y608" s="18"/>
+      <c r="F608" s="19"/>
+      <c r="G608" s="19"/>
+      <c r="H608" s="19"/>
+      <c r="I608" s="19"/>
+      <c r="J608" s="19"/>
+      <c r="K608" s="19"/>
+      <c r="L608" s="19"/>
+      <c r="M608" s="19"/>
+      <c r="N608" s="19"/>
+      <c r="O608" s="19"/>
+      <c r="P608" s="19"/>
+      <c r="Q608" s="19"/>
+      <c r="R608" s="19"/>
+      <c r="S608" s="19"/>
+      <c r="T608" s="19"/>
+      <c r="U608" s="19"/>
+      <c r="V608" s="19"/>
+      <c r="W608" s="19"/>
+      <c r="X608" s="19"/>
+      <c r="Y608" s="19"/>
       <c r="Z608" s="8"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="19" t="s">
+      <c r="A609" s="20" t="s">
         <v>1550</v>
       </c>
-      <c r="B609" s="19" t="s">
+      <c r="B609" s="20" t="s">
         <v>1551</v>
       </c>
-      <c r="C609" s="20">
+      <c r="C609" s="21">
         <v>84.0</v>
       </c>
-      <c r="D609" s="21" t="s">
+      <c r="D609" s="22" t="s">
         <v>1552</v>
       </c>
       <c r="E609" s="23"/>
@@ -27812,52 +27812,52 @@
       <c r="Z610" s="14"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="B611" s="21" t="s">
+      <c r="A611" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="B611" s="22" t="s">
         <v>1555</v>
       </c>
       <c r="C611" s="11">
         <v>92.0</v>
       </c>
-      <c r="D611" s="21" t="s">
+      <c r="D611" s="22" t="s">
         <v>1556</v>
       </c>
       <c r="E611" s="80"/>
       <c r="F611" s="10"/>
       <c r="G611" s="46"/>
-      <c r="H611" s="18"/>
-      <c r="I611" s="18"/>
-      <c r="J611" s="18"/>
-      <c r="K611" s="18"/>
-      <c r="L611" s="18"/>
-      <c r="M611" s="18"/>
-      <c r="N611" s="18"/>
-      <c r="O611" s="18"/>
-      <c r="P611" s="18"/>
-      <c r="Q611" s="18"/>
-      <c r="R611" s="18"/>
-      <c r="S611" s="18"/>
-      <c r="T611" s="18"/>
-      <c r="U611" s="18"/>
-      <c r="V611" s="18"/>
-      <c r="W611" s="18"/>
-      <c r="X611" s="18"/>
-      <c r="Y611" s="18"/>
+      <c r="H611" s="19"/>
+      <c r="I611" s="19"/>
+      <c r="J611" s="19"/>
+      <c r="K611" s="19"/>
+      <c r="L611" s="19"/>
+      <c r="M611" s="19"/>
+      <c r="N611" s="19"/>
+      <c r="O611" s="19"/>
+      <c r="P611" s="19"/>
+      <c r="Q611" s="19"/>
+      <c r="R611" s="19"/>
+      <c r="S611" s="19"/>
+      <c r="T611" s="19"/>
+      <c r="U611" s="19"/>
+      <c r="V611" s="19"/>
+      <c r="W611" s="19"/>
+      <c r="X611" s="19"/>
+      <c r="Y611" s="19"/>
       <c r="Z611" s="8"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B612" s="21" t="s">
+      <c r="A612" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B612" s="22" t="s">
         <v>1557</v>
       </c>
       <c r="C612" s="11">
         <v>80.0</v>
       </c>
-      <c r="D612" s="21" t="s">
+      <c r="D612" s="22" t="s">
         <v>1558</v>
       </c>
       <c r="E612" s="80" t="s">
@@ -27865,24 +27865,24 @@
       </c>
       <c r="F612" s="10"/>
       <c r="G612" s="46"/>
-      <c r="H612" s="18"/>
-      <c r="I612" s="18"/>
-      <c r="J612" s="18"/>
-      <c r="K612" s="18"/>
-      <c r="L612" s="18"/>
-      <c r="M612" s="18"/>
-      <c r="N612" s="18"/>
-      <c r="O612" s="18"/>
-      <c r="P612" s="18"/>
-      <c r="Q612" s="18"/>
-      <c r="R612" s="18"/>
-      <c r="S612" s="18"/>
-      <c r="T612" s="18"/>
-      <c r="U612" s="18"/>
-      <c r="V612" s="18"/>
-      <c r="W612" s="18"/>
-      <c r="X612" s="18"/>
-      <c r="Y612" s="18"/>
+      <c r="H612" s="19"/>
+      <c r="I612" s="19"/>
+      <c r="J612" s="19"/>
+      <c r="K612" s="19"/>
+      <c r="L612" s="19"/>
+      <c r="M612" s="19"/>
+      <c r="N612" s="19"/>
+      <c r="O612" s="19"/>
+      <c r="P612" s="19"/>
+      <c r="Q612" s="19"/>
+      <c r="R612" s="19"/>
+      <c r="S612" s="19"/>
+      <c r="T612" s="19"/>
+      <c r="U612" s="19"/>
+      <c r="V612" s="19"/>
+      <c r="W612" s="19"/>
+      <c r="X612" s="19"/>
+      <c r="Y612" s="19"/>
       <c r="Z612" s="8"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
@@ -28138,7 +28138,7 @@
       <c r="Z619" s="8"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="18" t="s">
+      <c r="A620" s="19" t="s">
         <v>1569</v>
       </c>
       <c r="B620" s="10" t="s">
@@ -30161,7 +30161,7 @@
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="10" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B676" s="10" t="s">
         <v>1694</v>
@@ -30197,7 +30197,7 @@
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="27" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="B677" s="27" t="s">
         <v>1696</v>
@@ -30232,16 +30232,16 @@
       <c r="Z677" s="8"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="B678" s="19" t="s">
+      <c r="A678" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="B678" s="20" t="s">
         <v>1698</v>
       </c>
-      <c r="C678" s="20">
+      <c r="C678" s="21">
         <v>84.0</v>
       </c>
-      <c r="D678" s="21" t="s">
+      <c r="D678" s="22" t="s">
         <v>1699</v>
       </c>
       <c r="E678" s="23"/>
@@ -30268,8 +30268,8 @@
       <c r="Z678" s="5"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="19" t="s">
-        <v>228</v>
+      <c r="A679" s="20" t="s">
+        <v>201</v>
       </c>
       <c r="B679" s="27" t="s">
         <v>1700</v>
@@ -30377,7 +30377,7 @@
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="10" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="B682" s="10" t="s">
         <v>1707</v>
@@ -30413,7 +30413,7 @@
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="10" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="B683" s="17" t="s">
         <v>1709</v>
@@ -30449,7 +30449,7 @@
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="75" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B684" s="10" t="s">
         <v>1711</v>
@@ -30485,7 +30485,7 @@
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="10" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B685" s="34" t="s">
         <v>1713</v>
@@ -30521,7 +30521,7 @@
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="10" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B686" s="10" t="s">
         <v>1715</v>
@@ -30773,7 +30773,7 @@
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B693" s="27" t="s">
         <v>1732</v>
@@ -30809,7 +30809,7 @@
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B694" s="27" t="s">
         <v>1734</v>
@@ -30845,7 +30845,7 @@
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B695" s="27" t="s">
         <v>1736</v>
@@ -30881,7 +30881,7 @@
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B696" s="27" t="s">
         <v>1738</v>
@@ -30917,7 +30917,7 @@
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B697" s="27" t="s">
         <v>1740</v>
@@ -30953,7 +30953,7 @@
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B698" s="27" t="s">
         <v>1742</v>
@@ -30989,7 +30989,7 @@
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="27" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B699" s="27" t="s">
         <v>1744</v>
@@ -31025,7 +31025,7 @@
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="10" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B700" s="10" t="s">
         <v>1746</v>
@@ -31061,7 +31061,7 @@
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="49" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B701" s="49" t="s">
         <v>1748</v>
@@ -31131,13 +31131,13 @@
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="94" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B703" s="94" t="s">
         <v>1752</v>
       </c>
       <c r="C703" s="11"/>
-      <c r="D703" s="21" t="s">
+      <c r="D703" s="22" t="s">
         <v>1753</v>
       </c>
       <c r="E703" s="80" t="s">
@@ -31145,24 +31145,24 @@
       </c>
       <c r="F703" s="10"/>
       <c r="G703" s="46"/>
-      <c r="H703" s="18"/>
-      <c r="I703" s="18"/>
-      <c r="J703" s="18"/>
-      <c r="K703" s="18"/>
-      <c r="L703" s="18"/>
-      <c r="M703" s="18"/>
-      <c r="N703" s="18"/>
-      <c r="O703" s="18"/>
-      <c r="P703" s="18"/>
-      <c r="Q703" s="18"/>
-      <c r="R703" s="18"/>
-      <c r="S703" s="18"/>
-      <c r="T703" s="18"/>
-      <c r="U703" s="18"/>
-      <c r="V703" s="18"/>
-      <c r="W703" s="18"/>
-      <c r="X703" s="18"/>
-      <c r="Y703" s="18"/>
+      <c r="H703" s="19"/>
+      <c r="I703" s="19"/>
+      <c r="J703" s="19"/>
+      <c r="K703" s="19"/>
+      <c r="L703" s="19"/>
+      <c r="M703" s="19"/>
+      <c r="N703" s="19"/>
+      <c r="O703" s="19"/>
+      <c r="P703" s="19"/>
+      <c r="Q703" s="19"/>
+      <c r="R703" s="19"/>
+      <c r="S703" s="19"/>
+      <c r="T703" s="19"/>
+      <c r="U703" s="19"/>
+      <c r="V703" s="19"/>
+      <c r="W703" s="19"/>
+      <c r="X703" s="19"/>
+      <c r="Y703" s="19"/>
       <c r="Z703" s="8"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
@@ -31554,10 +31554,10 @@
       <c r="Z714" s="8"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="19" t="s">
+      <c r="A715" s="20" t="s">
         <v>1774</v>
       </c>
-      <c r="B715" s="19" t="s">
+      <c r="B715" s="20" t="s">
         <v>1775</v>
       </c>
       <c r="C715" s="95">
@@ -38014,14 +38014,14 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="3"/>
+      <c r="Y1" s="4"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -38084,10 +38084,10 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -38117,19 +38117,19 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -38154,19 +38154,19 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>37</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -38191,19 +38191,19 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -38228,19 +38228,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>70</v>
+        <v>56</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -38265,15 +38265,15 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -38298,15 +38298,15 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -38331,15 +38331,15 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -38364,19 +38364,19 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>97</v>
+        <v>85</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -38401,15 +38401,15 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -38434,10 +38434,10 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -38465,19 +38465,19 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>119</v>
+        <v>101</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -38502,15 +38502,15 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -38535,19 +38535,19 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>138</v>
+        <v>34</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -38572,19 +38572,19 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -38609,19 +38609,19 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>168</v>
+        <v>143</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -38646,19 +38646,19 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>183</v>
+        <v>155</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>158</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -38683,19 +38683,19 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -38720,19 +38720,19 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>204</v>
+        <v>85</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>174</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -38757,19 +38757,19 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -38793,19 +38793,19 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -38830,19 +38830,19 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -38867,15 +38867,15 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -38900,7 +38900,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -38929,19 +38929,19 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -38966,15 +38966,15 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -38999,19 +38999,19 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>248</v>
+        <v>143</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>225</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -39036,15 +39036,15 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -39069,10 +39069,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -39100,15 +39100,15 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -39133,19 +39133,19 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>277</v>
+        <v>247</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -39170,10 +39170,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -39201,19 +39201,19 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>294</v>
+        <v>259</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>261</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -39238,19 +39238,19 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>309</v>
+        <v>275</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>276</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -39275,19 +39275,19 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>323</v>
+        <v>275</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -39312,16 +39312,16 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>337</v>
+        <v>298</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>339</v>
+        <v>275</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>299</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -39347,19 +39347,19 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>355</v>
+        <v>311</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>312</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -39384,19 +39384,19 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>368</v>
+        <v>329</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>369</v>
+        <v>34</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>330</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>379</v>
+        <v>338</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -39421,15 +39421,15 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -39454,19 +39454,19 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -39491,19 +39491,19 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -39528,19 +39528,19 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>397</v>
+        <v>356</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -39565,15 +39565,15 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>401</v>
+        <v>362</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -39598,15 +39598,15 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>404</v>
+        <v>365</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -39631,19 +39631,19 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="5" t="s">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>411</v>
+        <v>375</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -39668,19 +39668,19 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>416</v>
+        <v>379</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -39705,16 +39705,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>421</v>
+        <v>382</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>422</v>
+        <v>34</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>383</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -39740,15 +39740,15 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -39773,15 +39773,15 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -39806,15 +39806,15 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>441</v>
+        <v>399</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>443</v>
+        <v>400</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -39839,19 +39839,19 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>445</v>
+        <v>404</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>448</v>
+        <v>143</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>406</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -39876,19 +39876,19 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>457</v>
+        <v>417</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>459</v>
+        <v>34</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -39913,19 +39913,19 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>466</v>
+        <v>143</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>431</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -39950,15 +39950,15 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -39983,19 +39983,19 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>473</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>474</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -40020,19 +40020,19 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>477</v>
+        <v>85</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>463</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -40057,15 +40057,15 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -40090,19 +40090,19 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>481</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>482</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>483</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -40127,19 +40127,19 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="18" t="s">
         <v>487</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -40164,15 +40164,15 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -40197,19 +40197,19 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -40234,10 +40234,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -40265,19 +40265,19 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>499</v>
+        <v>311</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>509</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -40302,15 +40302,15 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -40335,15 +40335,15 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -40368,19 +40368,19 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>508</v>
+        <v>85</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>528</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -40405,19 +40405,19 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>512</v>
+        <v>85</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>538</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -40445,16 +40445,16 @@
         <v>26</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -40479,19 +40479,19 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -40516,19 +40516,19 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>531</v>
+        <v>550</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>551</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -40553,19 +40553,19 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -40590,16 +40590,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>549</v>
+        <v>34</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>567</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -40625,16 +40625,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="5" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="22" t="s">
-        <v>557</v>
+        <v>34</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>578</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
@@ -40659,11 +40659,11 @@
       <c r="Y76" s="8"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="B77" s="52" t="s">
-        <v>560</v>
+      <c r="A77" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B77" s="54" t="s">
+        <v>590</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>

--- a/data/FRAGRANCES.xlsx
+++ b/data/FRAGRANCES.xlsx
@@ -53,48 +53,48 @@
     <t>Not carried by any of the 12 retailers checked.</t>
   </si>
   <si>
+    <t>Ajmal</t>
+  </si>
+  <si>
+    <t>Verde</t>
+  </si>
+  <si>
+    <t>Brand carried by Scent Split and The Perfumed Court, this one not.</t>
+  </si>
+  <si>
+    <t>American Perfumer</t>
+  </si>
+  <si>
+    <t>Black Walnut</t>
+  </si>
+  <si>
+    <t>House brand of the Chicago shop. Buy direct.</t>
+  </si>
+  <si>
     <t>19-69</t>
   </si>
   <si>
-    <t>Ajmal</t>
-  </si>
-  <si>
-    <t>Verde</t>
+    <t>Akro</t>
   </si>
   <si>
     <t>Miami Blue</t>
   </si>
   <si>
-    <t>Brand carried by Scent Split and The Perfumed Court, this one not.</t>
+    <t>Ink</t>
+  </si>
+  <si>
+    <t>Bloom Perfumery</t>
+  </si>
+  <si>
+    <t>https://bloomperfume.co.uk/products/ink</t>
   </si>
   <si>
     <t xml:space="preserve">Disappointing, smells nothing like cocaine </t>
   </si>
   <si>
-    <t>American Perfumer</t>
-  </si>
-  <si>
-    <t>Black Walnut</t>
-  </si>
-  <si>
-    <t>House brand of the Chicago shop. Buy direct.</t>
-  </si>
-  <si>
-    <t>Akro</t>
-  </si>
-  <si>
-    <t>Ink</t>
-  </si>
-  <si>
-    <t>Bloom Perfumery</t>
-  </si>
-  <si>
     <t>Acqua di Parma</t>
   </si>
   <si>
-    <t>https://bloomperfume.co.uk/products/ink</t>
-  </si>
-  <si>
     <t>Rosa Nobile</t>
   </si>
   <si>
@@ -119,19 +119,34 @@
     <t>Café Tabac</t>
   </si>
   <si>
+    <t xml:space="preserve">Tobacco shop, Ybor City, keeps going </t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharp rhubarb, loved at first but got less appealing the more I wore </t>
+  </si>
+  <si>
+    <t>Sueño Latino</t>
+  </si>
+  <si>
     <t>Spelled Akro. Ministry of Scent sample sold out.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tobacco shop, Ybor City, keeps going </t>
-  </si>
-  <si>
-    <t>Signature</t>
+    <t>Peppers, then sweet fruit, maybe too powdery later. Kinda basic.</t>
+  </si>
+  <si>
+    <t>Aesop</t>
   </si>
   <si>
     <t>Astier de Villatte</t>
   </si>
   <si>
-    <t xml:space="preserve">Sharp rhubarb, loved at first but got less appealing the more I wore </t>
+    <t>Hwyl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Way too smoky </t>
   </si>
   <si>
     <t>Mantes La Jolie</t>
@@ -143,21 +158,6 @@
     <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
   </si>
   <si>
-    <t>Sueño Latino</t>
-  </si>
-  <si>
-    <t>Peppers, then sweet fruit, maybe too powdery later. Kinda basic.</t>
-  </si>
-  <si>
-    <t>Aesop</t>
-  </si>
-  <si>
-    <t>Hwyl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Way too smoky </t>
-  </si>
-  <si>
     <t>Agar Olfactory</t>
   </si>
   <si>
@@ -173,13 +173,25 @@
     <t xml:space="preserve">Duplicative realistic earth and wet </t>
   </si>
   <si>
+    <t>Cereale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?? Toothpaste </t>
+  </si>
+  <si>
+    <t>Matsu Musk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncooked grocery store button mushrooms </t>
+  </si>
+  <si>
     <t>Price shows when you select the size, usually $5-10.</t>
   </si>
   <si>
-    <t>Cereale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">?? Toothpaste </t>
+    <t>Rushlight</t>
+  </si>
+  <si>
+    <t>Yellow floral, really compelling, honeycomb and honesuckle, kinda Moon Bloom, stinks a lot but I like the stink</t>
   </si>
   <si>
     <t>Azzaro</t>
@@ -188,30 +200,18 @@
     <t>Azzaro pour Homme</t>
   </si>
   <si>
-    <t>Matsu Musk</t>
-  </si>
-  <si>
     <t>The Perfumed Court</t>
   </si>
   <si>
-    <t xml:space="preserve">Uncooked grocery store button mushrooms </t>
+    <t>Amouage</t>
+  </si>
+  <si>
+    <t>Beach Hut Man</t>
   </si>
   <si>
     <t>https://theperfumedcourt.com</t>
   </si>
   <si>
-    <t>Rushlight</t>
-  </si>
-  <si>
-    <t>Yellow floral, really compelling, honeycomb and honesuckle, kinda Moon Bloom, stinks a lot but I like the stink</t>
-  </si>
-  <si>
-    <t>Amouage</t>
-  </si>
-  <si>
-    <t>Beach Hut Man</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mint forward, has kind of a gross cantaloupe vibe. </t>
   </si>
   <si>
@@ -239,6 +239,12 @@
     <t>Cheapest sample on the list.</t>
   </si>
   <si>
+    <t>Brioche</t>
+  </si>
+  <si>
+    <t>Bread and bran, sweet honey, a nice and not gourmand fragrance</t>
+  </si>
+  <si>
     <t>Bvlgari</t>
   </si>
   <si>
@@ -251,12 +257,6 @@
     <t>https://mapleprime.com/products/bvlgari-rose-goldea-blossom-delight-eau-de-parfum-for-women</t>
   </si>
   <si>
-    <t>Brioche</t>
-  </si>
-  <si>
-    <t>Bread and bran, sweet honey, a nice and not gourmand fragrance</t>
-  </si>
-  <si>
     <t>Andrea Maack</t>
   </si>
   <si>
@@ -281,40 +281,46 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>All three decant sizes out of stock. Re-check.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lemon cookie for some reason but some pencil shavings </t>
   </si>
   <si>
-    <t>All three decant sizes out of stock. Re-check.</t>
+    <t>Caron</t>
+  </si>
+  <si>
+    <t>Coup de Fouet</t>
   </si>
   <si>
     <t>Ceramic</t>
   </si>
   <si>
-    <t>Caron</t>
+    <t>Vintage market only.</t>
   </si>
   <si>
     <t xml:space="preserve">Powder and nice but hits a truck stop soap after a minute </t>
   </si>
   <si>
-    <t>Coup de Fouet</t>
-  </si>
-  <si>
-    <t>Vintage market only.</t>
-  </si>
-  <si>
     <t>Tauer Perfumes</t>
   </si>
   <si>
+    <t>Poivre</t>
+  </si>
+  <si>
     <t>L'Air des Alpes Suisses</t>
   </si>
   <si>
+    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
+  </si>
+  <si>
     <t>Bleh I don't like this dude I will die on this hill</t>
   </si>
   <si>
-    <t>Poivre</t>
-  </si>
-  <si>
-    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
+    <t>Chanel</t>
+  </si>
+  <si>
+    <t>No. 19</t>
   </si>
   <si>
     <t>Sundowner</t>
@@ -323,36 +329,30 @@
     <t>Scrubber. Chocolate note disgusted me</t>
   </si>
   <si>
-    <t>Chanel</t>
-  </si>
-  <si>
-    <t>No. 19</t>
-  </si>
-  <si>
     <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
   </si>
   <si>
+    <t>Coach</t>
+  </si>
+  <si>
+    <t>Coach Green</t>
+  </si>
+  <si>
     <t>L'Air du Désert Marocain</t>
   </si>
   <si>
+    <t>DecantX</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wanted to love, didn't </t>
   </si>
   <si>
-    <t>Coach</t>
-  </si>
-  <si>
-    <t>Coach Green</t>
-  </si>
-  <si>
-    <t>DecantX</t>
+    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
   </si>
   <si>
     <t>Sandalo</t>
   </si>
   <si>
-    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cheap soap started great but then muddy cleaning product, huge bummer </t>
   </si>
   <si>
@@ -377,16 +377,25 @@
     <t xml:space="preserve">Too sweet kinda gay nah </t>
   </si>
   <si>
+    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+  </si>
+  <si>
     <t>Armani Privé</t>
   </si>
   <si>
     <t>Rose Alexandrie</t>
   </si>
   <si>
+    <t>Comme des Garçons</t>
+  </si>
+  <si>
+    <t>Series 2 Red: Carnation</t>
+  </si>
+  <si>
     <t>Grape soda</t>
   </si>
   <si>
-    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+    <t>Discontinued Red series. Vintage market.</t>
   </si>
   <si>
     <t>Rose Milano</t>
@@ -395,19 +404,25 @@
     <t xml:space="preserve">Simple and duplicative but rare I like it at this degree </t>
   </si>
   <si>
-    <t>Comme des Garçons</t>
+    <t>Dolce &amp; Gabbana</t>
+  </si>
+  <si>
+    <t>D&amp;G Anthology L'Amoureux 6</t>
   </si>
   <si>
     <t>Rose d'Arabie</t>
   </si>
   <si>
-    <t>Series 2 Red: Carnation</t>
-  </si>
-  <si>
     <t xml:space="preserve">A great rose but not my favorite. Deep. </t>
   </si>
   <si>
-    <t>Discontinued Red series. Vintage market.</t>
+    <t>DSH Perfumes</t>
+  </si>
+  <si>
+    <t>Rubis Rose</t>
+  </si>
+  <si>
+    <t>https://www.dshperfumes.com</t>
   </si>
   <si>
     <t>Musc Shamal</t>
@@ -416,33 +431,18 @@
     <t xml:space="preserve">Slightly more interesting than a plain musk, tips a bit sweet resin </t>
   </si>
   <si>
-    <t>Dolce &amp; Gabbana</t>
-  </si>
-  <si>
-    <t>D&amp;G Anthology L'Amoureux 6</t>
-  </si>
-  <si>
     <t>Cuir Nu</t>
   </si>
   <si>
     <t xml:space="preserve">Insane </t>
   </si>
   <si>
-    <t>DSH Perfumes</t>
-  </si>
-  <si>
-    <t>Rubis Rose</t>
-  </si>
-  <si>
     <t>Rouge Malachite</t>
   </si>
   <si>
     <t xml:space="preserve">Gourmand </t>
   </si>
   <si>
-    <t>https://www.dshperfumes.com</t>
-  </si>
-  <si>
     <t>Pivoine Suzhou</t>
   </si>
   <si>
@@ -455,19 +455,37 @@
     <t xml:space="preserve">Shouldn't like this, neroli and plain orange, but it's got something special </t>
   </si>
   <si>
+    <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
+  </si>
+  <si>
     <t>Jasmin Kusamono</t>
   </si>
   <si>
     <t xml:space="preserve">Plain non-indolic jasmine, lovely basic floral </t>
   </si>
   <si>
+    <t>Ensar Oud</t>
+  </si>
+  <si>
+    <t>Japanese Red Rose oil</t>
+  </si>
+  <si>
+    <t>Sells direct only.</t>
+  </si>
+  <si>
     <t>Thé Yulong</t>
   </si>
   <si>
     <t>Same old tea</t>
   </si>
   <si>
-    <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
+    <t>Eris Parfums</t>
+  </si>
+  <si>
+    <t>Green Spell</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
   </si>
   <si>
     <t>Santal Dan Sha</t>
@@ -482,36 +500,18 @@
     <t xml:space="preserve">Tuberose? Tube much. </t>
   </si>
   <si>
-    <t>Ensar Oud</t>
-  </si>
-  <si>
-    <t>Japanese Red Rose oil</t>
-  </si>
-  <si>
-    <t>Sells direct only.</t>
-  </si>
-  <si>
     <t>Bleu Lazuli</t>
   </si>
   <si>
     <t xml:space="preserve">Not at all </t>
   </si>
   <si>
-    <t>Eris Parfums</t>
-  </si>
-  <si>
-    <t>Green Spell</t>
-  </si>
-  <si>
     <t>Bois d'Encens</t>
   </si>
   <si>
     <t xml:space="preserve">Starts promising, ends nice basic wood </t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
-  </si>
-  <si>
     <t>Arquiste</t>
   </si>
   <si>
@@ -521,6 +521,9 @@
     <t>Salty and oily, olive and trees? Need to try again, maybe don't like the dry down</t>
   </si>
   <si>
+    <t>Indigo Perfumery has the 50ml bottle.</t>
+  </si>
+  <si>
     <t>Astrophil &amp; Stella</t>
   </si>
   <si>
@@ -530,6 +533,18 @@
     <t xml:space="preserve">Tuberose and magnolia, or green tea and plum. Optical illusion for noses. </t>
   </si>
   <si>
+    <t>Floris</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>Scent Split</t>
+  </si>
+  <si>
+    <t>https://scentsplit.com</t>
+  </si>
+  <si>
     <t>Chloé Atelier des Fleurs</t>
   </si>
   <si>
@@ -557,9 +572,6 @@
     <t>I love this. It's a lot and kinda wears me, but very good green.</t>
   </si>
   <si>
-    <t>Indigo Perfumery has the 50ml bottle.</t>
-  </si>
-  <si>
     <t>Baruti</t>
   </si>
   <si>
@@ -569,51 +581,39 @@
     <t xml:space="preserve">Wow, metallic and starched shirts. No reason to wear it but very cool. </t>
   </si>
   <si>
-    <t>Floris</t>
-  </si>
-  <si>
-    <t>Elite</t>
-  </si>
-  <si>
-    <t>Scent Split</t>
-  </si>
-  <si>
-    <t>https://scentsplit.com</t>
+    <t>DecantX sample sold out.</t>
   </si>
   <si>
     <t>BeauFort London</t>
   </si>
   <si>
+    <t>Goutal</t>
+  </si>
+  <si>
     <t>Fathom V</t>
   </si>
   <si>
+    <t>Gardenia Passion</t>
+  </si>
+  <si>
     <t xml:space="preserve">Probably a no. Eirik says vase water. Cumin? </t>
   </si>
   <si>
+    <t>Parfums Raffy</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
+  </si>
+  <si>
     <t>The Grudge</t>
   </si>
   <si>
     <t>Billie Eilish</t>
   </si>
   <si>
-    <t>DecantX sample sold out.</t>
-  </si>
-  <si>
     <t>Eilish No. 2</t>
   </si>
   <si>
-    <t>Goutal</t>
-  </si>
-  <si>
-    <t>Gardenia Passion</t>
-  </si>
-  <si>
-    <t>Parfums Raffy</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
-  </si>
-  <si>
     <t xml:space="preserve">Opened great, weird middle, interesting end. Worth another visit. </t>
   </si>
   <si>
@@ -626,12 +626,24 @@
     <t>Yeesh. I think it's very well crafted but 2 MUCH</t>
   </si>
   <si>
+    <t>Listed, out of stock. Re-check.</t>
+  </si>
+  <si>
     <t>Mango Yuzu Gasoline</t>
   </si>
   <si>
     <t>Points for realism and saying what it is, but too strong on all counts</t>
   </si>
   <si>
+    <t>Un Matin d'Orage</t>
+  </si>
+  <si>
+    <t>DecantX / Maple Prime</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
+  </si>
+  <si>
     <t>Boka</t>
   </si>
   <si>
@@ -641,24 +653,12 @@
     <t>Great zesty citrus opening but goes away immediately</t>
   </si>
   <si>
-    <t>Listed, out of stock. Re-check.</t>
-  </si>
-  <si>
     <t>Živeli</t>
   </si>
   <si>
     <t>Absolute scrubber omG</t>
   </si>
   <si>
-    <t>Un Matin d'Orage</t>
-  </si>
-  <si>
-    <t>DecantX / Maple Prime</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
-  </si>
-  <si>
     <t>Bon Parfumeur</t>
   </si>
   <si>
@@ -668,45 +668,51 @@
     <t xml:space="preserve">A similar thing I don't like from something else idk </t>
   </si>
   <si>
+    <t>Decants listed at both, sold out at both.</t>
+  </si>
+  <si>
     <t>BORNTOSTANDOUT</t>
   </si>
   <si>
     <t>Naked Laundry</t>
   </si>
   <si>
+    <t>Guerlain</t>
+  </si>
+  <si>
     <t xml:space="preserve">Organic cherry cough drop </t>
   </si>
   <si>
+    <t>Cuir Intense</t>
+  </si>
+  <si>
+    <t>DecantX has 2ml at $8.79.</t>
+  </si>
+  <si>
     <t>Dirty Rice</t>
   </si>
   <si>
     <t>Neither dirty nor rice</t>
   </si>
   <si>
+    <t>Santal Pao Rosa</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
+  </si>
+  <si>
     <t>Warm Air</t>
   </si>
   <si>
     <t xml:space="preserve">Thought it was good but NO! </t>
   </si>
   <si>
-    <t>Decants listed at both, sold out at both.</t>
-  </si>
-  <si>
     <t>Nanatopia</t>
   </si>
   <si>
     <t>Banana bread no thank you</t>
   </si>
   <si>
-    <t>Guerlain</t>
-  </si>
-  <si>
-    <t>Cuir Intense</t>
-  </si>
-  <si>
-    <t>DecantX has 2ml at $8.79.</t>
-  </si>
-  <si>
     <t>Bortnikoff</t>
   </si>
   <si>
@@ -716,7 +722,7 @@
     <t xml:space="preserve">Oh wow, the blue toothpaste I used as a child </t>
   </si>
   <si>
-    <t>Santal Pao Rosa</t>
+    <t>Only source found.</t>
   </si>
   <si>
     <t>Boy Smells</t>
@@ -725,24 +731,33 @@
     <t>Rose Load</t>
   </si>
   <si>
-    <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
-  </si>
-  <si>
     <t xml:space="preserve">Another rose, nice green but sour </t>
   </si>
   <si>
+    <t>Jasmin Grandiflorum Extrait 30</t>
+  </si>
+  <si>
+    <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
+  </si>
+  <si>
     <t>Gyan</t>
   </si>
   <si>
     <t xml:space="preserve">Very not my normal thing but I'm really digging it thus far. </t>
   </si>
   <si>
+    <t>Eau de Guerlain</t>
+  </si>
+  <si>
     <t>Le Gemme Tygar</t>
   </si>
   <si>
     <t>Wow. Crazy grapefruit opening, deep ambroxan base, lasts forever. Maybe too beast but really compelling, I want to try all of them</t>
   </si>
   <si>
+    <t>A vintage version is also listed at $6.99, likely the one you want.</t>
+  </si>
+  <si>
     <t>Kilian</t>
   </si>
   <si>
@@ -752,46 +767,58 @@
     <t>Smells like Nestea to me but Eirik loves it</t>
   </si>
   <si>
+    <t>Hermès</t>
+  </si>
+  <si>
+    <t>Hermessence Poivre Samarcande</t>
+  </si>
+  <si>
+    <t>Perfumeniche has the full bottle.</t>
+  </si>
+  <si>
     <t>Kologne, Shield of Protection</t>
   </si>
   <si>
-    <t>Only source found.</t>
+    <t>Universal Flowering</t>
   </si>
   <si>
     <t>Not remembering why it was a no, but it was a no</t>
   </si>
   <si>
-    <t>Jasmin Grandiflorum Extrait 30</t>
-  </si>
-  <si>
-    <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
+    <t>Holy Hell</t>
+  </si>
+  <si>
+    <t>Sells direct.</t>
+  </si>
+  <si>
+    <t>(note row)</t>
   </si>
   <si>
     <t>L'Heure Verte</t>
   </si>
   <si>
-    <t>Eau de Guerlain</t>
-  </si>
-  <si>
     <t xml:space="preserve">No idea what people are saying with absinthe and licorice. It smells fine, dna of that Angel's Share sweetness. </t>
   </si>
   <si>
-    <t>A vintage version is also listed at $6.99, likely the one you want.</t>
+    <t>Isabelle Larignon</t>
+  </si>
+  <si>
+    <t>Le Flocon de Johann K</t>
+  </si>
+  <si>
+    <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
   </si>
   <si>
     <t>Roses on Ice</t>
   </si>
   <si>
-    <t>Hermès</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ozonic cucumber, so strange. Maybe smells like cheap body spray but I don't know, I like smelling it.  </t>
   </si>
   <si>
-    <t>Hermessence Poivre Samarcande</t>
-  </si>
-  <si>
-    <t>Perfumeniche has the full bottle.</t>
+    <t>J.F. Schwarzlose Berlin</t>
+  </si>
+  <si>
+    <t>Trance</t>
   </si>
   <si>
     <t>Rolling in Love</t>
@@ -800,13 +827,7 @@
     <t>Almond, nice, too sweet to wear</t>
   </si>
   <si>
-    <t>Universal Flowering</t>
-  </si>
-  <si>
-    <t>Holy Hell</t>
-  </si>
-  <si>
-    <t>Sells direct.</t>
+    <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
   </si>
   <si>
     <t>Byredo</t>
@@ -815,55 +836,37 @@
     <t>Casablanca Lily</t>
   </si>
   <si>
+    <t>Joop</t>
+  </si>
+  <si>
     <t>Floral and HONEY this is irresistable</t>
   </si>
   <si>
-    <t>(note row)</t>
+    <t>Homme Absolute</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com</t>
   </si>
   <si>
     <t>La Tulipe</t>
   </si>
   <si>
-    <t>Isabelle Larignon</t>
-  </si>
-  <si>
     <t xml:space="preserve">A familiar flower I've never smelled before, surprised I love this </t>
   </si>
   <si>
-    <t>Le Flocon de Johann K</t>
-  </si>
-  <si>
-    <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
-  </si>
-  <si>
     <t>Open Sky</t>
   </si>
   <si>
     <t xml:space="preserve">Pot and pomelo, addictive </t>
   </si>
   <si>
-    <t>J.F. Schwarzlose Berlin</t>
-  </si>
-  <si>
-    <t>Trance</t>
-  </si>
-  <si>
-    <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
-  </si>
-  <si>
     <t>Cuir Obscur</t>
   </si>
   <si>
     <t>Amaretto to rose and leather, probably many like it but I'm into this combination</t>
   </si>
   <si>
-    <t>Joop</t>
-  </si>
-  <si>
-    <t>Homme Absolute</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com</t>
+    <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
   </si>
   <si>
     <t>Mojave Ghost</t>
@@ -872,162 +875,159 @@
     <t xml:space="preserve">Subtle as to be almost indistinguishable, but nice? Not getting the hype but might try the candle or something. </t>
   </si>
   <si>
+    <t>L'Occitane</t>
+  </si>
+  <si>
+    <t>Eau du Val (Magnolia)</t>
+  </si>
+  <si>
+    <t>Perfumed Court has Eau des Baux only.</t>
+  </si>
+  <si>
     <t>Inflorescence</t>
   </si>
   <si>
     <t xml:space="preserve">Very white floral, less babysitter than la tulipe </t>
   </si>
   <si>
+    <t>Lancôme</t>
+  </si>
+  <si>
+    <t>Cuir de Lancôme</t>
+  </si>
+  <si>
     <t>Pulp</t>
   </si>
   <si>
     <t xml:space="preserve">Don't like this fig, way too something. Coats the nose and throat </t>
   </si>
   <si>
-    <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
+    <t>Loewe</t>
+  </si>
+  <si>
+    <t>Pour Homme</t>
+  </si>
+  <si>
+    <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
   </si>
   <si>
     <t>Space Rage Travx</t>
   </si>
   <si>
-    <t>L'Occitane</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pulp again </t>
   </si>
   <si>
-    <t>Eau du Val (Magnolia)</t>
-  </si>
-  <si>
-    <t>Perfumed Court has Eau des Baux only.</t>
+    <t>Maison Margiela</t>
+  </si>
+  <si>
+    <t>(untitled)</t>
+  </si>
+  <si>
+    <t>Perfumeniche</t>
+  </si>
+  <si>
+    <t>https://perfumeniche.com</t>
   </si>
   <si>
     <t>Oud Immortel</t>
   </si>
   <si>
-    <t>Lancôme</t>
-  </si>
-  <si>
-    <t>Cuir de Lancôme</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dry down pretty gross. </t>
   </si>
   <si>
-    <t>Loewe</t>
-  </si>
-  <si>
-    <t>Pour Homme</t>
-  </si>
-  <si>
-    <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
-  </si>
-  <si>
     <t>Young Rose</t>
   </si>
   <si>
     <t xml:space="preserve">Insane citrus blast, very bad </t>
   </si>
   <si>
-    <t>Maison Margiela</t>
-  </si>
-  <si>
-    <t>(untitled)</t>
-  </si>
-  <si>
-    <t>Perfumeniche</t>
-  </si>
-  <si>
-    <t>https://perfumeniche.com</t>
-  </si>
-  <si>
     <t>Bal d'Afrique</t>
   </si>
   <si>
     <t xml:space="preserve">Good and interesting but hits me as pineapple and coconut so no </t>
   </si>
   <si>
+    <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
+  </si>
+  <si>
     <t>Desert Dawn</t>
   </si>
   <si>
     <t xml:space="preserve">Boring powdery sandalwood </t>
   </si>
   <si>
+    <t>Marc Jacobs</t>
+  </si>
+  <si>
+    <t>Bang</t>
+  </si>
+  <si>
     <t>Gypsy Water</t>
   </si>
   <si>
     <t xml:space="preserve">Lemon creamsicle, utterly gone after 15 mins </t>
   </si>
   <si>
-    <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
+    <t>Maya Njie</t>
+  </si>
+  <si>
+    <t>Nordic Cedar</t>
   </si>
   <si>
     <t>Blanche</t>
   </si>
   <si>
-    <t>Marc Jacobs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fabric softener </t>
   </si>
   <si>
-    <t>Bang</t>
+    <t>https://mayanjie.com/products/discovery-set</t>
   </si>
   <si>
     <t>Pour Un Homme de Caron</t>
   </si>
   <si>
-    <t>Maya Njie</t>
-  </si>
-  <si>
-    <t>Nordic Cedar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beautiful lavender Fougeres, more subtle than Lav Extreme, dumb reach </t>
   </si>
   <si>
-    <t>https://mayanjie.com/products/discovery-set</t>
-  </si>
-  <si>
     <t>Yatagan</t>
   </si>
   <si>
     <t>Like Un Homme but more animalic</t>
   </si>
   <si>
+    <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
+  </si>
+  <si>
     <t>Tabac Blond</t>
   </si>
   <si>
     <t xml:space="preserve">Not for me, Grandma Doris, but great on Eirik </t>
   </si>
   <si>
+    <t>Miller Harris</t>
+  </si>
+  <si>
+    <t>Le Cèdre</t>
+  </si>
+  <si>
+    <t>Miller Harris direct</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
+  </si>
+  <si>
     <t>Tabac Noir</t>
   </si>
   <si>
     <t>Sweet</t>
   </si>
   <si>
-    <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
-  </si>
-  <si>
     <t>Pour Un Homme de Caron Le Matin</t>
   </si>
   <si>
     <t xml:space="preserve">Boring but nice freshie </t>
   </si>
   <si>
-    <t>Miller Harris</t>
-  </si>
-  <si>
-    <t>Le Cèdre</t>
-  </si>
-  <si>
-    <t>Miller Harris direct</t>
-  </si>
-  <si>
-    <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
-  </si>
-  <si>
     <t>Pour Un Homme de Caron Le Soir</t>
   </si>
   <si>
@@ -1049,13 +1049,19 @@
     <t xml:space="preserve">Pure floral, old lady but not powdery. I like it! </t>
   </si>
   <si>
+    <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
+  </si>
+  <si>
     <t>Rose</t>
   </si>
   <si>
     <t>Classic, linear, I really like florals from this house but not a standout rose</t>
   </si>
   <si>
-    <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
+    <t>Wander Through the Parks</t>
+  </si>
+  <si>
+    <t>https://www.millerharris.com</t>
   </si>
   <si>
     <t>Jockey Club</t>
@@ -1064,30 +1070,33 @@
     <t xml:space="preserve">JFK all the way, dumb reach, def has that old person thing in a good way but ultimately too much </t>
   </si>
   <si>
-    <t>Wander Through the Parks</t>
-  </si>
-  <si>
     <t>Number Six</t>
   </si>
   <si>
-    <t>https://www.millerharris.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simple old man + lemon, but nice enough. Weak. </t>
   </si>
   <si>
     <t>Almond</t>
   </si>
   <si>
+    <t>50ml sold out, no sample listing.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Probably fine but I barely smell it </t>
   </si>
   <si>
     <t>Marem</t>
   </si>
   <si>
+    <t>Feuilles de Tabac</t>
+  </si>
+  <si>
     <t xml:space="preserve">Red currant, citrus and rose. Not sure what I think. </t>
   </si>
   <si>
+    <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
+  </si>
+  <si>
     <t>CB I Hate Perfume</t>
   </si>
   <si>
@@ -1097,21 +1106,12 @@
     <t xml:space="preserve">Love this dirt and sunshine </t>
   </si>
   <si>
-    <t>50ml sold out, no sample listing.</t>
-  </si>
-  <si>
     <t>A Room with a View</t>
   </si>
   <si>
     <t xml:space="preserve">Very intriguing, try the non water extrait. Soapy. </t>
   </si>
   <si>
-    <t>Feuilles de Tabac</t>
-  </si>
-  <si>
-    <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
-  </si>
-  <si>
     <t>At the Beach 1966</t>
   </si>
   <si>
@@ -1124,33 +1124,33 @@
     <t xml:space="preserve">Probably very good but I've smelled too many similar dirt and rain and moss ones </t>
   </si>
   <si>
+    <t>Montale</t>
+  </si>
+  <si>
     <t>In the Library</t>
   </si>
   <si>
+    <t>Intense Pepper</t>
+  </si>
+  <si>
+    <t>Twisted Lily</t>
+  </si>
+  <si>
     <t xml:space="preserve">Can't smell nothin, doesn't smell like a library tho </t>
   </si>
   <si>
+    <t>https://twistedlily.com/products/intense-pepper-sample</t>
+  </si>
+  <si>
     <t>Boy</t>
   </si>
   <si>
     <t>As beautiful and complex and wearable as I could hope, not too feminine but still real Chanel</t>
   </si>
   <si>
-    <t>Montale</t>
-  </si>
-  <si>
-    <t>Intense Pepper</t>
-  </si>
-  <si>
-    <t>Twisted Lily</t>
-  </si>
-  <si>
     <t>Paris – Paris</t>
   </si>
   <si>
-    <t>https://twistedlily.com/products/intense-pepper-sample</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nice rose </t>
   </si>
   <si>
@@ -1163,19 +1163,22 @@
     <t>Sycomore</t>
   </si>
   <si>
+    <t>DecantX and Maple Prime have no sample in stock.</t>
+  </si>
+  <si>
     <t>31 Rue Cambon</t>
   </si>
   <si>
+    <t>Prissana</t>
+  </si>
+  <si>
+    <t>Nefer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apparently a masterpiece. Giving it too many chances. It's diaper and sour underneath all the great stuff I smell. Drydown is better. </t>
   </si>
   <si>
-    <t>DecantX and Maple Prime have no sample in stock.</t>
-  </si>
-  <si>
-    <t>Prissana</t>
-  </si>
-  <si>
-    <t>Nefer</t>
+    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
   </si>
   <si>
     <t>Coromandel</t>
@@ -1184,9 +1187,6 @@
     <t xml:space="preserve">Magic </t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
-  </si>
-  <si>
     <t>1957</t>
   </si>
   <si>
@@ -1211,129 +1211,129 @@
     <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
   </si>
   <si>
+    <t>Weeping Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dastardly. Nice for a literal minute then gross amber maple syrup </t>
+  </si>
+  <si>
     <t>Nest</t>
   </si>
   <si>
-    <t>Weeping Rose</t>
-  </si>
-  <si>
     <t>Black Tulip</t>
   </si>
   <si>
-    <t xml:space="preserve">Dastardly. Nice for a literal minute then gross amber maple syrup </t>
+    <t>Chloé</t>
+  </si>
+  <si>
+    <t>Rose Tangerine</t>
   </si>
   <si>
     <t>Olfactive Studio</t>
   </si>
   <si>
+    <t xml:space="preserve">Sparkly and bright and rose, it's good. I think I like Chloe in general. </t>
+  </si>
+  <si>
     <t>Flash Back</t>
   </si>
   <si>
-    <t>Chloé</t>
-  </si>
-  <si>
-    <t>Rose Tangerine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sparkly and bright and rose, it's good. I think I like Chloe in general. </t>
-  </si>
-  <si>
     <t>Listed as Flashback in New York.</t>
   </si>
   <si>
+    <t>Sous les Pins</t>
+  </si>
+  <si>
+    <t>Something underneath that I hate</t>
+  </si>
+  <si>
     <t>One Day</t>
   </si>
   <si>
     <t>Taipei</t>
   </si>
   <si>
-    <t>Sous les Pins</t>
-  </si>
-  <si>
-    <t>Something underneath that I hate</t>
-  </si>
-  <si>
     <t>Ministry of Scent sample sold out.</t>
   </si>
   <si>
     <t>Chloé Eau de Parfum</t>
   </si>
   <si>
+    <t xml:space="preserve">So classic and good, not old lady, easy to wear but very feminine </t>
+  </si>
+  <si>
     <t>Ormonde Jayne</t>
   </si>
   <si>
-    <t xml:space="preserve">So classic and good, not old lady, easy to wear but very feminine </t>
-  </si>
-  <si>
     <t>Montabaco Intensivo</t>
   </si>
   <si>
+    <t>Clue Perfumery</t>
+  </si>
+  <si>
+    <t>Dandelion Butter</t>
+  </si>
+  <si>
     <t>Bloom has standard Montabaco at $10, not Intensivo.</t>
   </si>
   <si>
-    <t>Clue Perfumery</t>
-  </si>
-  <si>
-    <t>Dandelion Butter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Weeds with fat, as advertised. It's really nice. Doesn't last long. </t>
   </si>
   <si>
+    <t>Amy</t>
+  </si>
+  <si>
     <t>Paco Rabanne</t>
   </si>
   <si>
     <t>Maple Prime has full bottles from $38.99, no small size anywhere.</t>
   </si>
   <si>
-    <t>Amy</t>
+    <t>Morel Map</t>
   </si>
   <si>
     <t>Duplicate of the row above.</t>
   </si>
   <si>
+    <t xml:space="preserve">Damp mossy forest floor, beautiful </t>
+  </si>
+  <si>
     <t>Papillon Artisan</t>
   </si>
   <si>
-    <t>Morel Map</t>
-  </si>
-  <si>
     <t>Tobacco Rose</t>
   </si>
   <si>
-    <t xml:space="preserve">Damp mossy forest floor, beautiful </t>
+    <t>Warm Bulb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I like it but I don't love it on. More of a novelty. </t>
   </si>
   <si>
     <t>Perfumed Court $10.94. Papillon's own site sells full bottles only.</t>
   </si>
   <si>
-    <t>Warm Bulb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I like it but I don't love it on. More of a novelty. </t>
-  </si>
-  <si>
     <t>Parfumerie Particulière</t>
   </si>
   <si>
     <t>Black Tar</t>
   </si>
   <si>
+    <t>With the Candlestick</t>
+  </si>
+  <si>
     <t>Ministry of Scent has 2ml at $7.00.</t>
   </si>
   <si>
+    <t>Bad candy? Clumsy</t>
+  </si>
+  <si>
     <t>Penhaligon's</t>
   </si>
   <si>
-    <t>With the Candlestick</t>
-  </si>
-  <si>
     <t>Blenheim Bouquet</t>
   </si>
   <si>
-    <t>Bad candy? Clumsy</t>
-  </si>
-  <si>
     <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
   </si>
   <si>
@@ -1355,12 +1355,12 @@
     <t>Serpentine</t>
   </si>
   <si>
+    <t>Nice! Probably duplicative but I could wear this.</t>
+  </si>
+  <si>
     <t>Liquid Love</t>
   </si>
   <si>
-    <t>Nice! Probably duplicative but I could wear this.</t>
-  </si>
-  <si>
     <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
   </si>
   <si>
@@ -1373,16 +1373,22 @@
     <t>Their own site would not load when I tried.</t>
   </si>
   <si>
+    <t>Amazingreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not a favorite. </t>
+  </si>
+  <si>
     <t>Ierofante</t>
   </si>
   <si>
     <t>Worth confirming the spelling.</t>
   </si>
   <si>
-    <t>Amazingreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not a favorite. </t>
+    <t>Incense: Kyoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Really good, light and airy but incense. Wood but maybe the immortelle changes it? Could be a bottle. </t>
   </si>
   <si>
     <t>Robert Piguet</t>
@@ -1394,12 +1400,6 @@
     <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
   </si>
   <si>
-    <t>Incense: Kyoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Really good, light and airy but incense. Wood but maybe the immortelle changes it? Could be a bottle. </t>
-  </si>
-  <si>
     <t>Vaquera: Classique Perdu</t>
   </si>
   <si>
@@ -1412,43 +1412,55 @@
     <t xml:space="preserve">Citrus, then warm spice. Clove? I shouldn't like this but it feels like an easy summer splash on cologne that isn't basic </t>
   </si>
   <si>
+    <t>Ganja</t>
+  </si>
+  <si>
+    <t>I liked it then didn't then did then didn't then DID!</t>
+  </si>
+  <si>
     <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
   </si>
   <si>
+    <t>Odeur 10</t>
+  </si>
+  <si>
+    <t>Like a row of washing machines in action. Metal, clean, not detergent but very soapy, don't want to wear but very good</t>
+  </si>
+  <si>
     <t>Rogue Perfumery</t>
   </si>
   <si>
     <t>(discovery set)</t>
   </si>
   <si>
-    <t>Ganja</t>
-  </si>
-  <si>
-    <t>I liked it then didn't then did then didn't then DID!</t>
-  </si>
-  <si>
     <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
   </si>
   <si>
-    <t>Odeur 10</t>
-  </si>
-  <si>
-    <t>Like a row of washing machines in action. Metal, clean, not detergent but very soapy, don't want to wear but very good</t>
-  </si>
-  <si>
     <t>Monocle Scent Four: Yoyogi</t>
   </si>
   <si>
     <t>Pleasant wood, just kind of a watered down Laurel</t>
   </si>
   <si>
+    <t>Dot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweet and maybe well crafted but no </t>
+  </si>
+  <si>
+    <t>Incense: Ouarzazate</t>
+  </si>
+  <si>
+    <t>Not as special as the others but a nice woody scent, dry down ends kinda sour</t>
+  </si>
+  <si>
     <t>Rogue's own discovery set is sold out and most of their line with it.</t>
   </si>
   <si>
-    <t>Dot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweet and maybe well crafted but no </t>
+    <t>Dia x Meg Webster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amber pepper wood, doesn't last for shit </t>
   </si>
   <si>
     <t>Romeo Gigli</t>
@@ -1460,31 +1472,28 @@
     <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
   </si>
   <si>
-    <t>Incense: Ouarzazate</t>
-  </si>
-  <si>
-    <t>Not as special as the others but a nice woody scent, dry down ends kinda sour</t>
-  </si>
-  <si>
-    <t>Dia x Meg Webster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber pepper wood, doesn't last for shit </t>
-  </si>
-  <si>
     <t>Incense: Zagorsk</t>
   </si>
   <si>
     <t>Not into this one</t>
   </si>
   <si>
+    <t>Artek: Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factory smells a bit. But not very interesting </t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is likely very beautiful but it is instantly a public bathroom after a cleaning. Maybe in Europe. </t>
+  </si>
+  <si>
     <t>Cheapest on the list.</t>
   </si>
   <si>
-    <t>Artek: Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factory smells a bit. But not very interesting </t>
+    <t xml:space="preserve">Photorealistic pot smell. Amazing. Absolutely not. </t>
   </si>
   <si>
     <t>Sanctuary</t>
@@ -1496,12 +1505,6 @@
     <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
   </si>
   <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is likely very beautiful but it is instantly a public bathroom after a cleaning. Maybe in Europe. </t>
-  </si>
-  <si>
     <t>Senyokô</t>
   </si>
   <si>
@@ -1511,9 +1514,6 @@
     <t>https://indigoperfumery.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Photorealistic pot smell. Amazing. Absolutely not. </t>
-  </si>
-  <si>
     <t>Incense: Jaisalmer</t>
   </si>
   <si>
@@ -1523,6 +1523,12 @@
     <t>Indigo carries the line, no samples listed.</t>
   </si>
   <si>
+    <t>Monocle Scent Two: Laurel</t>
+  </si>
+  <si>
+    <t>Wow. The wood I've not been able to find.</t>
+  </si>
+  <si>
     <t>Serge Lutens</t>
   </si>
   <si>
@@ -1532,31 +1538,34 @@
     <t>https://www.decantx.com/products/serge-lutens-poivre-noir-eau-de-parfum-unisex</t>
   </si>
   <si>
-    <t>Monocle Scent Two: Laurel</t>
-  </si>
-  <si>
-    <t>Wow. The wood I've not been able to find.</t>
-  </si>
-  <si>
     <t>Celluloid Galbanum</t>
   </si>
   <si>
     <t xml:space="preserve">Perfect white floral with a hint of Ziplock bags, not overly tuberose </t>
   </si>
   <si>
+    <t>Chlorophyll Gardenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
+  </si>
+  <si>
+    <t>Odeur 53</t>
+  </si>
+  <si>
+    <t>Mineral and clay and hot bulb, so cool</t>
+  </si>
+  <si>
     <t>Sample listed, sold out. Maple Prime has 100ml at $76.99.</t>
   </si>
   <si>
-    <t>Chlorophyll Gardenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
-  </si>
-  <si>
-    <t>Odeur 53</t>
-  </si>
-  <si>
-    <t>Mineral and clay and hot bulb, so cool</t>
+    <t>Radish Vetiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spicy, photorealistic. Maybe too odd to wear but very into it. </t>
+  </si>
+  <si>
+    <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
   </si>
   <si>
     <t>Vitriol d'Œillet</t>
@@ -1565,10 +1574,10 @@
     <t>Not at any of the three retailers that carry Serge Lutens.</t>
   </si>
   <si>
-    <t>Radish Vetiver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spicy, photorealistic. Maybe too odd to wear but very into it. </t>
+    <t>Blackpepper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black pepper for sure. Doesn't last. I'd definitely spray this on if it were around. </t>
   </si>
   <si>
     <t>Fils de Joie</t>
@@ -1577,15 +1586,6 @@
     <t>https://theperfumedcourt.com/products/serge-lutens-fils-de-joie-edp-decant-sample</t>
   </si>
   <si>
-    <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
-  </si>
-  <si>
-    <t>Blackpepper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black pepper for sure. Doesn't last. I'd definitely spray this on if it were around. </t>
-  </si>
-  <si>
     <t>Monocle Scent One: Hinoki</t>
   </si>
   <si>
@@ -1598,13 +1598,28 @@
     <t xml:space="preserve">Pleasant floral, not to special </t>
   </si>
   <si>
+    <t>Cologne: Citrico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
+  </si>
+  <si>
+    <t>Cologne: Vettiveru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So straightforward, just vetiver </t>
+  </si>
+  <si>
+    <t>Monocle Scent Five: Syros</t>
+  </si>
+  <si>
+    <t>2 much turmeric 4 me</t>
+  </si>
+  <si>
     <t>1ml is $9.99. Discontinued from the Noire collection.</t>
   </si>
   <si>
-    <t>Cologne: Citrico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
+    <t>Wonderoud</t>
   </si>
   <si>
     <t>SJP</t>
@@ -1613,31 +1628,52 @@
     <t>Stash SJP</t>
   </si>
   <si>
+    <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
+  </si>
+  <si>
     <t>MicroPerfumes / Maple Prime</t>
   </si>
   <si>
     <t>https://microperfumes.com/products/stash-edp-sample-vial</t>
   </si>
   <si>
-    <t>Cologne: Vettiveru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So straightforward, just vetiver </t>
-  </si>
-  <si>
-    <t>Monocle Scent Five: Syros</t>
-  </si>
-  <si>
-    <t>2 much turmeric 4 me</t>
+    <t>Coqui Coqui</t>
+  </si>
+  <si>
+    <t>Eucaced</t>
+  </si>
+  <si>
+    <t>Very brash eucalyptus and cedar. I like it?</t>
+  </si>
+  <si>
+    <t>Rosas Secas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tart rose but dried roses, nice! </t>
+  </si>
+  <si>
+    <t>Maderas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard to describe. Warm spice underneath </t>
+  </si>
+  <si>
+    <t>Coqui coqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice shaving cream, doesn't last </t>
   </si>
   <si>
     <t>Sample and 10ml both sold out.</t>
   </si>
   <si>
-    <t>Wonderoud</t>
-  </si>
-  <si>
-    <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
+    <t>Coty</t>
+  </si>
+  <si>
+    <t>Stetson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I think this is even better than like, Polo. It feels very complex and warm. Dumb winter reach. </t>
   </si>
   <si>
     <t>The 7 Virtues</t>
@@ -1646,16 +1682,16 @@
     <t>Vetiver Elemi</t>
   </si>
   <si>
-    <t>Coqui Coqui</t>
-  </si>
-  <si>
     <t>Perfumed Court carries the brand, only three other scents.</t>
   </si>
   <si>
-    <t>Eucaced</t>
-  </si>
-  <si>
-    <t>Very brash eucalyptus and cedar. I like it?</t>
+    <t>Creed</t>
+  </si>
+  <si>
+    <t>Original Vetiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soapy and greens and bug spray needs more time on skin but a more wearable Guerlain </t>
   </si>
   <si>
     <t>The House of Oud</t>
@@ -1664,13 +1700,19 @@
     <t>Almond Harmony</t>
   </si>
   <si>
-    <t>Rosas Secas</t>
+    <t>Silver Mountain Water</t>
   </si>
   <si>
     <t>Maple Prime has 75ml at $127.99.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tart rose but dried roses, nice! </t>
+    <t xml:space="preserve">Fine, subtle, freshie, eh </t>
+  </si>
+  <si>
+    <t>White Flowers</t>
+  </si>
+  <si>
+    <t>Weirdly bad, I don't get it</t>
   </si>
   <si>
     <t>Une Nuit Nomade</t>
@@ -1679,10 +1721,7 @@
     <t>Chemin d'Amande</t>
   </si>
   <si>
-    <t>Maderas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard to describe. Warm spice underneath </t>
+    <t>Czech &amp; Speake</t>
   </si>
   <si>
     <t>Vilhelm Parfumerie</t>
@@ -1691,55 +1730,58 @@
     <t>Fleur Burlesque</t>
   </si>
   <si>
+    <t>No. 88</t>
+  </si>
+  <si>
     <t>https://twistedlily.com/products/fleur-burlesque-sample</t>
   </si>
   <si>
-    <t>Coqui coqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice shaving cream, doesn't last </t>
-  </si>
-  <si>
-    <t>Coty</t>
-  </si>
-  <si>
-    <t>Stetson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I think this is even better than like, Polo. It feels very complex and warm. Dumb winter reach. </t>
-  </si>
-  <si>
-    <t>Creed</t>
-  </si>
-  <si>
-    <t>Original Vetiver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soapy and greens and bug spray needs more time on skin but a more wearable Guerlain </t>
+    <t>I don't get it. Supposed to be old man British, but smells like grape Nerds to me</t>
+  </si>
+  <si>
+    <t>d'Annam</t>
+  </si>
+  <si>
+    <t>In the Garden</t>
+  </si>
+  <si>
+    <t>White floral, lovely, duplicative but maybe...?</t>
+  </si>
+  <si>
+    <t>Da Lat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complex rose, liking it less the more I try it. </t>
+  </si>
+  <si>
+    <t>D'Orsay</t>
+  </si>
+  <si>
+    <t>Sweet Disruption W.T.</t>
+  </si>
+  <si>
+    <t>Too minty</t>
   </si>
   <si>
     <t>Scent Split lists it sold out.</t>
   </si>
   <si>
-    <t>Silver Mountain Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine, subtle, freshie, eh </t>
-  </si>
-  <si>
     <t>YSL</t>
   </si>
   <si>
     <t>Rive Gauche Pour Homme</t>
   </si>
   <si>
+    <t>D&amp;Scent Studios</t>
+  </si>
+  <si>
+    <t>Verdant Halo</t>
+  </si>
+  <si>
     <t>Only the women's Rive Gauche turns up.</t>
   </si>
   <si>
-    <t>White Flowers</t>
-  </si>
-  <si>
-    <t>Weirdly bad, I don't get it</t>
+    <t>Green and dry and bitter, could try again</t>
   </si>
   <si>
     <t>Kouros</t>
@@ -1748,49 +1790,55 @@
     <t>Maple Prime has 100ml at $80.99, no sample anywhere.</t>
   </si>
   <si>
+    <t>Der Duft</t>
+  </si>
+  <si>
+    <t>Cinematic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon drops, some floor cleaner </t>
+  </si>
+  <si>
     <t>Frédéric Malle</t>
   </si>
   <si>
     <t>French Lover</t>
   </si>
   <si>
-    <t>Czech &amp; Speake</t>
+    <t>Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interesting but no </t>
   </si>
   <si>
     <t>https://www.decantx.com/products/frederic-malle-french-lover-eau-de-parfum-for-men</t>
   </si>
   <si>
-    <t>No. 88</t>
-  </si>
-  <si>
-    <t>I don't get it. Supposed to be old man British, but smells like grape Nerds to me</t>
-  </si>
-  <si>
-    <t>d'Annam</t>
-  </si>
-  <si>
-    <t>In the Garden</t>
-  </si>
-  <si>
-    <t>White floral, lovely, duplicative but maybe...?</t>
-  </si>
-  <si>
-    <t>Da Lat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complex rose, liking it less the more I try it. </t>
+    <t>Match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super subtle, burnt match I guess </t>
+  </si>
+  <si>
+    <t>Dior</t>
+  </si>
+  <si>
+    <t>Thé Cachemire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tea and floral, citrus at the upfront, well crafted and I enjoy smelling it. Got better over time too. Duplicative but great. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice rose. Didn't get to wear on skin tho </t>
   </si>
   <si>
     <t>Also in your Maple Prime cart at 1.2ml for $12.99.</t>
   </si>
   <si>
-    <t>D'Orsay</t>
-  </si>
-  <si>
-    <t>Sweet Disruption W.T.</t>
-  </si>
-  <si>
-    <t>Too minty</t>
+    <t>Dune</t>
+  </si>
+  <si>
+    <t>Interesting and complex. Utlimately a bit too sweet for me but well crafted and quite nice.</t>
   </si>
   <si>
     <t>Viktor &amp; Rolf</t>
@@ -1802,31 +1850,31 @@
     <t>https://www.decantx.com/products/viktor-rolf-spicebomb-metallic-musk-eau-de-parfum-for-men</t>
   </si>
   <si>
-    <t>D&amp;Scent Studios</t>
-  </si>
-  <si>
-    <t>Verdant Halo</t>
-  </si>
-  <si>
-    <t>Green and dry and bitter, could try again</t>
-  </si>
-  <si>
-    <t>Der Duft</t>
-  </si>
-  <si>
-    <t>Cinematic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lemon drops, some floor cleaner </t>
+    <t>Jules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old fashioned and complex, I think no </t>
+  </si>
+  <si>
+    <t>Diorissimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild and bold and feminine. Not for me but really good. </t>
+  </si>
+  <si>
+    <t>Dior Addict Eau de Toilette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intriguing and layered, don't think I want to smell like it but I'm still sniffing? </t>
   </si>
   <si>
     <t>This is Viktor &amp; Rolf Spicebomb Metallic Musk.</t>
   </si>
   <si>
-    <t>Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interesting but no </t>
+    <t>Bois d'Argent</t>
+  </si>
+  <si>
+    <t>Grandma Doris' trailer</t>
   </si>
   <si>
     <t>Buongiorno</t>
@@ -1835,10 +1883,10 @@
     <t>DecantX has it at $13.29.</t>
   </si>
   <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Super subtle, burnt match I guess </t>
+    <t>Eden-Roc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquatic but I could wear it. Well made, subtle. </t>
   </si>
   <si>
     <t>Moss Cologne</t>
@@ -1847,13 +1895,10 @@
     <t>Luckyscent carries Bortnikoff too.</t>
   </si>
   <si>
-    <t>Dior</t>
-  </si>
-  <si>
-    <t>Thé Cachemire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tea and floral, citrus at the upfront, well crafted and I enjoy smelling it. Got better over time too. Duplicative but great. </t>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of them were gross </t>
   </si>
   <si>
     <t>Vanilla Black Pepper</t>
@@ -1862,46 +1907,58 @@
     <t>Ministry of Scent</t>
   </si>
   <si>
+    <t>Diptyque</t>
+  </si>
+  <si>
     <t>https://ministryofscent.com/products/vanilla-black-pepper</t>
   </si>
   <si>
-    <t xml:space="preserve">Nice rose. Didn't get to wear on skin tho </t>
-  </si>
-  <si>
-    <t>Dune</t>
-  </si>
-  <si>
-    <t>Interesting and complex. Utlimately a bit too sweet for me but well crafted and quite nice.</t>
-  </si>
-  <si>
-    <t>Jules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old fashioned and complex, I think no </t>
+    <t>Lilyphéa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too light to be higher than this, but it's so pleasant. Watery floral and stems, not a recognizable flower but really nice. </t>
+  </si>
+  <si>
+    <t>Fleur de Peau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lovely clean French soap </t>
+  </si>
+  <si>
+    <t>Eau des Sens</t>
+  </si>
+  <si>
+    <t>Lovely but absolutely not for me, very "clean girl" and maybe I hate Neroli</t>
+  </si>
+  <si>
+    <t>Tam Dao</t>
+  </si>
+  <si>
+    <t>omG peanut butter wtf, think I need to try again. Isn't this tuberose?</t>
   </si>
   <si>
     <t>Formerly Tigerlily Perfumery, San Francisco.</t>
   </si>
   <si>
-    <t>Diorissimo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wild and bold and feminine. Not for me but really good. </t>
-  </si>
-  <si>
     <t>Les Bains Guerbois</t>
   </si>
   <si>
     <t>Rose Graffiti</t>
   </si>
   <si>
+    <t>Philosykos</t>
+  </si>
+  <si>
+    <t>Juicy weird fig leaf, green, love it, maybe too coconut smell on my bod</t>
+  </si>
+  <si>
     <t>No 1ml listed for this one.</t>
   </si>
   <si>
-    <t>Dior Addict Eau de Toilette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intriguing and layered, don't think I want to smell like it but I'm still sniffing? </t>
+    <t>L’Ombre Dans L’Eau Eau de Parfum</t>
+  </si>
+  <si>
+    <t>Almost awesome? Green, roses, interesting, but just ends up muddy to me or something. But I can see why i sought it out based on reviews.</t>
   </si>
   <si>
     <t>Angelos Creations Olfactives</t>
@@ -1910,34 +1967,55 @@
     <t>Pothos</t>
   </si>
   <si>
-    <t>Bois d'Argent</t>
-  </si>
-  <si>
     <t>https://www.luckyscent.com/products/pothos-by-angelos-creations-olfactives</t>
   </si>
   <si>
-    <t>Grandma Doris' trailer</t>
-  </si>
-  <si>
-    <t>Eden-Roc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aquatic but I could wear it. Well made, subtle. </t>
-  </si>
-  <si>
-    <t>Poison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All of them were gross </t>
-  </si>
-  <si>
-    <t>Diptyque</t>
-  </si>
-  <si>
-    <t>Lilyphéa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Too light to be higher than this, but it's so pleasant. Watery floral and stems, not a recognizable flower but really nice. </t>
+    <t xml:space="preserve">That sweet shit everybody likes </t>
+  </si>
+  <si>
+    <t>Dolce&amp;Gabbana</t>
+  </si>
+  <si>
+    <t>The One for Men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meh, high school </t>
+  </si>
+  <si>
+    <t>Dries Van Noten</t>
+  </si>
+  <si>
+    <t>Raving Rose</t>
+  </si>
+  <si>
+    <t>Rose and wood, a little sharp and very nice</t>
+  </si>
+  <si>
+    <t>DS&amp;Durga</t>
+  </si>
+  <si>
+    <t>Rose Atlantic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold standard </t>
+  </si>
+  <si>
+    <t>Crush Balls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surprisingly pleasant and easy to wear. Not super special but I kept enjoying it. </t>
+  </si>
+  <si>
+    <t>Golfjazz</t>
+  </si>
+  <si>
+    <t>Really grew on me, unusual and close to Bistro and Crush Balls but I might prefer it?</t>
+  </si>
+  <si>
+    <t>Bistro Waters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green pepper, lime, oakmoss, so sharp and clean and nice </t>
   </si>
   <si>
     <t>CBCB Fragrances</t>
@@ -1949,40 +2027,37 @@
     <t>https://www.luckyscent.com/products/comrade-by-cbcb-fragrances</t>
   </si>
   <si>
-    <t>Fleur de Peau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lovely clean French soap </t>
-  </si>
-  <si>
-    <t>Eau des Sens</t>
-  </si>
-  <si>
-    <t>Lovely but absolutely not for me, very "clean girl" and maybe I hate Neroli</t>
-  </si>
-  <si>
-    <t>Tam Dao</t>
-  </si>
-  <si>
-    <t>omG peanut butter wtf, think I need to try again. Isn't this tuberose?</t>
-  </si>
-  <si>
-    <t>Philosykos</t>
-  </si>
-  <si>
-    <t>Juicy weird fig leaf, green, love it, maybe too coconut smell on my bod</t>
-  </si>
-  <si>
-    <t>L’Ombre Dans L’Eau Eau de Parfum</t>
-  </si>
-  <si>
-    <t>Almost awesome? Green, roses, interesting, but just ends up muddy to me or something. But I can see why i sought it out based on reviews.</t>
+    <t>Coriander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spicy, herbal, love it </t>
+  </si>
+  <si>
+    <t>Jazmin Yucatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmine and corn tortillas. Quite nice! </t>
+  </si>
+  <si>
+    <t>I Don't Know What</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woody subtle may be interesting when layered with a crazy floral like gardenia but not special on its own </t>
+  </si>
+  <si>
+    <t>Spectral Doorway</t>
+  </si>
+  <si>
+    <t>Pleasant enough, chalky, not very special</t>
   </si>
   <si>
     <t>Geranium Absolue</t>
   </si>
   <si>
-    <t xml:space="preserve">That sweet shit everybody likes </t>
+    <t>Black Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pineapple, black pepper, nice but not crazy special </t>
   </si>
   <si>
     <t>Granado</t>
@@ -1991,148 +2066,73 @@
     <t>Amazônico</t>
   </si>
   <si>
-    <t>Dolce&amp;Gabbana</t>
-  </si>
-  <si>
-    <t>The One for Men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meh, high school </t>
-  </si>
-  <si>
-    <t>Dries Van Noten</t>
-  </si>
-  <si>
-    <t>Raving Rose</t>
-  </si>
-  <si>
-    <t>Rose and wood, a little sharp and very nice</t>
+    <t>Grey Blazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disappointingly bland. Meant to be Grey Flannel updated. Just floral and soft and nothing. </t>
+  </si>
+  <si>
+    <t>Durga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuberose and too much cantaloupe </t>
   </si>
   <si>
     <t>Apotecário</t>
   </si>
   <si>
-    <t>DS&amp;Durga</t>
-  </si>
-  <si>
-    <t>Rose Atlantic</t>
+    <t>Rockaway Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marine, but for a lake. Not good. </t>
   </si>
   <si>
     <t>Boemia</t>
   </si>
   <si>
-    <t xml:space="preserve">Gold standard </t>
-  </si>
-  <si>
-    <t>Crush Balls</t>
+    <t>Roman Ruin Cypress</t>
+  </si>
+  <si>
+    <t>Nah</t>
   </si>
   <si>
     <t>Elixir 1870</t>
   </si>
   <si>
-    <t xml:space="preserve">Surprisingly pleasant and easy to wear. Not super special but I kept enjoying it. </t>
+    <t>Cognac Reign</t>
+  </si>
+  <si>
+    <t>Too much orris or something? Powdery and sharp over the nice cognac. Almost very good but I dont like it.</t>
   </si>
   <si>
     <t>Époque Tropical</t>
   </si>
   <si>
-    <t>Golfjazz</t>
+    <t>Sweet Do Nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoky, not me </t>
   </si>
   <si>
     <t>Esplendor</t>
   </si>
   <si>
-    <t>Really grew on me, unusual and close to Bistro and Crush Balls but I might prefer it?</t>
+    <t>Brown Flowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indolic jasmine, apparently coffee? Just kinda muddy and big.  </t>
   </si>
   <si>
     <t>Expedição</t>
   </si>
   <si>
-    <t>Bistro Waters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green pepper, lime, oakmoss, so sharp and clean and nice </t>
-  </si>
-  <si>
     <t>Infusão Botânica</t>
   </si>
   <si>
-    <t>Coriander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spicy, herbal, love it </t>
+    <t>Debaser</t>
   </si>
   <si>
     <t>Nostalgia</t>
-  </si>
-  <si>
-    <t>Jazmin Yucatan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmine and corn tortillas. Quite nice! </t>
-  </si>
-  <si>
-    <t>I Don't Know What</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woody subtle may be interesting when layered with a crazy floral like gardenia but not special on its own </t>
-  </si>
-  <si>
-    <t>Spectral Doorway</t>
-  </si>
-  <si>
-    <t>Pleasant enough, chalky, not very special</t>
-  </si>
-  <si>
-    <t>Black Magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pineapple, black pepper, nice but not crazy special </t>
-  </si>
-  <si>
-    <t>Grey Blazer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disappointingly bland. Meant to be Grey Flannel updated. Just floral and soft and nothing. </t>
-  </si>
-  <si>
-    <t>Durga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuberose and too much cantaloupe </t>
-  </si>
-  <si>
-    <t>Rockaway Beach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marine, but for a lake. Not good. </t>
-  </si>
-  <si>
-    <t>Roman Ruin Cypress</t>
-  </si>
-  <si>
-    <t>Nah</t>
-  </si>
-  <si>
-    <t>Cognac Reign</t>
-  </si>
-  <si>
-    <t>Too much orris or something? Powdery and sharp over the nice cognac. Almost very good but I dont like it.</t>
-  </si>
-  <si>
-    <t>Sweet Do Nothing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoky, not me </t>
-  </si>
-  <si>
-    <t>Brown Flowers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indolic jasmine, apparently coffee? Just kinda muddy and big.  </t>
-  </si>
-  <si>
-    <t>Debaser</t>
   </si>
   <si>
     <t>Green Rhubarb and Cane Sugar</t>
@@ -5768,12 +5768,6 @@
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -5782,6 +5776,12 @@
     </xf>
     <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -6135,16 +6135,16 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" s="11">
         <v>71.0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="12"/>
@@ -6171,7 +6171,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>27</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>29</v>
@@ -6243,7 +6243,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>31</v>
@@ -6288,7 +6288,7 @@
         <v>85.0</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="12"/>
@@ -6318,13 +6318,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="11">
         <v>80.0</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="12"/>
@@ -6354,13 +6354,13 @@
         <v>33</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C8" s="11">
         <v>70.0</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="12"/>
@@ -6387,16 +6387,16 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="11">
         <v>40.0</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="27"/>
@@ -6498,13 +6498,13 @@
         <v>48</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="11">
         <v>75.0</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="12"/>
@@ -6534,13 +6534,13 @@
         <v>48</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" s="11">
         <v>75.0</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="12"/>
@@ -6567,16 +6567,16 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C14" s="11">
         <v>90.0</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="12"/>
@@ -6603,10 +6603,10 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="C15" s="11">
         <v>40.0</v>
@@ -6639,7 +6639,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>67</v>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>69</v>
@@ -6750,13 +6750,13 @@
         <v>71</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C19" s="11">
         <v>87.0</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -6900,7 +6900,7 @@
         <v>83.0</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -6930,13 +6930,13 @@
         <v>81</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C24" s="11">
         <v>65.0</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="12"/>
@@ -6966,13 +6966,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="11">
         <v>45.0</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="27"/>
@@ -7002,13 +7002,13 @@
         <v>96</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C26" s="11">
         <v>35.0</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="27"/>
@@ -7038,13 +7038,13 @@
         <v>96</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="11">
         <v>50.0</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="12"/>
@@ -7071,10 +7071,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="11">
         <v>82.0</v>
@@ -7215,16 +7215,16 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" s="11">
         <v>83.0</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="12"/>
@@ -7251,16 +7251,16 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C33" s="11">
         <v>88.0</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="12"/>
@@ -7287,16 +7287,16 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C34" s="11">
         <v>86.0</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="12"/>
@@ -7323,16 +7323,16 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C35" s="11">
         <v>87.0</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="12"/>
@@ -7359,16 +7359,16 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C36" s="11">
         <v>60.0</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="12"/>
@@ -7395,16 +7395,16 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C37" s="11">
         <v>60.0</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="12"/>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>143</v>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B39" s="18" t="s">
         <v>145</v>
@@ -7503,16 +7503,16 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C40" s="11">
         <v>90.0</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="12"/>
@@ -7539,16 +7539,16 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C41" s="11">
         <v>82.0</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="12"/>
@@ -7575,16 +7575,16 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C42" s="11">
         <v>82.0</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="12"/>
@@ -7611,16 +7611,16 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C43" s="11">
         <v>84.0</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="12"/>
@@ -7647,16 +7647,16 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C44" s="11">
         <v>78.0</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="12"/>
@@ -7683,16 +7683,16 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C45" s="11">
         <v>87.0</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="12"/>
@@ -7755,16 +7755,16 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C47" s="11">
         <v>82.0</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="12"/>
@@ -7791,16 +7791,16 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C48" s="11">
         <v>87.0</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E48" s="10"/>
       <c r="F48" s="12"/>
@@ -7827,16 +7827,16 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C49" s="11">
         <v>60.0</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="12"/>
@@ -7863,16 +7863,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C50" s="11">
         <v>90.0</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="12"/>
@@ -7899,16 +7899,16 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="27" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C51" s="11">
         <v>88.0</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E51" s="27"/>
       <c r="F51" s="35"/>
@@ -7935,16 +7935,16 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C52" s="11">
         <v>82.0</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="27"/>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="27"/>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C54" s="11">
         <v>69.0</v>
@@ -8078,13 +8078,13 @@
         <v>201</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C56" s="11">
         <v>88.0</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E56" s="27"/>
       <c r="F56" s="27"/>
@@ -8111,16 +8111,16 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="27" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C57" s="11">
         <v>87.0</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E57" s="27"/>
       <c r="F57" s="27"/>
@@ -8147,16 +8147,16 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="27" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C58" s="37">
         <v>40.0</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E58" s="27"/>
       <c r="F58" s="27"/>
@@ -8219,16 +8219,16 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C60" s="11">
         <v>50.0</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E60" s="10"/>
       <c r="F60" s="12"/>
@@ -8255,16 +8255,16 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C61" s="11">
         <v>40.0</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E61" s="17"/>
       <c r="F61" s="12"/>
@@ -8291,16 +8291,16 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C62" s="11">
         <v>40.0</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E62" s="10"/>
       <c r="F62" s="12"/>
@@ -8327,16 +8327,16 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C63" s="20">
         <v>40.0</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E63" s="22"/>
       <c r="F63" s="23"/>
@@ -8363,16 +8363,16 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C64" s="11">
         <v>65.0</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E64" s="10"/>
       <c r="F64" s="12"/>
@@ -8399,16 +8399,16 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C65" s="11">
         <v>85.0</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
@@ -8435,16 +8435,16 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C66" s="11">
         <v>88.0</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E66" s="10"/>
       <c r="F66" s="12"/>
@@ -8471,16 +8471,16 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C67" s="11">
         <v>88.0</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
@@ -8507,16 +8507,16 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C68" s="11">
         <v>50.0</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="12"/>
@@ -8543,16 +8543,16 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C69" s="40">
         <v>50.0</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="41"/>
@@ -8579,16 +8579,16 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C70" s="11">
         <v>50.0</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E70" s="10"/>
       <c r="F70" s="12"/>
@@ -8615,16 +8615,16 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C71" s="11">
         <v>84.0</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="12"/>
@@ -8651,16 +8651,16 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C72" s="11">
         <v>60.0</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="12"/>
@@ -8687,16 +8687,16 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="16" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C73" s="11">
         <v>99.0</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="12"/>
@@ -8723,16 +8723,16 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C74" s="11">
         <v>90.0</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="12"/>
@@ -8759,16 +8759,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C75" s="11">
         <v>89.0</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E75" s="17"/>
       <c r="F75" s="12"/>
@@ -8795,16 +8795,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C76" s="11">
         <v>86.0</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E76" s="10"/>
       <c r="F76" s="12"/>
@@ -8831,16 +8831,16 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C77" s="11">
         <v>84.0</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E77" s="10"/>
       <c r="F77" s="12"/>
@@ -8867,16 +8867,16 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C78" s="11">
         <v>83.0</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="12"/>
@@ -8903,16 +8903,16 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C79" s="11">
         <v>83.0</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E79" s="10"/>
       <c r="F79" s="12"/>
@@ -8939,16 +8939,16 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C80" s="11">
         <v>82.0</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="12"/>
@@ -8975,16 +8975,16 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B81" s="44" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C81" s="11">
         <v>81.0</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E81" s="10"/>
       <c r="F81" s="12"/>
@@ -9011,16 +9011,16 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C82" s="11">
         <v>80.0</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="12"/>
@@ -9047,7 +9047,7 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>309</v>
@@ -9083,16 +9083,16 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C84" s="11">
         <v>74.0</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E84" s="10"/>
       <c r="F84" s="12"/>
@@ -9119,16 +9119,16 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C85" s="11">
         <v>71.0</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="12"/>
@@ -9155,16 +9155,16 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C86" s="11">
         <v>70.0</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="12"/>
@@ -9191,16 +9191,16 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C87" s="11">
         <v>96.0</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E87" s="10"/>
       <c r="F87" s="12"/>
@@ -9227,7 +9227,7 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" s="16" t="s">
         <v>325</v>
@@ -9263,16 +9263,16 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C89" s="11">
         <v>86.0</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E89" s="10"/>
       <c r="F89" s="12"/>
@@ -9299,16 +9299,16 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C90" s="11">
         <v>84.0</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E90" s="10"/>
       <c r="F90" s="12"/>
@@ -9335,16 +9335,16 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C91" s="11">
         <v>83.0</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="12"/>
@@ -9371,7 +9371,7 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>338</v>
@@ -9482,13 +9482,13 @@
         <v>340</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C95" s="11">
         <v>87.0</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E95" s="17"/>
       <c r="F95" s="12"/>
@@ -9518,13 +9518,13 @@
         <v>340</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C96" s="11">
         <v>85.0</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E96" s="10"/>
       <c r="F96" s="12"/>
@@ -9554,7 +9554,7 @@
         <v>340</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C97" s="11">
         <v>82.0</v>
@@ -9596,7 +9596,7 @@
         <v>80.0</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="12"/>
@@ -9626,11 +9626,11 @@
         <v>340</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E99" s="10"/>
       <c r="F99" s="12"/>
@@ -9657,16 +9657,16 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C100" s="11">
         <v>89.0</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="12"/>
@@ -9693,16 +9693,16 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C101" s="11">
         <v>85.0</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E101" s="17"/>
       <c r="F101" s="12"/>
@@ -9729,7 +9729,7 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>366</v>
@@ -9765,7 +9765,7 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>368</v>
@@ -9801,16 +9801,16 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C104" s="11">
         <v>70.0</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E104" s="10"/>
       <c r="F104" s="12"/>
@@ -9837,16 +9837,16 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C105" s="11">
         <v>88.0</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="12"/>
@@ -9873,10 +9873,10 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C106" s="11">
         <v>82.0</v>
@@ -9909,7 +9909,7 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>380</v>
@@ -9945,7 +9945,7 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>382</v>
@@ -9981,16 +9981,16 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C109" s="11">
         <v>71.0</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E109" s="10"/>
       <c r="F109" s="12"/>
@@ -10017,16 +10017,16 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C110" s="11">
         <v>90.0</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="12"/>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B111" s="17" t="s">
         <v>391</v>
@@ -10089,7 +10089,7 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>393</v>
@@ -10164,13 +10164,13 @@
         <v>395</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C114" s="11">
         <v>71.0</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E114" s="27"/>
       <c r="F114" s="27"/>
@@ -10197,16 +10197,16 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C115" s="11">
         <v>89.0</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E115" s="10"/>
       <c r="F115" s="12"/>
@@ -10233,16 +10233,16 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C116" s="11">
         <v>79.0</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E116" s="17"/>
       <c r="F116" s="12"/>
@@ -10269,7 +10269,7 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B117" s="17" t="s">
         <v>414</v>
@@ -10278,7 +10278,7 @@
         <v>91.0</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E117" s="17"/>
       <c r="F117" s="12"/>
@@ -10305,10 +10305,10 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="B118" s="21" t="s">
         <v>419</v>
-      </c>
-      <c r="B118" s="21" t="s">
-        <v>420</v>
       </c>
       <c r="C118" s="40">
         <v>90.0</v>
@@ -10317,7 +10317,7 @@
         <v>421</v>
       </c>
       <c r="E118" s="45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F118" s="10"/>
       <c r="G118" s="46"/>
@@ -10343,16 +10343,16 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C119" s="11">
         <v>90.0</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E119" s="10"/>
       <c r="F119" s="12"/>
@@ -10379,16 +10379,16 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="35" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C120" s="11">
         <v>70.0</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E120" s="27"/>
       <c r="F120" s="35"/>
@@ -10415,16 +10415,16 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C121" s="11">
         <v>55.0</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E121" s="10"/>
       <c r="F121" s="27"/>
@@ -10451,10 +10451,10 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B122" s="10" t="s">
         <v>419</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>420</v>
       </c>
       <c r="C122" s="11">
         <v>88.0</v>
@@ -10487,7 +10487,7 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B123" s="21" t="s">
         <v>442</v>
@@ -10523,7 +10523,7 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B124" s="27" t="s">
         <v>444</v>
@@ -10559,7 +10559,7 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B125" s="19" t="s">
         <v>446</v>
@@ -10568,7 +10568,7 @@
         <v>89.0</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E125" s="22"/>
       <c r="F125" s="47"/>
@@ -10595,16 +10595,16 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C126" s="11">
         <v>50.0</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E126" s="10"/>
       <c r="F126" s="12"/>
@@ -10631,16 +10631,16 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B127" s="35" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C127" s="11">
         <v>91.0</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E127" s="27"/>
       <c r="F127" s="27"/>
@@ -10667,7 +10667,7 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B128" s="35" t="s">
         <v>462</v>
@@ -10703,7 +10703,7 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B129" s="35" t="s">
         <v>464</v>
@@ -10739,16 +10739,16 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B130" s="35" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C130" s="11">
         <v>89.0</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E130" s="27"/>
       <c r="F130" s="27"/>
@@ -10775,16 +10775,16 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B131" s="35" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C131" s="11">
         <v>88.0</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E131" s="27"/>
       <c r="F131" s="27"/>
@@ -10811,7 +10811,7 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B132" s="35" t="s">
         <v>474</v>
@@ -10847,16 +10847,16 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B133" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C133" s="11">
         <v>86.0</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E133" s="27"/>
       <c r="F133" s="27"/>
@@ -10883,16 +10883,16 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B134" s="35" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C134" s="11">
         <v>85.0</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E134" s="27"/>
       <c r="F134" s="27"/>
@@ -10919,16 +10919,16 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B135" s="35" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C135" s="11">
         <v>83.0</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E135" s="27"/>
       <c r="F135" s="27"/>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B136" s="35" t="s">
         <v>486</v>
@@ -10991,16 +10991,16 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B137" s="35" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C137" s="11">
         <v>82.0</v>
       </c>
       <c r="D137" s="27" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E137" s="27"/>
       <c r="F137" s="27"/>
@@ -11027,16 +11027,16 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B138" s="35" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C138" s="11">
         <v>82.0</v>
       </c>
       <c r="D138" s="27" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E138" s="27"/>
       <c r="F138" s="27"/>
@@ -11063,16 +11063,16 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B139" s="26" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C139" s="11">
         <v>70.0</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E139" s="26"/>
       <c r="F139" s="12"/>
@@ -11099,7 +11099,7 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="49" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B140" s="50" t="s">
         <v>500</v>
@@ -11131,7 +11131,7 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="49" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B141" s="50" t="s">
         <v>501</v>
@@ -11163,16 +11163,16 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B142" s="52" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C142" s="11">
         <v>96.0</v>
       </c>
       <c r="D142" s="27" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E142" s="27"/>
       <c r="F142" s="27"/>
@@ -11199,7 +11199,7 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="53" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B143" s="16" t="s">
         <v>508</v>
@@ -11235,16 +11235,16 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C144" s="11">
         <v>91.0</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="12"/>
@@ -11271,16 +11271,16 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C145" s="11">
         <v>90.0</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E145" s="10"/>
       <c r="F145" s="12"/>
@@ -11307,16 +11307,16 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C146" s="11">
         <v>89.0</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E146" s="10"/>
       <c r="F146" s="12"/>
@@ -11343,7 +11343,7 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B147" s="10" t="s">
         <v>474</v>
@@ -11352,7 +11352,7 @@
         <v>88.0</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E147" s="10"/>
       <c r="F147" s="12"/>
@@ -11379,16 +11379,16 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C148" s="11">
         <v>87.0</v>
       </c>
       <c r="D148" s="27" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E148" s="27"/>
       <c r="F148" s="27"/>
@@ -11415,7 +11415,7 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B149" s="10" t="s">
         <v>524</v>
@@ -11451,7 +11451,7 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B150" s="10" t="s">
         <v>526</v>
@@ -11487,16 +11487,16 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C151" s="11">
         <v>85.0</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E151" s="10"/>
       <c r="F151" s="12"/>
@@ -11523,16 +11523,16 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C152" s="11">
         <v>85.0</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E152" s="10"/>
       <c r="F152" s="12"/>
@@ -11559,16 +11559,16 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C153" s="11">
         <v>84.0</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E153" s="10"/>
       <c r="F153" s="12"/>
@@ -11595,16 +11595,16 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C154" s="11">
         <v>83.0</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E154" s="10"/>
       <c r="F154" s="12"/>
@@ -11631,16 +11631,16 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C155" s="11">
         <v>89.0</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E155" s="10"/>
       <c r="F155" s="12"/>
@@ -11667,16 +11667,16 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="27" t="s">
+        <v>541</v>
+      </c>
+      <c r="B156" s="35" t="s">
         <v>544</v>
-      </c>
-      <c r="B156" s="35" t="s">
-        <v>550</v>
       </c>
       <c r="C156" s="11">
         <v>89.0</v>
       </c>
       <c r="D156" s="27" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="E156" s="27"/>
       <c r="F156" s="27"/>
@@ -11703,16 +11703,16 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="C157" s="11">
         <v>85.0</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E157" s="10"/>
       <c r="F157" s="12"/>
@@ -11739,16 +11739,16 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="10" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="C158" s="11">
         <v>65.0</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="E158" s="10"/>
       <c r="F158" s="12"/>
@@ -11775,16 +11775,16 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="16" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="B159" s="54" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="C159" s="11">
         <v>92.0</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="E159" s="10"/>
       <c r="F159" s="12"/>
@@ -11811,16 +11811,16 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="10" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C160" s="11">
         <v>70.0</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="E160" s="10"/>
       <c r="F160" s="12"/>
@@ -11847,16 +11847,16 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="10" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="B161" s="26" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="C161" s="11">
         <v>68.0</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E161" s="26"/>
       <c r="F161" s="12"/>
@@ -11883,16 +11883,16 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="B162" s="10" t="s">
         <v>565</v>
-      </c>
-      <c r="B162" s="10" t="s">
-        <v>574</v>
       </c>
       <c r="C162" s="11">
         <v>35.0</v>
       </c>
       <c r="D162" s="26" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="E162" s="10"/>
       <c r="F162" s="27"/>
@@ -11919,16 +11919,16 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="55" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C163" s="11">
         <v>79.0</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="E163" s="17"/>
       <c r="F163" s="12"/>
@@ -11955,16 +11955,16 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="10" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="C164" s="11">
         <v>88.0</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="E164" s="17"/>
       <c r="F164" s="12"/>
@@ -11991,16 +11991,16 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="10" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="C165" s="11">
         <v>65.0</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E165" s="17"/>
       <c r="F165" s="12"/>
@@ -12027,16 +12027,16 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="19" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="B166" s="19" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C166" s="20">
         <v>80.0</v>
       </c>
       <c r="D166" s="21" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="E166" s="22"/>
       <c r="F166" s="29"/>
@@ -12063,16 +12063,16 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="27" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C167" s="20">
         <v>86.0</v>
       </c>
       <c r="D167" s="56" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="E167" s="27"/>
       <c r="F167" s="27"/>
@@ -12099,16 +12099,16 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="35" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B168" s="35" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="C168" s="11">
         <v>77.0</v>
       </c>
       <c r="D168" s="57" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E168" s="27"/>
       <c r="F168" s="35"/>
@@ -12135,16 +12135,16 @@
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="10" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C169" s="11">
         <v>68.0</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E169" s="10"/>
       <c r="F169" s="12"/>
@@ -12171,16 +12171,16 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="10" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C170" s="11">
         <v>64.0</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E170" s="10"/>
       <c r="F170" s="12"/>
@@ -12207,16 +12207,16 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="27" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B171" s="57" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="C171" s="11">
         <v>89.0</v>
       </c>
       <c r="D171" s="27" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="E171" s="27"/>
       <c r="F171" s="27"/>
@@ -12243,14 +12243,14 @@
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="10" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B172" s="10"/>
       <c r="C172" s="11">
         <v>87.0</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="E172" s="10"/>
       <c r="F172" s="12"/>
@@ -12277,16 +12277,16 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="27" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B173" s="27" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C173" s="11">
         <v>87.0</v>
       </c>
       <c r="D173" s="27" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="E173" s="27"/>
       <c r="F173" s="27"/>
@@ -12313,16 +12313,16 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="27" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B174" s="27" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C174" s="11">
         <v>86.0</v>
       </c>
       <c r="D174" s="27" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="E174" s="27"/>
       <c r="F174" s="27"/>
@@ -12349,16 +12349,16 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="10" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B175" s="33" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="C175" s="11">
         <v>84.0</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="E175" s="33"/>
       <c r="F175" s="12"/>
@@ -12385,16 +12385,16 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="10" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C176" s="11">
         <v>81.0</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="E176" s="17"/>
       <c r="F176" s="12"/>
@@ -12421,16 +12421,16 @@
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="10" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="C177" s="11">
         <v>70.0</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="E177" s="10"/>
       <c r="F177" s="27"/>
@@ -12457,16 +12457,16 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="27" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B178" s="27" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C178" s="11">
         <v>87.0</v>
       </c>
       <c r="D178" s="27" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="E178" s="27"/>
       <c r="F178" s="27"/>
@@ -12493,16 +12493,16 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="10" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C179" s="11">
         <v>50.0</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="E179" s="10"/>
       <c r="F179" s="27"/>
@@ -12529,16 +12529,16 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="27" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B180" s="27" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C180" s="11">
         <v>87.0</v>
       </c>
       <c r="D180" s="27" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="E180" s="27"/>
       <c r="F180" s="35"/>
@@ -12565,16 +12565,16 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="10" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C181" s="11">
         <v>84.0</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="E181" s="10"/>
       <c r="F181" s="12"/>
@@ -12601,16 +12601,16 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="10" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="C182" s="11">
         <v>62.0</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="E182" s="10"/>
       <c r="F182" s="12"/>
@@ -12637,16 +12637,16 @@
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="B183" s="10" t="s">
         <v>639</v>
-      </c>
-      <c r="B183" s="10" t="s">
-        <v>649</v>
       </c>
       <c r="C183" s="11">
         <v>30.0</v>
       </c>
       <c r="D183" s="26" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="E183" s="10"/>
       <c r="F183" s="27"/>
@@ -12673,16 +12673,16 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="10" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C184" s="11">
         <v>80.0</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="E184" s="17"/>
       <c r="F184" s="12"/>
@@ -12709,16 +12709,16 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="10" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B185" s="33" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C185" s="11">
         <v>78.0</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E185" s="33"/>
       <c r="F185" s="12"/>
@@ -12745,19 +12745,19 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C186" s="40">
         <v>78.0</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E186" s="45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F186" s="10"/>
       <c r="G186" s="46"/>
@@ -12783,16 +12783,16 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="10" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C187" s="11">
         <v>76.0</v>
       </c>
       <c r="D187" s="10" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E187" s="10"/>
       <c r="F187" s="12"/>
@@ -12819,16 +12819,16 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="10" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C188" s="11">
         <v>91.0</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E188" s="10"/>
       <c r="F188" s="12"/>
@@ -12855,16 +12855,16 @@
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C189" s="11">
         <v>97.0</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E189" s="10"/>
       <c r="F189" s="12"/>
@@ -12891,16 +12891,16 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="16" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B190" s="16" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C190" s="11">
         <v>95.0</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="E190" s="10"/>
       <c r="F190" s="12"/>
@@ -12926,17 +12926,17 @@
       <c r="Z190" s="14"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="60" t="s">
-        <v>666</v>
-      </c>
-      <c r="B191" s="61" t="s">
-        <v>674</v>
+      <c r="A191" s="58" t="s">
+        <v>659</v>
+      </c>
+      <c r="B191" s="59" t="s">
+        <v>664</v>
       </c>
       <c r="C191" s="11">
         <v>95.0</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="E191" s="17"/>
       <c r="F191" s="12"/>
@@ -12963,16 +12963,16 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="B192" s="16" t="s">
         <v>666</v>
-      </c>
-      <c r="B192" s="16" t="s">
-        <v>678</v>
       </c>
       <c r="C192" s="11">
         <v>94.0</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="E192" s="10"/>
       <c r="F192" s="12"/>
@@ -12999,16 +12999,16 @@
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C193" s="11">
         <v>90.0</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="E193" s="10"/>
       <c r="F193" s="12"/>
@@ -13035,16 +13035,16 @@
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="C194" s="11">
         <v>87.0</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="E194" s="10"/>
       <c r="F194" s="12"/>
@@ -13071,16 +13071,16 @@
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="27" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B195" s="27" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="C195" s="11">
         <v>87.0</v>
       </c>
       <c r="D195" s="27" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="E195" s="27"/>
       <c r="F195" s="35"/>
@@ -13107,16 +13107,16 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="B196" s="62" t="s">
-        <v>688</v>
+        <v>659</v>
+      </c>
+      <c r="B196" s="60" t="s">
+        <v>677</v>
       </c>
       <c r="C196" s="11">
         <v>85.0</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E196" s="10"/>
       <c r="F196" s="12"/>
@@ -13143,16 +13143,16 @@
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C197" s="11">
         <v>81.0</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="E197" s="17"/>
       <c r="F197" s="12"/>
@@ -13179,16 +13179,16 @@
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="C198" s="11">
         <v>80.0</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="E198" s="10"/>
       <c r="F198" s="12"/>
@@ -13215,16 +13215,16 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="C199" s="11">
         <v>79.0</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="12"/>
@@ -13251,16 +13251,16 @@
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="27" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B200" s="27" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C200" s="11">
         <v>79.0</v>
       </c>
       <c r="D200" s="27" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="E200" s="27"/>
       <c r="F200" s="35"/>
@@ -13287,16 +13287,16 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C201" s="11">
         <v>65.0</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="E201" s="10"/>
       <c r="F201" s="12"/>
@@ -13323,16 +13323,16 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C202" s="11">
         <v>63.0</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="E202" s="17"/>
       <c r="F202" s="12"/>
@@ -13359,16 +13359,16 @@
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C203" s="11">
         <v>60.0</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="E203" s="17"/>
       <c r="F203" s="12"/>
@@ -13395,16 +13395,16 @@
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="10" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C204" s="11">
         <v>50.0</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E204" s="10"/>
       <c r="F204" s="12"/>
@@ -13431,10 +13431,10 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="63" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B205" s="36" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C205" s="11"/>
       <c r="D205" s="27"/>
@@ -13463,7 +13463,7 @@
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>707</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>709</v>
@@ -13535,7 +13535,7 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="27" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B208" s="56" t="s">
         <v>711</v>
@@ -13571,7 +13571,7 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>713</v>
@@ -13607,7 +13607,7 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>715</v>
@@ -13643,7 +13643,7 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B211" s="17" t="s">
         <v>717</v>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>719</v>
@@ -13715,7 +13715,7 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B213" s="64" t="s">
         <v>721</v>
@@ -13747,7 +13747,7 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B214" s="64" t="s">
         <v>722</v>
@@ -13779,7 +13779,7 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B215" s="64" t="s">
         <v>723</v>
@@ -13811,7 +13811,7 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B216" s="64" t="s">
         <v>724</v>
@@ -13843,7 +13843,7 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B217" s="64" t="s">
         <v>725</v>
@@ -13875,7 +13875,7 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B218" s="64" t="s">
         <v>726</v>
@@ -13907,7 +13907,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B219" s="64" t="s">
         <v>727</v>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B220" s="64" t="s">
         <v>728</v>
@@ -13971,7 +13971,7 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B221" s="64" t="s">
         <v>729</v>
@@ -14003,7 +14003,7 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B222" s="64" t="s">
         <v>730</v>
@@ -14035,7 +14035,7 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B223" s="64" t="s">
         <v>731</v>
@@ -14067,7 +14067,7 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B224" s="65" t="s">
         <v>732</v>
@@ -14099,7 +14099,7 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B225" s="64" t="s">
         <v>733</v>
@@ -14131,7 +14131,7 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B226" s="64" t="s">
         <v>734</v>
@@ -14163,7 +14163,7 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B227" s="64" t="s">
         <v>735</v>
@@ -14195,7 +14195,7 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B228" s="64" t="s">
         <v>736</v>
@@ -14227,7 +14227,7 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B229" s="64" t="s">
         <v>737</v>
@@ -14259,7 +14259,7 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B230" s="64" t="s">
         <v>738</v>
@@ -14291,7 +14291,7 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B231" s="64" t="s">
         <v>739</v>
@@ -14323,7 +14323,7 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B232" s="64" t="s">
         <v>740</v>
@@ -14355,7 +14355,7 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B233" s="64" t="s">
         <v>741</v>
@@ -14387,7 +14387,7 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B234" s="64" t="s">
         <v>742</v>
@@ -14419,7 +14419,7 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B235" s="64" t="s">
         <v>743</v>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B236" s="64" t="s">
         <v>744</v>
@@ -14483,7 +14483,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B237" s="64" t="s">
         <v>745</v>
@@ -15235,7 +15235,7 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="35" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B258" s="35" t="s">
         <v>794</v>
@@ -15271,7 +15271,7 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="69" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B259" s="69" t="s">
         <v>796</v>
@@ -15305,7 +15305,7 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="69" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B260" s="69" t="s">
         <v>798</v>
@@ -15511,7 +15511,7 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>811</v>
@@ -15547,7 +15547,7 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="27" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B267" s="27" t="s">
         <v>813</v>
@@ -15583,7 +15583,7 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="27" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B268" s="27" t="s">
         <v>815</v>
@@ -15619,7 +15619,7 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>817</v>
@@ -15655,7 +15655,7 @@
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>819</v>
@@ -15691,7 +15691,7 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>821</v>
@@ -15727,7 +15727,7 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>823</v>
@@ -15763,7 +15763,7 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>825</v>
@@ -15799,7 +15799,7 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B274" s="17" t="s">
         <v>827</v>
@@ -15835,7 +15835,7 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B275" s="10" t="s">
         <v>829</v>
@@ -15871,10 +15871,10 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="C276" s="11"/>
       <c r="D276" s="10"/>
@@ -15903,7 +15903,7 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B277" s="10" t="s">
         <v>831</v>
@@ -15939,7 +15939,7 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B278" s="17" t="s">
         <v>833</v>
@@ -15975,7 +15975,7 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B279" s="33" t="s">
         <v>835</v>
@@ -16011,7 +16011,7 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>823</v>
@@ -16335,7 +16335,7 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="10" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>856</v>
@@ -16371,10 +16371,10 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="10" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="B290" s="17" t="s">
-        <v>683</v>
+        <v>706</v>
       </c>
       <c r="C290" s="11">
         <v>87.0</v>
@@ -16479,7 +16479,7 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="16" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B293" s="16" t="s">
         <v>864</v>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B294" s="27" t="s">
         <v>866</v>
@@ -16551,7 +16551,7 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B295" s="10" t="s">
         <v>868</v>
@@ -16587,7 +16587,7 @@
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B296" s="27" t="s">
         <v>870</v>
@@ -16623,10 +16623,10 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B297" s="27" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C297" s="11">
         <v>87.0</v>
@@ -16659,7 +16659,7 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B298" s="27" t="s">
         <v>873</v>
@@ -16695,7 +16695,7 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B299" s="27" t="s">
         <v>875</v>
@@ -16731,7 +16731,7 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B300" s="27" t="s">
         <v>877</v>
@@ -16767,7 +16767,7 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B301" s="27" t="s">
         <v>879</v>
@@ -16803,7 +16803,7 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B302" s="35" t="s">
         <v>881</v>
@@ -16839,7 +16839,7 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B303" s="27" t="s">
         <v>883</v>
@@ -16875,7 +16875,7 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B304" s="27" t="s">
         <v>885</v>
@@ -16911,7 +16911,7 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B305" s="27" t="s">
         <v>886</v>
@@ -16947,7 +16947,7 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B306" s="27" t="s">
         <v>887</v>
@@ -16983,7 +16983,7 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B307" s="27" t="s">
         <v>888</v>
@@ -17019,10 +17019,10 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="27" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B308" s="27" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C308" s="11">
         <v>83.0</v>
@@ -17055,7 +17055,7 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="35" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B309" s="35" t="s">
         <v>891</v>
@@ -17091,7 +17091,7 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>893</v>
@@ -17127,7 +17127,7 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>895</v>
@@ -17163,7 +17163,7 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B312" s="26" t="s">
         <v>897</v>
@@ -17199,7 +17199,7 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B313" s="26" t="s">
         <v>899</v>
@@ -17235,7 +17235,7 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B314" s="26" t="s">
         <v>901</v>
@@ -17271,7 +17271,7 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B315" s="66" t="s">
         <v>903</v>
@@ -17307,7 +17307,7 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B316" s="17" t="s">
         <v>905</v>
@@ -17343,7 +17343,7 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B317" s="17" t="s">
         <v>907</v>
@@ -17379,7 +17379,7 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>909</v>
@@ -17415,7 +17415,7 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B319" s="17" t="s">
         <v>911</v>
@@ -17451,7 +17451,7 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>913</v>
@@ -17487,7 +17487,7 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>915</v>
@@ -17883,7 +17883,7 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B332" s="16" t="s">
         <v>939</v>
@@ -17919,7 +17919,7 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B333" s="26" t="s">
         <v>941</v>
@@ -17955,7 +17955,7 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B334" s="17" t="s">
         <v>943</v>
@@ -17991,7 +17991,7 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B335" s="10" t="s">
         <v>945</v>
@@ -18027,7 +18027,7 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="27" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B336" s="57" t="s">
         <v>947</v>
@@ -18063,7 +18063,7 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B337" s="17" t="s">
         <v>949</v>
@@ -18099,7 +18099,7 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B338" s="33" t="s">
         <v>951</v>
@@ -18135,7 +18135,7 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B339" s="26" t="s">
         <v>953</v>
@@ -18171,7 +18171,7 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>955</v>
@@ -18207,7 +18207,7 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>957</v>
@@ -18243,7 +18243,7 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>959</v>
@@ -18279,7 +18279,7 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="27" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B343" s="57" t="s">
         <v>961</v>
@@ -18315,7 +18315,7 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="27" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B344" s="27" t="s">
         <v>963</v>
@@ -20151,7 +20151,7 @@
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B395" s="10" t="s">
         <v>1080</v>
@@ -20187,7 +20187,7 @@
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>1082</v>
@@ -20475,7 +20475,7 @@
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="74" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B404" s="27" t="s">
         <v>1103</v>
@@ -20511,7 +20511,7 @@
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="26" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>1105</v>
@@ -20655,7 +20655,7 @@
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="10" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B409" s="10" t="s">
         <v>1115</v>
@@ -20691,7 +20691,7 @@
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="10" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>1117</v>
@@ -20727,7 +20727,7 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="10" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>1119</v>
@@ -21051,7 +21051,7 @@
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>1139</v>
@@ -21449,7 +21449,7 @@
       <c r="A431" s="75" t="s">
         <v>1143</v>
       </c>
-      <c r="B431" s="62" t="s">
+      <c r="B431" s="60" t="s">
         <v>1158</v>
       </c>
       <c r="C431" s="11">
@@ -21843,7 +21843,7 @@
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B442" s="78" t="s">
         <v>1185</v>
@@ -21879,7 +21879,7 @@
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>1187</v>
@@ -21915,7 +21915,7 @@
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>1189</v>
@@ -22311,7 +22311,7 @@
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>1216</v>
@@ -22659,7 +22659,7 @@
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="35" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B465" s="35" t="s">
         <v>1235</v>
@@ -22695,7 +22695,7 @@
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>1237</v>
@@ -22731,7 +22731,7 @@
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>1239</v>
@@ -22767,7 +22767,7 @@
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>1241</v>
@@ -22803,7 +22803,7 @@
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>1243</v>
@@ -22839,7 +22839,7 @@
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>1245</v>
@@ -22875,7 +22875,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>1247</v>
@@ -22911,7 +22911,7 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>1249</v>
@@ -22947,7 +22947,7 @@
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>1251</v>
@@ -23451,7 +23451,7 @@
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B487" s="17" t="s">
         <v>1285</v>
@@ -23559,7 +23559,7 @@
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="21" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B490" s="21" t="s">
         <v>1292</v>
@@ -23571,7 +23571,7 @@
         <v>1293</v>
       </c>
       <c r="E490" s="45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F490" s="10"/>
       <c r="G490" s="46"/>
@@ -24947,7 +24947,7 @@
     </row>
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B529" s="10" t="s">
         <v>1375</v>
@@ -24983,7 +24983,7 @@
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="27" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B530" s="27" t="s">
         <v>1377</v>
@@ -25199,7 +25199,7 @@
     </row>
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B536" s="35" t="s">
         <v>1390</v>
@@ -25235,7 +25235,7 @@
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B537" s="35" t="s">
         <v>1392</v>
@@ -25271,7 +25271,7 @@
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B538" s="35" t="s">
         <v>1394</v>
@@ -25307,7 +25307,7 @@
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B539" s="35" t="s">
         <v>1396</v>
@@ -25343,7 +25343,7 @@
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B540" s="35" t="s">
         <v>1398</v>
@@ -25379,7 +25379,7 @@
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B541" s="35" t="s">
         <v>1400</v>
@@ -25415,7 +25415,7 @@
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B542" s="27" t="s">
         <v>1402</v>
@@ -25451,7 +25451,7 @@
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B543" s="10" t="s">
         <v>1404</v>
@@ -25487,7 +25487,7 @@
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B544" s="10" t="s">
         <v>1406</v>
@@ -25631,7 +25631,7 @@
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="44" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B548" s="10" t="s">
         <v>1416</v>
@@ -26063,7 +26063,7 @@
     </row>
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B560" s="10" t="s">
         <v>1443</v>
@@ -26099,7 +26099,7 @@
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B561" s="10" t="s">
         <v>1021</v>
@@ -27069,7 +27069,7 @@
     </row>
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B588" s="17" t="s">
         <v>1514</v>
@@ -27105,7 +27105,7 @@
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B589" s="17" t="s">
         <v>1516</v>
@@ -27140,10 +27140,10 @@
       <c r="Z589" s="14"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="60" t="s">
-        <v>467</v>
-      </c>
-      <c r="B590" s="60" t="s">
+      <c r="A590" s="58" t="s">
+        <v>471</v>
+      </c>
+      <c r="B590" s="58" t="s">
         <v>1518</v>
       </c>
       <c r="C590" s="11">
@@ -27177,7 +27177,7 @@
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B591" s="10" t="s">
         <v>1520</v>
@@ -27321,7 +27321,7 @@
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="30" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B595" s="26" t="s">
         <v>1530</v>
@@ -27573,7 +27573,7 @@
     </row>
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B602" s="26" t="s">
         <v>1545</v>
@@ -27609,7 +27609,7 @@
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B603" s="26" t="s">
         <v>1547</v>
@@ -27645,7 +27645,7 @@
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>1549</v>
@@ -27681,7 +27681,7 @@
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B605" s="66" t="s">
         <v>1551</v>
@@ -27717,7 +27717,7 @@
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B606" s="10" t="s">
         <v>1553</v>
@@ -27863,7 +27863,7 @@
     </row>
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="21" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B610" s="21" t="s">
         <v>1563</v>
@@ -30211,7 +30211,7 @@
     </row>
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="10" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="B675" s="10" t="s">
         <v>1702</v>
@@ -30247,7 +30247,7 @@
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="27" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B676" s="27" t="s">
         <v>1704</v>
@@ -30283,7 +30283,7 @@
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="19" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B677" s="19" t="s">
         <v>1706</v>
@@ -30319,7 +30319,7 @@
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="19" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B678" s="27" t="s">
         <v>1708</v>
@@ -30427,7 +30427,7 @@
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="10" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B681" s="10" t="s">
         <v>1715</v>
@@ -30463,7 +30463,7 @@
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="10" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B682" s="17" t="s">
         <v>1717</v>
@@ -30499,7 +30499,7 @@
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="75" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B683" s="10" t="s">
         <v>1719</v>
@@ -30535,7 +30535,7 @@
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="10" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B684" s="33" t="s">
         <v>1721</v>
@@ -30571,7 +30571,7 @@
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="10" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B685" s="10" t="s">
         <v>1723</v>
@@ -30823,7 +30823,7 @@
     </row>
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B692" s="27" t="s">
         <v>1740</v>
@@ -30859,7 +30859,7 @@
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B693" s="27" t="s">
         <v>1742</v>
@@ -30895,7 +30895,7 @@
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B694" s="27" t="s">
         <v>1744</v>
@@ -30931,7 +30931,7 @@
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B695" s="27" t="s">
         <v>1746</v>
@@ -30967,7 +30967,7 @@
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B696" s="27" t="s">
         <v>1748</v>
@@ -31003,7 +31003,7 @@
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B697" s="27" t="s">
         <v>1750</v>
@@ -31039,7 +31039,7 @@
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="27" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B698" s="27" t="s">
         <v>1752</v>
@@ -31075,7 +31075,7 @@
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="10" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B699" s="10" t="s">
         <v>1754</v>
@@ -31111,7 +31111,7 @@
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="49" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B700" s="49" t="s">
         <v>1756</v>
@@ -38169,15 +38169,15 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -38202,15 +38202,15 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -38235,19 +38235,19 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>26</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -38272,19 +38272,19 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -38309,16 +38309,16 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>74</v>
@@ -38346,19 +38346,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -38383,15 +38383,15 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -38416,15 +38416,15 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -38449,10 +38449,10 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -38482,19 +38482,19 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="D12" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -38519,15 +38519,15 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -38552,10 +38552,10 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -38583,19 +38583,19 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -38620,15 +38620,15 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -38653,19 +38653,19 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -38690,19 +38690,19 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -38727,19 +38727,19 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>199</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -38764,19 +38764,19 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -38801,19 +38801,19 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -38838,19 +38838,19 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>237</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -38875,19 +38875,19 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -38911,19 +38911,19 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -38948,19 +38948,19 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -38985,15 +38985,15 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
@@ -39018,7 +39018,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -39047,19 +39047,19 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
@@ -39084,15 +39084,15 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -39117,19 +39117,19 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -39154,15 +39154,15 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -39187,10 +39187,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -39218,15 +39218,15 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -39251,19 +39251,19 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -39288,10 +39288,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -39319,19 +39319,19 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D36" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>324</v>
-      </c>
       <c r="E36" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
@@ -39356,19 +39356,19 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
@@ -39393,19 +39393,19 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -39430,16 +39430,16 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -39465,19 +39465,19 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D40" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>378</v>
-      </c>
       <c r="E40" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
@@ -39502,16 +39502,16 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>387</v>
-      </c>
       <c r="C41" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>398</v>
@@ -39539,15 +39539,15 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
@@ -39572,16 +39572,16 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>408</v>
@@ -39609,16 +39609,16 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>413</v>
@@ -39646,19 +39646,19 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>417</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
@@ -39683,15 +39683,15 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
@@ -39716,15 +39716,15 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
@@ -39749,19 +39749,19 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
@@ -39792,13 +39792,13 @@
         <v>434</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
@@ -39823,13 +39823,13 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>440</v>
@@ -39858,10 +39858,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -39927,12 +39927,12 @@
         <v>450</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
@@ -39957,19 +39957,19 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
@@ -39994,19 +39994,19 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
@@ -40031,19 +40031,19 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
@@ -40068,15 +40068,15 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
@@ -40101,16 +40101,16 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>502</v>
@@ -40138,19 +40138,19 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
@@ -40175,15 +40175,15 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
@@ -40208,19 +40208,19 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
@@ -40245,19 +40245,19 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
@@ -40282,15 +40282,15 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
@@ -40315,19 +40315,19 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
@@ -40352,10 +40352,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -40383,19 +40383,19 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
@@ -40420,15 +40420,15 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
@@ -40453,15 +40453,15 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
@@ -40486,19 +40486,19 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
@@ -40523,19 +40523,19 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -40560,19 +40560,19 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -40597,19 +40597,19 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
@@ -40637,16 +40637,16 @@
         <v>201</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>622</v>
+        <v>641</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
@@ -40671,19 +40671,19 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
@@ -40708,16 +40708,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>630</v>
+        <v>649</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>631</v>
+        <v>650</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -40743,16 +40743,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>642</v>
+        <v>668</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>643</v>
+        <v>669</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>644</v>
+        <v>670</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -40777,14 +40777,14 @@
       <c r="Y76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="58" t="s">
+      <c r="A77" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="B77" s="58" t="s">
-        <v>655</v>
+      <c r="B77" s="61" t="s">
+        <v>679</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -40810,14 +40810,14 @@
       <c r="Y77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B78" s="59" t="s">
-        <v>658</v>
+      <c r="A78" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B78" s="62" t="s">
+        <v>683</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -40843,14 +40843,14 @@
       <c r="Y78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B79" s="59" t="s">
-        <v>665</v>
+      <c r="A79" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B79" s="62" t="s">
+        <v>688</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -40876,14 +40876,14 @@
       <c r="Y79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B80" s="59" t="s">
-        <v>668</v>
+      <c r="A80" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B80" s="62" t="s">
+        <v>691</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -40909,14 +40909,14 @@
       <c r="Y80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B81" s="59" t="s">
-        <v>671</v>
+      <c r="A81" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B81" s="62" t="s">
+        <v>694</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -40942,14 +40942,14 @@
       <c r="Y81" s="9"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B82" s="59" t="s">
-        <v>673</v>
+      <c r="A82" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B82" s="62" t="s">
+        <v>697</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -40975,14 +40975,14 @@
       <c r="Y82" s="9"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B83" s="59" t="s">
-        <v>675</v>
+      <c r="A83" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B83" s="62" t="s">
+        <v>700</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -41008,14 +41008,14 @@
       <c r="Y83" s="9"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B84" s="59" t="s">
-        <v>677</v>
+      <c r="A84" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B84" s="62" t="s">
+        <v>703</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -41041,14 +41041,14 @@
       <c r="Y84" s="9"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B85" s="59" t="s">
-        <v>680</v>
+      <c r="A85" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B85" s="62" t="s">
+        <v>704</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -41074,14 +41074,14 @@
       <c r="Y85" s="9"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B86" s="59" t="s">
-        <v>683</v>
+      <c r="A86" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B86" s="62" t="s">
+        <v>706</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>

--- a/data/FRAGRANCES.xlsx
+++ b/data/FRAGRANCES.xlsx
@@ -35,12 +35,12 @@
     <t>Date tried</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>Where to buy</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
@@ -98,24 +98,24 @@
     <t>Akro</t>
   </si>
   <si>
+    <t>Aedes de Venustas</t>
+  </si>
+  <si>
     <t>Ink</t>
   </si>
   <si>
+    <t>Café Tabac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tobacco shop, Ybor City, keeps going </t>
+  </si>
+  <si>
     <t>Bloom Perfumery</t>
   </si>
   <si>
-    <t>Aedes de Venustas</t>
-  </si>
-  <si>
     <t>https://bloomperfume.co.uk/products/ink</t>
   </si>
   <si>
-    <t>Café Tabac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tobacco shop, Ybor City, keeps going </t>
-  </si>
-  <si>
     <t>Signature</t>
   </si>
   <si>
@@ -131,15 +131,15 @@
     <t>Aesop</t>
   </si>
   <si>
+    <t>Hwyl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Way too smoky </t>
+  </si>
+  <si>
     <t>Spelled Akro. Ministry of Scent sample sold out.</t>
   </si>
   <si>
-    <t>Hwyl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Way too smoky </t>
-  </si>
-  <si>
     <t>Angelos Creations Olfactives</t>
   </si>
   <si>
@@ -170,21 +170,21 @@
     <t>Cereale</t>
   </si>
   <si>
+    <t>Astier de Villatte</t>
+  </si>
+  <si>
     <t xml:space="preserve">?? Toothpaste </t>
   </si>
   <si>
-    <t>Astier de Villatte</t>
-  </si>
-  <si>
     <t>Mantes La Jolie</t>
   </si>
   <si>
+    <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
+  </si>
+  <si>
     <t>Matsu Musk</t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/products/mantes-la-jolie-by-astier-de-villatte</t>
-  </si>
-  <si>
     <t xml:space="preserve">Uncooked grocery store button mushrooms </t>
   </si>
   <si>
@@ -197,42 +197,42 @@
     <t>Yellow floral, really compelling, honeycomb and honesuckle, kinda Moon Bloom, stinks a lot but I like the stink</t>
   </si>
   <si>
+    <t>Price shows when you select the size, usually $5-10.</t>
+  </si>
+  <si>
     <t>Honeyed Vetiver</t>
   </si>
   <si>
-    <t>Price shows when you select the size, usually $5-10.</t>
+    <t>Azzaro</t>
+  </si>
+  <si>
+    <t>Azzaro pour Homme</t>
+  </si>
+  <si>
+    <t>Cheapest sample on the list.</t>
   </si>
   <si>
     <t>Madame Chouteau</t>
   </si>
   <si>
-    <t>Azzaro</t>
-  </si>
-  <si>
-    <t>Azzaro pour Homme</t>
-  </si>
-  <si>
-    <t>Cheapest sample on the list.</t>
+    <t>Bohoboco</t>
+  </si>
+  <si>
+    <t>Vanilla Black Pepper</t>
+  </si>
+  <si>
+    <t>Ministry of Scent</t>
+  </si>
+  <si>
+    <t>https://ministryofscent.com/products/vanilla-black-pepper</t>
   </si>
   <si>
     <t>Garden of the Heart of Heaven</t>
   </si>
   <si>
-    <t>Bohoboco</t>
-  </si>
-  <si>
-    <t>Vanilla Black Pepper</t>
-  </si>
-  <si>
     <t>Black Walnut</t>
   </si>
   <si>
-    <t>Ministry of Scent</t>
-  </si>
-  <si>
-    <t>https://ministryofscent.com/products/vanilla-black-pepper</t>
-  </si>
-  <si>
     <t>Amouage</t>
   </si>
   <si>
@@ -251,33 +251,33 @@
     <t>Interlude Woman</t>
   </si>
   <si>
+    <t>Formerly Tigerlily Perfumery, San Francisco.</t>
+  </si>
+  <si>
     <t>Lotsa stuff I like, reviews said kiwi, my vibe was just a mild no</t>
   </si>
   <si>
-    <t>Formerly Tigerlily Perfumery, San Francisco.</t>
+    <t>Bortnikoff</t>
+  </si>
+  <si>
+    <t>Moss Cologne</t>
+  </si>
+  <si>
+    <t>Scent Split</t>
   </si>
   <si>
     <t>Anatole Lebreton</t>
   </si>
   <si>
+    <t>https://scentsplit.com</t>
+  </si>
+  <si>
     <t>L'Eau de Merzhin</t>
   </si>
   <si>
     <t>Cool but ultimately a watery mess</t>
   </si>
   <si>
-    <t>Bortnikoff</t>
-  </si>
-  <si>
-    <t>Moss Cologne</t>
-  </si>
-  <si>
-    <t>Scent Split</t>
-  </si>
-  <si>
-    <t>https://scentsplit.com</t>
-  </si>
-  <si>
     <t>Brioche</t>
   </si>
   <si>
@@ -290,21 +290,21 @@
     <t>Andrea Maack</t>
   </si>
   <si>
+    <t>Bvlgari</t>
+  </si>
+  <si>
     <t>Osmo</t>
   </si>
   <si>
-    <t>Bvlgari</t>
+    <t>Rose Goldea Blossom Delight</t>
+  </si>
+  <si>
+    <t>Maple Prime</t>
   </si>
   <si>
     <t xml:space="preserve">Try this again? Says it's marine but I got a big food vibe of something savory </t>
   </si>
   <si>
-    <t>Rose Goldea Blossom Delight</t>
-  </si>
-  <si>
-    <t>Maple Prime</t>
-  </si>
-  <si>
     <t>https://mapleprime.com/products/bvlgari-rose-goldea-blossom-delight-eau-de-parfum-for-women</t>
   </si>
   <si>
@@ -320,22 +320,28 @@
     <t xml:space="preserve">Dirt. Probably great layered with something. </t>
   </si>
   <si>
+    <t>All three decant sizes out of stock. Re-check.</t>
+  </si>
+  <si>
+    <t>Caron</t>
+  </si>
+  <si>
+    <t>Coup de Fouet</t>
+  </si>
+  <si>
     <t>Dual</t>
   </si>
   <si>
-    <t>All three decant sizes out of stock. Re-check.</t>
+    <t>Vintage market only.</t>
   </si>
   <si>
     <t xml:space="preserve">Lemon cookie for some reason but some pencil shavings </t>
   </si>
   <si>
-    <t>Caron</t>
-  </si>
-  <si>
-    <t>Coup de Fouet</t>
-  </si>
-  <si>
-    <t>Vintage market only.</t>
+    <t>Poivre</t>
+  </si>
+  <si>
+    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
   </si>
   <si>
     <t>Ceramic</t>
@@ -344,10 +350,13 @@
     <t xml:space="preserve">Powder and nice but hits a truck stop soap after a minute </t>
   </si>
   <si>
-    <t>Poivre</t>
-  </si>
-  <si>
-    <t>Scent Split has Poivre Sacre and Poivre Imperial, modern reinterpretations, not the original.</t>
+    <t>CBCB Fragrances</t>
+  </si>
+  <si>
+    <t>Comrade</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/comrade-by-cbcb-fragrances</t>
   </si>
   <si>
     <t>Tauer Perfumes</t>
@@ -359,15 +368,6 @@
     <t>Bleh I don't like this dude I will die on this hill</t>
   </si>
   <si>
-    <t>CBCB Fragrances</t>
-  </si>
-  <si>
-    <t>Comrade</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/comrade-by-cbcb-fragrances</t>
-  </si>
-  <si>
     <t>Sundowner</t>
   </si>
   <si>
@@ -386,42 +386,42 @@
     <t xml:space="preserve">Cheap soap started great but then muddy cleaning product, huge bummer </t>
   </si>
   <si>
+    <t>Chanel</t>
+  </si>
+  <si>
     <t>Argos</t>
   </si>
   <si>
+    <t>No. 19</t>
+  </si>
+  <si>
     <t>Adonis Awakens</t>
   </si>
   <si>
-    <t>Chanel</t>
-  </si>
-  <si>
-    <t>No. 19</t>
+    <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
   </si>
   <si>
     <t xml:space="preserve">Rose, great at first but ultimately dries down too candy-like </t>
   </si>
   <si>
-    <t>No decant retailer checked carries Chanel. eBay or vintage sellers.</t>
+    <t>Coach</t>
+  </si>
+  <si>
+    <t>Coach Green</t>
+  </si>
+  <si>
+    <t>DecantX</t>
+  </si>
+  <si>
+    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
   </si>
   <si>
     <t>Pallas Athene</t>
   </si>
   <si>
-    <t>Coach</t>
-  </si>
-  <si>
     <t>Rose, good at first but ultimately dries down too candy-like</t>
   </si>
   <si>
-    <t>Coach Green</t>
-  </si>
-  <si>
-    <t>DecantX</t>
-  </si>
-  <si>
-    <t>https://www.decantx.com/products/coach-green-eau-de-toilette-for-men</t>
-  </si>
-  <si>
     <t>Triumph Of Bacchus</t>
   </si>
   <si>
@@ -437,13 +437,22 @@
     <t>Grape soda</t>
   </si>
   <si>
+    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+  </si>
+  <si>
     <t>Rose Milano</t>
   </si>
   <si>
     <t xml:space="preserve">Simple and duplicative but rare I like it at this degree </t>
   </si>
   <si>
-    <t>Maple Prime lists 2ml and 4.5ml, both sold out.</t>
+    <t>Comme des Garçons</t>
+  </si>
+  <si>
+    <t>Series 2 Red: Carnation</t>
+  </si>
+  <si>
+    <t>Discontinued Red series. Vintage market.</t>
   </si>
   <si>
     <t>Rose d'Arabie</t>
@@ -452,25 +461,25 @@
     <t xml:space="preserve">A great rose but not my favorite. Deep. </t>
   </si>
   <si>
-    <t>Comme des Garçons</t>
-  </si>
-  <si>
-    <t>Series 2 Red: Carnation</t>
-  </si>
-  <si>
-    <t>Discontinued Red series. Vintage market.</t>
+    <t>Dolce &amp; Gabbana</t>
+  </si>
+  <si>
+    <t>D&amp;G Anthology L'Amoureux 6</t>
   </si>
   <si>
     <t>Musc Shamal</t>
   </si>
   <si>
+    <t>DSH Perfumes</t>
+  </si>
+  <si>
+    <t>Rubis Rose</t>
+  </si>
+  <si>
     <t xml:space="preserve">Slightly more interesting than a plain musk, tips a bit sweet resin </t>
   </si>
   <si>
-    <t>Dolce &amp; Gabbana</t>
-  </si>
-  <si>
-    <t>D&amp;G Anthology L'Amoureux 6</t>
+    <t>https://www.dshperfumes.com</t>
   </si>
   <si>
     <t>Cuir Nu</t>
@@ -479,15 +488,6 @@
     <t xml:space="preserve">Insane </t>
   </si>
   <si>
-    <t>DSH Perfumes</t>
-  </si>
-  <si>
-    <t>Rubis Rose</t>
-  </si>
-  <si>
-    <t>https://www.dshperfumes.com</t>
-  </si>
-  <si>
     <t>Rouge Malachite</t>
   </si>
   <si>
@@ -506,13 +506,31 @@
     <t xml:space="preserve">Shouldn't like this, neroli and plain orange, but it's got something special </t>
   </si>
   <si>
+    <t>Jasmin Kusamono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain non-indolic jasmine, lovely basic floral </t>
+  </si>
+  <si>
+    <t>Thé Yulong</t>
+  </si>
+  <si>
+    <t>Same old tea</t>
+  </si>
+  <si>
+    <t>Santal Dan Sha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So generic, can't smell any notes? </t>
+  </si>
+  <si>
+    <t>Vert Malachite</t>
+  </si>
+  <si>
     <t>Samples from $6, discovery sets $25. Rubis Rose not confirmed listed; ask them.</t>
   </si>
   <si>
-    <t>Jasmin Kusamono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain non-indolic jasmine, lovely basic floral </t>
+    <t xml:space="preserve">Tuberose? Tube much. </t>
   </si>
   <si>
     <t>Ensar Oud</t>
@@ -524,10 +542,10 @@
     <t>Sells direct only.</t>
   </si>
   <si>
-    <t>Thé Yulong</t>
-  </si>
-  <si>
-    <t>Same old tea</t>
+    <t>Bleu Lazuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not at all </t>
   </si>
   <si>
     <t>Eris Parfums</t>
@@ -539,24 +557,6 @@
     <t>https://www.luckyscent.com/products/green-spell-by-eris-parfums</t>
   </si>
   <si>
-    <t>Santal Dan Sha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So generic, can't smell any notes? </t>
-  </si>
-  <si>
-    <t>Vert Malachite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuberose? Tube much. </t>
-  </si>
-  <si>
-    <t>Bleu Lazuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not at all </t>
-  </si>
-  <si>
     <t>Bois d'Encens</t>
   </si>
   <si>
@@ -572,34 +572,61 @@
     <t>Salty and oily, olive and trees? Need to try again, maybe don't like the dry down</t>
   </si>
   <si>
+    <t>Astrophil &amp; Stella</t>
+  </si>
+  <si>
+    <t>Shanghai 1930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuberose and magnolia, or green tea and plum. Optical illusion for noses. </t>
+  </si>
+  <si>
+    <t>Chloé Atelier des Fleurs</t>
+  </si>
+  <si>
+    <t>Magnolia Alba</t>
+  </si>
+  <si>
+    <t>The perfect white floral, lasts forever, doesn't smell girly</t>
+  </si>
+  <si>
     <t>Indigo Perfumery has the 50ml bottle.</t>
   </si>
   <si>
-    <t>Astrophil &amp; Stella</t>
-  </si>
-  <si>
-    <t>Shanghai 1930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuberose and magnolia, or green tea and plum. Optical illusion for noses. </t>
+    <t>Atelier des Ors</t>
+  </si>
+  <si>
+    <t>Rose Omeyyade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinda useless. Great bottle tho </t>
+  </si>
+  <si>
+    <t>Balmain</t>
+  </si>
+  <si>
+    <t>Vent Vert</t>
   </si>
   <si>
     <t>Floris</t>
   </si>
   <si>
+    <t>I love this. It's a lot and kinda wears me, but very good green.</t>
+  </si>
+  <si>
     <t>Elite</t>
   </si>
   <si>
-    <t>Chloé Atelier des Fleurs</t>
-  </si>
-  <si>
     <t>DecantX sample sold out.</t>
   </si>
   <si>
-    <t>Magnolia Alba</t>
-  </si>
-  <si>
-    <t>The perfect white floral, lasts forever, doesn't smell girly</t>
+    <t>Baruti</t>
+  </si>
+  <si>
+    <t>Hot Cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wow, metallic and starched shirts. No reason to wear it but very cool. </t>
   </si>
   <si>
     <t>Goutal</t>
@@ -611,241 +638,229 @@
     <t>Parfums Raffy</t>
   </si>
   <si>
-    <t>Atelier des Ors</t>
-  </si>
-  <si>
     <t>https://parfumsraffy.com/products/annick-goutal-gardenia-passion</t>
   </si>
   <si>
-    <t>Rose Omeyyade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinda useless. Great bottle tho </t>
-  </si>
-  <si>
-    <t>Balmain</t>
-  </si>
-  <si>
-    <t>Vent Vert</t>
-  </si>
-  <si>
-    <t>I love this. It's a lot and kinda wears me, but very good green.</t>
-  </si>
-  <si>
-    <t>Baruti</t>
-  </si>
-  <si>
-    <t>Hot Cotton</t>
+    <t>BeauFort London</t>
+  </si>
+  <si>
+    <t>Fathom V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probably a no. Eirik says vase water. Cumin? </t>
+  </si>
+  <si>
+    <t>The Grudge</t>
   </si>
   <si>
     <t>Listed, out of stock. Re-check.</t>
   </si>
   <si>
+    <t>Billie Eilish</t>
+  </si>
+  <si>
+    <t>Eilish No. 2</t>
+  </si>
+  <si>
     <t>Un Matin d'Orage</t>
   </si>
   <si>
+    <t xml:space="preserve">Opened great, weird middle, interesting end. Worth another visit. </t>
+  </si>
+  <si>
     <t>DecantX / Maple Prime</t>
   </si>
   <si>
     <t>https://www.decantx.com/products/annick-goutal-un-matin-dorage-eau-de-parfum-for-women</t>
   </si>
   <si>
-    <t xml:space="preserve">Wow, metallic and starched shirts. No reason to wear it but very cool. </t>
-  </si>
-  <si>
-    <t>BeauFort London</t>
-  </si>
-  <si>
-    <t>Fathom V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probably a no. Eirik says vase water. Cumin? </t>
+    <t>Wild Carrot Oud</t>
+  </si>
+  <si>
+    <t>Yeesh. I think it's very well crafted but 2 MUCH</t>
+  </si>
+  <si>
+    <t>Mango Yuzu Gasoline</t>
+  </si>
+  <si>
+    <t>Points for realism and saying what it is, but too strong on all counts</t>
+  </si>
+  <si>
+    <t>Boka</t>
   </si>
   <si>
     <t>Decants listed at both, sold out at both.</t>
   </si>
   <si>
+    <t>Zelen</t>
+  </si>
+  <si>
+    <t>Great zesty citrus opening but goes away immediately</t>
+  </si>
+  <si>
     <t>Granado</t>
   </si>
   <si>
     <t>Amazônico</t>
   </si>
   <si>
-    <t>The Grudge</t>
-  </si>
-  <si>
-    <t>Billie Eilish</t>
-  </si>
-  <si>
-    <t>Eilish No. 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opened great, weird middle, interesting end. Worth another visit. </t>
+    <t>Živeli</t>
+  </si>
+  <si>
+    <t>Absolute scrubber omG</t>
   </si>
   <si>
     <t>Apotecário</t>
   </si>
   <si>
-    <t>Wild Carrot Oud</t>
-  </si>
-  <si>
-    <t>Yeesh. I think it's very well crafted but 2 MUCH</t>
-  </si>
-  <si>
     <t>Boemia</t>
   </si>
   <si>
-    <t>Mango Yuzu Gasoline</t>
-  </si>
-  <si>
-    <t>Points for realism and saying what it is, but too strong on all counts</t>
+    <t>Bon Parfumeur</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A similar thing I don't like from something else idk </t>
   </si>
   <si>
     <t>Elixir 1870</t>
   </si>
   <si>
-    <t>Boka</t>
-  </si>
-  <si>
-    <t>Zelen</t>
-  </si>
-  <si>
-    <t>Great zesty citrus opening but goes away immediately</t>
+    <t>BORNTOSTANDOUT</t>
+  </si>
+  <si>
+    <t>Naked Laundry</t>
   </si>
   <si>
     <t>Époque Tropical</t>
   </si>
   <si>
-    <t>Živeli</t>
+    <t xml:space="preserve">Organic cherry cough drop </t>
   </si>
   <si>
     <t>Esplendor</t>
   </si>
   <si>
-    <t>Absolute scrubber omG</t>
+    <t>Dirty Rice</t>
+  </si>
+  <si>
+    <t>Neither dirty nor rice</t>
   </si>
   <si>
     <t>Expedição</t>
   </si>
   <si>
+    <t>Warm Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thought it was good but NO! </t>
+  </si>
+  <si>
     <t>Infusão Botânica</t>
   </si>
   <si>
-    <t>Bon Parfumeur</t>
-  </si>
-  <si>
-    <t>801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A similar thing I don't like from something else idk </t>
+    <t>Nanatopia</t>
+  </si>
+  <si>
+    <t>Banana bread no thank you</t>
   </si>
   <si>
     <t>Nostalgia</t>
   </si>
   <si>
-    <t>BORNTOSTANDOUT</t>
-  </si>
-  <si>
-    <t>Naked Laundry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic cherry cough drop </t>
-  </si>
-  <si>
     <t>Guerlain</t>
   </si>
   <si>
     <t>Cuir Intense</t>
   </si>
   <si>
-    <t>Dirty Rice</t>
-  </si>
-  <si>
-    <t>Neither dirty nor rice</t>
+    <t>Musk Cologne</t>
   </si>
   <si>
     <t>DecantX has 2ml at $8.79.</t>
   </si>
   <si>
-    <t>Warm Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thought it was good but NO! </t>
+    <t xml:space="preserve">Oh wow, the blue toothpaste I used as a child </t>
   </si>
   <si>
     <t>Santal Pao Rosa</t>
   </si>
   <si>
+    <t>Boy Smells</t>
+  </si>
+  <si>
     <t>https://www.decantx.com/products/guerlain-santal-pao-rosa-eau-de-parfum-unisex</t>
   </si>
   <si>
-    <t>Nanatopia</t>
-  </si>
-  <si>
-    <t>Banana bread no thank you</t>
-  </si>
-  <si>
-    <t>Musk Cologne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oh wow, the blue toothpaste I used as a child </t>
-  </si>
-  <si>
-    <t>Boy Smells</t>
+    <t>Rose Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another rose, nice green but sour </t>
+  </si>
+  <si>
+    <t>Gyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very not my normal thing but I'm really digging it thus far. </t>
+  </si>
+  <si>
+    <t>Le Gemme Tygar</t>
+  </si>
+  <si>
+    <t>Wow. Crazy grapefruit opening, deep ambroxan base, lasts forever. Maybe too beast but really compelling, I want to try all of them</t>
+  </si>
+  <si>
+    <t>Kilian</t>
+  </si>
+  <si>
+    <t>Imperial Tea</t>
+  </si>
+  <si>
+    <t>Smells like Nestea to me but Eirik loves it</t>
   </si>
   <si>
     <t>Only source found.</t>
   </si>
   <si>
-    <t>Rose Load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Another rose, nice green but sour </t>
+    <t>Kologne, Shield of Protection</t>
   </si>
   <si>
     <t>Jasmin Grandiflorum Extrait 30</t>
   </si>
   <si>
-    <t>Gyan</t>
+    <t>Not remembering why it was a no, but it was a no</t>
   </si>
   <si>
     <t>Your entry does not name a release. Closest is Shalimar Millesime Jasmin. Which one did you mean?</t>
   </si>
   <si>
-    <t xml:space="preserve">Very not my normal thing but I'm really digging it thus far. </t>
-  </si>
-  <si>
     <t>Eau de Guerlain</t>
   </si>
   <si>
-    <t>Le Gemme Tygar</t>
-  </si>
-  <si>
-    <t>Wow. Crazy grapefruit opening, deep ambroxan base, lasts forever. Maybe too beast but really compelling, I want to try all of them</t>
-  </si>
-  <si>
     <t>A vintage version is also listed at $6.99, likely the one you want.</t>
   </si>
   <si>
-    <t>Kilian</t>
+    <t>L'Heure Verte</t>
   </si>
   <si>
     <t>Hermès</t>
   </si>
   <si>
-    <t>Imperial Tea</t>
-  </si>
-  <si>
     <t>Hermessence Poivre Samarcande</t>
   </si>
   <si>
-    <t>Smells like Nestea to me but Eirik loves it</t>
+    <t xml:space="preserve">No idea what people are saying with absinthe and licorice. It smells fine, dna of that Angel's Share sweetness. </t>
   </si>
   <si>
     <t>Perfumeniche has the full bottle.</t>
   </si>
   <si>
-    <t>Kologne, Shield of Protection</t>
+    <t>Roses on Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ozonic cucumber, so strange. Maybe smells like cheap body spray but I don't know, I like smelling it.  </t>
   </si>
   <si>
     <t>Isabelle Larignon</t>
@@ -857,7 +872,10 @@
     <t>Also Indigo ($7.00), Perfumed Court ($6.99), Luckyscent.</t>
   </si>
   <si>
-    <t>Not remembering why it was a no, but it was a no</t>
+    <t>Rolling in Love</t>
+  </si>
+  <si>
+    <t>Almond, nice, too sweet to wear</t>
   </si>
   <si>
     <t>J.F. Schwarzlose Berlin</t>
@@ -869,43 +887,43 @@
     <t>Luckyscent carries the brand but not Trance. Possibly discontinued.</t>
   </si>
   <si>
+    <t>Byredo</t>
+  </si>
+  <si>
+    <t>Casablanca Lily</t>
+  </si>
+  <si>
     <t>Joop</t>
   </si>
   <si>
+    <t>Floral and HONEY this is irresistable</t>
+  </si>
+  <si>
     <t>Homme Absolute</t>
   </si>
   <si>
     <t>https://parfumsraffy.com</t>
   </si>
   <si>
-    <t>L'Heure Verte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No idea what people are saying with absinthe and licorice. It smells fine, dna of that Angel's Share sweetness. </t>
-  </si>
-  <si>
-    <t>Roses on Ice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ozonic cucumber, so strange. Maybe smells like cheap body spray but I don't know, I like smelling it.  </t>
-  </si>
-  <si>
-    <t>Rolling in Love</t>
-  </si>
-  <si>
-    <t>Almond, nice, too sweet to wear</t>
+    <t>La Tulipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A familiar flower I've never smelled before, surprised I love this </t>
+  </si>
+  <si>
+    <t>Open Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pot and pomelo, addictive </t>
+  </si>
+  <si>
+    <t>Cuir Obscur</t>
   </si>
   <si>
     <t>Raffy has plain Joop!. Maple Prime lists Joop! Absolute in full bottles. May not be the release you want.</t>
   </si>
   <si>
-    <t>Byredo</t>
-  </si>
-  <si>
-    <t>Casablanca Lily</t>
-  </si>
-  <si>
-    <t>Floral and HONEY this is irresistable</t>
+    <t>Amaretto to rose and leather, probably many like it but I'm into this combination</t>
   </si>
   <si>
     <t>L'Occitane</t>
@@ -914,13 +932,13 @@
     <t>Eau du Val (Magnolia)</t>
   </si>
   <si>
+    <t>Mojave Ghost</t>
+  </si>
+  <si>
     <t>Perfumed Court has Eau des Baux only.</t>
   </si>
   <si>
-    <t>La Tulipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A familiar flower I've never smelled before, surprised I love this </t>
+    <t xml:space="preserve">Subtle as to be almost indistinguishable, but nice? Not getting the hype but might try the candle or something. </t>
   </si>
   <si>
     <t>Lancôme</t>
@@ -929,10 +947,10 @@
     <t>Cuir de Lancôme</t>
   </si>
   <si>
-    <t>Open Sky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pot and pomelo, addictive </t>
+    <t>Inflorescence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very white floral, less babysitter than la tulipe </t>
   </si>
   <si>
     <t>Les Bains Guerbois</t>
@@ -941,30 +959,30 @@
     <t>Rose Graffiti</t>
   </si>
   <si>
-    <t>Cuir Obscur</t>
+    <t>Pulp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't like this fig, way too something. Coats the nose and throat </t>
   </si>
   <si>
     <t>No 1ml listed for this one.</t>
   </si>
   <si>
-    <t>Amaretto to rose and leather, probably many like it but I'm into this combination</t>
-  </si>
-  <si>
     <t>Loewe</t>
   </si>
   <si>
+    <t>Space Rage Travx</t>
+  </si>
+  <si>
     <t>Pour Homme</t>
   </si>
   <si>
-    <t>Mojave Ghost</t>
+    <t xml:space="preserve">Pulp again </t>
   </si>
   <si>
     <t>Perfumed Court carries Loewe, only Paula's Ibiza Eclectic.</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtle as to be almost indistinguishable, but nice? Not getting the hype but might try the candle or something. </t>
-  </si>
-  <si>
     <t>Maison Margiela</t>
   </si>
   <si>
@@ -974,108 +992,90 @@
     <t>Perfumeniche</t>
   </si>
   <si>
+    <t>Oud Immortel</t>
+  </si>
+  <si>
     <t>https://perfumeniche.com</t>
   </si>
   <si>
-    <t>Inflorescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very white floral, less babysitter than la tulipe </t>
-  </si>
-  <si>
-    <t>Pulp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't like this fig, way too something. Coats the nose and throat </t>
-  </si>
-  <si>
-    <t>Space Rage Travx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulp again </t>
-  </si>
-  <si>
-    <t>Oud Immortel</t>
+    <t xml:space="preserve">Dry down pretty gross. </t>
+  </si>
+  <si>
+    <t>Young Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insane citrus blast, very bad </t>
   </si>
   <si>
     <t>The original, not the L'Eau. DecantX and Perfumed Court stock only the L'Eau.</t>
   </si>
   <si>
+    <t>Bal d'Afrique</t>
+  </si>
+  <si>
     <t>Marc Jacobs</t>
   </si>
   <si>
     <t>Bang</t>
   </si>
   <si>
-    <t xml:space="preserve">Dry down pretty gross. </t>
+    <t xml:space="preserve">Good and interesting but hits me as pineapple and coconut so no </t>
   </si>
   <si>
     <t>Maya Njie</t>
   </si>
   <si>
+    <t>Desert Dawn</t>
+  </si>
+  <si>
     <t>Nordic Cedar</t>
   </si>
   <si>
-    <t>Young Rose</t>
+    <t xml:space="preserve">Boring powdery sandalwood </t>
   </si>
   <si>
     <t>https://mayanjie.com/products/discovery-set</t>
   </si>
   <si>
-    <t xml:space="preserve">Insane citrus blast, very bad </t>
-  </si>
-  <si>
-    <t>Bal d'Afrique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good and interesting but hits me as pineapple and coconut so no </t>
-  </si>
-  <si>
-    <t>Desert Dawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boring powdery sandalwood </t>
-  </si>
-  <si>
     <t>Gypsy Water</t>
   </si>
   <si>
+    <t xml:space="preserve">Lemon creamsicle, utterly gone after 15 mins </t>
+  </si>
+  <si>
+    <t>Blanche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabric softener </t>
+  </si>
+  <si>
+    <t>Pour Un Homme de Caron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beautiful lavender Fougeres, more subtle than Lav Extreme, dumb reach </t>
+  </si>
+  <si>
     <t>Discovery set. Confirm Nordic Cedar is one of the five.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lemon creamsicle, utterly gone after 15 mins </t>
+    <t>Yatagan</t>
+  </si>
+  <si>
+    <t>Like Un Homme but more animalic</t>
   </si>
   <si>
     <t>Miller Harris</t>
   </si>
   <si>
-    <t>Blanche</t>
-  </si>
-  <si>
     <t>Le Cèdre</t>
   </si>
   <si>
     <t>Miller Harris direct</t>
   </si>
   <si>
-    <t xml:space="preserve">Fabric softener </t>
-  </si>
-  <si>
     <t>https://www.millerharris.com/products/le-cedre-eau-de-parfum-sample</t>
   </si>
   <si>
-    <t>Pour Un Homme de Caron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beautiful lavender Fougeres, more subtle than Lav Extreme, dumb reach </t>
-  </si>
-  <si>
-    <t>Yatagan</t>
-  </si>
-  <si>
-    <t>Like Un Homme but more animalic</t>
-  </si>
-  <si>
     <t>Tabac Blond</t>
   </si>
   <si>
@@ -1088,105 +1088,105 @@
     <t>Sweet</t>
   </si>
   <si>
+    <t>Pour Un Homme de Caron Le Matin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boring but nice freshie </t>
+  </si>
+  <si>
+    <t>Pour Un Homme de Caron Le Soir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pretty good not great, not better than original </t>
+  </si>
+  <si>
+    <t>Caswell-Massey</t>
+  </si>
+  <si>
+    <t>Honeysuckle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfect perfect perfect. Doesn't last. </t>
+  </si>
+  <si>
     <t>No decant retailer carries Miller Harris. House sells 2ml samples.</t>
   </si>
   <si>
-    <t>Pour Un Homme de Caron Le Matin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boring but nice freshie </t>
+    <t>Orchid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure floral, old lady but not powdery. I like it! </t>
   </si>
   <si>
     <t>Wander Through the Parks</t>
   </si>
   <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Classic, linear, I really like florals from this house but not a standout rose</t>
+  </si>
+  <si>
     <t>https://www.millerharris.com</t>
   </si>
   <si>
-    <t>Pour Un Homme de Caron Le Soir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pretty good not great, not better than original </t>
-  </si>
-  <si>
-    <t>Caswell-Massey</t>
-  </si>
-  <si>
-    <t>Honeysuckle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfect perfect perfect. Doesn't last. </t>
-  </si>
-  <si>
-    <t>Orchid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure floral, old lady but not powdery. I like it! </t>
+    <t>Jockey Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JFK all the way, dumb reach, def has that old person thing in a good way but ultimately too much </t>
+  </si>
+  <si>
+    <t>Number Six</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple old man + lemon, but nice enough. Weak. </t>
+  </si>
+  <si>
+    <t>Almond</t>
   </si>
   <si>
     <t>50ml sold out, no sample listing.</t>
   </si>
   <si>
-    <t>Rose</t>
+    <t xml:space="preserve">Probably fine but I barely smell it </t>
   </si>
   <si>
     <t>Feuilles de Tabac</t>
   </si>
   <si>
-    <t>Classic, linear, I really like florals from this house but not a standout rose</t>
+    <t>Marem</t>
   </si>
   <si>
     <t>https://www.millerharris.com/products/feuilles-de-tabac-1-2ml-veil</t>
   </si>
   <si>
-    <t>Jockey Club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JFK all the way, dumb reach, def has that old person thing in a good way but ultimately too much </t>
-  </si>
-  <si>
-    <t>Number Six</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple old man + lemon, but nice enough. Weak. </t>
-  </si>
-  <si>
-    <t>Almond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probably fine but I barely smell it </t>
-  </si>
-  <si>
-    <t>Marem</t>
+    <t xml:space="preserve">Red currant, citrus and rose. Not sure what I think. </t>
+  </si>
+  <si>
+    <t>CB I Hate Perfume</t>
+  </si>
+  <si>
+    <t>To See A Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love this dirt and sunshine </t>
   </si>
   <si>
     <t>Montale</t>
   </si>
   <si>
-    <t xml:space="preserve">Red currant, citrus and rose. Not sure what I think. </t>
-  </si>
-  <si>
     <t>Intense Pepper</t>
   </si>
   <si>
-    <t>CB I Hate Perfume</t>
-  </si>
-  <si>
     <t>Twisted Lily</t>
   </si>
   <si>
-    <t>To See A Flower</t>
+    <t>A Room with a View</t>
   </si>
   <si>
     <t>https://twistedlily.com/products/intense-pepper-sample</t>
   </si>
   <si>
-    <t xml:space="preserve">Love this dirt and sunshine </t>
-  </si>
-  <si>
-    <t>A Room with a View</t>
-  </si>
-  <si>
     <t xml:space="preserve">Very intriguing, try the non water extrait. Soapy. </t>
   </si>
   <si>
@@ -1199,10 +1199,16 @@
     <t>Black March</t>
   </si>
   <si>
+    <t xml:space="preserve">Probably very good but I've smelled too many similar dirt and rain and moss ones </t>
+  </si>
+  <si>
+    <t>In the Library</t>
+  </si>
+  <si>
     <t>DecantX and Maple Prime have no sample in stock.</t>
   </si>
   <si>
-    <t xml:space="preserve">Probably very good but I've smelled too many similar dirt and rain and moss ones </t>
+    <t xml:space="preserve">Can't smell nothin, doesn't smell like a library tho </t>
   </si>
   <si>
     <t>Nest</t>
@@ -1211,13 +1217,13 @@
     <t>Black Tulip</t>
   </si>
   <si>
-    <t>In the Library</t>
-  </si>
-  <si>
     <t>Sells direct.</t>
   </si>
   <si>
-    <t xml:space="preserve">Can't smell nothin, doesn't smell like a library tho </t>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>As beautiful and complex and wearable as I could hope, not too feminine but still real Chanel</t>
   </si>
   <si>
     <t>Olfactive Studio</t>
@@ -1226,34 +1232,31 @@
     <t>Flash Back</t>
   </si>
   <si>
-    <t>Boy</t>
-  </si>
-  <si>
-    <t>As beautiful and complex and wearable as I could hope, not too feminine but still real Chanel</t>
+    <t>Paris – Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice rose </t>
   </si>
   <si>
     <t>Listed as Flashback in New York.</t>
   </si>
   <si>
-    <t>Paris – Paris</t>
-  </si>
-  <si>
     <t>One Day</t>
   </si>
   <si>
     <t>Taipei</t>
   </si>
   <si>
-    <t xml:space="preserve">Nice rose </t>
+    <t>Le Lion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No thanks </t>
   </si>
   <si>
     <t>Ministry of Scent sample sold out.</t>
   </si>
   <si>
-    <t>Le Lion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No thanks </t>
+    <t>Sycomore</t>
   </si>
   <si>
     <t>Ormonde Jayne</t>
@@ -1265,21 +1268,18 @@
     <t>Bloom has standard Montabaco at $10, not Intensivo.</t>
   </si>
   <si>
-    <t>Sycomore</t>
+    <t>31 Rue Cambon</t>
   </si>
   <si>
     <t>Paco Rabanne</t>
   </si>
   <si>
+    <t xml:space="preserve">Apparently a masterpiece. Giving it too many chances. It's diaper and sour underneath all the great stuff I smell. Drydown is better. </t>
+  </si>
+  <si>
     <t>Maple Prime has full bottles from $38.99, no small size anywhere.</t>
   </si>
   <si>
-    <t>31 Rue Cambon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apparently a masterpiece. Giving it too many chances. It's diaper and sour underneath all the great stuff I smell. Drydown is better. </t>
-  </si>
-  <si>
     <t>Duplicate of the row above.</t>
   </si>
   <si>
@@ -1310,31 +1310,43 @@
     <t>Black Tar</t>
   </si>
   <si>
+    <t>Ministry of Scent has 2ml at $7.00.</t>
+  </si>
+  <si>
     <t>Bleu de Chanel</t>
   </si>
   <si>
-    <t>Ministry of Scent has 2ml at $7.00.</t>
+    <t>Parfums Quartana</t>
+  </si>
+  <si>
+    <t>Forest of the Golden Dream</t>
   </si>
   <si>
     <t xml:space="preserve">Nice, basic cologne </t>
   </si>
   <si>
+    <t>Their own site would not load when I tried.</t>
+  </si>
+  <si>
     <t>Chasing Scents</t>
   </si>
   <si>
     <t>Tea Service</t>
   </si>
   <si>
-    <t>Parfums Quartana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sweet tea in a rubber </t>
   </si>
   <si>
-    <t>Forest of the Golden Dream</t>
-  </si>
-  <si>
-    <t>Their own site would not load when I tried.</t>
+    <t>Ierofante</t>
+  </si>
+  <si>
+    <t>Worth confirming the spelling.</t>
+  </si>
+  <si>
+    <t>Penhaligon's</t>
+  </si>
+  <si>
+    <t>Blenheim Bouquet</t>
   </si>
   <si>
     <t>Weeping Rose</t>
@@ -1343,10 +1355,7 @@
     <t xml:space="preserve">Dastardly. Nice for a literal minute then gross amber maple syrup </t>
   </si>
   <si>
-    <t>Ierofante</t>
-  </si>
-  <si>
-    <t>Worth confirming the spelling.</t>
+    <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
   </si>
   <si>
     <t>Chloé</t>
@@ -1358,15 +1367,6 @@
     <t xml:space="preserve">Sparkly and bright and rose, it's good. I think I like Chloe in general. </t>
   </si>
   <si>
-    <t>Penhaligon's</t>
-  </si>
-  <si>
-    <t>Blenheim Bouquet</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/blenheim-bouquet-by-penhaligons</t>
-  </si>
-  <si>
     <t>Sous les Pins</t>
   </si>
   <si>
@@ -1379,9 +1379,15 @@
     <t xml:space="preserve">So classic and good, not old lady, easy to wear but very feminine </t>
   </si>
   <si>
+    <t>Liquid Love</t>
+  </si>
+  <si>
     <t>Clue Perfumery</t>
   </si>
   <si>
+    <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
+  </si>
+  <si>
     <t>Dandelion Butter</t>
   </si>
   <si>
@@ -1391,64 +1397,61 @@
     <t>Amy</t>
   </si>
   <si>
+    <t>Prissana</t>
+  </si>
+  <si>
+    <t>Nefer</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
+  </si>
+  <si>
     <t>Morel Map</t>
   </si>
   <si>
-    <t>Liquid Love</t>
-  </si>
-  <si>
     <t xml:space="preserve">Damp mossy forest floor, beautiful </t>
   </si>
   <si>
-    <t>Luckyscent and Scent Split carry Penhaligon's but not this one.</t>
-  </si>
-  <si>
     <t>Warm Bulb</t>
   </si>
   <si>
     <t xml:space="preserve">I like it but I don't love it on. More of a novelty. </t>
   </si>
   <si>
-    <t>Prissana</t>
-  </si>
-  <si>
-    <t>Nefer</t>
-  </si>
-  <si>
-    <t>https://www.luckyscent.com/products/nefer-by-parfum-prissana</t>
-  </si>
-  <si>
     <t>With the Candlestick</t>
   </si>
   <si>
+    <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
+  </si>
+  <si>
     <t>Bad candy? Clumsy</t>
   </si>
   <si>
+    <t>Robert Piguet</t>
+  </si>
+  <si>
+    <t>Bandit</t>
+  </si>
+  <si>
     <t>Need to try on my skin but so nice</t>
   </si>
   <si>
+    <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
+  </si>
+  <si>
     <t>Monocle Scent Three: Sugi</t>
   </si>
   <si>
     <t xml:space="preserve">Similar to Setchu but leaves me wanting more </t>
   </si>
   <si>
-    <t>Brand and name are reversed in your sheet. Bloom lists it sold out.</t>
-  </si>
-  <si>
     <t>Series 1 Leaves: Lily</t>
   </si>
   <si>
     <t xml:space="preserve">Simple white floral but a flower I'm not that familiar with </t>
   </si>
   <si>
-    <t>Robert Piguet</t>
-  </si>
-  <si>
-    <t>Bandit</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/robert-piguet-bandi</t>
+    <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
   </si>
   <si>
     <t>Serpentine</t>
@@ -1457,6 +1460,15 @@
     <t>Nice! Probably duplicative but I could wear this.</t>
   </si>
   <si>
+    <t>Rogue Perfumery</t>
+  </si>
+  <si>
+    <t>(discovery set)</t>
+  </si>
+  <si>
+    <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
+  </si>
+  <si>
     <t>Amazingreen</t>
   </si>
   <si>
@@ -1469,24 +1481,24 @@
     <t xml:space="preserve">Really good, light and airy but incense. Wood but maybe the immortelle changes it? Could be a bottle. </t>
   </si>
   <si>
-    <t>Listed, out of stock. Perfumed Court has Fracas and Futur only.</t>
-  </si>
-  <si>
-    <t>Rogue Perfumery</t>
-  </si>
-  <si>
-    <t>(discovery set)</t>
+    <t>Rogue's own discovery set is sold out and most of their line with it.</t>
   </si>
   <si>
     <t>Vaquera: Classique Perdu</t>
   </si>
   <si>
-    <t>https://www.luckyscent.com/brands/rogue-perfumery</t>
+    <t>Romeo Gigli</t>
   </si>
   <si>
     <t>I can't tell if this is tricking me? Apparently it smells like 90s A&amp;F mall scent, but I love it. Floral but tomato leaf but something spicy? Could turn terrible, but we will see</t>
   </si>
   <si>
+    <t>Romeo di Romeo Gigli</t>
+  </si>
+  <si>
+    <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
+  </si>
+  <si>
     <t>Cologne: Anbar</t>
   </si>
   <si>
@@ -1499,22 +1511,13 @@
     <t>I liked it then didn't then did then didn't then DID!</t>
   </si>
   <si>
-    <t>Rogue's own discovery set is sold out and most of their line with it.</t>
-  </si>
-  <si>
     <t>Odeur 10</t>
   </si>
   <si>
     <t>Like a row of washing machines in action. Metal, clean, not detergent but very soapy, don't want to wear but very good</t>
   </si>
   <si>
-    <t>Romeo Gigli</t>
-  </si>
-  <si>
-    <t>Romeo di Romeo Gigli</t>
-  </si>
-  <si>
-    <t>https://parfumsraffy.com/products/romeo-gigli-perfume</t>
+    <t>Cheapest on the list.</t>
   </si>
   <si>
     <t>Monocle Scent Four: Yoyogi</t>
@@ -1523,39 +1526,36 @@
     <t>Pleasant wood, just kind of a watered down Laurel</t>
   </si>
   <si>
+    <t>Sanctuary</t>
+  </si>
+  <si>
+    <t>Javan Rhino</t>
+  </si>
+  <si>
+    <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
+  </si>
+  <si>
     <t>Dot</t>
   </si>
   <si>
     <t xml:space="preserve">Sweet and maybe well crafted but no </t>
   </si>
   <si>
-    <t>Cheapest on the list.</t>
-  </si>
-  <si>
-    <t>Sanctuary</t>
+    <t>Senyokô</t>
+  </si>
+  <si>
+    <t>Indigo Perfumery</t>
   </si>
   <si>
     <t>Incense: Ouarzazate</t>
   </si>
   <si>
-    <t>Javan Rhino</t>
+    <t>https://indigoperfumery.com</t>
   </si>
   <si>
     <t>Not as special as the others but a nice woody scent, dry down ends kinda sour</t>
   </si>
   <si>
-    <t>Could not identify this house. Zoologist makes a Rhinoceros; Scent Split has it at $7.99 for 1ml.</t>
-  </si>
-  <si>
-    <t>Senyokô</t>
-  </si>
-  <si>
-    <t>Indigo Perfumery</t>
-  </si>
-  <si>
-    <t>https://indigoperfumery.com</t>
-  </si>
-  <si>
     <t>Dia x Meg Webster</t>
   </si>
   <si>
@@ -1595,10 +1595,13 @@
     <t xml:space="preserve">Photorealistic pot smell. Amazing. Absolutely not. </t>
   </si>
   <si>
+    <t>Incense: Jaisalmer</t>
+  </si>
+  <si>
     <t>Sample listed, sold out. Maple Prime has 100ml at $76.99.</t>
   </si>
   <si>
-    <t>Incense: Jaisalmer</t>
+    <t>Incense: Avignon</t>
   </si>
   <si>
     <t>Vitriol d'Œillet</t>
@@ -1607,9 +1610,6 @@
     <t>Not at any of the three retailers that carry Serge Lutens.</t>
   </si>
   <si>
-    <t>Incense: Avignon</t>
-  </si>
-  <si>
     <t>Fils de Joie</t>
   </si>
   <si>
@@ -1625,10 +1625,31 @@
     <t>Celluloid Galbanum</t>
   </si>
   <si>
+    <t xml:space="preserve">Perfect white floral with a hint of Ziplock bags, not overly tuberose </t>
+  </si>
+  <si>
+    <t>Chlorophyll Gardenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
+  </si>
+  <si>
+    <t>Odeur 53</t>
+  </si>
+  <si>
+    <t>Mineral and clay and hot bulb, so cool</t>
+  </si>
+  <si>
+    <t>Radish Vetiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spicy, photorealistic. Maybe too odd to wear but very into it. </t>
+  </si>
+  <si>
     <t>1ml is $9.99. Discontinued from the Noire collection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Perfect white floral with a hint of Ziplock bags, not overly tuberose </t>
+    <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
   </si>
   <si>
     <t>SJP</t>
@@ -1637,76 +1658,61 @@
     <t>Stash SJP</t>
   </si>
   <si>
-    <t>Chlorophyll Gardenia</t>
-  </si>
-  <si>
     <t>MicroPerfumes / Maple Prime</t>
   </si>
   <si>
-    <t xml:space="preserve">Lovely, sour then floral. Not too much of either. Really lasts. </t>
-  </si>
-  <si>
     <t>https://microperfumes.com/products/stash-edp-sample-vial</t>
   </si>
   <si>
-    <t>Odeur 53</t>
-  </si>
-  <si>
-    <t>Mineral and clay and hot bulb, so cool</t>
-  </si>
-  <si>
-    <t>Radish Vetiver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spicy, photorealistic. Maybe too odd to wear but very into it. </t>
-  </si>
-  <si>
-    <t>Cypress and chamomile, another great wood but not near Laurel for me</t>
-  </si>
-  <si>
     <t>Blackpepper</t>
   </si>
   <si>
     <t xml:space="preserve">Black pepper for sure. Doesn't last. I'd definitely spray this on if it were around. </t>
   </si>
   <si>
+    <t>Monocle Scent One: Hinoki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced and beautiful wood, but a sourness makes me not want to wear it </t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleasant floral, not to special </t>
+  </si>
+  <si>
+    <t>Cologne: Citrico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
+  </si>
+  <si>
     <t>Sample and 10ml both sold out.</t>
   </si>
   <si>
-    <t>Monocle Scent One: Hinoki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balanced and beautiful wood, but a sourness makes me not want to wear it </t>
-  </si>
-  <si>
-    <t>Grace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pleasant floral, not to special </t>
+    <t>Cologne: Vettiveru</t>
   </si>
   <si>
     <t>Geranium Absolue</t>
   </si>
   <si>
-    <t>Cologne: Citrico</t>
+    <t xml:space="preserve">So straightforward, just vetiver </t>
   </si>
   <si>
     <t>The 7 Virtues</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleasant opening, lemon cookie dry down </t>
-  </si>
-  <si>
     <t>Vetiver Elemi</t>
   </si>
   <si>
+    <t>Monocle Scent Five: Syros</t>
+  </si>
+  <si>
     <t>Perfumed Court carries the brand, only three other scents.</t>
   </si>
   <si>
-    <t>Cologne: Vettiveru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So straightforward, just vetiver </t>
+    <t>2 much turmeric 4 me</t>
   </si>
   <si>
     <t>The House of Oud</t>
@@ -1715,25 +1721,28 @@
     <t>Almond Harmony</t>
   </si>
   <si>
+    <t>Wonderoud</t>
+  </si>
+  <si>
+    <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
+  </si>
+  <si>
     <t>Maple Prime has 75ml at $127.99.</t>
   </si>
   <si>
-    <t>Monocle Scent Five: Syros</t>
-  </si>
-  <si>
-    <t>2 much turmeric 4 me</t>
-  </si>
-  <si>
     <t>Une Nuit Nomade</t>
   </si>
   <si>
+    <t>Coqui Coqui</t>
+  </si>
+  <si>
     <t>Chemin d'Amande</t>
   </si>
   <si>
-    <t>Wonderoud</t>
-  </si>
-  <si>
-    <t>Pepper and wood, love it, doesn't last. Try wonderwoood!</t>
+    <t>Eucaced</t>
+  </si>
+  <si>
+    <t>Very brash eucalyptus and cedar. I like it?</t>
   </si>
   <si>
     <t>Universal Flowering</t>
@@ -1742,13 +1751,10 @@
     <t>Holy Hell</t>
   </si>
   <si>
-    <t>Coqui Coqui</t>
-  </si>
-  <si>
-    <t>Eucaced</t>
-  </si>
-  <si>
-    <t>Very brash eucalyptus and cedar. I like it?</t>
+    <t>Rosas Secas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tart rose but dried roses, nice! </t>
   </si>
   <si>
     <t>Viktor &amp; Rolf</t>
@@ -1760,12 +1766,6 @@
     <t>https://www.decantx.com/products/viktor-rolf-spicebomb-metallic-musk-eau-de-parfum-for-men</t>
   </si>
   <si>
-    <t>Rosas Secas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tart rose but dried roses, nice! </t>
-  </si>
-  <si>
     <t>Maderas</t>
   </si>
   <si>
@@ -1793,18 +1793,18 @@
     <t>Creed</t>
   </si>
   <si>
+    <t>Original Vetiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soapy and greens and bug spray needs more time on skin but a more wearable Guerlain </t>
+  </si>
+  <si>
     <t>Vilhelm Parfumerie</t>
   </si>
   <si>
-    <t>Original Vetiver</t>
-  </si>
-  <si>
     <t>Fleur Burlesque</t>
   </si>
   <si>
-    <t xml:space="preserve">Soapy and greens and bug spray needs more time on skin but a more wearable Guerlain </t>
-  </si>
-  <si>
     <t>https://twistedlily.com/products/fleur-burlesque-sample</t>
   </si>
   <si>
@@ -1823,52 +1823,52 @@
     <t>Czech &amp; Speake</t>
   </si>
   <si>
+    <t>Scent Split lists it sold out.</t>
+  </si>
+  <si>
     <t>No. 88</t>
   </si>
   <si>
     <t>I don't get it. Supposed to be old man British, but smells like grape Nerds to me</t>
   </si>
   <si>
+    <t>YSL</t>
+  </si>
+  <si>
+    <t>Rive Gauche Pour Homme</t>
+  </si>
+  <si>
+    <t>Only the women's Rive Gauche turns up.</t>
+  </si>
+  <si>
     <t>d'Annam</t>
   </si>
   <si>
-    <t>Scent Split lists it sold out.</t>
-  </si>
-  <si>
     <t>In the Garden</t>
   </si>
   <si>
     <t>White floral, lovely, duplicative but maybe...?</t>
   </si>
   <si>
+    <t>Kouros</t>
+  </si>
+  <si>
+    <t>Maple Prime has 100ml at $80.99, no sample anywhere.</t>
+  </si>
+  <si>
     <t>Da Lat</t>
   </si>
   <si>
-    <t>YSL</t>
-  </si>
-  <si>
-    <t>Rive Gauche Pour Homme</t>
-  </si>
-  <si>
     <t xml:space="preserve">Complex rose, liking it less the more I try it. </t>
   </si>
   <si>
-    <t>Only the women's Rive Gauche turns up.</t>
-  </si>
-  <si>
     <t>D'Orsay</t>
   </si>
   <si>
     <t>Sweet Disruption W.T.</t>
   </si>
   <si>
-    <t>Kouros</t>
-  </si>
-  <si>
     <t>Too minty</t>
-  </si>
-  <si>
-    <t>Maple Prime has 100ml at $80.99, no sample anywhere.</t>
   </si>
   <si>
     <t>D&amp;Scent Studios</t>
@@ -5750,10 +5750,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -6155,7 +6155,7 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -6324,16 +6324,16 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>32</v>
       </c>
       <c r="C6" s="10">
         <v>85.0</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="11"/>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>34</v>
@@ -6396,7 +6396,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>36</v>
@@ -6435,13 +6435,13 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="10">
         <v>40.0</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="27"/>
@@ -6549,7 +6549,7 @@
         <v>75.0</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
@@ -6579,7 +6579,7 @@
         <v>46</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="10">
         <v>75.0</v>
@@ -6651,7 +6651,7 @@
         <v>58</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="8"/>
@@ -6683,7 +6683,7 @@
         <v>58</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="8"/>
@@ -6715,7 +6715,7 @@
         <v>58</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="8"/>
@@ -6747,7 +6747,7 @@
         <v>58</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="8"/>
@@ -6857,7 +6857,7 @@
         <v>40.0</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="11"/>
@@ -6884,16 +6884,16 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C22" s="19">
         <v>82.0</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="30"/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>88</v>
@@ -6959,13 +6959,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" s="10">
         <v>70.0</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="11"/>
@@ -7067,13 +7067,13 @@
         <v>91</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C27" s="10">
         <v>83.0</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
@@ -7103,13 +7103,13 @@
         <v>91</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="10">
         <v>65.0</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="11"/>
@@ -7136,16 +7136,16 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C29" s="10">
         <v>45.0</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="27"/>
@@ -7172,7 +7172,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>118</v>
@@ -7208,7 +7208,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>120</v>
@@ -7280,16 +7280,16 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C33" s="10">
         <v>60.0</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E33" s="26"/>
       <c r="F33" s="11"/>
@@ -7316,16 +7316,16 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C34" s="10">
         <v>60.0</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="11"/>
@@ -7352,7 +7352,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>136</v>
@@ -7427,13 +7427,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C37" s="10">
         <v>88.0</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="11"/>
@@ -7463,13 +7463,13 @@
         <v>138</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C38" s="10">
         <v>86.0</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="11"/>
@@ -7499,13 +7499,13 @@
         <v>138</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C39" s="10">
         <v>87.0</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="11"/>
@@ -7535,13 +7535,13 @@
         <v>138</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C40" s="10">
         <v>60.0</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="11"/>
@@ -7679,13 +7679,13 @@
         <v>138</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C44" s="10">
         <v>90.0</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="11"/>
@@ -7715,13 +7715,13 @@
         <v>138</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C45" s="10">
         <v>82.0</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="11"/>
@@ -7751,13 +7751,13 @@
         <v>138</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C46" s="10">
         <v>82.0</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="11"/>
@@ -7787,13 +7787,13 @@
         <v>138</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C47" s="10">
         <v>84.0</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="11"/>
@@ -7823,13 +7823,13 @@
         <v>138</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C48" s="10">
         <v>78.0</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="11"/>
@@ -7928,16 +7928,16 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C51" s="10">
         <v>82.0</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E51" s="16"/>
       <c r="F51" s="11"/>
@@ -7964,16 +7964,16 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C52" s="10">
         <v>87.0</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="11"/>
@@ -8000,16 +8000,16 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C53" s="10">
         <v>60.0</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="11"/>
@@ -8036,16 +8036,16 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C54" s="10">
         <v>90.0</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="11"/>
@@ -8072,16 +8072,16 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="27" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C55" s="10">
         <v>88.0</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E55" s="27"/>
       <c r="F55" s="36"/>
@@ -8108,16 +8108,16 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="27" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C56" s="10">
         <v>82.0</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E56" s="27"/>
       <c r="F56" s="27"/>
@@ -8143,11 +8143,11 @@
       <c r="Z56" s="24"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="B57" s="38" t="s">
-        <v>219</v>
+      <c r="A57" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="37" t="s">
+        <v>212</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="27"/>
@@ -8176,16 +8176,16 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C58" s="10">
         <v>69.0</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="11"/>
@@ -8212,16 +8212,16 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C59" s="10">
         <v>81.0</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="11"/>
@@ -8248,16 +8248,16 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C60" s="10">
         <v>88.0</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="27"/>
@@ -8284,16 +8284,16 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="27" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C61" s="10">
         <v>87.0</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E61" s="27"/>
       <c r="F61" s="27"/>
@@ -8320,16 +8320,16 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" s="27" t="s">
         <v>230</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>234</v>
       </c>
       <c r="C62" s="40">
         <v>40.0</v>
       </c>
       <c r="D62" s="41" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E62" s="27"/>
       <c r="F62" s="27"/>
@@ -8356,16 +8356,16 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="20" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C63" s="10">
         <v>80.0</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E63" s="27"/>
       <c r="F63" s="27"/>
@@ -8392,16 +8392,16 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="26" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C64" s="10">
         <v>50.0</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="11"/>
@@ -8428,16 +8428,16 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" s="16" t="s">
         <v>243</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>248</v>
       </c>
       <c r="C65" s="10">
         <v>40.0</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E65" s="16"/>
       <c r="F65" s="11"/>
@@ -8464,16 +8464,16 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C66" s="10">
         <v>40.0</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="11"/>
@@ -8500,16 +8500,16 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="18" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C67" s="19">
         <v>40.0</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="23"/>
@@ -8536,16 +8536,16 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C68" s="10">
         <v>65.0</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="11"/>
@@ -8572,16 +8572,16 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C69" s="10">
         <v>85.0</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="11"/>
@@ -8608,16 +8608,16 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C70" s="10">
         <v>88.0</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="11"/>
@@ -8644,16 +8644,16 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C71" s="10">
         <v>88.0</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="11"/>
@@ -8680,16 +8680,16 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C72" s="10">
         <v>50.0</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E72" s="26"/>
       <c r="F72" s="11"/>
@@ -8716,16 +8716,16 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C73" s="43">
         <v>50.0</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E73" s="16"/>
       <c r="F73" s="44"/>
@@ -8752,16 +8752,16 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C74" s="10">
         <v>50.0</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="11"/>
@@ -8788,16 +8788,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C75" s="10">
         <v>84.0</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="11"/>
@@ -8824,16 +8824,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C76" s="10">
         <v>60.0</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E76" s="16"/>
       <c r="F76" s="11"/>
@@ -8860,16 +8860,16 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="15" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C77" s="10">
         <v>99.0</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="11"/>
@@ -8896,16 +8896,16 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C78" s="10">
         <v>90.0</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="11"/>
@@ -8932,16 +8932,16 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C79" s="10">
         <v>89.0</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E79" s="16"/>
       <c r="F79" s="11"/>
@@ -8968,16 +8968,16 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C80" s="10">
         <v>86.0</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="11"/>
@@ -9004,16 +9004,16 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C81" s="10">
         <v>84.0</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="11"/>
@@ -9040,16 +9040,16 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C82" s="10">
         <v>83.0</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="11"/>
@@ -9076,16 +9076,16 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C83" s="10">
         <v>83.0</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E83" s="8"/>
       <c r="F83" s="11"/>
@@ -9112,16 +9112,16 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C84" s="10">
         <v>82.0</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="11"/>
@@ -9148,16 +9148,16 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B85" s="47" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C85" s="10">
         <v>81.0</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="11"/>
@@ -9184,16 +9184,16 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C86" s="10">
         <v>80.0</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="E86" s="8"/>
       <c r="F86" s="11"/>
@@ -9220,16 +9220,16 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C87" s="10">
         <v>79.0</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="11"/>
@@ -9256,16 +9256,16 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C88" s="10">
         <v>74.0</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="11"/>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>341</v>
@@ -9301,7 +9301,7 @@
         <v>71.0</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E89" s="8"/>
       <c r="F89" s="11"/>
@@ -9328,16 +9328,16 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C90" s="10">
         <v>70.0</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="11"/>
@@ -9364,16 +9364,16 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C91" s="10">
         <v>96.0</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E91" s="8"/>
       <c r="F91" s="11"/>
@@ -9400,16 +9400,16 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C92" s="10">
         <v>89.0</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="11"/>
@@ -9436,7 +9436,7 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>354</v>
@@ -9472,7 +9472,7 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>356</v>
@@ -9508,16 +9508,16 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C95" s="10">
         <v>83.0</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E95" s="8"/>
       <c r="F95" s="11"/>
@@ -9544,16 +9544,16 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C96" s="10">
         <v>83.0</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E96" s="8"/>
       <c r="F96" s="11"/>
@@ -9580,16 +9580,16 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C97" s="10">
         <v>93.0</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="11"/>
@@ -9616,16 +9616,16 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C98" s="10">
         <v>91.0</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="11"/>
@@ -9652,16 +9652,16 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C99" s="10">
         <v>87.0</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E99" s="16"/>
       <c r="F99" s="11"/>
@@ -9688,16 +9688,16 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C100" s="10">
         <v>85.0</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="11"/>
@@ -9724,16 +9724,16 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C101" s="10">
         <v>82.0</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E101" s="8"/>
       <c r="F101" s="11"/>
@@ -9760,16 +9760,16 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C102" s="10">
         <v>80.0</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E102" s="8"/>
       <c r="F102" s="11"/>
@@ -9796,14 +9796,14 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E103" s="8"/>
       <c r="F103" s="11"/>
@@ -9830,16 +9830,16 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C104" s="10">
         <v>89.0</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="11"/>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C105" s="10">
         <v>85.0</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>392</v>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>394</v>
@@ -9947,7 +9947,7 @@
         <v>82.0</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="11"/>
@@ -9974,16 +9974,16 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C108" s="10">
         <v>70.0</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E108" s="8"/>
       <c r="F108" s="11"/>
@@ -10010,16 +10010,16 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C109" s="10">
         <v>88.0</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E109" s="8"/>
       <c r="F109" s="11"/>
@@ -10046,16 +10046,16 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C110" s="10">
         <v>82.0</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E110" s="8"/>
       <c r="F110" s="11"/>
@@ -10082,16 +10082,16 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C111" s="10">
         <v>74.0</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E111" s="8"/>
       <c r="F111" s="11"/>
@@ -10118,16 +10118,16 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C112" s="10">
         <v>74.0</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E112" s="8"/>
       <c r="F112" s="11"/>
@@ -10154,16 +10154,16 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C113" s="10">
         <v>71.0</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E113" s="8"/>
       <c r="F113" s="11"/>
@@ -10190,7 +10190,7 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B114" s="16" t="s">
         <v>423</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B115" s="16" t="s">
         <v>428</v>
@@ -10262,16 +10262,16 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C116" s="10">
         <v>80.0</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E116" s="8"/>
       <c r="F116" s="11"/>
@@ -10298,16 +10298,16 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="27" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C117" s="10">
         <v>74.0</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E117" s="27"/>
       <c r="F117" s="27"/>
@@ -10334,16 +10334,16 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="27" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C118" s="10">
         <v>71.0</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E118" s="27"/>
       <c r="F118" s="27"/>
@@ -10370,16 +10370,16 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C119" s="10">
         <v>89.0</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E119" s="8"/>
       <c r="F119" s="11"/>
@@ -10406,7 +10406,7 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>451</v>
@@ -10442,7 +10442,7 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B121" s="16" t="s">
         <v>453</v>
@@ -10478,19 +10478,19 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C122" s="43">
         <v>90.0</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E122" s="48" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F122" s="8"/>
       <c r="G122" s="49"/>
@@ -10516,16 +10516,16 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C123" s="10">
         <v>90.0</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E123" s="8"/>
       <c r="F123" s="11"/>
@@ -10552,16 +10552,16 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="36" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C124" s="10">
         <v>70.0</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E124" s="27"/>
       <c r="F124" s="36"/>
@@ -10588,7 +10588,7 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>468</v>
@@ -10597,7 +10597,7 @@
         <v>55.0</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E125" s="8"/>
       <c r="F125" s="27"/>
@@ -10624,16 +10624,16 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C126" s="10">
         <v>88.0</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E126" s="8"/>
       <c r="F126" s="11"/>
@@ -10660,16 +10660,16 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B127" s="20" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C127" s="10">
         <v>87.0</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E127" s="27"/>
       <c r="F127" s="27"/>
@@ -10696,16 +10696,16 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C128" s="10">
         <v>91.0</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E128" s="27"/>
       <c r="F128" s="27"/>
@@ -10732,16 +10732,16 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C129" s="19">
         <v>89.0</v>
       </c>
       <c r="D129" s="20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E129" s="22"/>
       <c r="F129" s="50"/>
@@ -10768,16 +10768,16 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C130" s="10">
         <v>50.0</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E130" s="8"/>
       <c r="F130" s="11"/>
@@ -10804,16 +10804,16 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C131" s="10">
         <v>91.0</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E131" s="27"/>
       <c r="F131" s="27"/>
@@ -10840,16 +10840,16 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C132" s="10">
         <v>91.0</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E132" s="27"/>
       <c r="F132" s="27"/>
@@ -10876,16 +10876,16 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C133" s="10">
         <v>90.0</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E133" s="27"/>
       <c r="F133" s="27"/>
@@ -10912,16 +10912,16 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C134" s="10">
         <v>89.0</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E134" s="27"/>
       <c r="F134" s="27"/>
@@ -10948,16 +10948,16 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C135" s="10">
         <v>88.0</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E135" s="27"/>
       <c r="F135" s="27"/>
@@ -10984,16 +10984,16 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C136" s="10">
         <v>87.0</v>
       </c>
       <c r="D136" s="27" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E136" s="27"/>
       <c r="F136" s="27"/>
@@ -11020,16 +11020,16 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C137" s="10">
         <v>86.0</v>
       </c>
       <c r="D137" s="27" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E137" s="27"/>
       <c r="F137" s="27"/>
@@ -11056,16 +11056,16 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B138" s="36" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C138" s="10">
         <v>85.0</v>
       </c>
       <c r="D138" s="27" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E138" s="27"/>
       <c r="F138" s="27"/>
@@ -11092,7 +11092,7 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B139" s="36" t="s">
         <v>514</v>
@@ -11128,7 +11128,7 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B140" s="36" t="s">
         <v>516</v>
@@ -11164,7 +11164,7 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B141" s="36" t="s">
         <v>518</v>
@@ -11200,7 +11200,7 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B142" s="36" t="s">
         <v>524</v>
@@ -11236,10 +11236,10 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B143" s="26" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C143" s="10">
         <v>70.0</v>
@@ -11272,10 +11272,10 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B144" s="53" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C144" s="10"/>
       <c r="D144" s="27"/>
@@ -11304,10 +11304,10 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B145" s="53" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="27"/>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B146" s="55" t="s">
         <v>534</v>
@@ -11372,7 +11372,7 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B147" s="15" t="s">
         <v>536</v>
@@ -11381,7 +11381,7 @@
         <v>94.0</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E147" s="8"/>
       <c r="F147" s="11"/>
@@ -11408,16 +11408,16 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C148" s="10">
         <v>91.0</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E148" s="8"/>
       <c r="F148" s="11"/>
@@ -11444,16 +11444,16 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B149" s="36" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C149" s="10">
         <v>90.0</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="E149" s="8"/>
       <c r="F149" s="11"/>
@@ -11480,16 +11480,16 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C150" s="10">
         <v>89.0</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E150" s="8"/>
       <c r="F150" s="11"/>
@@ -11516,16 +11516,16 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C151" s="10">
         <v>88.0</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E151" s="8"/>
       <c r="F151" s="11"/>
@@ -11552,7 +11552,7 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B152" s="27" t="s">
         <v>550</v>
@@ -11588,16 +11588,16 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C153" s="10">
         <v>86.0</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E153" s="8"/>
       <c r="F153" s="11"/>
@@ -11624,16 +11624,16 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C154" s="10">
         <v>86.0</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E154" s="8"/>
       <c r="F154" s="11"/>
@@ -11660,16 +11660,16 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C155" s="10">
         <v>85.0</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E155" s="8"/>
       <c r="F155" s="11"/>
@@ -11696,16 +11696,16 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C156" s="10">
         <v>85.0</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E156" s="8"/>
       <c r="F156" s="11"/>
@@ -11732,16 +11732,16 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B157" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C157" s="10">
         <v>84.0</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E157" s="8"/>
       <c r="F157" s="11"/>
@@ -11768,16 +11768,16 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C158" s="10">
         <v>83.0</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E158" s="8"/>
       <c r="F158" s="11"/>
@@ -11804,16 +11804,16 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C159" s="10">
         <v>89.0</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E159" s="8"/>
       <c r="F159" s="11"/>
@@ -11840,16 +11840,16 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="27" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B160" s="36" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C160" s="10">
         <v>89.0</v>
       </c>
       <c r="D160" s="27" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E160" s="27"/>
       <c r="F160" s="27"/>
@@ -11876,7 +11876,7 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="8" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B161" s="8" t="s">
         <v>584</v>
@@ -11987,13 +11987,13 @@
         <v>592</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C164" s="10">
         <v>70.0</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E164" s="8"/>
       <c r="F164" s="11"/>
@@ -12095,13 +12095,13 @@
         <v>602</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C167" s="10">
         <v>79.0</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E167" s="16"/>
       <c r="F167" s="11"/>
@@ -12128,16 +12128,16 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="8" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B168" s="16" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C168" s="10">
         <v>88.0</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E168" s="16"/>
       <c r="F168" s="11"/>
@@ -12164,16 +12164,16 @@
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="8" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C169" s="10">
         <v>65.0</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E169" s="16"/>
       <c r="F169" s="11"/>
@@ -12200,16 +12200,16 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="18" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C170" s="19">
         <v>80.0</v>
       </c>
       <c r="D170" s="20" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E170" s="22"/>
       <c r="F170" s="30"/>
@@ -12918,10 +12918,10 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="B190" s="20" t="s">
         <v>243</v>
-      </c>
-      <c r="B190" s="20" t="s">
-        <v>248</v>
       </c>
       <c r="C190" s="43">
         <v>78.0</v>
@@ -12930,7 +12930,7 @@
         <v>660</v>
       </c>
       <c r="E190" s="48" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="49"/>
@@ -13606,7 +13606,7 @@
       <c r="A209" s="64" t="s">
         <v>667</v>
       </c>
-      <c r="B209" s="38" t="s">
+      <c r="B209" s="37" t="s">
         <v>700</v>
       </c>
       <c r="C209" s="10"/>
@@ -13636,7 +13636,7 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B210" s="8" t="s">
         <v>701</v>
@@ -13672,7 +13672,7 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B211" s="8" t="s">
         <v>703</v>
@@ -13708,7 +13708,7 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B212" s="59" t="s">
         <v>705</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B213" s="8" t="s">
         <v>707</v>
@@ -13780,7 +13780,7 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B214" s="8" t="s">
         <v>709</v>
@@ -13816,7 +13816,7 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B215" s="16" t="s">
         <v>711</v>
@@ -13852,7 +13852,7 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>713</v>
@@ -13888,7 +13888,7 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B217" s="65" t="s">
         <v>715</v>
@@ -13920,7 +13920,7 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B218" s="65" t="s">
         <v>716</v>
@@ -13952,7 +13952,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B219" s="65" t="s">
         <v>717</v>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B220" s="65" t="s">
         <v>718</v>
@@ -14016,7 +14016,7 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B221" s="65" t="s">
         <v>719</v>
@@ -14048,7 +14048,7 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B222" s="65" t="s">
         <v>720</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B223" s="65" t="s">
         <v>721</v>
@@ -14112,7 +14112,7 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B224" s="65" t="s">
         <v>722</v>
@@ -14144,7 +14144,7 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B225" s="65" t="s">
         <v>723</v>
@@ -14176,7 +14176,7 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B226" s="65" t="s">
         <v>724</v>
@@ -14208,7 +14208,7 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B227" s="65" t="s">
         <v>725</v>
@@ -14240,7 +14240,7 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B228" s="66" t="s">
         <v>726</v>
@@ -14272,7 +14272,7 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B229" s="65" t="s">
         <v>727</v>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B230" s="65" t="s">
         <v>728</v>
@@ -14336,7 +14336,7 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B231" s="65" t="s">
         <v>729</v>
@@ -14368,7 +14368,7 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B232" s="65" t="s">
         <v>730</v>
@@ -14400,7 +14400,7 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B233" s="65" t="s">
         <v>731</v>
@@ -14432,7 +14432,7 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B234" s="65" t="s">
         <v>732</v>
@@ -14464,7 +14464,7 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B235" s="65" t="s">
         <v>733</v>
@@ -14496,7 +14496,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B236" s="65" t="s">
         <v>734</v>
@@ -14528,7 +14528,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B237" s="65" t="s">
         <v>735</v>
@@ -14560,7 +14560,7 @@
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B238" s="65" t="s">
         <v>736</v>
@@ -14592,7 +14592,7 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B239" s="65" t="s">
         <v>737</v>
@@ -14624,7 +14624,7 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B240" s="65" t="s">
         <v>738</v>
@@ -14656,7 +14656,7 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B241" s="65" t="s">
         <v>739</v>
@@ -15408,7 +15408,7 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="36" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B262" s="36" t="s">
         <v>788</v>
@@ -15444,7 +15444,7 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="70" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B263" s="70" t="s">
         <v>790</v>
@@ -15478,7 +15478,7 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="70" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B264" s="70" t="s">
         <v>792</v>
@@ -16512,7 +16512,7 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="8" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B293" s="8" t="s">
         <v>853</v>
@@ -16548,10 +16548,10 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="8" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B294" s="16" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C294" s="10">
         <v>87.0</v>
@@ -16656,7 +16656,7 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="15" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B297" s="15" t="s">
         <v>861</v>
@@ -16692,7 +16692,7 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B298" s="27" t="s">
         <v>863</v>
@@ -16728,7 +16728,7 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B299" s="8" t="s">
         <v>865</v>
@@ -16764,7 +16764,7 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B300" s="27" t="s">
         <v>867</v>
@@ -16800,10 +16800,10 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B301" s="27" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C301" s="10">
         <v>87.0</v>
@@ -16836,7 +16836,7 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B302" s="27" t="s">
         <v>870</v>
@@ -16872,7 +16872,7 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B303" s="27" t="s">
         <v>872</v>
@@ -16908,7 +16908,7 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B304" s="27" t="s">
         <v>874</v>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B305" s="27" t="s">
         <v>876</v>
@@ -16980,7 +16980,7 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B306" s="36" t="s">
         <v>878</v>
@@ -17016,7 +17016,7 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B307" s="27" t="s">
         <v>880</v>
@@ -17052,7 +17052,7 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B308" s="27" t="s">
         <v>882</v>
@@ -17088,7 +17088,7 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B309" s="27" t="s">
         <v>883</v>
@@ -17124,7 +17124,7 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B310" s="27" t="s">
         <v>884</v>
@@ -17160,7 +17160,7 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B311" s="27" t="s">
         <v>885</v>
@@ -17196,10 +17196,10 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="27" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B312" s="27" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C312" s="10">
         <v>83.0</v>
@@ -17232,7 +17232,7 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="36" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B313" s="36" t="s">
         <v>888</v>
@@ -17268,7 +17268,7 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B314" s="8" t="s">
         <v>890</v>
@@ -17304,7 +17304,7 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B315" s="8" t="s">
         <v>892</v>
@@ -17340,7 +17340,7 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B316" s="26" t="s">
         <v>894</v>
@@ -17376,7 +17376,7 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B317" s="26" t="s">
         <v>896</v>
@@ -17412,7 +17412,7 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B318" s="26" t="s">
         <v>898</v>
@@ -17448,7 +17448,7 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B319" s="67" t="s">
         <v>900</v>
@@ -17484,7 +17484,7 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B320" s="16" t="s">
         <v>902</v>
@@ -17520,7 +17520,7 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B321" s="16" t="s">
         <v>904</v>
@@ -17556,7 +17556,7 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B322" s="8" t="s">
         <v>906</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B323" s="16" t="s">
         <v>908</v>
@@ -17628,7 +17628,7 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B324" s="8" t="s">
         <v>910</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B325" s="8" t="s">
         <v>912</v>
@@ -18060,7 +18060,7 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="15" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B336" s="15" t="s">
         <v>936</v>
@@ -18096,7 +18096,7 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B337" s="26" t="s">
         <v>938</v>
@@ -18132,7 +18132,7 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B338" s="16" t="s">
         <v>940</v>
@@ -18168,7 +18168,7 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B339" s="8" t="s">
         <v>942</v>
@@ -18204,7 +18204,7 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="27" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B340" s="60" t="s">
         <v>944</v>
@@ -18240,7 +18240,7 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B341" s="16" t="s">
         <v>946</v>
@@ -18276,7 +18276,7 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B342" s="34" t="s">
         <v>948</v>
@@ -18312,7 +18312,7 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B343" s="26" t="s">
         <v>950</v>
@@ -18348,7 +18348,7 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B344" s="8" t="s">
         <v>952</v>
@@ -18384,7 +18384,7 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B345" s="8" t="s">
         <v>954</v>
@@ -18420,7 +18420,7 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B346" s="8" t="s">
         <v>956</v>
@@ -18456,7 +18456,7 @@
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="27" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B347" s="60" t="s">
         <v>958</v>
@@ -18492,7 +18492,7 @@
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="27" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B348" s="27" t="s">
         <v>960</v>
@@ -20328,7 +20328,7 @@
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B399" s="8" t="s">
         <v>1077</v>
@@ -20364,7 +20364,7 @@
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B400" s="8" t="s">
         <v>1079</v>
@@ -20652,7 +20652,7 @@
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="76" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B408" s="27" t="s">
         <v>1100</v>
@@ -20688,7 +20688,7 @@
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="26" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B409" s="8" t="s">
         <v>1102</v>
@@ -20832,7 +20832,7 @@
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B413" s="8" t="s">
         <v>1112</v>
@@ -20868,7 +20868,7 @@
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B414" s="8" t="s">
         <v>1114</v>
@@ -20904,7 +20904,7 @@
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B415" s="8" t="s">
         <v>1116</v>
@@ -21228,7 +21228,7 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B424" s="8" t="s">
         <v>1136</v>
@@ -22020,7 +22020,7 @@
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B446" s="80" t="s">
         <v>1182</v>
@@ -22056,7 +22056,7 @@
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B447" s="8" t="s">
         <v>1184</v>
@@ -22092,7 +22092,7 @@
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B448" s="8" t="s">
         <v>1186</v>
@@ -22488,7 +22488,7 @@
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B459" s="8" t="s">
         <v>1213</v>
@@ -22884,7 +22884,7 @@
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="36" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B470" s="36" t="s">
         <v>1238</v>
@@ -22920,7 +22920,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B471" s="8" t="s">
         <v>1240</v>
@@ -22956,7 +22956,7 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B472" s="8" t="s">
         <v>1242</v>
@@ -22992,7 +22992,7 @@
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B473" s="8" t="s">
         <v>1244</v>
@@ -23028,7 +23028,7 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B474" s="8" t="s">
         <v>1246</v>
@@ -23064,7 +23064,7 @@
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B475" s="8" t="s">
         <v>1248</v>
@@ -23100,7 +23100,7 @@
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B476" s="8" t="s">
         <v>1250</v>
@@ -23136,7 +23136,7 @@
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B477" s="8" t="s">
         <v>1252</v>
@@ -23172,7 +23172,7 @@
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B478" s="8" t="s">
         <v>1254</v>
@@ -23676,7 +23676,7 @@
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="8" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B492" s="16" t="s">
         <v>1288</v>
@@ -23784,7 +23784,7 @@
     </row>
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="20" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B495" s="20" t="s">
         <v>1295</v>
@@ -23796,7 +23796,7 @@
         <v>1296</v>
       </c>
       <c r="E495" s="48" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F495" s="8"/>
       <c r="G495" s="49"/>
@@ -25172,7 +25172,7 @@
     </row>
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B534" s="8" t="s">
         <v>1378</v>
@@ -25208,7 +25208,7 @@
     </row>
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="27" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B535" s="27" t="s">
         <v>1380</v>
@@ -25424,7 +25424,7 @@
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B541" s="36" t="s">
         <v>1393</v>
@@ -25460,7 +25460,7 @@
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B542" s="36" t="s">
         <v>1395</v>
@@ -25496,7 +25496,7 @@
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B543" s="36" t="s">
         <v>1397</v>
@@ -25532,7 +25532,7 @@
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B544" s="36" t="s">
         <v>1399</v>
@@ -25568,7 +25568,7 @@
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B545" s="36" t="s">
         <v>1401</v>
@@ -25604,7 +25604,7 @@
     </row>
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B546" s="36" t="s">
         <v>1403</v>
@@ -25640,7 +25640,7 @@
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="24" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B547" s="27" t="s">
         <v>1405</v>
@@ -25676,7 +25676,7 @@
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B548" s="8" t="s">
         <v>1407</v>
@@ -25712,7 +25712,7 @@
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B549" s="8" t="s">
         <v>1409</v>
@@ -26288,7 +26288,7 @@
     </row>
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B565" s="8" t="s">
         <v>1446</v>
@@ -26324,7 +26324,7 @@
     </row>
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B566" s="8" t="s">
         <v>1018</v>
@@ -27294,7 +27294,7 @@
     </row>
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B593" s="16" t="s">
         <v>1517</v>
@@ -27330,7 +27330,7 @@
     </row>
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B594" s="16" t="s">
         <v>1519</v>
@@ -27366,7 +27366,7 @@
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="61" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B595" s="61" t="s">
         <v>1521</v>
@@ -27402,7 +27402,7 @@
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B596" s="8" t="s">
         <v>1523</v>
@@ -27546,7 +27546,7 @@
     </row>
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="31" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B600" s="26" t="s">
         <v>1533</v>
@@ -28088,7 +28088,7 @@
     </row>
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="20" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B615" s="20" t="s">
         <v>1566</v>
@@ -30436,7 +30436,7 @@
     </row>
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B680" s="8" t="s">
         <v>1705</v>
@@ -30472,7 +30472,7 @@
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="27" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B681" s="27" t="s">
         <v>1707</v>
@@ -30508,7 +30508,7 @@
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="18" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B682" s="18" t="s">
         <v>1709</v>
@@ -30544,7 +30544,7 @@
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="18" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B683" s="27" t="s">
         <v>1711</v>
@@ -30652,7 +30652,7 @@
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B686" s="8" t="s">
         <v>1718</v>
@@ -30688,7 +30688,7 @@
     </row>
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B687" s="16" t="s">
         <v>1720</v>
@@ -30724,7 +30724,7 @@
     </row>
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="77" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B688" s="8" t="s">
         <v>1722</v>
@@ -30760,7 +30760,7 @@
     </row>
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B689" s="34" t="s">
         <v>1724</v>
@@ -30796,7 +30796,7 @@
     </row>
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B690" s="8" t="s">
         <v>1726</v>
@@ -31048,7 +31048,7 @@
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B697" s="27" t="s">
         <v>1743</v>
@@ -31084,7 +31084,7 @@
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B698" s="27" t="s">
         <v>1745</v>
@@ -31120,7 +31120,7 @@
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B699" s="27" t="s">
         <v>1747</v>
@@ -31156,7 +31156,7 @@
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B700" s="27" t="s">
         <v>1749</v>
@@ -31192,7 +31192,7 @@
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B701" s="27" t="s">
         <v>1751</v>
@@ -31228,7 +31228,7 @@
     </row>
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B702" s="27" t="s">
         <v>1753</v>
@@ -31264,7 +31264,7 @@
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="27" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B703" s="27" t="s">
         <v>1755</v>
@@ -31300,7 +31300,7 @@
     </row>
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="8" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B704" s="8" t="s">
         <v>1757</v>
@@ -31336,7 +31336,7 @@
     </row>
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="52" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B705" s="52" t="s">
         <v>1759</v>
@@ -38362,13 +38362,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -38466,16 +38466,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -38535,7 +38535,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>54</v>
@@ -38544,10 +38544,10 @@
         <v>44</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -38572,10 +38572,10 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>14</v>
@@ -38584,7 +38584,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -38609,19 +38609,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="D8" s="21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -38646,16 +38646,16 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>90</v>
@@ -38683,19 +38683,19 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>97</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -38720,15 +38720,15 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -38753,15 +38753,15 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -38786,16 +38786,16 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
@@ -38821,15 +38821,15 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -38854,19 +38854,19 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>135</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -38891,15 +38891,15 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -38924,10 +38924,10 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -38955,19 +38955,19 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>157</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
@@ -38992,15 +38992,15 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -39025,19 +39025,19 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -39062,19 +39062,19 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
@@ -39099,19 +39099,19 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
@@ -39136,19 +39136,19 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
@@ -39172,11 +39172,11 @@
       <c r="Y23" s="24"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="37" t="s">
-        <v>217</v>
+      <c r="A24" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>44</v>
@@ -39205,11 +39205,11 @@
       <c r="Y24" s="24"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="37" t="s">
-        <v>217</v>
+      <c r="A25" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>44</v>
@@ -39238,11 +39238,11 @@
       <c r="Y25" s="24"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="37" t="s">
-        <v>217</v>
+      <c r="A26" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>44</v>
@@ -39271,11 +39271,11 @@
       <c r="Y26" s="24"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="37" t="s">
-        <v>217</v>
+      <c r="A27" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>44</v>
@@ -39304,11 +39304,11 @@
       <c r="Y27" s="24"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="37" t="s">
-        <v>217</v>
+      <c r="A28" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>44</v>
@@ -39337,11 +39337,11 @@
       <c r="Y28" s="24"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="37" t="s">
-        <v>217</v>
+      <c r="A29" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>44</v>
@@ -39370,11 +39370,11 @@
       <c r="Y29" s="24"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="37" t="s">
-        <v>217</v>
+      <c r="A30" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>44</v>
@@ -39403,11 +39403,11 @@
       <c r="Y30" s="24"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="37" t="s">
-        <v>217</v>
+      <c r="A31" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>44</v>
@@ -39436,11 +39436,11 @@
       <c r="Y31" s="24"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="37" t="s">
-        <v>217</v>
+      <c r="A32" s="38" t="s">
+        <v>228</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>44</v>
@@ -39470,10 +39470,10 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>14</v>
@@ -39482,7 +39482,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -39507,19 +39507,19 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
@@ -39544,10 +39544,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>14</v>
@@ -39556,7 +39556,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
@@ -39580,10 +39580,10 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>14</v>
@@ -39592,7 +39592,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
@@ -39617,19 +39617,19 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
@@ -39654,19 +39654,19 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
@@ -39691,15 +39691,15 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
@@ -39724,19 +39724,19 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -39761,15 +39761,15 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
@@ -39794,10 +39794,10 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -39825,19 +39825,19 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="9" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
@@ -39862,15 +39862,15 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
@@ -39895,19 +39895,19 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="9" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
@@ -39932,10 +39932,10 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -39963,19 +39963,19 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
@@ -40000,19 +40000,19 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
@@ -40037,19 +40037,19 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
@@ -40074,16 +40074,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
@@ -40109,19 +40109,19 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="9" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
@@ -40146,15 +40146,15 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
@@ -40179,19 +40179,19 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
@@ -40216,10 +40216,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>14</v>
@@ -40228,7 +40228,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
@@ -40253,19 +40253,19 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
@@ -40290,15 +40290,15 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
@@ -40323,10 +40323,10 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -40362,10 +40362,10 @@
         <v>426</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>427</v>
@@ -40399,13 +40399,13 @@
         <v>431</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
@@ -40430,15 +40430,15 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
@@ -40463,15 +40463,15 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
@@ -40496,16 +40496,16 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="9" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
@@ -40531,15 +40531,15 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="9" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
@@ -40564,19 +40564,19 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="9" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
@@ -40601,19 +40601,19 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
@@ -40638,19 +40638,19 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D66" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>489</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>495</v>
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
@@ -40675,19 +40675,19 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
@@ -40712,15 +40712,15 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
@@ -40745,16 +40745,16 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C69" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="D69" s="21" t="s">
         <v>512</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>513</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>519</v>
@@ -40788,13 +40788,13 @@
         <v>522</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D70" s="21" t="s">
         <v>523</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
@@ -40822,12 +40822,12 @@
         <v>521</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
@@ -40864,7 +40864,7 @@
         <v>533</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
@@ -40889,19 +40889,19 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="9" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
@@ -40925,11 +40925,11 @@
       <c r="Y73" s="24"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B74" s="37" t="s">
-        <v>557</v>
+      <c r="A74" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" s="38" t="s">
+        <v>560</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>44</v>
@@ -40959,15 +40959,15 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="9" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
@@ -40992,19 +40992,19 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="9" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
@@ -41029,10 +41029,10 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
@@ -41060,15 +41060,15 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
@@ -41093,16 +41093,16 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>591</v>
@@ -41130,19 +41130,19 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D80" s="21" t="s">
         <v>597</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
@@ -41167,15 +41167,15 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
@@ -41200,15 +41200,15 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
